--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E3E98A-6682-471E-AB8E-35564D7F551E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEADA47-44DD-45A3-870B-A297A55DE267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1184,6 +1184,105 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1208,6 +1307,129 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1271,190 +1493,76 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1466,230 +1574,122 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1889,22 +1889,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:colOff>209550</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>316096</xdr:rowOff>
+      <xdr:rowOff>337611</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA9EDA42-FC62-47FC-08D7-767A37441BB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{567A91EB-9C64-4F57-B6C9-0B5A52920A10}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1926,8 +1926,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="200025" y="971550"/>
-          <a:ext cx="7772400" cy="4792846"/>
+          <a:off x="152400" y="990600"/>
+          <a:ext cx="7772400" cy="4795311"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2146,85 +2146,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2244,46 +2244,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="19" t="s">
+      <c r="H13" s="54"/>
+      <c r="I13" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="20"/>
-      <c r="K13" s="21"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="54"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="19"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="21"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="54"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="19"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="21"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2292,13 +2292,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3306,219 +3306,219 @@
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="73" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="73" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="73" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="73"/>
+    <col min="1" max="3" width="5.140625" style="21" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="21" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="21" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="72" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="97"/>
+      <c r="F2" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="79">
+      <c r="G2" s="97"/>
+      <c r="H2" s="100">
         <v>45805</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="81"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="93" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="94"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="96"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="98" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="96"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="99"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="62"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="95" t="s">
+      <c r="A7" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="96"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="98" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="99"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="62"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="98" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="99"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="62"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="97"/>
-      <c r="D9" s="102" t="s">
+      <c r="C9" s="64"/>
+      <c r="D9" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="99"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="62"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="103"/>
-      <c r="B10" s="101" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="99"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="62"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="104"/>
-      <c r="B11" s="101" t="s">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="99"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="62"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="98" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="99"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="62"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="105" t="s">
+      <c r="A13" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="109"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="70"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -3539,991 +3539,976 @@
     <row r="30" ht="12.75" customHeight="1"/>
     <row r="31" ht="12.75" customHeight="1"/>
     <row r="32" ht="12.75" customHeight="1"/>
-    <row r="33" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="73" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="34" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="35" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="36" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="37" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="38" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="39" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="40" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="41" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="42" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="43" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="44" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="45" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="46" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="47" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="48" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="49" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="50" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="51" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="52" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="53" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="54" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="55" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="56" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="57" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="58" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="59" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="60" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="61" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="63" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="64" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" s="21" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -4536,6 +4521,21 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4554,19 +4554,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="42" t="s">
+      <c r="E1" s="117"/>
+      <c r="F1" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="43"/>
+      <c r="G1" s="117"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4578,48 +4578,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="37"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="44" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="44" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="27">
+      <c r="G2" s="119"/>
+      <c r="H2" s="101">
         <v>45807</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="31"/>
+      <c r="J2" s="105"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="37"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="32"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="106"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="33"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="107"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -5979,19 +5979,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="42" t="s">
+      <c r="E1" s="117"/>
+      <c r="F1" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="43"/>
+      <c r="G1" s="117"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6003,190 +6003,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="37"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="44" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="44" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="27">
+      <c r="G2" s="119"/>
+      <c r="H2" s="101">
         <v>45810</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="31"/>
+      <c r="J2" s="105"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="37"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="32"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="106"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="37"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="32"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="59" t="s">
+      <c r="B5" s="123"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="60"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="130"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="131"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="61"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="63"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="133"/>
+      <c r="C7" s="133"/>
+      <c r="D7" s="133"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="134"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="64"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="135"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="64"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="135"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="37"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="64"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="135"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="37"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="64"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="135"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="64"/>
+      <c r="A12" s="111"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="135"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="64"/>
+      <c r="A13" s="111"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="135"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="53"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="131"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="127" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="52" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="136" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="21"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="54"/>
       <c r="I15" s="13" t="s">
         <v>16</v>
       </c>
@@ -6195,11 +6195,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
       <c r="D16" s="13" t="s">
         <v>18</v>
       </c>
@@ -6212,18 +6212,18 @@
       <c r="G16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="65" t="s">
+      <c r="H16" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="20"/>
-      <c r="J16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="131"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="51">
+      <c r="A17" s="128">
         <v>1</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="15" t="s">
         <v>72</v>
       </c>
@@ -6234,81 +6234,81 @@
       <c r="G17" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="53"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="131"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="51"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
+      <c r="A18" s="128"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="53"/>
+      <c r="H18" s="136"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="131"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="51"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="A19" s="128"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="53"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="131"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="51"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
+      <c r="A20" s="128"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="53"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="131"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
+      <c r="A21" s="128"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="53"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="131"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
+      <c r="A22" s="128"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="53"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="131"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="56"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="57"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="126"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="50"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="139"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7289,11 +7289,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -7310,16 +7315,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -7333,427 +7333,427 @@
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="118" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="118" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="118" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="118"/>
+    <col min="1" max="3" width="5.140625" style="25" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="25" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="25" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="146" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="147"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="156"/>
+      <c r="F1" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="114"/>
-      <c r="H1" s="115" t="s">
+      <c r="G1" s="156"/>
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="117" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="119"/>
-      <c r="B2" s="120"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="122" t="s">
+      <c r="A2" s="149"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="123"/>
-      <c r="F2" s="122" t="s">
+      <c r="E2" s="158"/>
+      <c r="F2" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="123"/>
-      <c r="H2" s="187">
+      <c r="G2" s="158"/>
+      <c r="H2" s="161">
         <v>45810</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="143"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="119"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="128"/>
+      <c r="A3" s="149"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="144"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="134"/>
+      <c r="A4" s="152"/>
+      <c r="B4" s="153"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="142"/>
+      <c r="I4" s="142"/>
+      <c r="J4" s="145"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="135"/>
-      <c r="B5" s="136"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="137"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="28"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="135"/>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="137"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="28"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="135"/>
-      <c r="B7" s="136"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="137"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="135"/>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="137"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="135"/>
-      <c r="B9" s="136"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="137"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="135"/>
-      <c r="B10" s="136"/>
-      <c r="C10" s="136"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="137"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="135"/>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="137"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="135"/>
-      <c r="B12" s="136"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="136"/>
-      <c r="J12" s="137"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="135"/>
-      <c r="B13" s="136"/>
-      <c r="C13" s="136"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="136"/>
-      <c r="I13" s="136"/>
-      <c r="J13" s="137"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="135"/>
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="137"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="135"/>
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="136"/>
-      <c r="J15" s="137"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="135"/>
-      <c r="B16" s="136"/>
-      <c r="C16" s="136"/>
-      <c r="D16" s="136"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="137"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="135"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="137"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="135"/>
-      <c r="B18" s="136"/>
-      <c r="C18" s="136"/>
-      <c r="D18" s="136"/>
-      <c r="E18" s="136"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="136"/>
-      <c r="H18" s="136"/>
-      <c r="I18" s="136"/>
-      <c r="J18" s="137"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="135"/>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="136"/>
-      <c r="H19" s="136"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="137"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="135"/>
-      <c r="B20" s="136"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="137"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="135"/>
-      <c r="B21" s="136"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="136"/>
-      <c r="G21" s="136"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="136"/>
-      <c r="J21" s="137"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="135"/>
-      <c r="B22" s="136"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="137"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="28"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="135"/>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="136"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="136"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="137"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="28"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="136"/>
-      <c r="C24" s="136"/>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="136"/>
-      <c r="G24" s="136"/>
-      <c r="H24" s="136"/>
-      <c r="I24" s="136"/>
-      <c r="J24" s="137"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="28"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="135"/>
-      <c r="B25" s="136"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="136"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="136"/>
-      <c r="H25" s="136"/>
-      <c r="I25" s="136"/>
-      <c r="J25" s="137"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="28"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="135"/>
-      <c r="B26" s="136"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="136"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="136"/>
-      <c r="G26" s="136"/>
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="137"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="135"/>
-      <c r="B27" s="136"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="136"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="136"/>
-      <c r="H27" s="136"/>
-      <c r="I27" s="136"/>
-      <c r="J27" s="137"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="28"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="135"/>
-      <c r="B28" s="136"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="136"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="136"/>
-      <c r="G28" s="136"/>
-      <c r="H28" s="136"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="137"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="28"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="135"/>
-      <c r="B29" s="136"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="136"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="136"/>
-      <c r="G29" s="136"/>
-      <c r="H29" s="136"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="137"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="28"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="135"/>
-      <c r="B30" s="136"/>
-      <c r="C30" s="136"/>
-      <c r="D30" s="136"/>
-      <c r="E30" s="136"/>
-      <c r="F30" s="136"/>
-      <c r="G30" s="136"/>
-      <c r="H30" s="136"/>
-      <c r="I30" s="136"/>
-      <c r="J30" s="137"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="135"/>
-      <c r="B31" s="136"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="136"/>
-      <c r="E31" s="136"/>
-      <c r="F31" s="136"/>
-      <c r="G31" s="136"/>
-      <c r="H31" s="136"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="137"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="135"/>
-      <c r="B32" s="136"/>
-      <c r="C32" s="136"/>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
-      <c r="G32" s="136"/>
-      <c r="H32" s="136"/>
-      <c r="I32" s="136"/>
-      <c r="J32" s="137"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="28"/>
     </row>
     <row r="33" spans="1:10" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A33" s="138"/>
-      <c r="B33" s="139"/>
-      <c r="C33" s="139"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="140"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="31"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7766,7 +7766,7 @@
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="J44" s="141"/>
+      <c r="J44" s="32"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8747,429 +8747,429 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="6" width="2.85546875" style="118" customWidth="1"/>
-    <col min="7" max="20" width="8.140625" style="118" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="118" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="118"/>
+    <col min="1" max="6" width="2.85546875" style="25" customWidth="1"/>
+    <col min="7" max="20" width="8.140625" style="25" customWidth="1"/>
+    <col min="21" max="26" width="8.7109375" style="25" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="186" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="113" t="s">
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="113" t="s">
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="113" t="s">
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="155" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="113" t="s">
+      <c r="P1" s="156"/>
+      <c r="Q1" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="114"/>
-      <c r="S1" s="113" t="s">
+      <c r="R1" s="156"/>
+      <c r="S1" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="144"/>
+      <c r="T1" s="183"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="119"/>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="122" t="s">
+      <c r="A2" s="149"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="122" t="s">
+      <c r="H2" s="187"/>
+      <c r="I2" s="187"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="123"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="146"/>
+      <c r="L2" s="187"/>
+      <c r="M2" s="187"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="158"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="177"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="119"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="121"/>
-      <c r="S3" s="126"/>
-      <c r="T3" s="147"/>
+      <c r="A3" s="149"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="151"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="150"/>
+      <c r="N3" s="151"/>
+      <c r="O3" s="159"/>
+      <c r="P3" s="151"/>
+      <c r="Q3" s="159"/>
+      <c r="R3" s="151"/>
+      <c r="S3" s="159"/>
+      <c r="T3" s="178"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="132"/>
-      <c r="T4" s="148"/>
+      <c r="A4" s="152"/>
+      <c r="B4" s="153"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="153"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="153"/>
+      <c r="M4" s="153"/>
+      <c r="N4" s="154"/>
+      <c r="O4" s="160"/>
+      <c r="P4" s="154"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="154"/>
+      <c r="S4" s="160"/>
+      <c r="T4" s="179"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="180" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="150" t="s">
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="182" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="143"/>
-      <c r="R5" s="143"/>
-      <c r="S5" s="143"/>
-      <c r="T5" s="144"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="181"/>
+      <c r="M5" s="181"/>
+      <c r="N5" s="181"/>
+      <c r="O5" s="181"/>
+      <c r="P5" s="181"/>
+      <c r="Q5" s="181"/>
+      <c r="R5" s="181"/>
+      <c r="S5" s="181"/>
+      <c r="T5" s="183"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="151" t="s">
+      <c r="A6" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="152"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="154" t="s">
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="152"/>
-      <c r="K6" s="152"/>
-      <c r="L6" s="152"/>
-      <c r="M6" s="152"/>
-      <c r="N6" s="152"/>
-      <c r="O6" s="152"/>
-      <c r="P6" s="152"/>
-      <c r="Q6" s="152"/>
-      <c r="R6" s="152"/>
-      <c r="S6" s="152"/>
-      <c r="T6" s="155"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="169"/>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="169"/>
+      <c r="Q6" s="169"/>
+      <c r="R6" s="169"/>
+      <c r="S6" s="169"/>
+      <c r="T6" s="185"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="175" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="154" t="s">
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="184" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
-      <c r="O7" s="152"/>
-      <c r="P7" s="152"/>
-      <c r="Q7" s="152"/>
-      <c r="R7" s="152"/>
-      <c r="S7" s="152"/>
-      <c r="T7" s="155"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
+      <c r="R7" s="169"/>
+      <c r="S7" s="169"/>
+      <c r="T7" s="185"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
-      <c r="A8" s="135"/>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="136"/>
-      <c r="K8" s="136"/>
-      <c r="L8" s="136"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="136"/>
-      <c r="O8" s="136"/>
-      <c r="P8" s="136"/>
-      <c r="Q8" s="136"/>
-      <c r="R8" s="136"/>
-      <c r="S8" s="136"/>
-      <c r="T8" s="137"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="28"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="156"/>
-      <c r="B9" s="157"/>
-      <c r="C9" s="158" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="159"/>
-      <c r="E9" s="159" t="s">
+      <c r="D9" s="36"/>
+      <c r="E9" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="159"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="159"/>
-      <c r="I9" s="159"/>
-      <c r="J9" s="159"/>
-      <c r="K9" s="160"/>
-      <c r="L9" s="157"/>
-      <c r="M9" s="157"/>
-      <c r="N9" s="157"/>
-      <c r="O9" s="157"/>
-      <c r="P9" s="157"/>
-      <c r="Q9" s="157"/>
-      <c r="R9" s="157"/>
-      <c r="S9" s="157"/>
-      <c r="T9" s="161"/>
-      <c r="U9" s="157"/>
-      <c r="V9" s="157"/>
-      <c r="W9" s="157"/>
-      <c r="X9" s="157"/>
-      <c r="Y9" s="157"/>
-      <c r="Z9" s="157"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="34"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="34"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="34"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="156"/>
-      <c r="B10" s="157"/>
-      <c r="C10" s="162"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="157"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="157"/>
-      <c r="I10" s="157"/>
-      <c r="J10" s="157"/>
-      <c r="K10" s="163"/>
-      <c r="L10" s="157"/>
-      <c r="M10" s="157"/>
-      <c r="N10" s="157"/>
-      <c r="O10" s="157"/>
-      <c r="P10" s="157"/>
-      <c r="Q10" s="157"/>
-      <c r="R10" s="157"/>
-      <c r="S10" s="157"/>
-      <c r="T10" s="161"/>
-      <c r="U10" s="157"/>
-      <c r="V10" s="157"/>
-      <c r="W10" s="157"/>
-      <c r="X10" s="157"/>
-      <c r="Y10" s="157"/>
-      <c r="Z10" s="157"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="34"/>
+      <c r="V10" s="34"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="34"/>
+      <c r="Y10" s="34"/>
+      <c r="Z10" s="34"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="156"/>
-      <c r="B11" s="157"/>
-      <c r="C11" s="162"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="157"/>
-      <c r="G11" s="163"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="163"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="157"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-      <c r="T11" s="161"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="157"/>
-      <c r="W11" s="157"/>
-      <c r="X11" s="157"/>
-      <c r="Y11" s="157"/>
-      <c r="Z11" s="157"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="34"/>
+      <c r="W11" s="34"/>
+      <c r="X11" s="34"/>
+      <c r="Y11" s="34"/>
+      <c r="Z11" s="34"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="156"/>
-      <c r="B12" s="157"/>
-      <c r="C12" s="162"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="157"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="157"/>
-      <c r="I12" s="157"/>
-      <c r="J12" s="157"/>
-      <c r="K12" s="163"/>
-      <c r="L12" s="157"/>
-      <c r="M12" s="157"/>
-      <c r="N12" s="157"/>
-      <c r="O12" s="157"/>
-      <c r="P12" s="157"/>
-      <c r="Q12" s="157"/>
-      <c r="R12" s="157"/>
-      <c r="S12" s="157"/>
-      <c r="T12" s="161"/>
-      <c r="U12" s="157"/>
-      <c r="V12" s="157"/>
-      <c r="W12" s="157"/>
-      <c r="X12" s="157"/>
-      <c r="Y12" s="157"/>
-      <c r="Z12" s="157"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="34"/>
+      <c r="V12" s="34"/>
+      <c r="W12" s="34"/>
+      <c r="X12" s="34"/>
+      <c r="Y12" s="34"/>
+      <c r="Z12" s="34"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="156"/>
-      <c r="B13" s="157"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="165"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="165"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="165"/>
-      <c r="K13" s="166"/>
-      <c r="L13" s="157"/>
-      <c r="M13" s="157"/>
-      <c r="N13" s="157"/>
-      <c r="O13" s="157"/>
-      <c r="P13" s="157"/>
-      <c r="Q13" s="157"/>
-      <c r="R13" s="157"/>
-      <c r="S13" s="157"/>
-      <c r="T13" s="161"/>
-      <c r="U13" s="157"/>
-      <c r="V13" s="157"/>
-      <c r="W13" s="157"/>
-      <c r="X13" s="157"/>
-      <c r="Y13" s="157"/>
-      <c r="Z13" s="157"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="34"/>
+      <c r="W13" s="34"/>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13" s="34"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A14" s="135"/>
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="136"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="136"/>
-      <c r="Q14" s="136"/>
-      <c r="R14" s="136"/>
-      <c r="S14" s="136"/>
-      <c r="T14" s="137"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="151" t="s">
+      <c r="A15" s="175" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="153"/>
-      <c r="C15" s="167" t="s">
+      <c r="B15" s="170"/>
+      <c r="C15" s="176" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="153"/>
-      <c r="E15" s="168" t="s">
+      <c r="D15" s="170"/>
+      <c r="E15" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="153"/>
-      <c r="G15" s="168" t="s">
+      <c r="F15" s="170"/>
+      <c r="G15" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="152"/>
-      <c r="I15" s="153"/>
-      <c r="J15" s="168" t="s">
+      <c r="H15" s="169"/>
+      <c r="I15" s="170"/>
+      <c r="J15" s="174" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="153"/>
-      <c r="L15" s="168" t="s">
+      <c r="K15" s="170"/>
+      <c r="L15" s="174" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="152"/>
-      <c r="N15" s="153"/>
-      <c r="O15" s="168" t="s">
+      <c r="M15" s="169"/>
+      <c r="N15" s="170"/>
+      <c r="O15" s="174" t="s">
         <v>56</v>
       </c>
-      <c r="P15" s="152"/>
-      <c r="Q15" s="153"/>
-      <c r="R15" s="169" t="s">
+      <c r="P15" s="169"/>
+      <c r="Q15" s="170"/>
+      <c r="R15" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="S15" s="169" t="s">
+      <c r="S15" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="T15" s="170" t="s">
+      <c r="T15" s="45" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9177,495 +9177,495 @@
       <c r="A16" s="171">
         <v>1</v>
       </c>
-      <c r="B16" s="153"/>
+      <c r="B16" s="170"/>
       <c r="C16" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="153"/>
+      <c r="D16" s="170"/>
       <c r="E16" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="153"/>
+      <c r="F16" s="170"/>
       <c r="G16" s="173" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="152"/>
-      <c r="I16" s="153"/>
+      <c r="H16" s="169"/>
+      <c r="I16" s="170"/>
       <c r="J16" s="173" t="s">
         <v>63</v>
       </c>
-      <c r="K16" s="153"/>
-      <c r="L16" s="174" t="s">
+      <c r="K16" s="170"/>
+      <c r="L16" s="168" t="s">
         <v>64</v>
       </c>
-      <c r="M16" s="152"/>
-      <c r="N16" s="153"/>
-      <c r="O16" s="174" t="s">
+      <c r="M16" s="169"/>
+      <c r="N16" s="170"/>
+      <c r="O16" s="168" t="s">
         <v>65</v>
       </c>
-      <c r="P16" s="152"/>
-      <c r="Q16" s="153"/>
-      <c r="R16" s="175"/>
-      <c r="S16" s="175"/>
-      <c r="T16" s="176"/>
-      <c r="U16" s="177"/>
-      <c r="V16" s="177"/>
-      <c r="W16" s="177"/>
-      <c r="X16" s="177"/>
-      <c r="Y16" s="177"/>
-      <c r="Z16" s="177"/>
+      <c r="P16" s="169"/>
+      <c r="Q16" s="170"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="48"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="48"/>
+      <c r="X16" s="48"/>
+      <c r="Y16" s="48"/>
+      <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
       <c r="A17" s="171">
         <v>2</v>
       </c>
-      <c r="B17" s="153"/>
+      <c r="B17" s="170"/>
       <c r="C17" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="153"/>
+      <c r="D17" s="170"/>
       <c r="E17" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="153"/>
+      <c r="F17" s="170"/>
       <c r="G17" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="152"/>
-      <c r="I17" s="153"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="170"/>
       <c r="J17" s="173" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="153"/>
-      <c r="L17" s="174" t="s">
+      <c r="K17" s="170"/>
+      <c r="L17" s="168" t="s">
         <v>70</v>
       </c>
-      <c r="M17" s="152"/>
-      <c r="N17" s="153"/>
-      <c r="O17" s="174" t="s">
+      <c r="M17" s="169"/>
+      <c r="N17" s="170"/>
+      <c r="O17" s="168" t="s">
         <v>71</v>
       </c>
-      <c r="P17" s="152"/>
-      <c r="Q17" s="153"/>
-      <c r="R17" s="175"/>
-      <c r="S17" s="175"/>
-      <c r="T17" s="176"/>
-      <c r="U17" s="177"/>
-      <c r="V17" s="177"/>
-      <c r="W17" s="177"/>
-      <c r="X17" s="177"/>
-      <c r="Y17" s="177"/>
-      <c r="Z17" s="177"/>
+      <c r="P17" s="169"/>
+      <c r="Q17" s="170"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="48"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="48"/>
+      <c r="X17" s="48"/>
+      <c r="Y17" s="48"/>
+      <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="171"/>
-      <c r="B18" s="153"/>
+      <c r="B18" s="170"/>
       <c r="C18" s="172"/>
-      <c r="D18" s="153"/>
+      <c r="D18" s="170"/>
       <c r="E18" s="172"/>
-      <c r="F18" s="153"/>
+      <c r="F18" s="170"/>
       <c r="G18" s="173"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="153"/>
+      <c r="H18" s="169"/>
+      <c r="I18" s="170"/>
       <c r="J18" s="173"/>
-      <c r="K18" s="153"/>
-      <c r="L18" s="174"/>
-      <c r="M18" s="152"/>
-      <c r="N18" s="153"/>
-      <c r="O18" s="174"/>
-      <c r="P18" s="152"/>
-      <c r="Q18" s="153"/>
-      <c r="R18" s="175"/>
-      <c r="S18" s="175"/>
-      <c r="T18" s="176"/>
-      <c r="U18" s="177"/>
-      <c r="V18" s="177"/>
-      <c r="W18" s="177"/>
-      <c r="X18" s="177"/>
-      <c r="Y18" s="177"/>
-      <c r="Z18" s="177"/>
+      <c r="K18" s="170"/>
+      <c r="L18" s="168"/>
+      <c r="M18" s="169"/>
+      <c r="N18" s="170"/>
+      <c r="O18" s="168"/>
+      <c r="P18" s="169"/>
+      <c r="Q18" s="170"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="48"/>
+      <c r="V18" s="48"/>
+      <c r="W18" s="48"/>
+      <c r="X18" s="48"/>
+      <c r="Y18" s="48"/>
+      <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="171"/>
-      <c r="B19" s="153"/>
+      <c r="B19" s="170"/>
       <c r="C19" s="172"/>
-      <c r="D19" s="153"/>
+      <c r="D19" s="170"/>
       <c r="E19" s="172"/>
-      <c r="F19" s="153"/>
+      <c r="F19" s="170"/>
       <c r="G19" s="173"/>
-      <c r="H19" s="152"/>
-      <c r="I19" s="153"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="170"/>
       <c r="J19" s="173"/>
-      <c r="K19" s="153"/>
-      <c r="L19" s="174"/>
-      <c r="M19" s="152"/>
-      <c r="N19" s="153"/>
-      <c r="O19" s="174"/>
-      <c r="P19" s="152"/>
-      <c r="Q19" s="153"/>
-      <c r="R19" s="175"/>
-      <c r="S19" s="175"/>
-      <c r="T19" s="176"/>
-      <c r="U19" s="177"/>
-      <c r="V19" s="177"/>
-      <c r="W19" s="177"/>
-      <c r="X19" s="177"/>
-      <c r="Y19" s="177"/>
-      <c r="Z19" s="177"/>
+      <c r="K19" s="170"/>
+      <c r="L19" s="168"/>
+      <c r="M19" s="169"/>
+      <c r="N19" s="170"/>
+      <c r="O19" s="168"/>
+      <c r="P19" s="169"/>
+      <c r="Q19" s="170"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
       <c r="A20" s="171"/>
-      <c r="B20" s="153"/>
+      <c r="B20" s="170"/>
       <c r="C20" s="172"/>
-      <c r="D20" s="153"/>
+      <c r="D20" s="170"/>
       <c r="E20" s="172"/>
-      <c r="F20" s="153"/>
+      <c r="F20" s="170"/>
       <c r="G20" s="173"/>
-      <c r="H20" s="152"/>
-      <c r="I20" s="153"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="170"/>
       <c r="J20" s="173"/>
-      <c r="K20" s="153"/>
-      <c r="L20" s="174"/>
-      <c r="M20" s="152"/>
-      <c r="N20" s="153"/>
-      <c r="O20" s="174"/>
-      <c r="P20" s="152"/>
-      <c r="Q20" s="153"/>
-      <c r="R20" s="175"/>
-      <c r="S20" s="175"/>
-      <c r="T20" s="176"/>
-      <c r="U20" s="177"/>
-      <c r="V20" s="177"/>
-      <c r="W20" s="177"/>
-      <c r="X20" s="177"/>
-      <c r="Y20" s="177"/>
-      <c r="Z20" s="177"/>
+      <c r="K20" s="170"/>
+      <c r="L20" s="168"/>
+      <c r="M20" s="169"/>
+      <c r="N20" s="170"/>
+      <c r="O20" s="168"/>
+      <c r="P20" s="169"/>
+      <c r="Q20" s="170"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="48"/>
+      <c r="X20" s="48"/>
+      <c r="Y20" s="48"/>
+      <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="171"/>
-      <c r="B21" s="153"/>
+      <c r="B21" s="170"/>
       <c r="C21" s="172"/>
-      <c r="D21" s="153"/>
+      <c r="D21" s="170"/>
       <c r="E21" s="172"/>
-      <c r="F21" s="153"/>
+      <c r="F21" s="170"/>
       <c r="G21" s="173"/>
-      <c r="H21" s="152"/>
-      <c r="I21" s="153"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="170"/>
       <c r="J21" s="173"/>
-      <c r="K21" s="153"/>
-      <c r="L21" s="174"/>
-      <c r="M21" s="152"/>
-      <c r="N21" s="153"/>
-      <c r="O21" s="174"/>
-      <c r="P21" s="152"/>
-      <c r="Q21" s="153"/>
-      <c r="R21" s="175"/>
-      <c r="S21" s="175"/>
-      <c r="T21" s="176"/>
-      <c r="U21" s="177"/>
-      <c r="V21" s="177"/>
-      <c r="W21" s="177"/>
-      <c r="X21" s="177"/>
-      <c r="Y21" s="177"/>
-      <c r="Z21" s="177"/>
+      <c r="K21" s="170"/>
+      <c r="L21" s="168"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="170"/>
+      <c r="O21" s="168"/>
+      <c r="P21" s="169"/>
+      <c r="Q21" s="170"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="48"/>
+      <c r="X21" s="48"/>
+      <c r="Y21" s="48"/>
+      <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
       <c r="A22" s="171"/>
-      <c r="B22" s="153"/>
+      <c r="B22" s="170"/>
       <c r="C22" s="172"/>
-      <c r="D22" s="153"/>
+      <c r="D22" s="170"/>
       <c r="E22" s="172"/>
-      <c r="F22" s="153"/>
+      <c r="F22" s="170"/>
       <c r="G22" s="173"/>
-      <c r="H22" s="152"/>
-      <c r="I22" s="153"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="170"/>
       <c r="J22" s="173"/>
-      <c r="K22" s="153"/>
-      <c r="L22" s="174"/>
-      <c r="M22" s="152"/>
-      <c r="N22" s="153"/>
-      <c r="O22" s="174"/>
-      <c r="P22" s="152"/>
-      <c r="Q22" s="153"/>
-      <c r="R22" s="175"/>
-      <c r="S22" s="175"/>
-      <c r="T22" s="176"/>
-      <c r="U22" s="177"/>
-      <c r="V22" s="177"/>
-      <c r="W22" s="177"/>
-      <c r="X22" s="177"/>
-      <c r="Y22" s="177"/>
-      <c r="Z22" s="177"/>
+      <c r="K22" s="170"/>
+      <c r="L22" s="168"/>
+      <c r="M22" s="169"/>
+      <c r="N22" s="170"/>
+      <c r="O22" s="168"/>
+      <c r="P22" s="169"/>
+      <c r="Q22" s="170"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="47"/>
+      <c r="U22" s="48"/>
+      <c r="V22" s="48"/>
+      <c r="W22" s="48"/>
+      <c r="X22" s="48"/>
+      <c r="Y22" s="48"/>
+      <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="171"/>
-      <c r="B23" s="153"/>
+      <c r="B23" s="170"/>
       <c r="C23" s="172"/>
-      <c r="D23" s="153"/>
+      <c r="D23" s="170"/>
       <c r="E23" s="172"/>
-      <c r="F23" s="153"/>
+      <c r="F23" s="170"/>
       <c r="G23" s="173"/>
-      <c r="H23" s="152"/>
-      <c r="I23" s="153"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="170"/>
       <c r="J23" s="173"/>
-      <c r="K23" s="153"/>
-      <c r="L23" s="174"/>
-      <c r="M23" s="152"/>
-      <c r="N23" s="153"/>
-      <c r="O23" s="174"/>
-      <c r="P23" s="152"/>
-      <c r="Q23" s="153"/>
-      <c r="R23" s="175"/>
-      <c r="S23" s="175"/>
-      <c r="T23" s="176"/>
-      <c r="U23" s="177"/>
-      <c r="V23" s="177"/>
-      <c r="W23" s="177"/>
-      <c r="X23" s="177"/>
-      <c r="Y23" s="177"/>
-      <c r="Z23" s="177"/>
+      <c r="K23" s="170"/>
+      <c r="L23" s="168"/>
+      <c r="M23" s="169"/>
+      <c r="N23" s="170"/>
+      <c r="O23" s="168"/>
+      <c r="P23" s="169"/>
+      <c r="Q23" s="170"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="47"/>
+      <c r="U23" s="48"/>
+      <c r="V23" s="48"/>
+      <c r="W23" s="48"/>
+      <c r="X23" s="48"/>
+      <c r="Y23" s="48"/>
+      <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="171"/>
-      <c r="B24" s="153"/>
+      <c r="B24" s="170"/>
       <c r="C24" s="172"/>
-      <c r="D24" s="153"/>
+      <c r="D24" s="170"/>
       <c r="E24" s="172"/>
-      <c r="F24" s="153"/>
+      <c r="F24" s="170"/>
       <c r="G24" s="173"/>
-      <c r="H24" s="152"/>
-      <c r="I24" s="153"/>
+      <c r="H24" s="169"/>
+      <c r="I24" s="170"/>
       <c r="J24" s="173"/>
-      <c r="K24" s="153"/>
-      <c r="L24" s="174"/>
-      <c r="M24" s="152"/>
-      <c r="N24" s="153"/>
-      <c r="O24" s="174"/>
-      <c r="P24" s="152"/>
-      <c r="Q24" s="153"/>
-      <c r="R24" s="175"/>
-      <c r="S24" s="175"/>
-      <c r="T24" s="176"/>
-      <c r="U24" s="177"/>
-      <c r="V24" s="177"/>
-      <c r="W24" s="177"/>
-      <c r="X24" s="177"/>
-      <c r="Y24" s="177"/>
-      <c r="Z24" s="177"/>
+      <c r="K24" s="170"/>
+      <c r="L24" s="168"/>
+      <c r="M24" s="169"/>
+      <c r="N24" s="170"/>
+      <c r="O24" s="168"/>
+      <c r="P24" s="169"/>
+      <c r="Q24" s="170"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="47"/>
+      <c r="U24" s="48"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="48"/>
+      <c r="X24" s="48"/>
+      <c r="Y24" s="48"/>
+      <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="171"/>
-      <c r="B25" s="153"/>
+      <c r="B25" s="170"/>
       <c r="C25" s="172"/>
-      <c r="D25" s="153"/>
+      <c r="D25" s="170"/>
       <c r="E25" s="172"/>
-      <c r="F25" s="153"/>
+      <c r="F25" s="170"/>
       <c r="G25" s="173"/>
-      <c r="H25" s="152"/>
-      <c r="I25" s="153"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="170"/>
       <c r="J25" s="173"/>
-      <c r="K25" s="153"/>
-      <c r="L25" s="174"/>
-      <c r="M25" s="152"/>
-      <c r="N25" s="153"/>
-      <c r="O25" s="174"/>
-      <c r="P25" s="152"/>
-      <c r="Q25" s="153"/>
-      <c r="R25" s="175"/>
-      <c r="S25" s="175"/>
-      <c r="T25" s="176"/>
-      <c r="U25" s="177"/>
-      <c r="V25" s="177"/>
-      <c r="W25" s="177"/>
-      <c r="X25" s="177"/>
-      <c r="Y25" s="177"/>
-      <c r="Z25" s="177"/>
+      <c r="K25" s="170"/>
+      <c r="L25" s="168"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="170"/>
+      <c r="O25" s="168"/>
+      <c r="P25" s="169"/>
+      <c r="Q25" s="170"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="47"/>
+      <c r="U25" s="48"/>
+      <c r="V25" s="48"/>
+      <c r="W25" s="48"/>
+      <c r="X25" s="48"/>
+      <c r="Y25" s="48"/>
+      <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="171"/>
-      <c r="B26" s="153"/>
+      <c r="B26" s="170"/>
       <c r="C26" s="172"/>
-      <c r="D26" s="153"/>
+      <c r="D26" s="170"/>
       <c r="E26" s="172"/>
-      <c r="F26" s="153"/>
+      <c r="F26" s="170"/>
       <c r="G26" s="173"/>
-      <c r="H26" s="152"/>
-      <c r="I26" s="153"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="170"/>
       <c r="J26" s="173"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="174"/>
-      <c r="M26" s="152"/>
-      <c r="N26" s="153"/>
-      <c r="O26" s="174"/>
-      <c r="P26" s="152"/>
-      <c r="Q26" s="153"/>
-      <c r="R26" s="175"/>
-      <c r="S26" s="175"/>
-      <c r="T26" s="176"/>
-      <c r="U26" s="177"/>
-      <c r="V26" s="177"/>
-      <c r="W26" s="177"/>
-      <c r="X26" s="177"/>
-      <c r="Y26" s="177"/>
-      <c r="Z26" s="177"/>
+      <c r="K26" s="170"/>
+      <c r="L26" s="168"/>
+      <c r="M26" s="169"/>
+      <c r="N26" s="170"/>
+      <c r="O26" s="168"/>
+      <c r="P26" s="169"/>
+      <c r="Q26" s="170"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="47"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="48"/>
+      <c r="W26" s="48"/>
+      <c r="X26" s="48"/>
+      <c r="Y26" s="48"/>
+      <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="171"/>
-      <c r="B27" s="153"/>
+      <c r="B27" s="170"/>
       <c r="C27" s="172"/>
-      <c r="D27" s="153"/>
+      <c r="D27" s="170"/>
       <c r="E27" s="172"/>
-      <c r="F27" s="153"/>
+      <c r="F27" s="170"/>
       <c r="G27" s="173"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="153"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="170"/>
       <c r="J27" s="173"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="174"/>
-      <c r="M27" s="152"/>
-      <c r="N27" s="153"/>
-      <c r="O27" s="174"/>
-      <c r="P27" s="152"/>
-      <c r="Q27" s="153"/>
-      <c r="R27" s="175"/>
-      <c r="S27" s="175"/>
-      <c r="T27" s="176"/>
-      <c r="U27" s="177"/>
-      <c r="V27" s="177"/>
-      <c r="W27" s="177"/>
-      <c r="X27" s="177"/>
-      <c r="Y27" s="177"/>
-      <c r="Z27" s="177"/>
+      <c r="K27" s="170"/>
+      <c r="L27" s="168"/>
+      <c r="M27" s="169"/>
+      <c r="N27" s="170"/>
+      <c r="O27" s="168"/>
+      <c r="P27" s="169"/>
+      <c r="Q27" s="170"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="48"/>
+      <c r="V27" s="48"/>
+      <c r="W27" s="48"/>
+      <c r="X27" s="48"/>
+      <c r="Y27" s="48"/>
+      <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="171"/>
-      <c r="B28" s="153"/>
+      <c r="B28" s="170"/>
       <c r="C28" s="172"/>
-      <c r="D28" s="153"/>
+      <c r="D28" s="170"/>
       <c r="E28" s="172"/>
-      <c r="F28" s="153"/>
+      <c r="F28" s="170"/>
       <c r="G28" s="173"/>
-      <c r="H28" s="152"/>
-      <c r="I28" s="153"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="170"/>
       <c r="J28" s="173"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="174"/>
-      <c r="M28" s="152"/>
-      <c r="N28" s="153"/>
-      <c r="O28" s="174"/>
-      <c r="P28" s="152"/>
-      <c r="Q28" s="153"/>
-      <c r="R28" s="175"/>
-      <c r="S28" s="175"/>
-      <c r="T28" s="176"/>
-      <c r="U28" s="177"/>
-      <c r="V28" s="177"/>
-      <c r="W28" s="177"/>
-      <c r="X28" s="177"/>
-      <c r="Y28" s="177"/>
-      <c r="Z28" s="177"/>
+      <c r="K28" s="170"/>
+      <c r="L28" s="168"/>
+      <c r="M28" s="169"/>
+      <c r="N28" s="170"/>
+      <c r="O28" s="168"/>
+      <c r="P28" s="169"/>
+      <c r="Q28" s="170"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="48"/>
+      <c r="V28" s="48"/>
+      <c r="W28" s="48"/>
+      <c r="X28" s="48"/>
+      <c r="Y28" s="48"/>
+      <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="171"/>
-      <c r="B29" s="153"/>
+      <c r="B29" s="170"/>
       <c r="C29" s="172"/>
-      <c r="D29" s="153"/>
+      <c r="D29" s="170"/>
       <c r="E29" s="172"/>
-      <c r="F29" s="153"/>
+      <c r="F29" s="170"/>
       <c r="G29" s="173"/>
-      <c r="H29" s="152"/>
-      <c r="I29" s="153"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="170"/>
       <c r="J29" s="173"/>
-      <c r="K29" s="153"/>
-      <c r="L29" s="174"/>
-      <c r="M29" s="152"/>
-      <c r="N29" s="153"/>
-      <c r="O29" s="174"/>
-      <c r="P29" s="152"/>
-      <c r="Q29" s="153"/>
-      <c r="R29" s="175"/>
-      <c r="S29" s="175"/>
-      <c r="T29" s="176"/>
-      <c r="U29" s="177"/>
-      <c r="V29" s="177"/>
-      <c r="W29" s="177"/>
-      <c r="X29" s="177"/>
-      <c r="Y29" s="177"/>
-      <c r="Z29" s="177"/>
+      <c r="K29" s="170"/>
+      <c r="L29" s="168"/>
+      <c r="M29" s="169"/>
+      <c r="N29" s="170"/>
+      <c r="O29" s="168"/>
+      <c r="P29" s="169"/>
+      <c r="Q29" s="170"/>
+      <c r="R29" s="46"/>
+      <c r="S29" s="46"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="48"/>
+      <c r="V29" s="48"/>
+      <c r="W29" s="48"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="48"/>
+      <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="171"/>
-      <c r="B30" s="153"/>
+      <c r="B30" s="170"/>
       <c r="C30" s="172"/>
-      <c r="D30" s="153"/>
+      <c r="D30" s="170"/>
       <c r="E30" s="172"/>
-      <c r="F30" s="153"/>
+      <c r="F30" s="170"/>
       <c r="G30" s="173"/>
-      <c r="H30" s="152"/>
-      <c r="I30" s="153"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="170"/>
       <c r="J30" s="173"/>
-      <c r="K30" s="153"/>
-      <c r="L30" s="174"/>
-      <c r="M30" s="152"/>
-      <c r="N30" s="153"/>
-      <c r="O30" s="174"/>
-      <c r="P30" s="152"/>
-      <c r="Q30" s="153"/>
-      <c r="R30" s="175"/>
-      <c r="S30" s="175"/>
-      <c r="T30" s="176"/>
-      <c r="U30" s="177"/>
-      <c r="V30" s="177"/>
-      <c r="W30" s="177"/>
-      <c r="X30" s="177"/>
-      <c r="Y30" s="177"/>
-      <c r="Z30" s="177"/>
+      <c r="K30" s="170"/>
+      <c r="L30" s="168"/>
+      <c r="M30" s="169"/>
+      <c r="N30" s="170"/>
+      <c r="O30" s="168"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="170"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="47"/>
+      <c r="U30" s="48"/>
+      <c r="V30" s="48"/>
+      <c r="W30" s="48"/>
+      <c r="X30" s="48"/>
+      <c r="Y30" s="48"/>
+      <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="178"/>
-      <c r="B31" s="179"/>
-      <c r="C31" s="180"/>
-      <c r="D31" s="179"/>
-      <c r="E31" s="180"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="181"/>
-      <c r="H31" s="182"/>
-      <c r="I31" s="179"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="179"/>
-      <c r="L31" s="183"/>
-      <c r="M31" s="182"/>
-      <c r="N31" s="179"/>
-      <c r="O31" s="183"/>
-      <c r="P31" s="182"/>
-      <c r="Q31" s="179"/>
-      <c r="R31" s="184"/>
-      <c r="S31" s="184"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="177"/>
-      <c r="V31" s="177"/>
-      <c r="W31" s="177"/>
-      <c r="X31" s="177"/>
-      <c r="Y31" s="177"/>
-      <c r="Z31" s="177"/>
+      <c r="A31" s="165"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="167"/>
+      <c r="H31" s="163"/>
+      <c r="I31" s="164"/>
+      <c r="J31" s="167"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="162"/>
+      <c r="M31" s="163"/>
+      <c r="N31" s="164"/>
+      <c r="O31" s="162"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="164"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="49"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="48"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="48"/>
+      <c r="X31" s="48"/>
+      <c r="Y31" s="48"/>
+      <c r="Z31" s="48"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="186"/>
-      <c r="E32" s="186"/>
-      <c r="F32" s="186"/>
-      <c r="G32" s="186"/>
-      <c r="H32" s="186"/>
-      <c r="I32" s="186"/>
-      <c r="J32" s="186"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
     </row>
     <row r="33" spans="4:10" ht="12.75" customHeight="1">
-      <c r="D33" s="186"/>
-      <c r="E33" s="186"/>
-      <c r="F33" s="186"/>
-      <c r="G33" s="186"/>
-      <c r="H33" s="186"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="186"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
     </row>
     <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
@@ -10636,6 +10636,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -10657,121 +10772,6 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEADA47-44DD-45A3-870B-A297A55DE267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9137CF-6C69-4BAD-9F16-6EE4A4CB4CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1889,22 +1889,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>155864</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>103908</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:colOff>378730</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>337611</xdr:rowOff>
+      <xdr:rowOff>316470</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{567A91EB-9C64-4F57-B6C9-0B5A52920A10}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DEDE0B6-C191-3693-9317-8F2426DA5256}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1926,8 +1926,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="152400" y="990600"/>
-          <a:ext cx="7772400" cy="4795311"/>
+          <a:off x="155864" y="1004453"/>
+          <a:ext cx="7912139" cy="4576744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9137CF-6C69-4BAD-9F16-6EE4A4CB4CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358045DF-6FAE-4A09-8F0F-1ADA6F9B5808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1307,24 +1307,114 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1340,96 +1430,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1493,6 +1493,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1511,18 +1520,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1535,9 +1538,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1613,6 +1613,66 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1630,66 +1690,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1888,23 +1888,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>155864</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>103908</xdr:rowOff>
+      <xdr:rowOff>68036</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>378730</xdr:colOff>
+      <xdr:colOff>438151</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>316470</xdr:rowOff>
+      <xdr:rowOff>291347</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DEDE0B6-C191-3693-9317-8F2426DA5256}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D64DE78-96FF-F3A3-1D5B-42EE7335BF68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1926,8 +1926,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="155864" y="1004453"/>
-          <a:ext cx="7912139" cy="4576744"/>
+          <a:off x="381001" y="993322"/>
+          <a:ext cx="7772400" cy="4795311"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3313,19 +3313,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="95" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="95" t="s">
+      <c r="E1" s="68"/>
+      <c r="F1" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="68"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -3337,188 +3337,188 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="96" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="97"/>
-      <c r="F2" s="96" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="97"/>
-      <c r="H2" s="100">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>45805</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="89"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="64"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="65"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="84" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="70"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="65" t="s">
+      <c r="B6" s="72"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="62"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65" t="s">
+      <c r="B7" s="72"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="62"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="75"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65" t="s">
+      <c r="B8" s="72"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="62"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="75"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="60" t="s">
+      <c r="C9" s="73"/>
+      <c r="D9" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="62"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="75"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="74" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="62"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="75"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74" t="s">
+      <c r="A11" s="93"/>
+      <c r="B11" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="62"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="75"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="65" t="s">
+      <c r="B12" s="72"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="62"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="75"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="70"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4509,6 +4509,21 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -4521,21 +4536,6 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6047,23 +6047,23 @@
       <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="123"/>
+      <c r="B5" s="126"/>
       <c r="C5" s="117"/>
-      <c r="D5" s="129" t="s">
+      <c r="D5" s="131" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="130"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="132"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="130" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="53"/>
@@ -6074,19 +6074,19 @@
       <c r="G6" s="53"/>
       <c r="H6" s="53"/>
       <c r="I6" s="53"/>
-      <c r="J6" s="131"/>
+      <c r="J6" s="123"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="132"/>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="134"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="111"/>
@@ -6098,7 +6098,7 @@
       <c r="G8" s="56"/>
       <c r="H8" s="56"/>
       <c r="I8" s="56"/>
-      <c r="J8" s="135"/>
+      <c r="J8" s="136"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="111"/>
@@ -6110,7 +6110,7 @@
       <c r="G9" s="56"/>
       <c r="H9" s="56"/>
       <c r="I9" s="56"/>
-      <c r="J9" s="135"/>
+      <c r="J9" s="136"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="111"/>
@@ -6122,7 +6122,7 @@
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
       <c r="I10" s="56"/>
-      <c r="J10" s="135"/>
+      <c r="J10" s="136"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="111"/>
@@ -6134,7 +6134,7 @@
       <c r="G11" s="56"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
-      <c r="J11" s="135"/>
+      <c r="J11" s="136"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="111"/>
@@ -6146,7 +6146,7 @@
       <c r="G12" s="56"/>
       <c r="H12" s="56"/>
       <c r="I12" s="56"/>
-      <c r="J12" s="135"/>
+      <c r="J12" s="136"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="111"/>
@@ -6158,10 +6158,10 @@
       <c r="G13" s="56"/>
       <c r="H13" s="56"/>
       <c r="I13" s="56"/>
-      <c r="J13" s="135"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="130" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="53"/>
@@ -6172,15 +6172,15 @@
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
-      <c r="J14" s="131"/>
+      <c r="J14" s="123"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="130" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="53"/>
       <c r="C15" s="54"/>
-      <c r="D15" s="136" t="s">
+      <c r="D15" s="122" t="s">
         <v>75</v>
       </c>
       <c r="E15" s="53"/>
@@ -6195,7 +6195,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="127" t="s">
+      <c r="A16" s="130" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="53"/>
@@ -6216,10 +6216,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="53"/>
-      <c r="J16" s="131"/>
+      <c r="J16" s="123"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="128">
+      <c r="A17" s="124">
         <v>1</v>
       </c>
       <c r="B17" s="53"/>
@@ -6234,80 +6234,80 @@
       <c r="G17" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="136"/>
+      <c r="H17" s="122"/>
       <c r="I17" s="53"/>
-      <c r="J17" s="131"/>
+      <c r="J17" s="123"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="128"/>
+      <c r="A18" s="124"/>
       <c r="B18" s="53"/>
       <c r="C18" s="54"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="136"/>
+      <c r="H18" s="122"/>
       <c r="I18" s="53"/>
-      <c r="J18" s="131"/>
+      <c r="J18" s="123"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="128"/>
+      <c r="A19" s="124"/>
       <c r="B19" s="53"/>
       <c r="C19" s="54"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="136"/>
+      <c r="H19" s="122"/>
       <c r="I19" s="53"/>
-      <c r="J19" s="131"/>
+      <c r="J19" s="123"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="128"/>
+      <c r="A20" s="124"/>
       <c r="B20" s="53"/>
       <c r="C20" s="54"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="136"/>
+      <c r="H20" s="122"/>
       <c r="I20" s="53"/>
-      <c r="J20" s="131"/>
+      <c r="J20" s="123"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="128"/>
+      <c r="A21" s="124"/>
       <c r="B21" s="53"/>
       <c r="C21" s="54"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="136"/>
+      <c r="H21" s="122"/>
       <c r="I21" s="53"/>
-      <c r="J21" s="131"/>
+      <c r="J21" s="123"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="128"/>
+      <c r="A22" s="124"/>
       <c r="B22" s="53"/>
       <c r="C22" s="54"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="136"/>
+      <c r="H22" s="122"/>
       <c r="I22" s="53"/>
-      <c r="J22" s="131"/>
+      <c r="J22" s="123"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="124"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="126"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="129"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="138"/>
-      <c r="I23" s="125"/>
+      <c r="I23" s="128"/>
       <c r="J23" s="139"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7289,16 +7289,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -7315,11 +7310,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8754,7 +8754,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="174" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="147"/>
@@ -8765,14 +8765,14 @@
       <c r="G1" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="181"/>
-      <c r="I1" s="181"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
       <c r="J1" s="156"/>
       <c r="K1" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="181"/>
-      <c r="M1" s="181"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
       <c r="N1" s="156"/>
       <c r="O1" s="155" t="s">
         <v>7</v>
@@ -8785,7 +8785,7 @@
       <c r="S1" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="183"/>
+      <c r="T1" s="168"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="149"/>
@@ -8797,21 +8797,21 @@
       <c r="G2" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
       <c r="J2" s="158"/>
       <c r="K2" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="187"/>
-      <c r="M2" s="187"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
       <c r="N2" s="158"/>
       <c r="O2" s="157"/>
       <c r="P2" s="158"/>
       <c r="Q2" s="157"/>
       <c r="R2" s="158"/>
       <c r="S2" s="157"/>
-      <c r="T2" s="177"/>
+      <c r="T2" s="162"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="149"/>
@@ -8833,7 +8833,7 @@
       <c r="Q3" s="159"/>
       <c r="R3" s="151"/>
       <c r="S3" s="159"/>
-      <c r="T3" s="178"/>
+      <c r="T3" s="163"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="152"/>
@@ -8855,85 +8855,85 @@
       <c r="Q4" s="160"/>
       <c r="R4" s="154"/>
       <c r="S4" s="160"/>
-      <c r="T4" s="179"/>
+      <c r="T4" s="164"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="165" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="181"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
       <c r="F5" s="156"/>
-      <c r="G5" s="182" t="s">
+      <c r="G5" s="167" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="181"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="181"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="181"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="181"/>
-      <c r="O5" s="181"/>
-      <c r="P5" s="181"/>
-      <c r="Q5" s="181"/>
-      <c r="R5" s="181"/>
-      <c r="S5" s="181"/>
-      <c r="T5" s="183"/>
+      <c r="H5" s="166"/>
+      <c r="I5" s="166"/>
+      <c r="J5" s="166"/>
+      <c r="K5" s="166"/>
+      <c r="L5" s="166"/>
+      <c r="M5" s="166"/>
+      <c r="N5" s="166"/>
+      <c r="O5" s="166"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="166"/>
+      <c r="R5" s="166"/>
+      <c r="S5" s="166"/>
+      <c r="T5" s="168"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="175" t="s">
+      <c r="A6" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="169"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
-      <c r="E6" s="169"/>
-      <c r="F6" s="170"/>
-      <c r="G6" s="184" t="s">
+      <c r="B6" s="170"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="170"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="171"/>
+      <c r="G6" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="169"/>
-      <c r="I6" s="169"/>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="169"/>
-      <c r="Q6" s="169"/>
-      <c r="R6" s="169"/>
-      <c r="S6" s="169"/>
-      <c r="T6" s="185"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="170"/>
+      <c r="J6" s="170"/>
+      <c r="K6" s="170"/>
+      <c r="L6" s="170"/>
+      <c r="M6" s="170"/>
+      <c r="N6" s="170"/>
+      <c r="O6" s="170"/>
+      <c r="P6" s="170"/>
+      <c r="Q6" s="170"/>
+      <c r="R6" s="170"/>
+      <c r="S6" s="170"/>
+      <c r="T6" s="173"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="175" t="s">
+      <c r="A7" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="169"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="170"/>
-      <c r="G7" s="184" t="s">
+      <c r="B7" s="170"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="172" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="169"/>
-      <c r="R7" s="169"/>
-      <c r="S7" s="169"/>
-      <c r="T7" s="185"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="170"/>
+      <c r="K7" s="170"/>
+      <c r="L7" s="170"/>
+      <c r="M7" s="170"/>
+      <c r="N7" s="170"/>
+      <c r="O7" s="170"/>
+      <c r="P7" s="170"/>
+      <c r="Q7" s="170"/>
+      <c r="R7" s="170"/>
+      <c r="S7" s="170"/>
+      <c r="T7" s="173"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9132,37 +9132,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="175" t="s">
+      <c r="A15" s="169" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="170"/>
-      <c r="C15" s="176" t="s">
+      <c r="B15" s="171"/>
+      <c r="C15" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="170"/>
-      <c r="E15" s="174" t="s">
+      <c r="D15" s="171"/>
+      <c r="E15" s="176" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="170"/>
-      <c r="G15" s="174" t="s">
+      <c r="F15" s="171"/>
+      <c r="G15" s="176" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="169"/>
-      <c r="I15" s="170"/>
-      <c r="J15" s="174" t="s">
+      <c r="H15" s="170"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="176" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="170"/>
-      <c r="L15" s="174" t="s">
+      <c r="K15" s="171"/>
+      <c r="L15" s="176" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="169"/>
-      <c r="N15" s="170"/>
-      <c r="O15" s="174" t="s">
+      <c r="M15" s="170"/>
+      <c r="N15" s="171"/>
+      <c r="O15" s="176" t="s">
         <v>56</v>
       </c>
-      <c r="P15" s="169"/>
-      <c r="Q15" s="170"/>
+      <c r="P15" s="170"/>
+      <c r="Q15" s="171"/>
       <c r="R15" s="44" t="s">
         <v>57</v>
       </c>
@@ -9174,37 +9174,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="171">
+      <c r="A16" s="177">
         <v>1</v>
       </c>
-      <c r="B16" s="170"/>
-      <c r="C16" s="172" t="s">
+      <c r="B16" s="171"/>
+      <c r="C16" s="178" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="170"/>
-      <c r="E16" s="172" t="s">
+      <c r="D16" s="171"/>
+      <c r="E16" s="178" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="170"/>
-      <c r="G16" s="173" t="s">
+      <c r="F16" s="171"/>
+      <c r="G16" s="179" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="169"/>
-      <c r="I16" s="170"/>
-      <c r="J16" s="173" t="s">
+      <c r="H16" s="170"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="179" t="s">
         <v>63</v>
       </c>
-      <c r="K16" s="170"/>
-      <c r="L16" s="168" t="s">
+      <c r="K16" s="171"/>
+      <c r="L16" s="180" t="s">
         <v>64</v>
       </c>
-      <c r="M16" s="169"/>
-      <c r="N16" s="170"/>
-      <c r="O16" s="168" t="s">
+      <c r="M16" s="170"/>
+      <c r="N16" s="171"/>
+      <c r="O16" s="180" t="s">
         <v>65</v>
       </c>
-      <c r="P16" s="169"/>
-      <c r="Q16" s="170"/>
+      <c r="P16" s="170"/>
+      <c r="Q16" s="171"/>
       <c r="R16" s="46"/>
       <c r="S16" s="46"/>
       <c r="T16" s="47"/>
@@ -9216,37 +9216,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="171">
+      <c r="A17" s="177">
         <v>2</v>
       </c>
-      <c r="B17" s="170"/>
-      <c r="C17" s="172" t="s">
+      <c r="B17" s="171"/>
+      <c r="C17" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="170"/>
-      <c r="E17" s="172" t="s">
+      <c r="D17" s="171"/>
+      <c r="E17" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="170"/>
-      <c r="G17" s="173" t="s">
+      <c r="F17" s="171"/>
+      <c r="G17" s="179" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="169"/>
-      <c r="I17" s="170"/>
-      <c r="J17" s="173" t="s">
+      <c r="H17" s="170"/>
+      <c r="I17" s="171"/>
+      <c r="J17" s="179" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="170"/>
-      <c r="L17" s="168" t="s">
+      <c r="K17" s="171"/>
+      <c r="L17" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="M17" s="169"/>
-      <c r="N17" s="170"/>
-      <c r="O17" s="168" t="s">
+      <c r="M17" s="170"/>
+      <c r="N17" s="171"/>
+      <c r="O17" s="180" t="s">
         <v>71</v>
       </c>
-      <c r="P17" s="169"/>
-      <c r="Q17" s="170"/>
+      <c r="P17" s="170"/>
+      <c r="Q17" s="171"/>
       <c r="R17" s="46"/>
       <c r="S17" s="46"/>
       <c r="T17" s="47"/>
@@ -9258,23 +9258,23 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="171"/>
-      <c r="B18" s="170"/>
-      <c r="C18" s="172"/>
-      <c r="D18" s="170"/>
-      <c r="E18" s="172"/>
-      <c r="F18" s="170"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="169"/>
-      <c r="I18" s="170"/>
-      <c r="J18" s="173"/>
-      <c r="K18" s="170"/>
-      <c r="L18" s="168"/>
-      <c r="M18" s="169"/>
-      <c r="N18" s="170"/>
-      <c r="O18" s="168"/>
-      <c r="P18" s="169"/>
-      <c r="Q18" s="170"/>
+      <c r="A18" s="177"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="178"/>
+      <c r="D18" s="171"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="171"/>
+      <c r="G18" s="179"/>
+      <c r="H18" s="170"/>
+      <c r="I18" s="171"/>
+      <c r="J18" s="179"/>
+      <c r="K18" s="171"/>
+      <c r="L18" s="180"/>
+      <c r="M18" s="170"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="180"/>
+      <c r="P18" s="170"/>
+      <c r="Q18" s="171"/>
       <c r="R18" s="46"/>
       <c r="S18" s="46"/>
       <c r="T18" s="47"/>
@@ -9286,23 +9286,23 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="171"/>
-      <c r="B19" s="170"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="170"/>
-      <c r="E19" s="172"/>
-      <c r="F19" s="170"/>
-      <c r="G19" s="173"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="170"/>
-      <c r="J19" s="173"/>
-      <c r="K19" s="170"/>
-      <c r="L19" s="168"/>
-      <c r="M19" s="169"/>
-      <c r="N19" s="170"/>
-      <c r="O19" s="168"/>
-      <c r="P19" s="169"/>
-      <c r="Q19" s="170"/>
+      <c r="A19" s="177"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="171"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="179"/>
+      <c r="H19" s="170"/>
+      <c r="I19" s="171"/>
+      <c r="J19" s="179"/>
+      <c r="K19" s="171"/>
+      <c r="L19" s="180"/>
+      <c r="M19" s="170"/>
+      <c r="N19" s="171"/>
+      <c r="O19" s="180"/>
+      <c r="P19" s="170"/>
+      <c r="Q19" s="171"/>
       <c r="R19" s="46"/>
       <c r="S19" s="46"/>
       <c r="T19" s="47"/>
@@ -9314,23 +9314,23 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="171"/>
-      <c r="B20" s="170"/>
-      <c r="C20" s="172"/>
-      <c r="D20" s="170"/>
-      <c r="E20" s="172"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="169"/>
-      <c r="I20" s="170"/>
-      <c r="J20" s="173"/>
-      <c r="K20" s="170"/>
-      <c r="L20" s="168"/>
-      <c r="M20" s="169"/>
-      <c r="N20" s="170"/>
-      <c r="O20" s="168"/>
-      <c r="P20" s="169"/>
-      <c r="Q20" s="170"/>
+      <c r="A20" s="177"/>
+      <c r="B20" s="171"/>
+      <c r="C20" s="178"/>
+      <c r="D20" s="171"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="179"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="171"/>
+      <c r="J20" s="179"/>
+      <c r="K20" s="171"/>
+      <c r="L20" s="180"/>
+      <c r="M20" s="170"/>
+      <c r="N20" s="171"/>
+      <c r="O20" s="180"/>
+      <c r="P20" s="170"/>
+      <c r="Q20" s="171"/>
       <c r="R20" s="46"/>
       <c r="S20" s="46"/>
       <c r="T20" s="47"/>
@@ -9342,23 +9342,23 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="171"/>
-      <c r="B21" s="170"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="170"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="170"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="170"/>
-      <c r="J21" s="173"/>
-      <c r="K21" s="170"/>
-      <c r="L21" s="168"/>
-      <c r="M21" s="169"/>
-      <c r="N21" s="170"/>
-      <c r="O21" s="168"/>
-      <c r="P21" s="169"/>
-      <c r="Q21" s="170"/>
+      <c r="A21" s="177"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="178"/>
+      <c r="D21" s="171"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="171"/>
+      <c r="G21" s="179"/>
+      <c r="H21" s="170"/>
+      <c r="I21" s="171"/>
+      <c r="J21" s="179"/>
+      <c r="K21" s="171"/>
+      <c r="L21" s="180"/>
+      <c r="M21" s="170"/>
+      <c r="N21" s="171"/>
+      <c r="O21" s="180"/>
+      <c r="P21" s="170"/>
+      <c r="Q21" s="171"/>
       <c r="R21" s="46"/>
       <c r="S21" s="46"/>
       <c r="T21" s="47"/>
@@ -9370,23 +9370,23 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="171"/>
-      <c r="B22" s="170"/>
-      <c r="C22" s="172"/>
-      <c r="D22" s="170"/>
-      <c r="E22" s="172"/>
-      <c r="F22" s="170"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="169"/>
-      <c r="I22" s="170"/>
-      <c r="J22" s="173"/>
-      <c r="K22" s="170"/>
-      <c r="L22" s="168"/>
-      <c r="M22" s="169"/>
-      <c r="N22" s="170"/>
-      <c r="O22" s="168"/>
-      <c r="P22" s="169"/>
-      <c r="Q22" s="170"/>
+      <c r="A22" s="177"/>
+      <c r="B22" s="171"/>
+      <c r="C22" s="178"/>
+      <c r="D22" s="171"/>
+      <c r="E22" s="178"/>
+      <c r="F22" s="171"/>
+      <c r="G22" s="179"/>
+      <c r="H22" s="170"/>
+      <c r="I22" s="171"/>
+      <c r="J22" s="179"/>
+      <c r="K22" s="171"/>
+      <c r="L22" s="180"/>
+      <c r="M22" s="170"/>
+      <c r="N22" s="171"/>
+      <c r="O22" s="180"/>
+      <c r="P22" s="170"/>
+      <c r="Q22" s="171"/>
       <c r="R22" s="46"/>
       <c r="S22" s="46"/>
       <c r="T22" s="47"/>
@@ -9398,23 +9398,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="171"/>
-      <c r="B23" s="170"/>
-      <c r="C23" s="172"/>
-      <c r="D23" s="170"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="170"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="170"/>
-      <c r="J23" s="173"/>
-      <c r="K23" s="170"/>
-      <c r="L23" s="168"/>
-      <c r="M23" s="169"/>
-      <c r="N23" s="170"/>
-      <c r="O23" s="168"/>
-      <c r="P23" s="169"/>
-      <c r="Q23" s="170"/>
+      <c r="A23" s="177"/>
+      <c r="B23" s="171"/>
+      <c r="C23" s="178"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="179"/>
+      <c r="H23" s="170"/>
+      <c r="I23" s="171"/>
+      <c r="J23" s="179"/>
+      <c r="K23" s="171"/>
+      <c r="L23" s="180"/>
+      <c r="M23" s="170"/>
+      <c r="N23" s="171"/>
+      <c r="O23" s="180"/>
+      <c r="P23" s="170"/>
+      <c r="Q23" s="171"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -9426,23 +9426,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="171"/>
-      <c r="B24" s="170"/>
-      <c r="C24" s="172"/>
-      <c r="D24" s="170"/>
-      <c r="E24" s="172"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="173"/>
-      <c r="H24" s="169"/>
-      <c r="I24" s="170"/>
-      <c r="J24" s="173"/>
-      <c r="K24" s="170"/>
-      <c r="L24" s="168"/>
-      <c r="M24" s="169"/>
-      <c r="N24" s="170"/>
-      <c r="O24" s="168"/>
-      <c r="P24" s="169"/>
-      <c r="Q24" s="170"/>
+      <c r="A24" s="177"/>
+      <c r="B24" s="171"/>
+      <c r="C24" s="178"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="178"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="179"/>
+      <c r="H24" s="170"/>
+      <c r="I24" s="171"/>
+      <c r="J24" s="179"/>
+      <c r="K24" s="171"/>
+      <c r="L24" s="180"/>
+      <c r="M24" s="170"/>
+      <c r="N24" s="171"/>
+      <c r="O24" s="180"/>
+      <c r="P24" s="170"/>
+      <c r="Q24" s="171"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -9454,23 +9454,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="171"/>
-      <c r="B25" s="170"/>
-      <c r="C25" s="172"/>
-      <c r="D25" s="170"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="170"/>
-      <c r="G25" s="173"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="170"/>
-      <c r="J25" s="173"/>
-      <c r="K25" s="170"/>
-      <c r="L25" s="168"/>
-      <c r="M25" s="169"/>
-      <c r="N25" s="170"/>
-      <c r="O25" s="168"/>
-      <c r="P25" s="169"/>
-      <c r="Q25" s="170"/>
+      <c r="A25" s="177"/>
+      <c r="B25" s="171"/>
+      <c r="C25" s="178"/>
+      <c r="D25" s="171"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="179"/>
+      <c r="H25" s="170"/>
+      <c r="I25" s="171"/>
+      <c r="J25" s="179"/>
+      <c r="K25" s="171"/>
+      <c r="L25" s="180"/>
+      <c r="M25" s="170"/>
+      <c r="N25" s="171"/>
+      <c r="O25" s="180"/>
+      <c r="P25" s="170"/>
+      <c r="Q25" s="171"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -9482,23 +9482,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="171"/>
-      <c r="B26" s="170"/>
-      <c r="C26" s="172"/>
-      <c r="D26" s="170"/>
-      <c r="E26" s="172"/>
-      <c r="F26" s="170"/>
-      <c r="G26" s="173"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="170"/>
-      <c r="J26" s="173"/>
-      <c r="K26" s="170"/>
-      <c r="L26" s="168"/>
-      <c r="M26" s="169"/>
-      <c r="N26" s="170"/>
-      <c r="O26" s="168"/>
-      <c r="P26" s="169"/>
-      <c r="Q26" s="170"/>
+      <c r="A26" s="177"/>
+      <c r="B26" s="171"/>
+      <c r="C26" s="178"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="178"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="179"/>
+      <c r="H26" s="170"/>
+      <c r="I26" s="171"/>
+      <c r="J26" s="179"/>
+      <c r="K26" s="171"/>
+      <c r="L26" s="180"/>
+      <c r="M26" s="170"/>
+      <c r="N26" s="171"/>
+      <c r="O26" s="180"/>
+      <c r="P26" s="170"/>
+      <c r="Q26" s="171"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -9510,23 +9510,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="171"/>
-      <c r="B27" s="170"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="170"/>
-      <c r="E27" s="172"/>
-      <c r="F27" s="170"/>
-      <c r="G27" s="173"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="173"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="168"/>
-      <c r="M27" s="169"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="168"/>
-      <c r="P27" s="169"/>
-      <c r="Q27" s="170"/>
+      <c r="A27" s="177"/>
+      <c r="B27" s="171"/>
+      <c r="C27" s="178"/>
+      <c r="D27" s="171"/>
+      <c r="E27" s="178"/>
+      <c r="F27" s="171"/>
+      <c r="G27" s="179"/>
+      <c r="H27" s="170"/>
+      <c r="I27" s="171"/>
+      <c r="J27" s="179"/>
+      <c r="K27" s="171"/>
+      <c r="L27" s="180"/>
+      <c r="M27" s="170"/>
+      <c r="N27" s="171"/>
+      <c r="O27" s="180"/>
+      <c r="P27" s="170"/>
+      <c r="Q27" s="171"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -9538,23 +9538,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="171"/>
-      <c r="B28" s="170"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="170"/>
-      <c r="E28" s="172"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="170"/>
-      <c r="J28" s="173"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="168"/>
-      <c r="M28" s="169"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="168"/>
-      <c r="P28" s="169"/>
-      <c r="Q28" s="170"/>
+      <c r="A28" s="177"/>
+      <c r="B28" s="171"/>
+      <c r="C28" s="178"/>
+      <c r="D28" s="171"/>
+      <c r="E28" s="178"/>
+      <c r="F28" s="171"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="170"/>
+      <c r="I28" s="171"/>
+      <c r="J28" s="179"/>
+      <c r="K28" s="171"/>
+      <c r="L28" s="180"/>
+      <c r="M28" s="170"/>
+      <c r="N28" s="171"/>
+      <c r="O28" s="180"/>
+      <c r="P28" s="170"/>
+      <c r="Q28" s="171"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -9566,23 +9566,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="171"/>
-      <c r="B29" s="170"/>
-      <c r="C29" s="172"/>
-      <c r="D29" s="170"/>
-      <c r="E29" s="172"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="169"/>
-      <c r="I29" s="170"/>
-      <c r="J29" s="173"/>
-      <c r="K29" s="170"/>
-      <c r="L29" s="168"/>
-      <c r="M29" s="169"/>
-      <c r="N29" s="170"/>
-      <c r="O29" s="168"/>
-      <c r="P29" s="169"/>
-      <c r="Q29" s="170"/>
+      <c r="A29" s="177"/>
+      <c r="B29" s="171"/>
+      <c r="C29" s="178"/>
+      <c r="D29" s="171"/>
+      <c r="E29" s="178"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="179"/>
+      <c r="H29" s="170"/>
+      <c r="I29" s="171"/>
+      <c r="J29" s="179"/>
+      <c r="K29" s="171"/>
+      <c r="L29" s="180"/>
+      <c r="M29" s="170"/>
+      <c r="N29" s="171"/>
+      <c r="O29" s="180"/>
+      <c r="P29" s="170"/>
+      <c r="Q29" s="171"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -9594,23 +9594,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="171"/>
-      <c r="B30" s="170"/>
-      <c r="C30" s="172"/>
-      <c r="D30" s="170"/>
-      <c r="E30" s="172"/>
-      <c r="F30" s="170"/>
-      <c r="G30" s="173"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="173"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="168"/>
-      <c r="M30" s="169"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="168"/>
-      <c r="P30" s="169"/>
-      <c r="Q30" s="170"/>
+      <c r="A30" s="177"/>
+      <c r="B30" s="171"/>
+      <c r="C30" s="178"/>
+      <c r="D30" s="171"/>
+      <c r="E30" s="178"/>
+      <c r="F30" s="171"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="171"/>
+      <c r="J30" s="179"/>
+      <c r="K30" s="171"/>
+      <c r="L30" s="180"/>
+      <c r="M30" s="170"/>
+      <c r="N30" s="171"/>
+      <c r="O30" s="180"/>
+      <c r="P30" s="170"/>
+      <c r="Q30" s="171"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -9622,23 +9622,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="165"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="166"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="166"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="167"/>
-      <c r="H31" s="163"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="167"/>
-      <c r="K31" s="164"/>
-      <c r="L31" s="162"/>
-      <c r="M31" s="163"/>
-      <c r="N31" s="164"/>
-      <c r="O31" s="162"/>
-      <c r="P31" s="163"/>
-      <c r="Q31" s="164"/>
+      <c r="A31" s="185"/>
+      <c r="B31" s="184"/>
+      <c r="C31" s="186"/>
+      <c r="D31" s="184"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="184"/>
+      <c r="G31" s="187"/>
+      <c r="H31" s="183"/>
+      <c r="I31" s="184"/>
+      <c r="J31" s="187"/>
+      <c r="K31" s="184"/>
+      <c r="L31" s="182"/>
+      <c r="M31" s="183"/>
+      <c r="N31" s="184"/>
+      <c r="O31" s="182"/>
+      <c r="P31" s="183"/>
+      <c r="Q31" s="184"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -10636,121 +10636,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -10772,6 +10657,121 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-24\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0ED55FF-7F00-4945-9519-F17C6F944C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBE29B2-3E37-4872-B5CF-DC7423550954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -318,33 +318,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>1
-①データベース上の全レコードのID,タスク名,カテゴリ名,期限,ステータス名,メモ,登録日時,更新日時が表示されている
-②リンクになっているIDを押下すると押下したIDのタスク詳細が表示される。
-2
-①データベース上の全レコードのID,タスク名,カテゴリ名,期限,ステータス名,メモ,登録日時,更新日時が表示されている
-②ページ内のメニューへ戻るボタンを押下すると、メニュー画面へ遷移する。</t>
-    <rPh sb="9" eb="10">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>1タスク詳細画面に遷移する。2メニュー画面に戻る。</t>
     <rPh sb="4" eb="8">
       <t>ショウサイガメン</t>
@@ -389,6 +362,30 @@
     </rPh>
     <rPh sb="74" eb="76">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1
+①データベース上の全レコードのID,タスク名,カテゴリ名,期限,ステータス名,メモ,登録日時,更新日時が表示されている
+②リンクになっているIDを押下すると押下したIDのタスク詳細へ遷移する。
+2
+①データベース上の全レコードのID,タスク名,カテゴリ名,期限,ステータス名,メモ,登録日時,更新日時が表示されている
+②ページ内のメニューへ戻るボタンを押下すると、メニュー画面へ遷移する。</t>
+    <rPh sb="9" eb="10">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ショウサイ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -1340,6 +1337,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1373,21 +1415,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1433,36 +1460,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1526,51 +1523,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1646,6 +1643,51 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1667,15 +1709,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1687,42 +1720,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1908,6 +1905,99 @@
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>①</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61488E80-1656-F70C-9C21-F0D6E130B67F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3305175" y="1543050"/>
+          <a:ext cx="1152525" cy="361950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800"/>
+            <a:t>ユーザー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800"/>
+            <a:t>ID:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800"/>
+            <a:t>〇〇</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800"/>
+            <a:t>ユーザー名</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800"/>
+            <a:t>:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800"/>
+            <a:t>〇〇</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3346,19 +3436,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="85" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="68"/>
-      <c r="F1" s="85" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="68"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -3370,190 +3460,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="97"/>
+      <c r="F2" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="97"/>
+      <c r="H2" s="100">
         <v>45805</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="63"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="64"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="65"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="70"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="74" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="75"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="74" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="75"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="64"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="74" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="75"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="95" t="s">
+      <c r="C9" s="62"/>
+      <c r="D9" s="74" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="64"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="71"/>
+      <c r="B10" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="62"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="64"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="72"/>
+      <c r="B11" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="62"/>
+      <c r="D11" s="74" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="64"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="75"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="75"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="95" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="75"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="71" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="75"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="97"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
-      <c r="H13" s="97"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="100"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="69"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4544,6 +4634,18 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4559,18 +4661,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6082,23 +6172,23 @@
       <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="126"/>
+      <c r="B5" s="123"/>
       <c r="C5" s="117"/>
-      <c r="D5" s="131" t="s">
+      <c r="D5" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="132"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="130"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="130" t="s">
+      <c r="A6" s="127" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="53"/>
@@ -6109,19 +6199,19 @@
       <c r="G6" s="53"/>
       <c r="H6" s="53"/>
       <c r="I6" s="53"/>
-      <c r="J6" s="123"/>
+      <c r="J6" s="131"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="133"/>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="135"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="133"/>
+      <c r="C7" s="133"/>
+      <c r="D7" s="133"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="134"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="111"/>
@@ -6133,7 +6223,7 @@
       <c r="G8" s="56"/>
       <c r="H8" s="56"/>
       <c r="I8" s="56"/>
-      <c r="J8" s="136"/>
+      <c r="J8" s="135"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="111"/>
@@ -6145,7 +6235,7 @@
       <c r="G9" s="56"/>
       <c r="H9" s="56"/>
       <c r="I9" s="56"/>
-      <c r="J9" s="136"/>
+      <c r="J9" s="135"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="111"/>
@@ -6157,7 +6247,7 @@
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
       <c r="I10" s="56"/>
-      <c r="J10" s="136"/>
+      <c r="J10" s="135"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="111"/>
@@ -6169,7 +6259,7 @@
       <c r="G11" s="56"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
-      <c r="J11" s="136"/>
+      <c r="J11" s="135"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="111"/>
@@ -6181,7 +6271,7 @@
       <c r="G12" s="56"/>
       <c r="H12" s="56"/>
       <c r="I12" s="56"/>
-      <c r="J12" s="136"/>
+      <c r="J12" s="135"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="111"/>
@@ -6193,10 +6283,10 @@
       <c r="G13" s="56"/>
       <c r="H13" s="56"/>
       <c r="I13" s="56"/>
-      <c r="J13" s="136"/>
+      <c r="J13" s="135"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="130" t="s">
+      <c r="A14" s="127" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="53"/>
@@ -6207,15 +6297,15 @@
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
-      <c r="J14" s="123"/>
+      <c r="J14" s="131"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="127" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="53"/>
       <c r="C15" s="54"/>
-      <c r="D15" s="122" t="s">
+      <c r="D15" s="136" t="s">
         <v>75</v>
       </c>
       <c r="E15" s="53"/>
@@ -6230,7 +6320,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="130" t="s">
+      <c r="A16" s="127" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="53"/>
@@ -6251,10 +6341,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="53"/>
-      <c r="J16" s="123"/>
+      <c r="J16" s="131"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="124">
+      <c r="A17" s="128">
         <v>1</v>
       </c>
       <c r="B17" s="53"/>
@@ -6269,80 +6359,80 @@
       <c r="G17" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="122"/>
+      <c r="H17" s="136"/>
       <c r="I17" s="53"/>
-      <c r="J17" s="123"/>
+      <c r="J17" s="131"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="124"/>
+      <c r="A18" s="128"/>
       <c r="B18" s="53"/>
       <c r="C18" s="54"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="122"/>
+      <c r="H18" s="136"/>
       <c r="I18" s="53"/>
-      <c r="J18" s="123"/>
+      <c r="J18" s="131"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="124"/>
+      <c r="A19" s="128"/>
       <c r="B19" s="53"/>
       <c r="C19" s="54"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="122"/>
+      <c r="H19" s="136"/>
       <c r="I19" s="53"/>
-      <c r="J19" s="123"/>
+      <c r="J19" s="131"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="124"/>
+      <c r="A20" s="128"/>
       <c r="B20" s="53"/>
       <c r="C20" s="54"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="122"/>
+      <c r="H20" s="136"/>
       <c r="I20" s="53"/>
-      <c r="J20" s="123"/>
+      <c r="J20" s="131"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="124"/>
+      <c r="A21" s="128"/>
       <c r="B21" s="53"/>
       <c r="C21" s="54"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="122"/>
+      <c r="H21" s="136"/>
       <c r="I21" s="53"/>
-      <c r="J21" s="123"/>
+      <c r="J21" s="131"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="124"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="53"/>
       <c r="C22" s="54"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="122"/>
+      <c r="H22" s="136"/>
       <c r="I22" s="53"/>
-      <c r="J22" s="123"/>
+      <c r="J22" s="131"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="127"/>
-      <c r="B23" s="128"/>
-      <c r="C23" s="129"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="126"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="138"/>
-      <c r="I23" s="128"/>
+      <c r="I23" s="125"/>
       <c r="J23" s="139"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7324,11 +7414,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -7345,16 +7440,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8789,7 +8879,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="186" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="147"/>
@@ -8800,14 +8890,14 @@
       <c r="G1" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
       <c r="J1" s="156"/>
       <c r="K1" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="166"/>
-      <c r="M1" s="166"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
       <c r="N1" s="156"/>
       <c r="O1" s="155" t="s">
         <v>7</v>
@@ -8820,7 +8910,7 @@
       <c r="S1" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="168"/>
+      <c r="T1" s="183"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="149"/>
@@ -8832,21 +8922,21 @@
       <c r="G2" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
+      <c r="H2" s="187"/>
+      <c r="I2" s="187"/>
       <c r="J2" s="158"/>
       <c r="K2" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="175"/>
-      <c r="M2" s="175"/>
+      <c r="L2" s="187"/>
+      <c r="M2" s="187"/>
       <c r="N2" s="158"/>
       <c r="O2" s="157"/>
       <c r="P2" s="158"/>
       <c r="Q2" s="157"/>
       <c r="R2" s="158"/>
       <c r="S2" s="157"/>
-      <c r="T2" s="162"/>
+      <c r="T2" s="177"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="149"/>
@@ -8868,7 +8958,7 @@
       <c r="Q3" s="159"/>
       <c r="R3" s="151"/>
       <c r="S3" s="159"/>
-      <c r="T3" s="163"/>
+      <c r="T3" s="178"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="152"/>
@@ -8890,85 +8980,85 @@
       <c r="Q4" s="160"/>
       <c r="R4" s="154"/>
       <c r="S4" s="160"/>
-      <c r="T4" s="164"/>
+      <c r="T4" s="179"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="165" t="s">
+      <c r="A5" s="180" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="166"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
       <c r="F5" s="156"/>
-      <c r="G5" s="167" t="s">
+      <c r="G5" s="182" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="166"/>
-      <c r="I5" s="166"/>
-      <c r="J5" s="166"/>
-      <c r="K5" s="166"/>
-      <c r="L5" s="166"/>
-      <c r="M5" s="166"/>
-      <c r="N5" s="166"/>
-      <c r="O5" s="166"/>
-      <c r="P5" s="166"/>
-      <c r="Q5" s="166"/>
-      <c r="R5" s="166"/>
-      <c r="S5" s="166"/>
-      <c r="T5" s="168"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="181"/>
+      <c r="M5" s="181"/>
+      <c r="N5" s="181"/>
+      <c r="O5" s="181"/>
+      <c r="P5" s="181"/>
+      <c r="Q5" s="181"/>
+      <c r="R5" s="181"/>
+      <c r="S5" s="181"/>
+      <c r="T5" s="183"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="169" t="s">
+      <c r="A6" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="170"/>
-      <c r="C6" s="170"/>
-      <c r="D6" s="170"/>
-      <c r="E6" s="170"/>
-      <c r="F6" s="171"/>
-      <c r="G6" s="172" t="s">
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="170"/>
-      <c r="I6" s="170"/>
-      <c r="J6" s="170"/>
-      <c r="K6" s="170"/>
-      <c r="L6" s="170"/>
-      <c r="M6" s="170"/>
-      <c r="N6" s="170"/>
-      <c r="O6" s="170"/>
-      <c r="P6" s="170"/>
-      <c r="Q6" s="170"/>
-      <c r="R6" s="170"/>
-      <c r="S6" s="170"/>
-      <c r="T6" s="173"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="169"/>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="169"/>
+      <c r="Q6" s="169"/>
+      <c r="R6" s="169"/>
+      <c r="S6" s="169"/>
+      <c r="T6" s="185"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="169" t="s">
+      <c r="A7" s="175" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="170"/>
-      <c r="E7" s="170"/>
-      <c r="F7" s="171"/>
-      <c r="G7" s="172" t="s">
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="184" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170"/>
-      <c r="J7" s="170"/>
-      <c r="K7" s="170"/>
-      <c r="L7" s="170"/>
-      <c r="M7" s="170"/>
-      <c r="N7" s="170"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="170"/>
-      <c r="Q7" s="170"/>
-      <c r="R7" s="170"/>
-      <c r="S7" s="170"/>
-      <c r="T7" s="173"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
+      <c r="R7" s="169"/>
+      <c r="S7" s="169"/>
+      <c r="T7" s="185"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9167,37 +9257,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="169" t="s">
+      <c r="A15" s="175" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="171"/>
-      <c r="C15" s="181" t="s">
+      <c r="B15" s="170"/>
+      <c r="C15" s="176" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="171"/>
-      <c r="E15" s="176" t="s">
+      <c r="D15" s="170"/>
+      <c r="E15" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="171"/>
-      <c r="G15" s="176" t="s">
+      <c r="F15" s="170"/>
+      <c r="G15" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="170"/>
-      <c r="I15" s="171"/>
-      <c r="J15" s="176" t="s">
+      <c r="H15" s="169"/>
+      <c r="I15" s="170"/>
+      <c r="J15" s="174" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="171"/>
-      <c r="L15" s="176" t="s">
+      <c r="K15" s="170"/>
+      <c r="L15" s="174" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="170"/>
-      <c r="N15" s="171"/>
-      <c r="O15" s="176" t="s">
+      <c r="M15" s="169"/>
+      <c r="N15" s="170"/>
+      <c r="O15" s="174" t="s">
         <v>56</v>
       </c>
-      <c r="P15" s="170"/>
-      <c r="Q15" s="171"/>
+      <c r="P15" s="169"/>
+      <c r="Q15" s="170"/>
       <c r="R15" s="44" t="s">
         <v>57</v>
       </c>
@@ -9209,37 +9299,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="177">
+      <c r="A16" s="171">
         <v>1</v>
       </c>
-      <c r="B16" s="171"/>
-      <c r="C16" s="178" t="s">
+      <c r="B16" s="170"/>
+      <c r="C16" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="171"/>
-      <c r="E16" s="178" t="s">
+      <c r="D16" s="170"/>
+      <c r="E16" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="171"/>
-      <c r="G16" s="179" t="s">
+      <c r="F16" s="170"/>
+      <c r="G16" s="173" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="170"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="179" t="s">
+      <c r="H16" s="169"/>
+      <c r="I16" s="170"/>
+      <c r="J16" s="173" t="s">
         <v>63</v>
       </c>
-      <c r="K16" s="171"/>
-      <c r="L16" s="180" t="s">
+      <c r="K16" s="170"/>
+      <c r="L16" s="168" t="s">
         <v>64</v>
       </c>
-      <c r="M16" s="170"/>
-      <c r="N16" s="171"/>
-      <c r="O16" s="180" t="s">
+      <c r="M16" s="169"/>
+      <c r="N16" s="170"/>
+      <c r="O16" s="168" t="s">
         <v>65</v>
       </c>
-      <c r="P16" s="170"/>
-      <c r="Q16" s="171"/>
+      <c r="P16" s="169"/>
+      <c r="Q16" s="170"/>
       <c r="R16" s="46"/>
       <c r="S16" s="46"/>
       <c r="T16" s="47"/>
@@ -9251,37 +9341,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="177">
+      <c r="A17" s="171">
         <v>2</v>
       </c>
-      <c r="B17" s="171"/>
-      <c r="C17" s="178" t="s">
+      <c r="B17" s="170"/>
+      <c r="C17" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="171"/>
-      <c r="E17" s="178" t="s">
+      <c r="D17" s="170"/>
+      <c r="E17" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="171"/>
-      <c r="G17" s="179" t="s">
+      <c r="F17" s="170"/>
+      <c r="G17" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="170"/>
-      <c r="I17" s="171"/>
-      <c r="J17" s="179" t="s">
+      <c r="H17" s="169"/>
+      <c r="I17" s="170"/>
+      <c r="J17" s="173" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="171"/>
-      <c r="L17" s="180" t="s">
+      <c r="K17" s="170"/>
+      <c r="L17" s="168" t="s">
         <v>70</v>
       </c>
-      <c r="M17" s="170"/>
-      <c r="N17" s="171"/>
-      <c r="O17" s="180" t="s">
+      <c r="M17" s="169"/>
+      <c r="N17" s="170"/>
+      <c r="O17" s="168" t="s">
         <v>71</v>
       </c>
-      <c r="P17" s="170"/>
-      <c r="Q17" s="171"/>
+      <c r="P17" s="169"/>
+      <c r="Q17" s="170"/>
       <c r="R17" s="46"/>
       <c r="S17" s="46"/>
       <c r="T17" s="47"/>
@@ -9293,23 +9383,23 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="177"/>
-      <c r="B18" s="171"/>
-      <c r="C18" s="178"/>
-      <c r="D18" s="171"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="171"/>
-      <c r="G18" s="179"/>
-      <c r="H18" s="170"/>
-      <c r="I18" s="171"/>
-      <c r="J18" s="179"/>
-      <c r="K18" s="171"/>
-      <c r="L18" s="180"/>
-      <c r="M18" s="170"/>
-      <c r="N18" s="171"/>
-      <c r="O18" s="180"/>
-      <c r="P18" s="170"/>
-      <c r="Q18" s="171"/>
+      <c r="A18" s="171"/>
+      <c r="B18" s="170"/>
+      <c r="C18" s="172"/>
+      <c r="D18" s="170"/>
+      <c r="E18" s="172"/>
+      <c r="F18" s="170"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="169"/>
+      <c r="I18" s="170"/>
+      <c r="J18" s="173"/>
+      <c r="K18" s="170"/>
+      <c r="L18" s="168"/>
+      <c r="M18" s="169"/>
+      <c r="N18" s="170"/>
+      <c r="O18" s="168"/>
+      <c r="P18" s="169"/>
+      <c r="Q18" s="170"/>
       <c r="R18" s="46"/>
       <c r="S18" s="46"/>
       <c r="T18" s="47"/>
@@ -9321,23 +9411,23 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="177"/>
-      <c r="B19" s="171"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="171"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="171"/>
-      <c r="G19" s="179"/>
-      <c r="H19" s="170"/>
-      <c r="I19" s="171"/>
-      <c r="J19" s="179"/>
-      <c r="K19" s="171"/>
-      <c r="L19" s="180"/>
-      <c r="M19" s="170"/>
-      <c r="N19" s="171"/>
-      <c r="O19" s="180"/>
-      <c r="P19" s="170"/>
-      <c r="Q19" s="171"/>
+      <c r="A19" s="171"/>
+      <c r="B19" s="170"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="170"/>
+      <c r="E19" s="172"/>
+      <c r="F19" s="170"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="170"/>
+      <c r="J19" s="173"/>
+      <c r="K19" s="170"/>
+      <c r="L19" s="168"/>
+      <c r="M19" s="169"/>
+      <c r="N19" s="170"/>
+      <c r="O19" s="168"/>
+      <c r="P19" s="169"/>
+      <c r="Q19" s="170"/>
       <c r="R19" s="46"/>
       <c r="S19" s="46"/>
       <c r="T19" s="47"/>
@@ -9349,23 +9439,23 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="177"/>
-      <c r="B20" s="171"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="171"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="171"/>
-      <c r="G20" s="179"/>
-      <c r="H20" s="170"/>
-      <c r="I20" s="171"/>
-      <c r="J20" s="179"/>
-      <c r="K20" s="171"/>
-      <c r="L20" s="180"/>
-      <c r="M20" s="170"/>
-      <c r="N20" s="171"/>
-      <c r="O20" s="180"/>
-      <c r="P20" s="170"/>
-      <c r="Q20" s="171"/>
+      <c r="A20" s="171"/>
+      <c r="B20" s="170"/>
+      <c r="C20" s="172"/>
+      <c r="D20" s="170"/>
+      <c r="E20" s="172"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="170"/>
+      <c r="J20" s="173"/>
+      <c r="K20" s="170"/>
+      <c r="L20" s="168"/>
+      <c r="M20" s="169"/>
+      <c r="N20" s="170"/>
+      <c r="O20" s="168"/>
+      <c r="P20" s="169"/>
+      <c r="Q20" s="170"/>
       <c r="R20" s="46"/>
       <c r="S20" s="46"/>
       <c r="T20" s="47"/>
@@ -9377,23 +9467,23 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="177"/>
-      <c r="B21" s="171"/>
-      <c r="C21" s="178"/>
-      <c r="D21" s="171"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="171"/>
-      <c r="G21" s="179"/>
-      <c r="H21" s="170"/>
-      <c r="I21" s="171"/>
-      <c r="J21" s="179"/>
-      <c r="K21" s="171"/>
-      <c r="L21" s="180"/>
-      <c r="M21" s="170"/>
-      <c r="N21" s="171"/>
-      <c r="O21" s="180"/>
-      <c r="P21" s="170"/>
-      <c r="Q21" s="171"/>
+      <c r="A21" s="171"/>
+      <c r="B21" s="170"/>
+      <c r="C21" s="172"/>
+      <c r="D21" s="170"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="170"/>
+      <c r="G21" s="173"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="170"/>
+      <c r="J21" s="173"/>
+      <c r="K21" s="170"/>
+      <c r="L21" s="168"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="170"/>
+      <c r="O21" s="168"/>
+      <c r="P21" s="169"/>
+      <c r="Q21" s="170"/>
       <c r="R21" s="46"/>
       <c r="S21" s="46"/>
       <c r="T21" s="47"/>
@@ -9405,23 +9495,23 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="177"/>
-      <c r="B22" s="171"/>
-      <c r="C22" s="178"/>
-      <c r="D22" s="171"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="171"/>
-      <c r="G22" s="179"/>
-      <c r="H22" s="170"/>
-      <c r="I22" s="171"/>
-      <c r="J22" s="179"/>
-      <c r="K22" s="171"/>
-      <c r="L22" s="180"/>
-      <c r="M22" s="170"/>
-      <c r="N22" s="171"/>
-      <c r="O22" s="180"/>
-      <c r="P22" s="170"/>
-      <c r="Q22" s="171"/>
+      <c r="A22" s="171"/>
+      <c r="B22" s="170"/>
+      <c r="C22" s="172"/>
+      <c r="D22" s="170"/>
+      <c r="E22" s="172"/>
+      <c r="F22" s="170"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="170"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="170"/>
+      <c r="L22" s="168"/>
+      <c r="M22" s="169"/>
+      <c r="N22" s="170"/>
+      <c r="O22" s="168"/>
+      <c r="P22" s="169"/>
+      <c r="Q22" s="170"/>
       <c r="R22" s="46"/>
       <c r="S22" s="46"/>
       <c r="T22" s="47"/>
@@ -9433,23 +9523,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="177"/>
-      <c r="B23" s="171"/>
-      <c r="C23" s="178"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="179"/>
-      <c r="H23" s="170"/>
-      <c r="I23" s="171"/>
-      <c r="J23" s="179"/>
-      <c r="K23" s="171"/>
-      <c r="L23" s="180"/>
-      <c r="M23" s="170"/>
-      <c r="N23" s="171"/>
-      <c r="O23" s="180"/>
-      <c r="P23" s="170"/>
-      <c r="Q23" s="171"/>
+      <c r="A23" s="171"/>
+      <c r="B23" s="170"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="170"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="170"/>
+      <c r="J23" s="173"/>
+      <c r="K23" s="170"/>
+      <c r="L23" s="168"/>
+      <c r="M23" s="169"/>
+      <c r="N23" s="170"/>
+      <c r="O23" s="168"/>
+      <c r="P23" s="169"/>
+      <c r="Q23" s="170"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -9461,23 +9551,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="177"/>
-      <c r="B24" s="171"/>
-      <c r="C24" s="178"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="179"/>
-      <c r="H24" s="170"/>
-      <c r="I24" s="171"/>
-      <c r="J24" s="179"/>
-      <c r="K24" s="171"/>
-      <c r="L24" s="180"/>
-      <c r="M24" s="170"/>
-      <c r="N24" s="171"/>
-      <c r="O24" s="180"/>
-      <c r="P24" s="170"/>
-      <c r="Q24" s="171"/>
+      <c r="A24" s="171"/>
+      <c r="B24" s="170"/>
+      <c r="C24" s="172"/>
+      <c r="D24" s="170"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="170"/>
+      <c r="G24" s="173"/>
+      <c r="H24" s="169"/>
+      <c r="I24" s="170"/>
+      <c r="J24" s="173"/>
+      <c r="K24" s="170"/>
+      <c r="L24" s="168"/>
+      <c r="M24" s="169"/>
+      <c r="N24" s="170"/>
+      <c r="O24" s="168"/>
+      <c r="P24" s="169"/>
+      <c r="Q24" s="170"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -9489,23 +9579,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="177"/>
-      <c r="B25" s="171"/>
-      <c r="C25" s="178"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="171"/>
-      <c r="G25" s="179"/>
-      <c r="H25" s="170"/>
-      <c r="I25" s="171"/>
-      <c r="J25" s="179"/>
-      <c r="K25" s="171"/>
-      <c r="L25" s="180"/>
-      <c r="M25" s="170"/>
-      <c r="N25" s="171"/>
-      <c r="O25" s="180"/>
-      <c r="P25" s="170"/>
-      <c r="Q25" s="171"/>
+      <c r="A25" s="171"/>
+      <c r="B25" s="170"/>
+      <c r="C25" s="172"/>
+      <c r="D25" s="170"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="170"/>
+      <c r="G25" s="173"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="170"/>
+      <c r="J25" s="173"/>
+      <c r="K25" s="170"/>
+      <c r="L25" s="168"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="170"/>
+      <c r="O25" s="168"/>
+      <c r="P25" s="169"/>
+      <c r="Q25" s="170"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -9517,23 +9607,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="177"/>
-      <c r="B26" s="171"/>
-      <c r="C26" s="178"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="178"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="179"/>
-      <c r="H26" s="170"/>
-      <c r="I26" s="171"/>
-      <c r="J26" s="179"/>
-      <c r="K26" s="171"/>
-      <c r="L26" s="180"/>
-      <c r="M26" s="170"/>
-      <c r="N26" s="171"/>
-      <c r="O26" s="180"/>
-      <c r="P26" s="170"/>
-      <c r="Q26" s="171"/>
+      <c r="A26" s="171"/>
+      <c r="B26" s="170"/>
+      <c r="C26" s="172"/>
+      <c r="D26" s="170"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="170"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="170"/>
+      <c r="J26" s="173"/>
+      <c r="K26" s="170"/>
+      <c r="L26" s="168"/>
+      <c r="M26" s="169"/>
+      <c r="N26" s="170"/>
+      <c r="O26" s="168"/>
+      <c r="P26" s="169"/>
+      <c r="Q26" s="170"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -9545,23 +9635,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="177"/>
-      <c r="B27" s="171"/>
-      <c r="C27" s="178"/>
-      <c r="D27" s="171"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="171"/>
-      <c r="G27" s="179"/>
-      <c r="H27" s="170"/>
-      <c r="I27" s="171"/>
-      <c r="J27" s="179"/>
-      <c r="K27" s="171"/>
-      <c r="L27" s="180"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="171"/>
-      <c r="O27" s="180"/>
-      <c r="P27" s="170"/>
-      <c r="Q27" s="171"/>
+      <c r="A27" s="171"/>
+      <c r="B27" s="170"/>
+      <c r="C27" s="172"/>
+      <c r="D27" s="170"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="170"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="170"/>
+      <c r="J27" s="173"/>
+      <c r="K27" s="170"/>
+      <c r="L27" s="168"/>
+      <c r="M27" s="169"/>
+      <c r="N27" s="170"/>
+      <c r="O27" s="168"/>
+      <c r="P27" s="169"/>
+      <c r="Q27" s="170"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -9573,23 +9663,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="177"/>
-      <c r="B28" s="171"/>
-      <c r="C28" s="178"/>
-      <c r="D28" s="171"/>
-      <c r="E28" s="178"/>
-      <c r="F28" s="171"/>
-      <c r="G28" s="179"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="171"/>
-      <c r="J28" s="179"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="180"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="171"/>
-      <c r="O28" s="180"/>
-      <c r="P28" s="170"/>
-      <c r="Q28" s="171"/>
+      <c r="A28" s="171"/>
+      <c r="B28" s="170"/>
+      <c r="C28" s="172"/>
+      <c r="D28" s="170"/>
+      <c r="E28" s="172"/>
+      <c r="F28" s="170"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="170"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="170"/>
+      <c r="L28" s="168"/>
+      <c r="M28" s="169"/>
+      <c r="N28" s="170"/>
+      <c r="O28" s="168"/>
+      <c r="P28" s="169"/>
+      <c r="Q28" s="170"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -9601,23 +9691,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="177"/>
-      <c r="B29" s="171"/>
-      <c r="C29" s="178"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="179"/>
-      <c r="H29" s="170"/>
-      <c r="I29" s="171"/>
-      <c r="J29" s="179"/>
-      <c r="K29" s="171"/>
-      <c r="L29" s="180"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="171"/>
-      <c r="O29" s="180"/>
-      <c r="P29" s="170"/>
-      <c r="Q29" s="171"/>
+      <c r="A29" s="171"/>
+      <c r="B29" s="170"/>
+      <c r="C29" s="172"/>
+      <c r="D29" s="170"/>
+      <c r="E29" s="172"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="170"/>
+      <c r="J29" s="173"/>
+      <c r="K29" s="170"/>
+      <c r="L29" s="168"/>
+      <c r="M29" s="169"/>
+      <c r="N29" s="170"/>
+      <c r="O29" s="168"/>
+      <c r="P29" s="169"/>
+      <c r="Q29" s="170"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -9629,23 +9719,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="177"/>
-      <c r="B30" s="171"/>
-      <c r="C30" s="178"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="179"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="171"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="171"/>
-      <c r="L30" s="180"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="171"/>
-      <c r="O30" s="180"/>
-      <c r="P30" s="170"/>
-      <c r="Q30" s="171"/>
+      <c r="A30" s="171"/>
+      <c r="B30" s="170"/>
+      <c r="C30" s="172"/>
+      <c r="D30" s="170"/>
+      <c r="E30" s="172"/>
+      <c r="F30" s="170"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="170"/>
+      <c r="J30" s="173"/>
+      <c r="K30" s="170"/>
+      <c r="L30" s="168"/>
+      <c r="M30" s="169"/>
+      <c r="N30" s="170"/>
+      <c r="O30" s="168"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="170"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -9657,23 +9747,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="185"/>
-      <c r="B31" s="184"/>
-      <c r="C31" s="186"/>
-      <c r="D31" s="184"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="184"/>
-      <c r="G31" s="187"/>
-      <c r="H31" s="183"/>
-      <c r="I31" s="184"/>
-      <c r="J31" s="187"/>
-      <c r="K31" s="184"/>
-      <c r="L31" s="182"/>
-      <c r="M31" s="183"/>
-      <c r="N31" s="184"/>
-      <c r="O31" s="182"/>
-      <c r="P31" s="183"/>
-      <c r="Q31" s="184"/>
+      <c r="A31" s="165"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="167"/>
+      <c r="H31" s="163"/>
+      <c r="I31" s="164"/>
+      <c r="J31" s="167"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="162"/>
+      <c r="M31" s="163"/>
+      <c r="N31" s="164"/>
+      <c r="O31" s="162"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="164"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -10671,6 +10761,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -10692,121 +10897,6 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F4A58C-D91D-4887-A4B6-B6C6AE6907E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D232B5-AF71-4C5D-9216-88435B4F9ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -542,13 +542,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>データベースに接続されていないこと</t>
-    <rPh sb="7" eb="9">
-      <t>セツゾク</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>エラー画面へ遷移する
 エラーの原因がデータベースに接続されていない旨通知する</t>
     <rPh sb="25" eb="27">
@@ -557,16 +550,8 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>〇</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t xml:space="preserve">正常系
 </t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>ログイン状態かつデータベースに接続されていること</t>
     <phoneticPr fontId="7"/>
   </si>
   <si>
@@ -586,6 +571,67 @@
     </rPh>
     <rPh sb="19" eb="23">
       <t>イチランヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>データベースに接続されているときのタスク一覧表示ボタンの押下</t>
+    <rPh sb="7" eb="9">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>登録されているタスク一覧が表示される</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>NOT NULL制約がないものに対して未入力がある場合のタスク一覧表示</t>
+    <rPh sb="8" eb="10">
+      <t>セイヤク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>「未入力」と表示される</t>
+    <rPh sb="1" eb="4">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -1797,6 +1843,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1812,6 +1891,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1842,84 +1966,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1983,6 +2029,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2001,18 +2056,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2025,9 +2074,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2103,6 +2149,69 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2121,70 +2230,91 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2192,90 +2322,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3994,19 +4040,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="107" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="95"/>
-      <c r="F1" s="107" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="95"/>
+      <c r="G1" s="80"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4018,190 +4064,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="108" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="109"/>
-      <c r="F2" s="108" t="s">
+      <c r="E2" s="99"/>
+      <c r="F2" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="109"/>
-      <c r="H2" s="112">
+      <c r="G2" s="99"/>
+      <c r="H2" s="102">
         <v>45805</v>
       </c>
-      <c r="I2" s="87" t="s">
+      <c r="I2" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="101"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="97"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="75" t="s">
+      <c r="B6" s="84"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="76"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="87"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="75" t="s">
+      <c r="B7" s="84"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="76"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="87"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="73"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="75" t="s">
+      <c r="B8" s="84"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="76"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="87"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="111" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="86" t="s">
+      <c r="C9" s="85"/>
+      <c r="D9" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="76"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="87"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="83"/>
-      <c r="B10" s="85" t="s">
+      <c r="A10" s="109"/>
+      <c r="B10" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="76"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="87"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="84"/>
-      <c r="B11" s="85" t="s">
+      <c r="A11" s="110"/>
+      <c r="B11" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="86" t="s">
+      <c r="C11" s="85"/>
+      <c r="D11" s="112" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="76"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="87"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="75" t="s">
+      <c r="B12" s="84"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="76"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="87"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="81"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="107"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5192,18 +5238,6 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5219,6 +5253,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6730,23 +6776,23 @@
       <c r="J4" s="118"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="135"/>
+      <c r="B5" s="138"/>
       <c r="C5" s="129"/>
-      <c r="D5" s="141" t="s">
+      <c r="D5" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="142"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="142" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="65"/>
@@ -6757,19 +6803,19 @@
       <c r="G6" s="65"/>
       <c r="H6" s="65"/>
       <c r="I6" s="65"/>
-      <c r="J6" s="143"/>
+      <c r="J6" s="135"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="144"/>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="145"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="145"/>
-      <c r="J7" s="146"/>
+      <c r="A7" s="145"/>
+      <c r="B7" s="146"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="146"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="146"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="147"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="123"/>
@@ -6781,7 +6827,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="68"/>
       <c r="I8" s="68"/>
-      <c r="J8" s="147"/>
+      <c r="J8" s="148"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="123"/>
@@ -6793,7 +6839,7 @@
       <c r="G9" s="68"/>
       <c r="H9" s="68"/>
       <c r="I9" s="68"/>
-      <c r="J9" s="147"/>
+      <c r="J9" s="148"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="123"/>
@@ -6805,7 +6851,7 @@
       <c r="G10" s="68"/>
       <c r="H10" s="68"/>
       <c r="I10" s="68"/>
-      <c r="J10" s="147"/>
+      <c r="J10" s="148"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="123"/>
@@ -6817,7 +6863,7 @@
       <c r="G11" s="68"/>
       <c r="H11" s="68"/>
       <c r="I11" s="68"/>
-      <c r="J11" s="147"/>
+      <c r="J11" s="148"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="123"/>
@@ -6829,7 +6875,7 @@
       <c r="G12" s="68"/>
       <c r="H12" s="68"/>
       <c r="I12" s="68"/>
-      <c r="J12" s="147"/>
+      <c r="J12" s="148"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="123"/>
@@ -6841,10 +6887,10 @@
       <c r="G13" s="68"/>
       <c r="H13" s="68"/>
       <c r="I13" s="68"/>
-      <c r="J13" s="147"/>
+      <c r="J13" s="148"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="142" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="65"/>
@@ -6855,15 +6901,15 @@
       <c r="G14" s="65"/>
       <c r="H14" s="65"/>
       <c r="I14" s="65"/>
-      <c r="J14" s="143"/>
+      <c r="J14" s="135"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="142" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="65"/>
       <c r="C15" s="66"/>
-      <c r="D15" s="148" t="s">
+      <c r="D15" s="134" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="65"/>
@@ -6878,7 +6924,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="139" t="s">
+      <c r="A16" s="142" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="65"/>
@@ -6899,10 +6945,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="65"/>
-      <c r="J16" s="143"/>
+      <c r="J16" s="135"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="140">
+      <c r="A17" s="136">
         <v>1</v>
       </c>
       <c r="B17" s="65"/>
@@ -6917,80 +6963,80 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="148"/>
+      <c r="H17" s="134"/>
       <c r="I17" s="65"/>
-      <c r="J17" s="143"/>
+      <c r="J17" s="135"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="140"/>
+      <c r="A18" s="136"/>
       <c r="B18" s="65"/>
       <c r="C18" s="66"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="148"/>
+      <c r="H18" s="134"/>
       <c r="I18" s="65"/>
-      <c r="J18" s="143"/>
+      <c r="J18" s="135"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="140"/>
+      <c r="A19" s="136"/>
       <c r="B19" s="65"/>
       <c r="C19" s="66"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="148"/>
+      <c r="H19" s="134"/>
       <c r="I19" s="65"/>
-      <c r="J19" s="143"/>
+      <c r="J19" s="135"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="140"/>
+      <c r="A20" s="136"/>
       <c r="B20" s="65"/>
       <c r="C20" s="66"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="148"/>
+      <c r="H20" s="134"/>
       <c r="I20" s="65"/>
-      <c r="J20" s="143"/>
+      <c r="J20" s="135"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="140"/>
+      <c r="A21" s="136"/>
       <c r="B21" s="65"/>
       <c r="C21" s="66"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="148"/>
+      <c r="H21" s="134"/>
       <c r="I21" s="65"/>
-      <c r="J21" s="143"/>
+      <c r="J21" s="135"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="140"/>
+      <c r="A22" s="136"/>
       <c r="B22" s="65"/>
       <c r="C22" s="66"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="148"/>
+      <c r="H22" s="134"/>
       <c r="I22" s="65"/>
-      <c r="J22" s="143"/>
+      <c r="J22" s="135"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="136"/>
-      <c r="B23" s="137"/>
-      <c r="C23" s="138"/>
+      <c r="A23" s="139"/>
+      <c r="B23" s="140"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="150"/>
-      <c r="I23" s="137"/>
+      <c r="I23" s="140"/>
       <c r="J23" s="151"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7972,16 +8018,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -7998,11 +8039,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9437,7 +9483,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="198" t="s">
+      <c r="A1" s="186" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="159"/>
@@ -9448,14 +9494,14 @@
       <c r="G1" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
       <c r="J1" s="168"/>
       <c r="K1" s="167" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
+      <c r="L1" s="178"/>
+      <c r="M1" s="178"/>
       <c r="N1" s="168"/>
       <c r="O1" s="167" t="s">
         <v>7</v>
@@ -9468,7 +9514,7 @@
       <c r="S1" s="167" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="195"/>
+      <c r="T1" s="180"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="161"/>
@@ -9480,16 +9526,16 @@
       <c r="G2" s="169" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
+      <c r="H2" s="187"/>
+      <c r="I2" s="187"/>
       <c r="J2" s="170"/>
       <c r="K2" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="199"/>
-      <c r="M2" s="199"/>
+      <c r="L2" s="187"/>
+      <c r="M2" s="187"/>
       <c r="N2" s="170"/>
-      <c r="O2" s="231">
+      <c r="O2" s="188">
         <v>45817</v>
       </c>
       <c r="P2" s="170"/>
@@ -9498,7 +9544,7 @@
       </c>
       <c r="R2" s="170"/>
       <c r="S2" s="169"/>
-      <c r="T2" s="189"/>
+      <c r="T2" s="174"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="161"/>
@@ -9520,7 +9566,7 @@
       <c r="Q3" s="171"/>
       <c r="R3" s="163"/>
       <c r="S3" s="171"/>
-      <c r="T3" s="190"/>
+      <c r="T3" s="175"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="164"/>
@@ -9542,85 +9588,85 @@
       <c r="Q4" s="172"/>
       <c r="R4" s="166"/>
       <c r="S4" s="172"/>
-      <c r="T4" s="191"/>
+      <c r="T4" s="176"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="192" t="s">
+      <c r="A5" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="193"/>
-      <c r="C5" s="193"/>
-      <c r="D5" s="193"/>
-      <c r="E5" s="193"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="178"/>
       <c r="F5" s="168"/>
-      <c r="G5" s="194" t="s">
+      <c r="G5" s="179" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="193"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="193"/>
-      <c r="K5" s="193"/>
-      <c r="L5" s="193"/>
-      <c r="M5" s="193"/>
-      <c r="N5" s="193"/>
-      <c r="O5" s="193"/>
-      <c r="P5" s="193"/>
-      <c r="Q5" s="193"/>
-      <c r="R5" s="193"/>
-      <c r="S5" s="193"/>
-      <c r="T5" s="195"/>
+      <c r="H5" s="178"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="178"/>
+      <c r="L5" s="178"/>
+      <c r="M5" s="178"/>
+      <c r="N5" s="178"/>
+      <c r="O5" s="178"/>
+      <c r="P5" s="178"/>
+      <c r="Q5" s="178"/>
+      <c r="R5" s="178"/>
+      <c r="S5" s="178"/>
+      <c r="T5" s="180"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="181" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="181"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="181"/>
-      <c r="E6" s="181"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="196" t="s">
+      <c r="B6" s="182"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="181"/>
-      <c r="I6" s="181"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="181"/>
-      <c r="L6" s="181"/>
-      <c r="M6" s="181"/>
-      <c r="N6" s="181"/>
-      <c r="O6" s="181"/>
-      <c r="P6" s="181"/>
-      <c r="Q6" s="181"/>
-      <c r="R6" s="181"/>
-      <c r="S6" s="181"/>
-      <c r="T6" s="197"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="182"/>
+      <c r="M6" s="182"/>
+      <c r="N6" s="182"/>
+      <c r="O6" s="182"/>
+      <c r="P6" s="182"/>
+      <c r="Q6" s="182"/>
+      <c r="R6" s="182"/>
+      <c r="S6" s="182"/>
+      <c r="T6" s="185"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="181"/>
-      <c r="C7" s="181"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="181"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="196" t="s">
+      <c r="B7" s="182"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="181"/>
-      <c r="I7" s="181"/>
-      <c r="J7" s="181"/>
-      <c r="K7" s="181"/>
-      <c r="L7" s="181"/>
-      <c r="M7" s="181"/>
-      <c r="N7" s="181"/>
-      <c r="O7" s="181"/>
-      <c r="P7" s="181"/>
-      <c r="Q7" s="181"/>
-      <c r="R7" s="181"/>
-      <c r="S7" s="181"/>
-      <c r="T7" s="197"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="182"/>
+      <c r="L7" s="182"/>
+      <c r="M7" s="182"/>
+      <c r="N7" s="182"/>
+      <c r="O7" s="182"/>
+      <c r="P7" s="182"/>
+      <c r="Q7" s="182"/>
+      <c r="R7" s="182"/>
+      <c r="S7" s="182"/>
+      <c r="T7" s="185"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9819,37 +9865,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="182"/>
-      <c r="C15" s="188" t="s">
+      <c r="B15" s="183"/>
+      <c r="C15" s="194" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="182"/>
-      <c r="E15" s="186" t="s">
+      <c r="D15" s="183"/>
+      <c r="E15" s="189" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="182"/>
-      <c r="G15" s="186" t="s">
+      <c r="F15" s="183"/>
+      <c r="G15" s="189" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="181"/>
-      <c r="I15" s="182"/>
-      <c r="J15" s="186" t="s">
+      <c r="H15" s="182"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="189" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="182"/>
-      <c r="L15" s="186" t="s">
+      <c r="K15" s="183"/>
+      <c r="L15" s="189" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="181"/>
-      <c r="N15" s="182"/>
-      <c r="O15" s="186" t="s">
+      <c r="M15" s="182"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="189" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="181"/>
-      <c r="Q15" s="182"/>
+      <c r="P15" s="182"/>
+      <c r="Q15" s="183"/>
       <c r="R15" s="44" t="s">
         <v>56</v>
       </c>
@@ -9861,37 +9907,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="183">
+      <c r="A16" s="190">
         <v>1</v>
       </c>
-      <c r="B16" s="182"/>
-      <c r="C16" s="184" t="s">
+      <c r="B16" s="183"/>
+      <c r="C16" s="191" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="182"/>
-      <c r="E16" s="184" t="s">
+      <c r="D16" s="183"/>
+      <c r="E16" s="191" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="182"/>
-      <c r="G16" s="185" t="s">
+      <c r="F16" s="183"/>
+      <c r="G16" s="192" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="181"/>
-      <c r="I16" s="182"/>
-      <c r="J16" s="185" t="s">
+      <c r="H16" s="182"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="192" t="s">
         <v>92</v>
       </c>
-      <c r="K16" s="182"/>
-      <c r="L16" s="180" t="s">
+      <c r="K16" s="183"/>
+      <c r="L16" s="193" t="s">
         <v>90</v>
       </c>
-      <c r="M16" s="181"/>
-      <c r="N16" s="182"/>
-      <c r="O16" s="180" t="s">
+      <c r="M16" s="182"/>
+      <c r="N16" s="183"/>
+      <c r="O16" s="193" t="s">
         <v>91</v>
       </c>
-      <c r="P16" s="181"/>
-      <c r="Q16" s="182"/>
+      <c r="P16" s="182"/>
+      <c r="Q16" s="183"/>
       <c r="R16" s="46"/>
       <c r="S16" s="46"/>
       <c r="T16" s="47"/>
@@ -9903,37 +9949,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="183">
+      <c r="A17" s="190">
         <v>2</v>
       </c>
-      <c r="B17" s="182"/>
-      <c r="C17" s="184" t="s">
+      <c r="B17" s="183"/>
+      <c r="C17" s="191" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="182"/>
-      <c r="E17" s="184" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="182"/>
-      <c r="G17" s="185" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="181"/>
-      <c r="I17" s="182"/>
-      <c r="J17" s="185" t="s">
-        <v>94</v>
-      </c>
-      <c r="K17" s="182"/>
-      <c r="L17" s="180" t="s">
+      <c r="D17" s="183"/>
+      <c r="E17" s="191" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="183"/>
+      <c r="G17" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="182"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="192" t="s">
+        <v>92</v>
+      </c>
+      <c r="K17" s="183"/>
+      <c r="L17" s="193" t="s">
         <v>90</v>
       </c>
-      <c r="M17" s="181"/>
-      <c r="N17" s="182"/>
-      <c r="O17" s="180" t="s">
-        <v>95</v>
-      </c>
-      <c r="P17" s="181"/>
-      <c r="Q17" s="182"/>
+      <c r="M17" s="182"/>
+      <c r="N17" s="183"/>
+      <c r="O17" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" s="182"/>
+      <c r="Q17" s="183"/>
       <c r="R17" s="46"/>
       <c r="S17" s="46"/>
       <c r="T17" s="47"/>
@@ -9945,37 +9991,37 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="183">
+      <c r="A18" s="190">
         <v>3</v>
       </c>
-      <c r="B18" s="182"/>
-      <c r="C18" s="184" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="182"/>
-      <c r="E18" s="184" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="182"/>
-      <c r="G18" s="185" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="181"/>
-      <c r="I18" s="182"/>
-      <c r="J18" s="185" t="s">
-        <v>98</v>
-      </c>
-      <c r="K18" s="182"/>
-      <c r="L18" s="180" t="s">
+      <c r="B18" s="183"/>
+      <c r="C18" s="191" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="183"/>
+      <c r="E18" s="191" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="183"/>
+      <c r="G18" s="192" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="182"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="192" t="s">
+        <v>92</v>
+      </c>
+      <c r="K18" s="183"/>
+      <c r="L18" s="193" t="s">
         <v>90</v>
       </c>
-      <c r="M18" s="181"/>
-      <c r="N18" s="182"/>
-      <c r="O18" s="180" t="s">
-        <v>99</v>
-      </c>
-      <c r="P18" s="181"/>
-      <c r="Q18" s="182"/>
+      <c r="M18" s="182"/>
+      <c r="N18" s="183"/>
+      <c r="O18" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="P18" s="182"/>
+      <c r="Q18" s="183"/>
       <c r="R18" s="46"/>
       <c r="S18" s="46"/>
       <c r="T18" s="47"/>
@@ -9986,24 +10032,38 @@
       <c r="Y18" s="48"/>
       <c r="Z18" s="48"/>
     </row>
-    <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="183"/>
-      <c r="B19" s="182"/>
-      <c r="C19" s="184"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="184"/>
-      <c r="F19" s="182"/>
-      <c r="G19" s="185"/>
-      <c r="H19" s="181"/>
-      <c r="I19" s="182"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="182"/>
-      <c r="L19" s="180"/>
-      <c r="M19" s="181"/>
-      <c r="N19" s="182"/>
-      <c r="O19" s="180"/>
-      <c r="P19" s="181"/>
-      <c r="Q19" s="182"/>
+    <row r="19" spans="1:26" ht="53.25" customHeight="1">
+      <c r="A19" s="190">
+        <v>4</v>
+      </c>
+      <c r="B19" s="183"/>
+      <c r="C19" s="191" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="183"/>
+      <c r="E19" s="191" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="183"/>
+      <c r="G19" s="192" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="182"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="192" t="s">
+        <v>92</v>
+      </c>
+      <c r="K19" s="183"/>
+      <c r="L19" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="M19" s="182"/>
+      <c r="N19" s="183"/>
+      <c r="O19" s="193" t="s">
+        <v>96</v>
+      </c>
+      <c r="P19" s="182"/>
+      <c r="Q19" s="183"/>
       <c r="R19" s="46"/>
       <c r="S19" s="46"/>
       <c r="T19" s="47"/>
@@ -10014,24 +10074,38 @@
       <c r="Y19" s="48"/>
       <c r="Z19" s="48"/>
     </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="183"/>
-      <c r="B20" s="182"/>
-      <c r="C20" s="184"/>
-      <c r="D20" s="182"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="182"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="181"/>
-      <c r="I20" s="182"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="182"/>
-      <c r="L20" s="180"/>
-      <c r="M20" s="181"/>
-      <c r="N20" s="182"/>
-      <c r="O20" s="180"/>
-      <c r="P20" s="181"/>
-      <c r="Q20" s="182"/>
+    <row r="20" spans="1:26" ht="55.5" customHeight="1">
+      <c r="A20" s="190">
+        <v>5</v>
+      </c>
+      <c r="B20" s="183"/>
+      <c r="C20" s="191" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="183"/>
+      <c r="E20" s="191" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="183"/>
+      <c r="G20" s="192" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="182"/>
+      <c r="I20" s="183"/>
+      <c r="J20" s="192" t="s">
+        <v>92</v>
+      </c>
+      <c r="K20" s="183"/>
+      <c r="L20" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="M20" s="182"/>
+      <c r="N20" s="183"/>
+      <c r="O20" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="P20" s="182"/>
+      <c r="Q20" s="183"/>
       <c r="R20" s="46"/>
       <c r="S20" s="46"/>
       <c r="T20" s="47"/>
@@ -10043,23 +10117,23 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="183"/>
-      <c r="B21" s="182"/>
-      <c r="C21" s="184"/>
-      <c r="D21" s="182"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="182"/>
-      <c r="G21" s="185"/>
-      <c r="H21" s="181"/>
-      <c r="I21" s="182"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="182"/>
-      <c r="L21" s="180"/>
-      <c r="M21" s="181"/>
-      <c r="N21" s="182"/>
-      <c r="O21" s="180"/>
-      <c r="P21" s="181"/>
-      <c r="Q21" s="182"/>
+      <c r="A21" s="190"/>
+      <c r="B21" s="183"/>
+      <c r="C21" s="191"/>
+      <c r="D21" s="183"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="183"/>
+      <c r="G21" s="192"/>
+      <c r="H21" s="182"/>
+      <c r="I21" s="183"/>
+      <c r="J21" s="192"/>
+      <c r="K21" s="183"/>
+      <c r="L21" s="193"/>
+      <c r="M21" s="182"/>
+      <c r="N21" s="183"/>
+      <c r="O21" s="193"/>
+      <c r="P21" s="182"/>
+      <c r="Q21" s="183"/>
       <c r="R21" s="46"/>
       <c r="S21" s="46"/>
       <c r="T21" s="47"/>
@@ -10071,23 +10145,23 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="183"/>
-      <c r="B22" s="182"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="182"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="182"/>
-      <c r="G22" s="185"/>
-      <c r="H22" s="181"/>
-      <c r="I22" s="182"/>
-      <c r="J22" s="185"/>
-      <c r="K22" s="182"/>
-      <c r="L22" s="180"/>
-      <c r="M22" s="181"/>
-      <c r="N22" s="182"/>
-      <c r="O22" s="180"/>
-      <c r="P22" s="181"/>
-      <c r="Q22" s="182"/>
+      <c r="A22" s="190"/>
+      <c r="B22" s="183"/>
+      <c r="C22" s="191"/>
+      <c r="D22" s="183"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="192"/>
+      <c r="H22" s="182"/>
+      <c r="I22" s="183"/>
+      <c r="J22" s="192"/>
+      <c r="K22" s="183"/>
+      <c r="L22" s="193"/>
+      <c r="M22" s="182"/>
+      <c r="N22" s="183"/>
+      <c r="O22" s="193"/>
+      <c r="P22" s="182"/>
+      <c r="Q22" s="183"/>
       <c r="R22" s="46"/>
       <c r="S22" s="46"/>
       <c r="T22" s="47"/>
@@ -10099,23 +10173,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="183"/>
-      <c r="B23" s="182"/>
-      <c r="C23" s="184"/>
-      <c r="D23" s="182"/>
-      <c r="E23" s="184"/>
-      <c r="F23" s="182"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="181"/>
-      <c r="I23" s="182"/>
-      <c r="J23" s="185"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="180"/>
-      <c r="M23" s="181"/>
-      <c r="N23" s="182"/>
-      <c r="O23" s="180"/>
-      <c r="P23" s="181"/>
-      <c r="Q23" s="182"/>
+      <c r="A23" s="190"/>
+      <c r="B23" s="183"/>
+      <c r="C23" s="191"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="191"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="192"/>
+      <c r="H23" s="182"/>
+      <c r="I23" s="183"/>
+      <c r="J23" s="192"/>
+      <c r="K23" s="183"/>
+      <c r="L23" s="193"/>
+      <c r="M23" s="182"/>
+      <c r="N23" s="183"/>
+      <c r="O23" s="193"/>
+      <c r="P23" s="182"/>
+      <c r="Q23" s="183"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -10127,23 +10201,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="183"/>
-      <c r="B24" s="182"/>
-      <c r="C24" s="184"/>
-      <c r="D24" s="182"/>
-      <c r="E24" s="184"/>
-      <c r="F24" s="182"/>
-      <c r="G24" s="185"/>
-      <c r="H24" s="181"/>
-      <c r="I24" s="182"/>
-      <c r="J24" s="185"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="180"/>
-      <c r="M24" s="181"/>
-      <c r="N24" s="182"/>
-      <c r="O24" s="180"/>
-      <c r="P24" s="181"/>
-      <c r="Q24" s="182"/>
+      <c r="A24" s="190"/>
+      <c r="B24" s="183"/>
+      <c r="C24" s="191"/>
+      <c r="D24" s="183"/>
+      <c r="E24" s="191"/>
+      <c r="F24" s="183"/>
+      <c r="G24" s="192"/>
+      <c r="H24" s="182"/>
+      <c r="I24" s="183"/>
+      <c r="J24" s="192"/>
+      <c r="K24" s="183"/>
+      <c r="L24" s="193"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="183"/>
+      <c r="O24" s="193"/>
+      <c r="P24" s="182"/>
+      <c r="Q24" s="183"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -10155,23 +10229,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="183"/>
-      <c r="B25" s="182"/>
-      <c r="C25" s="184"/>
-      <c r="D25" s="182"/>
-      <c r="E25" s="184"/>
-      <c r="F25" s="182"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="181"/>
-      <c r="I25" s="182"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="180"/>
-      <c r="M25" s="181"/>
-      <c r="N25" s="182"/>
-      <c r="O25" s="180"/>
-      <c r="P25" s="181"/>
-      <c r="Q25" s="182"/>
+      <c r="A25" s="190"/>
+      <c r="B25" s="183"/>
+      <c r="C25" s="191"/>
+      <c r="D25" s="183"/>
+      <c r="E25" s="191"/>
+      <c r="F25" s="183"/>
+      <c r="G25" s="192"/>
+      <c r="H25" s="182"/>
+      <c r="I25" s="183"/>
+      <c r="J25" s="192"/>
+      <c r="K25" s="183"/>
+      <c r="L25" s="193"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="183"/>
+      <c r="O25" s="193"/>
+      <c r="P25" s="182"/>
+      <c r="Q25" s="183"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -10183,23 +10257,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="183"/>
-      <c r="B26" s="182"/>
-      <c r="C26" s="184"/>
-      <c r="D26" s="182"/>
-      <c r="E26" s="184"/>
-      <c r="F26" s="182"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="181"/>
-      <c r="I26" s="182"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="180"/>
-      <c r="M26" s="181"/>
-      <c r="N26" s="182"/>
-      <c r="O26" s="180"/>
-      <c r="P26" s="181"/>
-      <c r="Q26" s="182"/>
+      <c r="A26" s="190"/>
+      <c r="B26" s="183"/>
+      <c r="C26" s="191"/>
+      <c r="D26" s="183"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="183"/>
+      <c r="G26" s="192"/>
+      <c r="H26" s="182"/>
+      <c r="I26" s="183"/>
+      <c r="J26" s="192"/>
+      <c r="K26" s="183"/>
+      <c r="L26" s="193"/>
+      <c r="M26" s="182"/>
+      <c r="N26" s="183"/>
+      <c r="O26" s="193"/>
+      <c r="P26" s="182"/>
+      <c r="Q26" s="183"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -10211,23 +10285,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="183"/>
-      <c r="B27" s="182"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="182"/>
-      <c r="E27" s="184"/>
-      <c r="F27" s="182"/>
-      <c r="G27" s="185"/>
-      <c r="H27" s="181"/>
-      <c r="I27" s="182"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="180"/>
-      <c r="M27" s="181"/>
-      <c r="N27" s="182"/>
-      <c r="O27" s="180"/>
-      <c r="P27" s="181"/>
-      <c r="Q27" s="182"/>
+      <c r="A27" s="190"/>
+      <c r="B27" s="183"/>
+      <c r="C27" s="191"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="191"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="192"/>
+      <c r="H27" s="182"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="183"/>
+      <c r="L27" s="193"/>
+      <c r="M27" s="182"/>
+      <c r="N27" s="183"/>
+      <c r="O27" s="193"/>
+      <c r="P27" s="182"/>
+      <c r="Q27" s="183"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -10239,23 +10313,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="183"/>
-      <c r="B28" s="182"/>
-      <c r="C28" s="184"/>
-      <c r="D28" s="182"/>
-      <c r="E28" s="184"/>
-      <c r="F28" s="182"/>
-      <c r="G28" s="185"/>
-      <c r="H28" s="181"/>
-      <c r="I28" s="182"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="180"/>
-      <c r="M28" s="181"/>
-      <c r="N28" s="182"/>
-      <c r="O28" s="180"/>
-      <c r="P28" s="181"/>
-      <c r="Q28" s="182"/>
+      <c r="A28" s="190"/>
+      <c r="B28" s="183"/>
+      <c r="C28" s="191"/>
+      <c r="D28" s="183"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="183"/>
+      <c r="G28" s="192"/>
+      <c r="H28" s="182"/>
+      <c r="I28" s="183"/>
+      <c r="J28" s="192"/>
+      <c r="K28" s="183"/>
+      <c r="L28" s="193"/>
+      <c r="M28" s="182"/>
+      <c r="N28" s="183"/>
+      <c r="O28" s="193"/>
+      <c r="P28" s="182"/>
+      <c r="Q28" s="183"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -10267,23 +10341,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="183"/>
-      <c r="B29" s="182"/>
-      <c r="C29" s="184"/>
-      <c r="D29" s="182"/>
-      <c r="E29" s="184"/>
-      <c r="F29" s="182"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="181"/>
-      <c r="I29" s="182"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="182"/>
-      <c r="L29" s="180"/>
-      <c r="M29" s="181"/>
-      <c r="N29" s="182"/>
-      <c r="O29" s="180"/>
-      <c r="P29" s="181"/>
-      <c r="Q29" s="182"/>
+      <c r="A29" s="190"/>
+      <c r="B29" s="183"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="192"/>
+      <c r="H29" s="182"/>
+      <c r="I29" s="183"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="183"/>
+      <c r="L29" s="193"/>
+      <c r="M29" s="182"/>
+      <c r="N29" s="183"/>
+      <c r="O29" s="193"/>
+      <c r="P29" s="182"/>
+      <c r="Q29" s="183"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -10295,23 +10369,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="183"/>
-      <c r="B30" s="182"/>
-      <c r="C30" s="184"/>
-      <c r="D30" s="182"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="182"/>
-      <c r="G30" s="185"/>
-      <c r="H30" s="181"/>
-      <c r="I30" s="182"/>
-      <c r="J30" s="185"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="180"/>
-      <c r="M30" s="181"/>
-      <c r="N30" s="182"/>
-      <c r="O30" s="180"/>
-      <c r="P30" s="181"/>
-      <c r="Q30" s="182"/>
+      <c r="A30" s="190"/>
+      <c r="B30" s="183"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="183"/>
+      <c r="E30" s="191"/>
+      <c r="F30" s="183"/>
+      <c r="G30" s="192"/>
+      <c r="H30" s="182"/>
+      <c r="I30" s="183"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="183"/>
+      <c r="L30" s="193"/>
+      <c r="M30" s="182"/>
+      <c r="N30" s="183"/>
+      <c r="O30" s="193"/>
+      <c r="P30" s="182"/>
+      <c r="Q30" s="183"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -10323,23 +10397,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="177"/>
-      <c r="B31" s="176"/>
-      <c r="C31" s="178"/>
-      <c r="D31" s="176"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="179"/>
-      <c r="H31" s="175"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="176"/>
-      <c r="L31" s="174"/>
-      <c r="M31" s="175"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="174"/>
-      <c r="P31" s="175"/>
-      <c r="Q31" s="176"/>
+      <c r="A31" s="198"/>
+      <c r="B31" s="197"/>
+      <c r="C31" s="199"/>
+      <c r="D31" s="197"/>
+      <c r="E31" s="199"/>
+      <c r="F31" s="197"/>
+      <c r="G31" s="200"/>
+      <c r="H31" s="196"/>
+      <c r="I31" s="197"/>
+      <c r="J31" s="200"/>
+      <c r="K31" s="197"/>
+      <c r="L31" s="195"/>
+      <c r="M31" s="196"/>
+      <c r="N31" s="197"/>
+      <c r="O31" s="195"/>
+      <c r="P31" s="196"/>
+      <c r="Q31" s="197"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11337,121 +11411,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -11473,6 +11432,121 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11495,64 +11569,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="210" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="220"/>
-      <c r="C1" s="221" t="s">
+      <c r="B1" s="210"/>
+      <c r="C1" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="222"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="224"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="226"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="216"/>
       <c r="N1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="224"/>
-      <c r="P1" s="226"/>
+      <c r="O1" s="214"/>
+      <c r="P1" s="216"/>
       <c r="Q1" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="224" t="s">
+      <c r="R1" s="214" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="226"/>
+      <c r="S1" s="216"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="220"/>
-      <c r="B2" s="220"/>
-      <c r="C2" s="221" t="s">
+      <c r="A2" s="210"/>
+      <c r="B2" s="210"/>
+      <c r="C2" s="211" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="222"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="225"/>
-      <c r="M2" s="226"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
+      <c r="M2" s="216"/>
       <c r="N2" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="O2" s="227"/>
-      <c r="P2" s="228"/>
+      <c r="O2" s="217"/>
+      <c r="P2" s="218"/>
       <c r="Q2" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="229">
+      <c r="R2" s="219">
         <v>44771</v>
       </c>
-      <c r="S2" s="230"/>
+      <c r="S2" s="220"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11582,1044 +11656,1232 @@
       <c r="B4" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="211" t="s">
+      <c r="C4" s="201" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="211" t="s">
+      <c r="D4" s="202"/>
+      <c r="E4" s="202"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="203"/>
+      <c r="H4" s="201" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="211" t="s">
+      <c r="I4" s="202"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="202"/>
+      <c r="L4" s="202"/>
+      <c r="M4" s="203"/>
+      <c r="N4" s="201" t="s">
         <v>86</v>
       </c>
-      <c r="O4" s="212"/>
-      <c r="P4" s="213"/>
+      <c r="O4" s="202"/>
+      <c r="P4" s="203"/>
       <c r="Q4" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="R4" s="211" t="s">
+      <c r="R4" s="201" t="s">
         <v>88</v>
       </c>
-      <c r="S4" s="213"/>
+      <c r="S4" s="203"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="214"/>
-      <c r="E5" s="214"/>
-      <c r="F5" s="214"/>
-      <c r="G5" s="214"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="214"/>
-      <c r="K5" s="214"/>
-      <c r="L5" s="214"/>
-      <c r="M5" s="214"/>
-      <c r="N5" s="215"/>
-      <c r="O5" s="216"/>
-      <c r="P5" s="217"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="204"/>
+      <c r="G5" s="204"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="204"/>
+      <c r="J5" s="204"/>
+      <c r="K5" s="204"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="204"/>
+      <c r="N5" s="205"/>
+      <c r="O5" s="206"/>
+      <c r="P5" s="207"/>
       <c r="Q5" s="59"/>
-      <c r="R5" s="218"/>
-      <c r="S5" s="219"/>
+      <c r="R5" s="208"/>
+      <c r="S5" s="209"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="200"/>
-      <c r="D6" s="200"/>
-      <c r="E6" s="200"/>
-      <c r="F6" s="200"/>
-      <c r="G6" s="200"/>
-      <c r="H6" s="200"/>
-      <c r="I6" s="200"/>
-      <c r="J6" s="200"/>
-      <c r="K6" s="200"/>
-      <c r="L6" s="200"/>
-      <c r="M6" s="200"/>
-      <c r="N6" s="208"/>
-      <c r="O6" s="209"/>
-      <c r="P6" s="210"/>
+      <c r="C6" s="221"/>
+      <c r="D6" s="221"/>
+      <c r="E6" s="221"/>
+      <c r="F6" s="221"/>
+      <c r="G6" s="221"/>
+      <c r="H6" s="221"/>
+      <c r="I6" s="221"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="221"/>
+      <c r="N6" s="226"/>
+      <c r="O6" s="227"/>
+      <c r="P6" s="228"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="207"/>
-      <c r="S6" s="207"/>
+      <c r="R6" s="225"/>
+      <c r="S6" s="225"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="200"/>
-      <c r="D7" s="200"/>
-      <c r="E7" s="200"/>
-      <c r="F7" s="200"/>
-      <c r="G7" s="200"/>
-      <c r="H7" s="200"/>
-      <c r="I7" s="200"/>
-      <c r="J7" s="200"/>
-      <c r="K7" s="200"/>
-      <c r="L7" s="200"/>
-      <c r="M7" s="200"/>
-      <c r="N7" s="204"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="206"/>
+      <c r="C7" s="221"/>
+      <c r="D7" s="221"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
+      <c r="H7" s="221"/>
+      <c r="I7" s="221"/>
+      <c r="J7" s="221"/>
+      <c r="K7" s="221"/>
+      <c r="L7" s="221"/>
+      <c r="M7" s="221"/>
+      <c r="N7" s="222"/>
+      <c r="O7" s="223"/>
+      <c r="P7" s="224"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="207"/>
-      <c r="S7" s="207"/>
+      <c r="R7" s="225"/>
+      <c r="S7" s="225"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="200"/>
-      <c r="D8" s="200"/>
-      <c r="E8" s="200"/>
-      <c r="F8" s="200"/>
-      <c r="G8" s="200"/>
-      <c r="H8" s="200"/>
-      <c r="I8" s="200"/>
-      <c r="J8" s="200"/>
-      <c r="K8" s="200"/>
-      <c r="L8" s="200"/>
-      <c r="M8" s="200"/>
-      <c r="N8" s="204"/>
-      <c r="O8" s="205"/>
-      <c r="P8" s="206"/>
+      <c r="C8" s="221"/>
+      <c r="D8" s="221"/>
+      <c r="E8" s="221"/>
+      <c r="F8" s="221"/>
+      <c r="G8" s="221"/>
+      <c r="H8" s="221"/>
+      <c r="I8" s="221"/>
+      <c r="J8" s="221"/>
+      <c r="K8" s="221"/>
+      <c r="L8" s="221"/>
+      <c r="M8" s="221"/>
+      <c r="N8" s="222"/>
+      <c r="O8" s="223"/>
+      <c r="P8" s="224"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="207"/>
-      <c r="S8" s="207"/>
+      <c r="R8" s="225"/>
+      <c r="S8" s="225"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="200"/>
-      <c r="E9" s="200"/>
-      <c r="F9" s="200"/>
-      <c r="G9" s="200"/>
-      <c r="H9" s="200"/>
-      <c r="I9" s="200"/>
-      <c r="J9" s="200"/>
-      <c r="K9" s="200"/>
-      <c r="L9" s="200"/>
-      <c r="M9" s="200"/>
-      <c r="N9" s="204"/>
-      <c r="O9" s="205"/>
-      <c r="P9" s="206"/>
+      <c r="C9" s="221"/>
+      <c r="D9" s="221"/>
+      <c r="E9" s="221"/>
+      <c r="F9" s="221"/>
+      <c r="G9" s="221"/>
+      <c r="H9" s="221"/>
+      <c r="I9" s="221"/>
+      <c r="J9" s="221"/>
+      <c r="K9" s="221"/>
+      <c r="L9" s="221"/>
+      <c r="M9" s="221"/>
+      <c r="N9" s="222"/>
+      <c r="O9" s="223"/>
+      <c r="P9" s="224"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="207"/>
-      <c r="S9" s="207"/>
+      <c r="R9" s="225"/>
+      <c r="S9" s="225"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="200"/>
-      <c r="D10" s="200"/>
-      <c r="E10" s="200"/>
-      <c r="F10" s="200"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="201"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
-      <c r="L10" s="202"/>
-      <c r="M10" s="203"/>
-      <c r="N10" s="204"/>
-      <c r="O10" s="205"/>
-      <c r="P10" s="206"/>
+      <c r="C10" s="221"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="221"/>
+      <c r="F10" s="221"/>
+      <c r="G10" s="221"/>
+      <c r="H10" s="229"/>
+      <c r="I10" s="230"/>
+      <c r="J10" s="230"/>
+      <c r="K10" s="230"/>
+      <c r="L10" s="230"/>
+      <c r="M10" s="231"/>
+      <c r="N10" s="222"/>
+      <c r="O10" s="223"/>
+      <c r="P10" s="224"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="207"/>
-      <c r="S10" s="207"/>
+      <c r="R10" s="225"/>
+      <c r="S10" s="225"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="200"/>
-      <c r="D11" s="200"/>
-      <c r="E11" s="200"/>
-      <c r="F11" s="200"/>
-      <c r="G11" s="200"/>
-      <c r="H11" s="201"/>
-      <c r="I11" s="202"/>
-      <c r="J11" s="202"/>
-      <c r="K11" s="202"/>
-      <c r="L11" s="202"/>
-      <c r="M11" s="203"/>
-      <c r="N11" s="204"/>
-      <c r="O11" s="205"/>
-      <c r="P11" s="206"/>
+      <c r="C11" s="221"/>
+      <c r="D11" s="221"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="221"/>
+      <c r="G11" s="221"/>
+      <c r="H11" s="229"/>
+      <c r="I11" s="230"/>
+      <c r="J11" s="230"/>
+      <c r="K11" s="230"/>
+      <c r="L11" s="230"/>
+      <c r="M11" s="231"/>
+      <c r="N11" s="222"/>
+      <c r="O11" s="223"/>
+      <c r="P11" s="224"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="207"/>
-      <c r="S11" s="207"/>
+      <c r="R11" s="225"/>
+      <c r="S11" s="225"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="200"/>
-      <c r="D12" s="200"/>
-      <c r="E12" s="200"/>
-      <c r="F12" s="200"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="201"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="202"/>
-      <c r="K12" s="202"/>
-      <c r="L12" s="202"/>
-      <c r="M12" s="203"/>
-      <c r="N12" s="204"/>
-      <c r="O12" s="205"/>
-      <c r="P12" s="206"/>
+      <c r="C12" s="221"/>
+      <c r="D12" s="221"/>
+      <c r="E12" s="221"/>
+      <c r="F12" s="221"/>
+      <c r="G12" s="221"/>
+      <c r="H12" s="229"/>
+      <c r="I12" s="230"/>
+      <c r="J12" s="230"/>
+      <c r="K12" s="230"/>
+      <c r="L12" s="230"/>
+      <c r="M12" s="231"/>
+      <c r="N12" s="222"/>
+      <c r="O12" s="223"/>
+      <c r="P12" s="224"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="207"/>
-      <c r="S12" s="207"/>
+      <c r="R12" s="225"/>
+      <c r="S12" s="225"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="201"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="202"/>
-      <c r="M13" s="203"/>
-      <c r="N13" s="204"/>
-      <c r="O13" s="205"/>
-      <c r="P13" s="206"/>
+      <c r="C13" s="221"/>
+      <c r="D13" s="221"/>
+      <c r="E13" s="221"/>
+      <c r="F13" s="221"/>
+      <c r="G13" s="221"/>
+      <c r="H13" s="229"/>
+      <c r="I13" s="230"/>
+      <c r="J13" s="230"/>
+      <c r="K13" s="230"/>
+      <c r="L13" s="230"/>
+      <c r="M13" s="231"/>
+      <c r="N13" s="222"/>
+      <c r="O13" s="223"/>
+      <c r="P13" s="224"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="207"/>
-      <c r="S13" s="207"/>
+      <c r="R13" s="225"/>
+      <c r="S13" s="225"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
-      <c r="F14" s="200"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="201"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-      <c r="M14" s="203"/>
-      <c r="N14" s="204"/>
-      <c r="O14" s="205"/>
-      <c r="P14" s="206"/>
+      <c r="C14" s="221"/>
+      <c r="D14" s="221"/>
+      <c r="E14" s="221"/>
+      <c r="F14" s="221"/>
+      <c r="G14" s="221"/>
+      <c r="H14" s="229"/>
+      <c r="I14" s="230"/>
+      <c r="J14" s="230"/>
+      <c r="K14" s="230"/>
+      <c r="L14" s="230"/>
+      <c r="M14" s="231"/>
+      <c r="N14" s="222"/>
+      <c r="O14" s="223"/>
+      <c r="P14" s="224"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="207"/>
-      <c r="S14" s="207"/>
+      <c r="R14" s="225"/>
+      <c r="S14" s="225"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="201"/>
-      <c r="I15" s="202"/>
-      <c r="J15" s="202"/>
-      <c r="K15" s="202"/>
-      <c r="L15" s="202"/>
-      <c r="M15" s="203"/>
-      <c r="N15" s="204"/>
-      <c r="O15" s="205"/>
-      <c r="P15" s="206"/>
+      <c r="C15" s="221"/>
+      <c r="D15" s="221"/>
+      <c r="E15" s="221"/>
+      <c r="F15" s="221"/>
+      <c r="G15" s="221"/>
+      <c r="H15" s="229"/>
+      <c r="I15" s="230"/>
+      <c r="J15" s="230"/>
+      <c r="K15" s="230"/>
+      <c r="L15" s="230"/>
+      <c r="M15" s="231"/>
+      <c r="N15" s="222"/>
+      <c r="O15" s="223"/>
+      <c r="P15" s="224"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="207"/>
-      <c r="S15" s="207"/>
+      <c r="R15" s="225"/>
+      <c r="S15" s="225"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="200"/>
-      <c r="F16" s="200"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="201"/>
-      <c r="I16" s="202"/>
-      <c r="J16" s="202"/>
-      <c r="K16" s="202"/>
-      <c r="L16" s="202"/>
-      <c r="M16" s="203"/>
-      <c r="N16" s="204"/>
-      <c r="O16" s="205"/>
-      <c r="P16" s="206"/>
+      <c r="C16" s="221"/>
+      <c r="D16" s="221"/>
+      <c r="E16" s="221"/>
+      <c r="F16" s="221"/>
+      <c r="G16" s="221"/>
+      <c r="H16" s="229"/>
+      <c r="I16" s="230"/>
+      <c r="J16" s="230"/>
+      <c r="K16" s="230"/>
+      <c r="L16" s="230"/>
+      <c r="M16" s="231"/>
+      <c r="N16" s="222"/>
+      <c r="O16" s="223"/>
+      <c r="P16" s="224"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="207"/>
-      <c r="S16" s="207"/>
+      <c r="R16" s="225"/>
+      <c r="S16" s="225"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="200"/>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="203"/>
-      <c r="N17" s="204"/>
-      <c r="O17" s="205"/>
-      <c r="P17" s="206"/>
+      <c r="C17" s="221"/>
+      <c r="D17" s="221"/>
+      <c r="E17" s="221"/>
+      <c r="F17" s="221"/>
+      <c r="G17" s="221"/>
+      <c r="H17" s="229"/>
+      <c r="I17" s="230"/>
+      <c r="J17" s="230"/>
+      <c r="K17" s="230"/>
+      <c r="L17" s="230"/>
+      <c r="M17" s="231"/>
+      <c r="N17" s="222"/>
+      <c r="O17" s="223"/>
+      <c r="P17" s="224"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="207"/>
-      <c r="S17" s="207"/>
+      <c r="R17" s="225"/>
+      <c r="S17" s="225"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="200"/>
-      <c r="D18" s="200"/>
-      <c r="E18" s="200"/>
-      <c r="F18" s="200"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="201"/>
-      <c r="I18" s="202"/>
-      <c r="J18" s="202"/>
-      <c r="K18" s="202"/>
-      <c r="L18" s="202"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="204"/>
-      <c r="O18" s="205"/>
-      <c r="P18" s="206"/>
+      <c r="C18" s="221"/>
+      <c r="D18" s="221"/>
+      <c r="E18" s="221"/>
+      <c r="F18" s="221"/>
+      <c r="G18" s="221"/>
+      <c r="H18" s="229"/>
+      <c r="I18" s="230"/>
+      <c r="J18" s="230"/>
+      <c r="K18" s="230"/>
+      <c r="L18" s="230"/>
+      <c r="M18" s="231"/>
+      <c r="N18" s="222"/>
+      <c r="O18" s="223"/>
+      <c r="P18" s="224"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="207"/>
-      <c r="S18" s="207"/>
+      <c r="R18" s="225"/>
+      <c r="S18" s="225"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="200"/>
-      <c r="D19" s="200"/>
-      <c r="E19" s="200"/>
-      <c r="F19" s="200"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="201"/>
-      <c r="I19" s="202"/>
-      <c r="J19" s="202"/>
-      <c r="K19" s="202"/>
-      <c r="L19" s="202"/>
-      <c r="M19" s="203"/>
-      <c r="N19" s="204"/>
-      <c r="O19" s="205"/>
-      <c r="P19" s="206"/>
+      <c r="C19" s="221"/>
+      <c r="D19" s="221"/>
+      <c r="E19" s="221"/>
+      <c r="F19" s="221"/>
+      <c r="G19" s="221"/>
+      <c r="H19" s="229"/>
+      <c r="I19" s="230"/>
+      <c r="J19" s="230"/>
+      <c r="K19" s="230"/>
+      <c r="L19" s="230"/>
+      <c r="M19" s="231"/>
+      <c r="N19" s="222"/>
+      <c r="O19" s="223"/>
+      <c r="P19" s="224"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="207"/>
-      <c r="S19" s="207"/>
+      <c r="R19" s="225"/>
+      <c r="S19" s="225"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="200"/>
-      <c r="D20" s="200"/>
-      <c r="E20" s="200"/>
-      <c r="F20" s="200"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="201"/>
-      <c r="I20" s="202"/>
-      <c r="J20" s="202"/>
-      <c r="K20" s="202"/>
-      <c r="L20" s="202"/>
-      <c r="M20" s="203"/>
-      <c r="N20" s="204"/>
-      <c r="O20" s="205"/>
-      <c r="P20" s="206"/>
+      <c r="C20" s="221"/>
+      <c r="D20" s="221"/>
+      <c r="E20" s="221"/>
+      <c r="F20" s="221"/>
+      <c r="G20" s="221"/>
+      <c r="H20" s="229"/>
+      <c r="I20" s="230"/>
+      <c r="J20" s="230"/>
+      <c r="K20" s="230"/>
+      <c r="L20" s="230"/>
+      <c r="M20" s="231"/>
+      <c r="N20" s="222"/>
+      <c r="O20" s="223"/>
+      <c r="P20" s="224"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="207"/>
-      <c r="S20" s="207"/>
+      <c r="R20" s="225"/>
+      <c r="S20" s="225"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="200"/>
-      <c r="D21" s="200"/>
-      <c r="E21" s="200"/>
-      <c r="F21" s="200"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="201"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="202"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="203"/>
-      <c r="N21" s="204"/>
-      <c r="O21" s="205"/>
-      <c r="P21" s="206"/>
+      <c r="C21" s="221"/>
+      <c r="D21" s="221"/>
+      <c r="E21" s="221"/>
+      <c r="F21" s="221"/>
+      <c r="G21" s="221"/>
+      <c r="H21" s="229"/>
+      <c r="I21" s="230"/>
+      <c r="J21" s="230"/>
+      <c r="K21" s="230"/>
+      <c r="L21" s="230"/>
+      <c r="M21" s="231"/>
+      <c r="N21" s="222"/>
+      <c r="O21" s="223"/>
+      <c r="P21" s="224"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="207"/>
-      <c r="S21" s="207"/>
+      <c r="R21" s="225"/>
+      <c r="S21" s="225"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="200"/>
-      <c r="D22" s="200"/>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="203"/>
-      <c r="N22" s="204"/>
-      <c r="O22" s="205"/>
-      <c r="P22" s="206"/>
+      <c r="C22" s="221"/>
+      <c r="D22" s="221"/>
+      <c r="E22" s="221"/>
+      <c r="F22" s="221"/>
+      <c r="G22" s="221"/>
+      <c r="H22" s="229"/>
+      <c r="I22" s="230"/>
+      <c r="J22" s="230"/>
+      <c r="K22" s="230"/>
+      <c r="L22" s="230"/>
+      <c r="M22" s="231"/>
+      <c r="N22" s="222"/>
+      <c r="O22" s="223"/>
+      <c r="P22" s="224"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="207"/>
-      <c r="S22" s="207"/>
+      <c r="R22" s="225"/>
+      <c r="S22" s="225"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="200"/>
-      <c r="D23" s="200"/>
-      <c r="E23" s="200"/>
-      <c r="F23" s="200"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="202"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="203"/>
-      <c r="N23" s="204"/>
-      <c r="O23" s="205"/>
-      <c r="P23" s="206"/>
+      <c r="C23" s="221"/>
+      <c r="D23" s="221"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="221"/>
+      <c r="G23" s="221"/>
+      <c r="H23" s="229"/>
+      <c r="I23" s="230"/>
+      <c r="J23" s="230"/>
+      <c r="K23" s="230"/>
+      <c r="L23" s="230"/>
+      <c r="M23" s="231"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="223"/>
+      <c r="P23" s="224"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="207"/>
-      <c r="S23" s="207"/>
+      <c r="R23" s="225"/>
+      <c r="S23" s="225"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="200"/>
-      <c r="D24" s="200"/>
-      <c r="E24" s="200"/>
-      <c r="F24" s="200"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="202"/>
-      <c r="J24" s="202"/>
-      <c r="K24" s="202"/>
-      <c r="L24" s="202"/>
-      <c r="M24" s="203"/>
-      <c r="N24" s="204"/>
-      <c r="O24" s="205"/>
-      <c r="P24" s="206"/>
+      <c r="C24" s="221"/>
+      <c r="D24" s="221"/>
+      <c r="E24" s="221"/>
+      <c r="F24" s="221"/>
+      <c r="G24" s="221"/>
+      <c r="H24" s="229"/>
+      <c r="I24" s="230"/>
+      <c r="J24" s="230"/>
+      <c r="K24" s="230"/>
+      <c r="L24" s="230"/>
+      <c r="M24" s="231"/>
+      <c r="N24" s="222"/>
+      <c r="O24" s="223"/>
+      <c r="P24" s="224"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="207"/>
-      <c r="S24" s="207"/>
+      <c r="R24" s="225"/>
+      <c r="S24" s="225"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="200"/>
-      <c r="D25" s="200"/>
-      <c r="E25" s="200"/>
-      <c r="F25" s="200"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="202"/>
-      <c r="J25" s="202"/>
-      <c r="K25" s="202"/>
-      <c r="L25" s="202"/>
-      <c r="M25" s="203"/>
-      <c r="N25" s="204"/>
-      <c r="O25" s="205"/>
-      <c r="P25" s="206"/>
+      <c r="C25" s="221"/>
+      <c r="D25" s="221"/>
+      <c r="E25" s="221"/>
+      <c r="F25" s="221"/>
+      <c r="G25" s="221"/>
+      <c r="H25" s="229"/>
+      <c r="I25" s="230"/>
+      <c r="J25" s="230"/>
+      <c r="K25" s="230"/>
+      <c r="L25" s="230"/>
+      <c r="M25" s="231"/>
+      <c r="N25" s="222"/>
+      <c r="O25" s="223"/>
+      <c r="P25" s="224"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="207"/>
-      <c r="S25" s="207"/>
+      <c r="R25" s="225"/>
+      <c r="S25" s="225"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="200"/>
-      <c r="D26" s="200"/>
-      <c r="E26" s="200"/>
-      <c r="F26" s="200"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="202"/>
-      <c r="J26" s="202"/>
-      <c r="K26" s="202"/>
-      <c r="L26" s="202"/>
-      <c r="M26" s="203"/>
-      <c r="N26" s="204"/>
-      <c r="O26" s="205"/>
-      <c r="P26" s="206"/>
+      <c r="C26" s="221"/>
+      <c r="D26" s="221"/>
+      <c r="E26" s="221"/>
+      <c r="F26" s="221"/>
+      <c r="G26" s="221"/>
+      <c r="H26" s="229"/>
+      <c r="I26" s="230"/>
+      <c r="J26" s="230"/>
+      <c r="K26" s="230"/>
+      <c r="L26" s="230"/>
+      <c r="M26" s="231"/>
+      <c r="N26" s="222"/>
+      <c r="O26" s="223"/>
+      <c r="P26" s="224"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="207"/>
-      <c r="S26" s="207"/>
+      <c r="R26" s="225"/>
+      <c r="S26" s="225"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="200"/>
-      <c r="D27" s="200"/>
-      <c r="E27" s="200"/>
-      <c r="F27" s="200"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="202"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="203"/>
-      <c r="N27" s="204"/>
-      <c r="O27" s="205"/>
-      <c r="P27" s="206"/>
+      <c r="C27" s="221"/>
+      <c r="D27" s="221"/>
+      <c r="E27" s="221"/>
+      <c r="F27" s="221"/>
+      <c r="G27" s="221"/>
+      <c r="H27" s="229"/>
+      <c r="I27" s="230"/>
+      <c r="J27" s="230"/>
+      <c r="K27" s="230"/>
+      <c r="L27" s="230"/>
+      <c r="M27" s="231"/>
+      <c r="N27" s="222"/>
+      <c r="O27" s="223"/>
+      <c r="P27" s="224"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="207"/>
-      <c r="S27" s="207"/>
+      <c r="R27" s="225"/>
+      <c r="S27" s="225"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="200"/>
-      <c r="D28" s="200"/>
-      <c r="E28" s="200"/>
-      <c r="F28" s="200"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="201"/>
-      <c r="I28" s="202"/>
-      <c r="J28" s="202"/>
-      <c r="K28" s="202"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="203"/>
-      <c r="N28" s="204"/>
-      <c r="O28" s="205"/>
-      <c r="P28" s="206"/>
+      <c r="C28" s="221"/>
+      <c r="D28" s="221"/>
+      <c r="E28" s="221"/>
+      <c r="F28" s="221"/>
+      <c r="G28" s="221"/>
+      <c r="H28" s="229"/>
+      <c r="I28" s="230"/>
+      <c r="J28" s="230"/>
+      <c r="K28" s="230"/>
+      <c r="L28" s="230"/>
+      <c r="M28" s="231"/>
+      <c r="N28" s="222"/>
+      <c r="O28" s="223"/>
+      <c r="P28" s="224"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="207"/>
-      <c r="S28" s="207"/>
+      <c r="R28" s="225"/>
+      <c r="S28" s="225"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="200"/>
-      <c r="D29" s="200"/>
-      <c r="E29" s="200"/>
-      <c r="F29" s="200"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="202"/>
-      <c r="K29" s="202"/>
-      <c r="L29" s="202"/>
-      <c r="M29" s="203"/>
-      <c r="N29" s="204"/>
-      <c r="O29" s="205"/>
-      <c r="P29" s="206"/>
+      <c r="C29" s="221"/>
+      <c r="D29" s="221"/>
+      <c r="E29" s="221"/>
+      <c r="F29" s="221"/>
+      <c r="G29" s="221"/>
+      <c r="H29" s="229"/>
+      <c r="I29" s="230"/>
+      <c r="J29" s="230"/>
+      <c r="K29" s="230"/>
+      <c r="L29" s="230"/>
+      <c r="M29" s="231"/>
+      <c r="N29" s="222"/>
+      <c r="O29" s="223"/>
+      <c r="P29" s="224"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="207"/>
-      <c r="S29" s="207"/>
+      <c r="R29" s="225"/>
+      <c r="S29" s="225"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="200"/>
-      <c r="D30" s="200"/>
-      <c r="E30" s="200"/>
-      <c r="F30" s="200"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="201"/>
-      <c r="I30" s="202"/>
-      <c r="J30" s="202"/>
-      <c r="K30" s="202"/>
-      <c r="L30" s="202"/>
-      <c r="M30" s="203"/>
-      <c r="N30" s="204"/>
-      <c r="O30" s="205"/>
-      <c r="P30" s="206"/>
+      <c r="C30" s="221"/>
+      <c r="D30" s="221"/>
+      <c r="E30" s="221"/>
+      <c r="F30" s="221"/>
+      <c r="G30" s="221"/>
+      <c r="H30" s="229"/>
+      <c r="I30" s="230"/>
+      <c r="J30" s="230"/>
+      <c r="K30" s="230"/>
+      <c r="L30" s="230"/>
+      <c r="M30" s="231"/>
+      <c r="N30" s="222"/>
+      <c r="O30" s="223"/>
+      <c r="P30" s="224"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="207"/>
-      <c r="S30" s="207"/>
+      <c r="R30" s="225"/>
+      <c r="S30" s="225"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="200"/>
-      <c r="D31" s="200"/>
-      <c r="E31" s="200"/>
-      <c r="F31" s="200"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="202"/>
-      <c r="M31" s="203"/>
-      <c r="N31" s="204"/>
-      <c r="O31" s="205"/>
-      <c r="P31" s="206"/>
+      <c r="C31" s="221"/>
+      <c r="D31" s="221"/>
+      <c r="E31" s="221"/>
+      <c r="F31" s="221"/>
+      <c r="G31" s="221"/>
+      <c r="H31" s="229"/>
+      <c r="I31" s="230"/>
+      <c r="J31" s="230"/>
+      <c r="K31" s="230"/>
+      <c r="L31" s="230"/>
+      <c r="M31" s="231"/>
+      <c r="N31" s="222"/>
+      <c r="O31" s="223"/>
+      <c r="P31" s="224"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="207"/>
-      <c r="S31" s="207"/>
+      <c r="R31" s="225"/>
+      <c r="S31" s="225"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="200"/>
-      <c r="D32" s="200"/>
-      <c r="E32" s="200"/>
-      <c r="F32" s="200"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="201"/>
-      <c r="I32" s="202"/>
-      <c r="J32" s="202"/>
-      <c r="K32" s="202"/>
-      <c r="L32" s="202"/>
-      <c r="M32" s="203"/>
-      <c r="N32" s="204"/>
-      <c r="O32" s="205"/>
-      <c r="P32" s="206"/>
+      <c r="C32" s="221"/>
+      <c r="D32" s="221"/>
+      <c r="E32" s="221"/>
+      <c r="F32" s="221"/>
+      <c r="G32" s="221"/>
+      <c r="H32" s="229"/>
+      <c r="I32" s="230"/>
+      <c r="J32" s="230"/>
+      <c r="K32" s="230"/>
+      <c r="L32" s="230"/>
+      <c r="M32" s="231"/>
+      <c r="N32" s="222"/>
+      <c r="O32" s="223"/>
+      <c r="P32" s="224"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="207"/>
-      <c r="S32" s="207"/>
+      <c r="R32" s="225"/>
+      <c r="S32" s="225"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="200"/>
-      <c r="D33" s="200"/>
-      <c r="E33" s="200"/>
-      <c r="F33" s="200"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="202"/>
-      <c r="J33" s="202"/>
-      <c r="K33" s="202"/>
-      <c r="L33" s="202"/>
-      <c r="M33" s="203"/>
-      <c r="N33" s="204"/>
-      <c r="O33" s="205"/>
-      <c r="P33" s="206"/>
+      <c r="C33" s="221"/>
+      <c r="D33" s="221"/>
+      <c r="E33" s="221"/>
+      <c r="F33" s="221"/>
+      <c r="G33" s="221"/>
+      <c r="H33" s="229"/>
+      <c r="I33" s="230"/>
+      <c r="J33" s="230"/>
+      <c r="K33" s="230"/>
+      <c r="L33" s="230"/>
+      <c r="M33" s="231"/>
+      <c r="N33" s="222"/>
+      <c r="O33" s="223"/>
+      <c r="P33" s="224"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="207"/>
-      <c r="S33" s="207"/>
+      <c r="R33" s="225"/>
+      <c r="S33" s="225"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="200"/>
-      <c r="D34" s="200"/>
-      <c r="E34" s="200"/>
-      <c r="F34" s="200"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="201"/>
-      <c r="I34" s="202"/>
-      <c r="J34" s="202"/>
-      <c r="K34" s="202"/>
-      <c r="L34" s="202"/>
-      <c r="M34" s="203"/>
-      <c r="N34" s="204"/>
-      <c r="O34" s="205"/>
-      <c r="P34" s="206"/>
+      <c r="C34" s="221"/>
+      <c r="D34" s="221"/>
+      <c r="E34" s="221"/>
+      <c r="F34" s="221"/>
+      <c r="G34" s="221"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="230"/>
+      <c r="J34" s="230"/>
+      <c r="K34" s="230"/>
+      <c r="L34" s="230"/>
+      <c r="M34" s="231"/>
+      <c r="N34" s="222"/>
+      <c r="O34" s="223"/>
+      <c r="P34" s="224"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="207"/>
-      <c r="S34" s="207"/>
+      <c r="R34" s="225"/>
+      <c r="S34" s="225"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="200"/>
-      <c r="D35" s="200"/>
-      <c r="E35" s="200"/>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="202"/>
-      <c r="J35" s="202"/>
-      <c r="K35" s="202"/>
-      <c r="L35" s="202"/>
-      <c r="M35" s="203"/>
-      <c r="N35" s="204"/>
-      <c r="O35" s="205"/>
-      <c r="P35" s="206"/>
+      <c r="C35" s="221"/>
+      <c r="D35" s="221"/>
+      <c r="E35" s="221"/>
+      <c r="F35" s="221"/>
+      <c r="G35" s="221"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="230"/>
+      <c r="J35" s="230"/>
+      <c r="K35" s="230"/>
+      <c r="L35" s="230"/>
+      <c r="M35" s="231"/>
+      <c r="N35" s="222"/>
+      <c r="O35" s="223"/>
+      <c r="P35" s="224"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="207"/>
-      <c r="S35" s="207"/>
+      <c r="R35" s="225"/>
+      <c r="S35" s="225"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="200"/>
-      <c r="D36" s="200"/>
-      <c r="E36" s="200"/>
-      <c r="F36" s="200"/>
-      <c r="G36" s="200"/>
-      <c r="H36" s="201"/>
-      <c r="I36" s="202"/>
-      <c r="J36" s="202"/>
-      <c r="K36" s="202"/>
-      <c r="L36" s="202"/>
-      <c r="M36" s="203"/>
-      <c r="N36" s="204"/>
-      <c r="O36" s="205"/>
-      <c r="P36" s="206"/>
+      <c r="C36" s="221"/>
+      <c r="D36" s="221"/>
+      <c r="E36" s="221"/>
+      <c r="F36" s="221"/>
+      <c r="G36" s="221"/>
+      <c r="H36" s="229"/>
+      <c r="I36" s="230"/>
+      <c r="J36" s="230"/>
+      <c r="K36" s="230"/>
+      <c r="L36" s="230"/>
+      <c r="M36" s="231"/>
+      <c r="N36" s="222"/>
+      <c r="O36" s="223"/>
+      <c r="P36" s="224"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="207"/>
-      <c r="S36" s="207"/>
+      <c r="R36" s="225"/>
+      <c r="S36" s="225"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="200"/>
-      <c r="D37" s="200"/>
-      <c r="E37" s="200"/>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="201"/>
-      <c r="I37" s="202"/>
-      <c r="J37" s="202"/>
-      <c r="K37" s="202"/>
-      <c r="L37" s="202"/>
-      <c r="M37" s="203"/>
-      <c r="N37" s="204"/>
-      <c r="O37" s="205"/>
-      <c r="P37" s="206"/>
+      <c r="C37" s="221"/>
+      <c r="D37" s="221"/>
+      <c r="E37" s="221"/>
+      <c r="F37" s="221"/>
+      <c r="G37" s="221"/>
+      <c r="H37" s="229"/>
+      <c r="I37" s="230"/>
+      <c r="J37" s="230"/>
+      <c r="K37" s="230"/>
+      <c r="L37" s="230"/>
+      <c r="M37" s="231"/>
+      <c r="N37" s="222"/>
+      <c r="O37" s="223"/>
+      <c r="P37" s="224"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="207"/>
-      <c r="S37" s="207"/>
+      <c r="R37" s="225"/>
+      <c r="S37" s="225"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="200"/>
-      <c r="D38" s="200"/>
-      <c r="E38" s="200"/>
-      <c r="F38" s="200"/>
-      <c r="G38" s="200"/>
-      <c r="H38" s="201"/>
-      <c r="I38" s="202"/>
-      <c r="J38" s="202"/>
-      <c r="K38" s="202"/>
-      <c r="L38" s="202"/>
-      <c r="M38" s="203"/>
-      <c r="N38" s="204"/>
-      <c r="O38" s="205"/>
-      <c r="P38" s="206"/>
+      <c r="C38" s="221"/>
+      <c r="D38" s="221"/>
+      <c r="E38" s="221"/>
+      <c r="F38" s="221"/>
+      <c r="G38" s="221"/>
+      <c r="H38" s="229"/>
+      <c r="I38" s="230"/>
+      <c r="J38" s="230"/>
+      <c r="K38" s="230"/>
+      <c r="L38" s="230"/>
+      <c r="M38" s="231"/>
+      <c r="N38" s="222"/>
+      <c r="O38" s="223"/>
+      <c r="P38" s="224"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="207"/>
-      <c r="S38" s="207"/>
+      <c r="R38" s="225"/>
+      <c r="S38" s="225"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="200"/>
-      <c r="D39" s="200"/>
-      <c r="E39" s="200"/>
-      <c r="F39" s="200"/>
-      <c r="G39" s="200"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="202"/>
-      <c r="J39" s="202"/>
-      <c r="K39" s="202"/>
-      <c r="L39" s="202"/>
-      <c r="M39" s="203"/>
-      <c r="N39" s="204"/>
-      <c r="O39" s="205"/>
-      <c r="P39" s="206"/>
+      <c r="C39" s="221"/>
+      <c r="D39" s="221"/>
+      <c r="E39" s="221"/>
+      <c r="F39" s="221"/>
+      <c r="G39" s="221"/>
+      <c r="H39" s="229"/>
+      <c r="I39" s="230"/>
+      <c r="J39" s="230"/>
+      <c r="K39" s="230"/>
+      <c r="L39" s="230"/>
+      <c r="M39" s="231"/>
+      <c r="N39" s="222"/>
+      <c r="O39" s="223"/>
+      <c r="P39" s="224"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="207"/>
-      <c r="S39" s="207"/>
+      <c r="R39" s="225"/>
+      <c r="S39" s="225"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="200"/>
-      <c r="D40" s="200"/>
-      <c r="E40" s="200"/>
-      <c r="F40" s="200"/>
-      <c r="G40" s="200"/>
-      <c r="H40" s="201"/>
-      <c r="I40" s="202"/>
-      <c r="J40" s="202"/>
-      <c r="K40" s="202"/>
-      <c r="L40" s="202"/>
-      <c r="M40" s="203"/>
-      <c r="N40" s="204"/>
-      <c r="O40" s="205"/>
-      <c r="P40" s="206"/>
+      <c r="C40" s="221"/>
+      <c r="D40" s="221"/>
+      <c r="E40" s="221"/>
+      <c r="F40" s="221"/>
+      <c r="G40" s="221"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="230"/>
+      <c r="J40" s="230"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="222"/>
+      <c r="O40" s="223"/>
+      <c r="P40" s="224"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="207"/>
-      <c r="S40" s="207"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="200"/>
-      <c r="D41" s="200"/>
-      <c r="E41" s="200"/>
-      <c r="F41" s="200"/>
-      <c r="G41" s="200"/>
-      <c r="H41" s="201"/>
-      <c r="I41" s="202"/>
-      <c r="J41" s="202"/>
-      <c r="K41" s="202"/>
-      <c r="L41" s="202"/>
-      <c r="M41" s="203"/>
-      <c r="N41" s="204"/>
-      <c r="O41" s="205"/>
-      <c r="P41" s="206"/>
+      <c r="C41" s="221"/>
+      <c r="D41" s="221"/>
+      <c r="E41" s="221"/>
+      <c r="F41" s="221"/>
+      <c r="G41" s="221"/>
+      <c r="H41" s="229"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="230"/>
+      <c r="K41" s="230"/>
+      <c r="L41" s="230"/>
+      <c r="M41" s="231"/>
+      <c r="N41" s="222"/>
+      <c r="O41" s="223"/>
+      <c r="P41" s="224"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="207"/>
-      <c r="S41" s="207"/>
+      <c r="R41" s="225"/>
+      <c r="S41" s="225"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="200"/>
-      <c r="D42" s="200"/>
-      <c r="E42" s="200"/>
-      <c r="F42" s="200"/>
-      <c r="G42" s="200"/>
-      <c r="H42" s="201"/>
-      <c r="I42" s="202"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="202"/>
-      <c r="L42" s="202"/>
-      <c r="M42" s="203"/>
-      <c r="N42" s="204"/>
-      <c r="O42" s="205"/>
-      <c r="P42" s="206"/>
+      <c r="C42" s="221"/>
+      <c r="D42" s="221"/>
+      <c r="E42" s="221"/>
+      <c r="F42" s="221"/>
+      <c r="G42" s="221"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="230"/>
+      <c r="J42" s="230"/>
+      <c r="K42" s="230"/>
+      <c r="L42" s="230"/>
+      <c r="M42" s="231"/>
+      <c r="N42" s="222"/>
+      <c r="O42" s="223"/>
+      <c r="P42" s="224"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="207"/>
-      <c r="S42" s="207"/>
+      <c r="R42" s="225"/>
+      <c r="S42" s="225"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="200"/>
-      <c r="D43" s="200"/>
-      <c r="E43" s="200"/>
-      <c r="F43" s="200"/>
-      <c r="G43" s="200"/>
-      <c r="H43" s="201"/>
-      <c r="I43" s="202"/>
-      <c r="J43" s="202"/>
-      <c r="K43" s="202"/>
-      <c r="L43" s="202"/>
-      <c r="M43" s="203"/>
-      <c r="N43" s="204"/>
-      <c r="O43" s="205"/>
-      <c r="P43" s="206"/>
+      <c r="C43" s="221"/>
+      <c r="D43" s="221"/>
+      <c r="E43" s="221"/>
+      <c r="F43" s="221"/>
+      <c r="G43" s="221"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="230"/>
+      <c r="J43" s="230"/>
+      <c r="K43" s="230"/>
+      <c r="L43" s="230"/>
+      <c r="M43" s="231"/>
+      <c r="N43" s="222"/>
+      <c r="O43" s="223"/>
+      <c r="P43" s="224"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="207"/>
-      <c r="S43" s="207"/>
+      <c r="R43" s="225"/>
+      <c r="S43" s="225"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="200"/>
-      <c r="D44" s="200"/>
-      <c r="E44" s="200"/>
-      <c r="F44" s="200"/>
-      <c r="G44" s="200"/>
-      <c r="H44" s="201"/>
-      <c r="I44" s="202"/>
-      <c r="J44" s="202"/>
-      <c r="K44" s="202"/>
-      <c r="L44" s="202"/>
-      <c r="M44" s="203"/>
-      <c r="N44" s="204"/>
-      <c r="O44" s="205"/>
-      <c r="P44" s="206"/>
+      <c r="C44" s="221"/>
+      <c r="D44" s="221"/>
+      <c r="E44" s="221"/>
+      <c r="F44" s="221"/>
+      <c r="G44" s="221"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="230"/>
+      <c r="J44" s="230"/>
+      <c r="K44" s="230"/>
+      <c r="L44" s="230"/>
+      <c r="M44" s="231"/>
+      <c r="N44" s="222"/>
+      <c r="O44" s="223"/>
+      <c r="P44" s="224"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="207"/>
-      <c r="S44" s="207"/>
+      <c r="R44" s="225"/>
+      <c r="S44" s="225"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="200"/>
-      <c r="D45" s="200"/>
-      <c r="E45" s="200"/>
-      <c r="F45" s="200"/>
-      <c r="G45" s="200"/>
-      <c r="H45" s="201"/>
-      <c r="I45" s="202"/>
-      <c r="J45" s="202"/>
-      <c r="K45" s="202"/>
-      <c r="L45" s="202"/>
-      <c r="M45" s="203"/>
-      <c r="N45" s="204"/>
-      <c r="O45" s="205"/>
-      <c r="P45" s="206"/>
+      <c r="C45" s="221"/>
+      <c r="D45" s="221"/>
+      <c r="E45" s="221"/>
+      <c r="F45" s="221"/>
+      <c r="G45" s="221"/>
+      <c r="H45" s="229"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="230"/>
+      <c r="K45" s="230"/>
+      <c r="L45" s="230"/>
+      <c r="M45" s="231"/>
+      <c r="N45" s="222"/>
+      <c r="O45" s="223"/>
+      <c r="P45" s="224"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="207"/>
-      <c r="S45" s="207"/>
+      <c r="R45" s="225"/>
+      <c r="S45" s="225"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="200"/>
-      <c r="D46" s="200"/>
-      <c r="E46" s="200"/>
-      <c r="F46" s="200"/>
-      <c r="G46" s="200"/>
-      <c r="H46" s="201"/>
-      <c r="I46" s="202"/>
-      <c r="J46" s="202"/>
-      <c r="K46" s="202"/>
-      <c r="L46" s="202"/>
-      <c r="M46" s="203"/>
-      <c r="N46" s="204"/>
-      <c r="O46" s="205"/>
-      <c r="P46" s="206"/>
+      <c r="C46" s="221"/>
+      <c r="D46" s="221"/>
+      <c r="E46" s="221"/>
+      <c r="F46" s="221"/>
+      <c r="G46" s="221"/>
+      <c r="H46" s="229"/>
+      <c r="I46" s="230"/>
+      <c r="J46" s="230"/>
+      <c r="K46" s="230"/>
+      <c r="L46" s="230"/>
+      <c r="M46" s="231"/>
+      <c r="N46" s="222"/>
+      <c r="O46" s="223"/>
+      <c r="P46" s="224"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="207"/>
-      <c r="S46" s="207"/>
+      <c r="R46" s="225"/>
+      <c r="S46" s="225"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="200"/>
-      <c r="D47" s="200"/>
-      <c r="E47" s="200"/>
-      <c r="F47" s="200"/>
-      <c r="G47" s="200"/>
-      <c r="H47" s="201"/>
-      <c r="I47" s="202"/>
-      <c r="J47" s="202"/>
-      <c r="K47" s="202"/>
-      <c r="L47" s="202"/>
-      <c r="M47" s="203"/>
-      <c r="N47" s="204"/>
-      <c r="O47" s="205"/>
-      <c r="P47" s="206"/>
+      <c r="C47" s="221"/>
+      <c r="D47" s="221"/>
+      <c r="E47" s="221"/>
+      <c r="F47" s="221"/>
+      <c r="G47" s="221"/>
+      <c r="H47" s="229"/>
+      <c r="I47" s="230"/>
+      <c r="J47" s="230"/>
+      <c r="K47" s="230"/>
+      <c r="L47" s="230"/>
+      <c r="M47" s="231"/>
+      <c r="N47" s="222"/>
+      <c r="O47" s="223"/>
+      <c r="P47" s="224"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="207"/>
-      <c r="S47" s="207"/>
+      <c r="R47" s="225"/>
+      <c r="S47" s="225"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="200"/>
-      <c r="D48" s="200"/>
-      <c r="E48" s="200"/>
-      <c r="F48" s="200"/>
-      <c r="G48" s="200"/>
-      <c r="H48" s="201"/>
-      <c r="I48" s="202"/>
-      <c r="J48" s="202"/>
-      <c r="K48" s="202"/>
-      <c r="L48" s="202"/>
-      <c r="M48" s="203"/>
-      <c r="N48" s="204"/>
-      <c r="O48" s="205"/>
-      <c r="P48" s="206"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="230"/>
+      <c r="L48" s="230"/>
+      <c r="M48" s="231"/>
+      <c r="N48" s="222"/>
+      <c r="O48" s="223"/>
+      <c r="P48" s="224"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="207"/>
-      <c r="S48" s="207"/>
+      <c r="R48" s="225"/>
+      <c r="S48" s="225"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="200"/>
-      <c r="D49" s="200"/>
-      <c r="E49" s="200"/>
-      <c r="F49" s="200"/>
-      <c r="G49" s="200"/>
-      <c r="H49" s="201"/>
-      <c r="I49" s="202"/>
-      <c r="J49" s="202"/>
-      <c r="K49" s="202"/>
-      <c r="L49" s="202"/>
-      <c r="M49" s="203"/>
-      <c r="N49" s="204"/>
-      <c r="O49" s="205"/>
-      <c r="P49" s="206"/>
+      <c r="C49" s="221"/>
+      <c r="D49" s="221"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="221"/>
+      <c r="G49" s="221"/>
+      <c r="H49" s="229"/>
+      <c r="I49" s="230"/>
+      <c r="J49" s="230"/>
+      <c r="K49" s="230"/>
+      <c r="L49" s="230"/>
+      <c r="M49" s="231"/>
+      <c r="N49" s="222"/>
+      <c r="O49" s="223"/>
+      <c r="P49" s="224"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="207"/>
-      <c r="S49" s="207"/>
+      <c r="R49" s="225"/>
+      <c r="S49" s="225"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="200"/>
-      <c r="D50" s="200"/>
-      <c r="E50" s="200"/>
-      <c r="F50" s="200"/>
-      <c r="G50" s="200"/>
-      <c r="H50" s="201"/>
-      <c r="I50" s="202"/>
-      <c r="J50" s="202"/>
-      <c r="K50" s="202"/>
-      <c r="L50" s="202"/>
-      <c r="M50" s="203"/>
-      <c r="N50" s="204"/>
-      <c r="O50" s="205"/>
-      <c r="P50" s="206"/>
+      <c r="C50" s="221"/>
+      <c r="D50" s="221"/>
+      <c r="E50" s="221"/>
+      <c r="F50" s="221"/>
+      <c r="G50" s="221"/>
+      <c r="H50" s="229"/>
+      <c r="I50" s="230"/>
+      <c r="J50" s="230"/>
+      <c r="K50" s="230"/>
+      <c r="L50" s="230"/>
+      <c r="M50" s="231"/>
+      <c r="N50" s="222"/>
+      <c r="O50" s="223"/>
+      <c r="P50" s="224"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="207"/>
-      <c r="S50" s="207"/>
+      <c r="R50" s="225"/>
+      <c r="S50" s="225"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="200"/>
-      <c r="D51" s="200"/>
-      <c r="E51" s="200"/>
-      <c r="F51" s="200"/>
-      <c r="G51" s="200"/>
-      <c r="H51" s="201"/>
-      <c r="I51" s="202"/>
-      <c r="J51" s="202"/>
-      <c r="K51" s="202"/>
-      <c r="L51" s="202"/>
-      <c r="M51" s="203"/>
-      <c r="N51" s="204"/>
-      <c r="O51" s="205"/>
-      <c r="P51" s="206"/>
+      <c r="C51" s="221"/>
+      <c r="D51" s="221"/>
+      <c r="E51" s="221"/>
+      <c r="F51" s="221"/>
+      <c r="G51" s="221"/>
+      <c r="H51" s="229"/>
+      <c r="I51" s="230"/>
+      <c r="J51" s="230"/>
+      <c r="K51" s="230"/>
+      <c r="L51" s="230"/>
+      <c r="M51" s="231"/>
+      <c r="N51" s="222"/>
+      <c r="O51" s="223"/>
+      <c r="P51" s="224"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="207"/>
-      <c r="S51" s="207"/>
+      <c r="R51" s="225"/>
+      <c r="S51" s="225"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="200"/>
-      <c r="D52" s="200"/>
-      <c r="E52" s="200"/>
-      <c r="F52" s="200"/>
-      <c r="G52" s="200"/>
-      <c r="H52" s="201"/>
-      <c r="I52" s="202"/>
-      <c r="J52" s="202"/>
-      <c r="K52" s="202"/>
-      <c r="L52" s="202"/>
-      <c r="M52" s="203"/>
-      <c r="N52" s="204"/>
-      <c r="O52" s="205"/>
-      <c r="P52" s="206"/>
+      <c r="C52" s="221"/>
+      <c r="D52" s="221"/>
+      <c r="E52" s="221"/>
+      <c r="F52" s="221"/>
+      <c r="G52" s="221"/>
+      <c r="H52" s="229"/>
+      <c r="I52" s="230"/>
+      <c r="J52" s="230"/>
+      <c r="K52" s="230"/>
+      <c r="L52" s="230"/>
+      <c r="M52" s="231"/>
+      <c r="N52" s="222"/>
+      <c r="O52" s="223"/>
+      <c r="P52" s="224"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="207"/>
-      <c r="S52" s="207"/>
+      <c r="R52" s="225"/>
+      <c r="S52" s="225"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -12637,194 +12899,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D232B5-AF71-4C5D-9216-88435B4F9ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0F3E0B-93B2-4AD6-B424-3659F2F6D49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="104">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -604,33 +604,62 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>NOT NULL制約がないものに対して未入力がある場合のタスク一覧表示</t>
-    <rPh sb="8" eb="10">
-      <t>セイヤク</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="19" eb="22">
+    <t>「未入力」と表示される</t>
+    <rPh sb="1" eb="4">
       <t>ミニュウリョク</t>
     </rPh>
-    <rPh sb="25" eb="27">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="33" eb="35">
+    <rPh sb="6" eb="8">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>「未入力」と表示される</t>
-    <rPh sb="1" eb="4">
+    <t>期限、メモが未入力の場合のタスク一覧表示</t>
+    <rPh sb="0" eb="2">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
       <t>ミニュウリョク</t>
     </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>タスクID、タスク名、カテゴリID、ユーザーID、ステータスコード、登録日時、更新日時の表示</t>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="34" eb="38">
+      <t>トウロクニチジ</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>コウシンニチジ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>必ず登録した内容が表示される</t>
+    <rPh sb="0" eb="1">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
     <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="7"/>
@@ -10088,7 +10117,7 @@
       </c>
       <c r="F20" s="183"/>
       <c r="G20" s="192" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H20" s="182"/>
       <c r="I20" s="183"/>
@@ -10102,7 +10131,7 @@
       <c r="M20" s="182"/>
       <c r="N20" s="183"/>
       <c r="O20" s="193" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P20" s="182"/>
       <c r="Q20" s="183"/>
@@ -10116,22 +10145,36 @@
       <c r="Y20" s="48"/>
       <c r="Z20" s="48"/>
     </row>
-    <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="190"/>
+    <row r="21" spans="1:26" ht="50.25" customHeight="1">
+      <c r="A21" s="190">
+        <v>6</v>
+      </c>
       <c r="B21" s="183"/>
-      <c r="C21" s="191"/>
+      <c r="C21" s="191" t="s">
+        <v>59</v>
+      </c>
       <c r="D21" s="183"/>
-      <c r="E21" s="191"/>
+      <c r="E21" s="191" t="s">
+        <v>95</v>
+      </c>
       <c r="F21" s="183"/>
-      <c r="G21" s="192"/>
+      <c r="G21" s="192" t="s">
+        <v>102</v>
+      </c>
       <c r="H21" s="182"/>
       <c r="I21" s="183"/>
-      <c r="J21" s="192"/>
+      <c r="J21" s="192" t="s">
+        <v>92</v>
+      </c>
       <c r="K21" s="183"/>
-      <c r="L21" s="193"/>
+      <c r="L21" s="193" t="s">
+        <v>90</v>
+      </c>
       <c r="M21" s="182"/>
       <c r="N21" s="183"/>
-      <c r="O21" s="193"/>
+      <c r="O21" s="193" t="s">
+        <v>103</v>
+      </c>
       <c r="P21" s="182"/>
       <c r="Q21" s="183"/>
       <c r="R21" s="46"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Desktop\プロ演最新\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0F3E0B-93B2-4AD6-B424-3659F2F6D49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49171F1E-DE71-492B-817D-15DB6F90474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7470" yWindow="705" windowWidth="11475" windowHeight="9180" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="109">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -287,22 +287,6 @@
     </rPh>
     <rPh sb="19" eb="21">
       <t>セツゾク</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>1タスク詳細画面に遷移する。2メニュー画面に戻る。</t>
-    <rPh sb="4" eb="8">
-      <t>ショウサイガメン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>モド</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -662,6 +646,52 @@
     <rPh sb="9" eb="11">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1タスク詳細画面に遷移する。
+2メニュー画面に戻る。</t>
+    <rPh sb="4" eb="8">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>正常系</t>
+    <rPh sb="0" eb="3">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>TaskDAOTest</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>select()</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>返ってくる値がNullではない。</t>
+    <rPh sb="0" eb="1">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="7"/>
   </si>
 </sst>
@@ -1655,7 +1685,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1848,6 +1878,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="15" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1965,6 +1998,9 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1992,9 +2028,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2351,6 +2384,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="10" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2377,23 +2413,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>276224</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>742949</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>131120</xdr:rowOff>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940D12F3-8A15-0E7A-D035-9108793564C8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96675552-1382-5028-9F15-4F92776114BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2415,8 +2451,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="276224" y="1057275"/>
-          <a:ext cx="8181975" cy="4522145"/>
+          <a:off x="609600" y="1076325"/>
+          <a:ext cx="7772400" cy="4295775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2902,85 +2938,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3000,46 +3036,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="66"/>
-      <c r="I13" s="64" t="s">
+      <c r="H13" s="67"/>
+      <c r="I13" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="65"/>
-      <c r="K13" s="66"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="67"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="64"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="66"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="67"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="64"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="66"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="67"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3048,13 +3084,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="67" t="s">
+      <c r="G17" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4069,19 +4105,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="97" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="97" t="s">
+      <c r="E1" s="81"/>
+      <c r="F1" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
+      <c r="G1" s="81"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4093,190 +4129,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="91"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="98" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="99"/>
-      <c r="F2" s="98" t="s">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="99"/>
-      <c r="H2" s="102">
+      <c r="G2" s="100"/>
+      <c r="H2" s="103">
         <v>45805</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="91"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="84"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="86" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84"/>
-      <c r="J6" s="87"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="88"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="84"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="86" t="s">
+      <c r="B7" s="85"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="87"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="88"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="86" t="s">
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="87"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="108" t="s">
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="88"/>
+    </row>
+    <row r="9" spans="1:10" ht="87" customHeight="1">
+      <c r="A9" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="111" t="s">
+      <c r="B9" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="112" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="87"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="88"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="109"/>
-      <c r="B10" s="111" t="s">
+      <c r="A10" s="111"/>
+      <c r="B10" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="87"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="88"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="110"/>
-      <c r="B11" s="111" t="s">
+      <c r="A11" s="112"/>
+      <c r="B11" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="85"/>
-      <c r="D11" s="112" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="87"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="83" t="s">
+      <c r="C11" s="86"/>
+      <c r="D11" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="88"/>
+    </row>
+    <row r="12" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A12" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="86" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="87"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="88"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="104"/>
-      <c r="C13" s="105"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="107"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="109"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5312,19 +5348,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="128" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="129"/>
-      <c r="F1" s="128" t="s">
+      <c r="E1" s="130"/>
+      <c r="F1" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="129"/>
+      <c r="G1" s="130"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5336,48 +5372,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="130" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="131"/>
-      <c r="F2" s="130" t="s">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="113">
+      <c r="G2" s="132"/>
+      <c r="H2" s="114">
         <v>45807</v>
       </c>
-      <c r="I2" s="116" t="s">
+      <c r="I2" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="117"/>
+      <c r="J2" s="118"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="118"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="119"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="119"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6737,19 +6773,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="128" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="129"/>
-      <c r="F1" s="128" t="s">
+      <c r="E1" s="130"/>
+      <c r="F1" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="129"/>
+      <c r="G1" s="130"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6761,190 +6797,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="130" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="131"/>
-      <c r="F2" s="130" t="s">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="113">
+      <c r="G2" s="132"/>
+      <c r="H2" s="114">
         <v>45810</v>
       </c>
-      <c r="I2" s="116" t="s">
+      <c r="I2" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="117"/>
+      <c r="J2" s="118"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="118"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="119"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="123"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="118"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="138"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="143" t="s">
+      <c r="B5" s="139"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="138"/>
-      <c r="J5" s="144"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="145"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="142" t="s">
+      <c r="A6" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="135"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="136"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="145"/>
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="146"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="146"/>
-      <c r="I7" s="146"/>
-      <c r="J7" s="147"/>
+      <c r="A7" s="146"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="148"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="123"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="148"/>
+      <c r="A8" s="124"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="149"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="123"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="148"/>
+      <c r="A9" s="124"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="149"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="123"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="148"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="149"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="148"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="149"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="123"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="148"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="149"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="123"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="148"/>
+      <c r="A13" s="124"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="149"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="142" t="s">
+      <c r="A14" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="135"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="136"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="142" t="s">
+      <c r="A15" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="134" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="13" t="s">
         <v>16</v>
       </c>
@@ -6953,11 +6989,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="142" t="s">
+      <c r="A16" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="66"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="67"/>
       <c r="D16" s="13" t="s">
         <v>18</v>
       </c>
@@ -6970,18 +7006,18 @@
       <c r="G16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="149" t="s">
+      <c r="H16" s="150" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="65"/>
-      <c r="J16" s="135"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="136"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="136">
+      <c r="A17" s="137">
         <v>1</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
       <c r="D17" s="15" t="s">
         <v>62</v>
       </c>
@@ -6992,81 +7028,81 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="134"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="136"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="136"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="66"/>
+      <c r="A18" s="137"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="67"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="136"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="136"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
+      <c r="A19" s="137"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="136"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="136"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="66"/>
+      <c r="A20" s="137"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="67"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="134"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="136"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="136"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
+      <c r="A21" s="137"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="136"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="136"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="66"/>
+      <c r="A22" s="137"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="67"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="136"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="139"/>
-      <c r="B23" s="140"/>
-      <c r="C23" s="141"/>
+      <c r="A23" s="140"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="142"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="140"/>
-      <c r="J23" s="151"/>
+      <c r="H23" s="151"/>
+      <c r="I23" s="141"/>
+      <c r="J23" s="152"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8098,19 +8134,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="167" t="s">
+      <c r="B1" s="160"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="168"/>
-      <c r="F1" s="167" t="s">
+      <c r="E1" s="169"/>
+      <c r="F1" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="168"/>
+      <c r="G1" s="169"/>
       <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
@@ -8122,48 +8158,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="161"/>
-      <c r="B2" s="162"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="169" t="s">
+      <c r="A2" s="162"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="170"/>
-      <c r="F2" s="169" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="170"/>
-      <c r="H2" s="173">
+      <c r="G2" s="171"/>
+      <c r="H2" s="174">
         <v>45810</v>
       </c>
-      <c r="I2" s="152" t="s">
+      <c r="I2" s="153" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="155"/>
+      <c r="J2" s="156"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="161"/>
-      <c r="B3" s="162"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="153"/>
-      <c r="I3" s="153"/>
-      <c r="J3" s="156"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="157"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="164"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="172"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="172"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="154"/>
-      <c r="I4" s="154"/>
-      <c r="J4" s="157"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="166"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="158"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="26"/>
@@ -9512,190 +9548,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="167" t="s">
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="168"/>
-      <c r="K1" s="167" t="s">
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
-      <c r="N1" s="168"/>
-      <c r="O1" s="167" t="s">
+      <c r="L1" s="179"/>
+      <c r="M1" s="179"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="168"/>
-      <c r="Q1" s="167" t="s">
+      <c r="P1" s="169"/>
+      <c r="Q1" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="168"/>
-      <c r="S1" s="167" t="s">
+      <c r="R1" s="169"/>
+      <c r="S1" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="180"/>
+      <c r="T1" s="181"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="161"/>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="169" t="s">
+      <c r="A2" s="162"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="169" t="s">
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="187"/>
-      <c r="M2" s="187"/>
-      <c r="N2" s="170"/>
-      <c r="O2" s="188">
+      <c r="L2" s="188"/>
+      <c r="M2" s="188"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="189">
         <v>45817</v>
       </c>
-      <c r="P2" s="170"/>
-      <c r="Q2" s="169" t="s">
+      <c r="P2" s="171"/>
+      <c r="Q2" s="170" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="170"/>
-      <c r="S2" s="169"/>
-      <c r="T2" s="174"/>
+      <c r="R2" s="171"/>
+      <c r="S2" s="170"/>
+      <c r="T2" s="175"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="161"/>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="171"/>
-      <c r="P3" s="163"/>
-      <c r="Q3" s="171"/>
-      <c r="R3" s="163"/>
-      <c r="S3" s="171"/>
-      <c r="T3" s="175"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="164"/>
+      <c r="O3" s="172"/>
+      <c r="P3" s="164"/>
+      <c r="Q3" s="172"/>
+      <c r="R3" s="164"/>
+      <c r="S3" s="172"/>
+      <c r="T3" s="176"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="164"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="172"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="166"/>
-      <c r="K4" s="172"/>
-      <c r="L4" s="165"/>
-      <c r="M4" s="165"/>
-      <c r="N4" s="166"/>
-      <c r="O4" s="172"/>
-      <c r="P4" s="166"/>
-      <c r="Q4" s="172"/>
-      <c r="R4" s="166"/>
-      <c r="S4" s="172"/>
-      <c r="T4" s="176"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="166"/>
+      <c r="C4" s="166"/>
+      <c r="D4" s="166"/>
+      <c r="E4" s="166"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="166"/>
+      <c r="I4" s="166"/>
+      <c r="J4" s="167"/>
+      <c r="K4" s="173"/>
+      <c r="L4" s="166"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="173"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="173"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="173"/>
+      <c r="T4" s="177"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="177" t="s">
+      <c r="A5" s="178" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="178"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="179" t="s">
+      <c r="B5" s="179"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="180" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="178"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="178"/>
-      <c r="L5" s="178"/>
-      <c r="M5" s="178"/>
-      <c r="N5" s="178"/>
-      <c r="O5" s="178"/>
-      <c r="P5" s="178"/>
-      <c r="Q5" s="178"/>
-      <c r="R5" s="178"/>
-      <c r="S5" s="178"/>
-      <c r="T5" s="180"/>
+      <c r="H5" s="179"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="179"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="179"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="179"/>
+      <c r="Q5" s="179"/>
+      <c r="R5" s="179"/>
+      <c r="S5" s="179"/>
+      <c r="T5" s="181"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="182" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="182"/>
-      <c r="C6" s="182"/>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="184" t="s">
+      <c r="B6" s="183"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="185" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="182"/>
-      <c r="I6" s="182"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="182"/>
-      <c r="L6" s="182"/>
-      <c r="M6" s="182"/>
-      <c r="N6" s="182"/>
-      <c r="O6" s="182"/>
-      <c r="P6" s="182"/>
-      <c r="Q6" s="182"/>
-      <c r="R6" s="182"/>
-      <c r="S6" s="182"/>
-      <c r="T6" s="185"/>
+      <c r="H6" s="183"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="183"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="183"/>
+      <c r="Q6" s="183"/>
+      <c r="R6" s="183"/>
+      <c r="S6" s="183"/>
+      <c r="T6" s="186"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="182" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="182"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="182"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="184" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="182"/>
-      <c r="I7" s="182"/>
-      <c r="J7" s="182"/>
-      <c r="K7" s="182"/>
-      <c r="L7" s="182"/>
-      <c r="M7" s="182"/>
-      <c r="N7" s="182"/>
-      <c r="O7" s="182"/>
-      <c r="P7" s="182"/>
-      <c r="Q7" s="182"/>
-      <c r="R7" s="182"/>
-      <c r="S7" s="182"/>
-      <c r="T7" s="185"/>
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="185" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="183"/>
+      <c r="M7" s="183"/>
+      <c r="N7" s="183"/>
+      <c r="O7" s="183"/>
+      <c r="P7" s="183"/>
+      <c r="Q7" s="183"/>
+      <c r="R7" s="183"/>
+      <c r="S7" s="183"/>
+      <c r="T7" s="186"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9894,37 +9930,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="183"/>
-      <c r="C15" s="194" t="s">
+      <c r="B15" s="184"/>
+      <c r="C15" s="195" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="183"/>
-      <c r="E15" s="189" t="s">
+      <c r="D15" s="184"/>
+      <c r="E15" s="190" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="183"/>
-      <c r="G15" s="189" t="s">
+      <c r="F15" s="184"/>
+      <c r="G15" s="190" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="182"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="189" t="s">
+      <c r="H15" s="183"/>
+      <c r="I15" s="184"/>
+      <c r="J15" s="190" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="183"/>
-      <c r="L15" s="189" t="s">
+      <c r="K15" s="184"/>
+      <c r="L15" s="190" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="182"/>
-      <c r="N15" s="183"/>
-      <c r="O15" s="189" t="s">
+      <c r="M15" s="183"/>
+      <c r="N15" s="184"/>
+      <c r="O15" s="190" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="182"/>
-      <c r="Q15" s="183"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="184"/>
       <c r="R15" s="44" t="s">
         <v>56</v>
       </c>
@@ -9936,40 +9972,46 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="190">
+      <c r="A16" s="191">
         <v>1</v>
       </c>
-      <c r="B16" s="183"/>
-      <c r="C16" s="191" t="s">
+      <c r="B16" s="184"/>
+      <c r="C16" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="183"/>
-      <c r="E16" s="191" t="s">
+      <c r="D16" s="184"/>
+      <c r="E16" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="183"/>
-      <c r="G16" s="192" t="s">
+      <c r="F16" s="184"/>
+      <c r="G16" s="193" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="183"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="184"/>
+      <c r="L16" s="194" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="182"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="K16" s="183"/>
-      <c r="L16" s="193" t="s">
+      <c r="M16" s="183"/>
+      <c r="N16" s="184"/>
+      <c r="O16" s="194" t="s">
         <v>90</v>
       </c>
-      <c r="M16" s="182"/>
-      <c r="N16" s="183"/>
-      <c r="O16" s="193" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="182"/>
-      <c r="Q16" s="183"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="47"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="184"/>
+      <c r="R16" s="233">
+        <v>45818</v>
+      </c>
+      <c r="S16" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T16" s="47" t="s">
+        <v>108</v>
+      </c>
       <c r="U16" s="48"/>
       <c r="V16" s="48"/>
       <c r="W16" s="48"/>
@@ -9978,40 +10020,46 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="190">
+      <c r="A17" s="191">
         <v>2</v>
       </c>
-      <c r="B17" s="183"/>
-      <c r="C17" s="191" t="s">
+      <c r="B17" s="184"/>
+      <c r="C17" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="183"/>
-      <c r="E17" s="191" t="s">
+      <c r="D17" s="184"/>
+      <c r="E17" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="183"/>
-      <c r="G17" s="192" t="s">
+      <c r="F17" s="184"/>
+      <c r="G17" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="183"/>
+      <c r="I17" s="184"/>
+      <c r="J17" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" s="184"/>
+      <c r="L17" s="194" t="s">
+        <v>89</v>
+      </c>
+      <c r="M17" s="183"/>
+      <c r="N17" s="184"/>
+      <c r="O17" s="194" t="s">
         <v>98</v>
       </c>
-      <c r="H17" s="182"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="K17" s="183"/>
-      <c r="L17" s="193" t="s">
-        <v>90</v>
-      </c>
-      <c r="M17" s="182"/>
-      <c r="N17" s="183"/>
-      <c r="O17" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="P17" s="182"/>
-      <c r="Q17" s="183"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="47"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="184"/>
+      <c r="R17" s="233">
+        <v>45818</v>
+      </c>
+      <c r="S17" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T17" s="47" t="s">
+        <v>108</v>
+      </c>
       <c r="U17" s="48"/>
       <c r="V17" s="48"/>
       <c r="W17" s="48"/>
@@ -10020,37 +10068,37 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="190">
+      <c r="A18" s="191">
         <v>3</v>
       </c>
-      <c r="B18" s="183"/>
-      <c r="C18" s="191" t="s">
+      <c r="B18" s="184"/>
+      <c r="C18" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="183"/>
-      <c r="E18" s="191" t="s">
+      <c r="D18" s="184"/>
+      <c r="E18" s="192" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="183"/>
-      <c r="G18" s="192" t="s">
+      <c r="F18" s="184"/>
+      <c r="G18" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="183"/>
+      <c r="I18" s="184"/>
+      <c r="J18" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="K18" s="184"/>
+      <c r="L18" s="194" t="s">
+        <v>89</v>
+      </c>
+      <c r="M18" s="183"/>
+      <c r="N18" s="184"/>
+      <c r="O18" s="194" t="s">
         <v>93</v>
       </c>
-      <c r="H18" s="182"/>
-      <c r="I18" s="183"/>
-      <c r="J18" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="K18" s="183"/>
-      <c r="L18" s="193" t="s">
-        <v>90</v>
-      </c>
-      <c r="M18" s="182"/>
-      <c r="N18" s="183"/>
-      <c r="O18" s="193" t="s">
-        <v>94</v>
-      </c>
-      <c r="P18" s="182"/>
-      <c r="Q18" s="183"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="184"/>
       <c r="R18" s="46"/>
       <c r="S18" s="46"/>
       <c r="T18" s="47"/>
@@ -10062,37 +10110,37 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A19" s="190">
+      <c r="A19" s="191">
         <v>4</v>
       </c>
-      <c r="B19" s="183"/>
-      <c r="C19" s="191" t="s">
+      <c r="B19" s="184"/>
+      <c r="C19" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="183"/>
-      <c r="E19" s="191" t="s">
+      <c r="D19" s="184"/>
+      <c r="E19" s="192" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="184"/>
+      <c r="G19" s="193" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="183"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="184"/>
+      <c r="L19" s="194" t="s">
+        <v>89</v>
+      </c>
+      <c r="M19" s="183"/>
+      <c r="N19" s="184"/>
+      <c r="O19" s="194" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="183"/>
-      <c r="G19" s="192" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="182"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="K19" s="183"/>
-      <c r="L19" s="193" t="s">
-        <v>90</v>
-      </c>
-      <c r="M19" s="182"/>
-      <c r="N19" s="183"/>
-      <c r="O19" s="193" t="s">
-        <v>96</v>
-      </c>
-      <c r="P19" s="182"/>
-      <c r="Q19" s="183"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="184"/>
       <c r="R19" s="46"/>
       <c r="S19" s="46"/>
       <c r="T19" s="47"/>
@@ -10104,37 +10152,37 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A20" s="190">
+      <c r="A20" s="191">
         <v>5</v>
       </c>
-      <c r="B20" s="183"/>
-      <c r="C20" s="191" t="s">
+      <c r="B20" s="184"/>
+      <c r="C20" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="183"/>
-      <c r="E20" s="191" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="183"/>
-      <c r="G20" s="192" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="182"/>
-      <c r="I20" s="183"/>
-      <c r="J20" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="K20" s="183"/>
-      <c r="L20" s="193" t="s">
-        <v>90</v>
-      </c>
-      <c r="M20" s="182"/>
-      <c r="N20" s="183"/>
-      <c r="O20" s="193" t="s">
+      <c r="D20" s="184"/>
+      <c r="E20" s="192" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="184"/>
+      <c r="G20" s="193" t="s">
         <v>100</v>
       </c>
-      <c r="P20" s="182"/>
-      <c r="Q20" s="183"/>
+      <c r="H20" s="183"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="184"/>
+      <c r="L20" s="194" t="s">
+        <v>89</v>
+      </c>
+      <c r="M20" s="183"/>
+      <c r="N20" s="184"/>
+      <c r="O20" s="194" t="s">
+        <v>99</v>
+      </c>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="184"/>
       <c r="R20" s="46"/>
       <c r="S20" s="46"/>
       <c r="T20" s="47"/>
@@ -10146,37 +10194,37 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A21" s="190">
+      <c r="A21" s="191">
         <v>6</v>
       </c>
-      <c r="B21" s="183"/>
-      <c r="C21" s="191" t="s">
+      <c r="B21" s="184"/>
+      <c r="C21" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="183"/>
-      <c r="E21" s="191" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="183"/>
-      <c r="G21" s="192" t="s">
+      <c r="D21" s="184"/>
+      <c r="E21" s="192" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="184"/>
+      <c r="G21" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21" s="183"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="184"/>
+      <c r="L21" s="194" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" s="183"/>
+      <c r="N21" s="184"/>
+      <c r="O21" s="194" t="s">
         <v>102</v>
       </c>
-      <c r="H21" s="182"/>
-      <c r="I21" s="183"/>
-      <c r="J21" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="K21" s="183"/>
-      <c r="L21" s="193" t="s">
-        <v>90</v>
-      </c>
-      <c r="M21" s="182"/>
-      <c r="N21" s="183"/>
-      <c r="O21" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="P21" s="182"/>
-      <c r="Q21" s="183"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="184"/>
       <c r="R21" s="46"/>
       <c r="S21" s="46"/>
       <c r="T21" s="47"/>
@@ -10187,24 +10235,24 @@
       <c r="Y21" s="48"/>
       <c r="Z21" s="48"/>
     </row>
-    <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="190"/>
-      <c r="B22" s="183"/>
-      <c r="C22" s="191"/>
-      <c r="D22" s="183"/>
-      <c r="E22" s="191"/>
-      <c r="F22" s="183"/>
-      <c r="G22" s="192"/>
-      <c r="H22" s="182"/>
-      <c r="I22" s="183"/>
-      <c r="J22" s="192"/>
-      <c r="K22" s="183"/>
-      <c r="L22" s="193"/>
-      <c r="M22" s="182"/>
-      <c r="N22" s="183"/>
-      <c r="O22" s="193"/>
-      <c r="P22" s="182"/>
-      <c r="Q22" s="183"/>
+    <row r="22" spans="1:26" ht="55.5" customHeight="1">
+      <c r="A22" s="191"/>
+      <c r="B22" s="184"/>
+      <c r="C22" s="192"/>
+      <c r="D22" s="184"/>
+      <c r="E22" s="192"/>
+      <c r="F22" s="184"/>
+      <c r="G22" s="193"/>
+      <c r="H22" s="183"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="193"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="194"/>
+      <c r="M22" s="183"/>
+      <c r="N22" s="184"/>
+      <c r="O22" s="194"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="184"/>
       <c r="R22" s="46"/>
       <c r="S22" s="46"/>
       <c r="T22" s="47"/>
@@ -10216,23 +10264,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="190"/>
-      <c r="B23" s="183"/>
-      <c r="C23" s="191"/>
-      <c r="D23" s="183"/>
-      <c r="E23" s="191"/>
-      <c r="F23" s="183"/>
-      <c r="G23" s="192"/>
-      <c r="H23" s="182"/>
-      <c r="I23" s="183"/>
-      <c r="J23" s="192"/>
-      <c r="K23" s="183"/>
-      <c r="L23" s="193"/>
-      <c r="M23" s="182"/>
-      <c r="N23" s="183"/>
-      <c r="O23" s="193"/>
-      <c r="P23" s="182"/>
-      <c r="Q23" s="183"/>
+      <c r="A23" s="191"/>
+      <c r="B23" s="184"/>
+      <c r="C23" s="192"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="192"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="193"/>
+      <c r="H23" s="183"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="193"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="194"/>
+      <c r="M23" s="183"/>
+      <c r="N23" s="184"/>
+      <c r="O23" s="194"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="184"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -10244,23 +10292,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="190"/>
-      <c r="B24" s="183"/>
-      <c r="C24" s="191"/>
-      <c r="D24" s="183"/>
-      <c r="E24" s="191"/>
-      <c r="F24" s="183"/>
-      <c r="G24" s="192"/>
-      <c r="H24" s="182"/>
-      <c r="I24" s="183"/>
-      <c r="J24" s="192"/>
-      <c r="K24" s="183"/>
-      <c r="L24" s="193"/>
-      <c r="M24" s="182"/>
-      <c r="N24" s="183"/>
-      <c r="O24" s="193"/>
-      <c r="P24" s="182"/>
-      <c r="Q24" s="183"/>
+      <c r="A24" s="191"/>
+      <c r="B24" s="184"/>
+      <c r="C24" s="192"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="192"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="193"/>
+      <c r="H24" s="183"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="193"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="194"/>
+      <c r="M24" s="183"/>
+      <c r="N24" s="184"/>
+      <c r="O24" s="194"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="184"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -10272,23 +10320,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="190"/>
-      <c r="B25" s="183"/>
-      <c r="C25" s="191"/>
-      <c r="D25" s="183"/>
-      <c r="E25" s="191"/>
-      <c r="F25" s="183"/>
-      <c r="G25" s="192"/>
-      <c r="H25" s="182"/>
-      <c r="I25" s="183"/>
-      <c r="J25" s="192"/>
-      <c r="K25" s="183"/>
-      <c r="L25" s="193"/>
-      <c r="M25" s="182"/>
-      <c r="N25" s="183"/>
-      <c r="O25" s="193"/>
-      <c r="P25" s="182"/>
-      <c r="Q25" s="183"/>
+      <c r="A25" s="191"/>
+      <c r="B25" s="184"/>
+      <c r="C25" s="192"/>
+      <c r="D25" s="184"/>
+      <c r="E25" s="192"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="193"/>
+      <c r="H25" s="183"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="193"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="194"/>
+      <c r="M25" s="183"/>
+      <c r="N25" s="184"/>
+      <c r="O25" s="194"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="184"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -10300,23 +10348,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="190"/>
-      <c r="B26" s="183"/>
-      <c r="C26" s="191"/>
-      <c r="D26" s="183"/>
-      <c r="E26" s="191"/>
-      <c r="F26" s="183"/>
-      <c r="G26" s="192"/>
-      <c r="H26" s="182"/>
-      <c r="I26" s="183"/>
-      <c r="J26" s="192"/>
-      <c r="K26" s="183"/>
-      <c r="L26" s="193"/>
-      <c r="M26" s="182"/>
-      <c r="N26" s="183"/>
-      <c r="O26" s="193"/>
-      <c r="P26" s="182"/>
-      <c r="Q26" s="183"/>
+      <c r="A26" s="191"/>
+      <c r="B26" s="184"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="184"/>
+      <c r="E26" s="192"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="193"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="193"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="194"/>
+      <c r="M26" s="183"/>
+      <c r="N26" s="184"/>
+      <c r="O26" s="194"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="184"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -10328,23 +10376,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="190"/>
-      <c r="B27" s="183"/>
-      <c r="C27" s="191"/>
-      <c r="D27" s="183"/>
-      <c r="E27" s="191"/>
-      <c r="F27" s="183"/>
-      <c r="G27" s="192"/>
-      <c r="H27" s="182"/>
-      <c r="I27" s="183"/>
-      <c r="J27" s="192"/>
-      <c r="K27" s="183"/>
-      <c r="L27" s="193"/>
-      <c r="M27" s="182"/>
-      <c r="N27" s="183"/>
-      <c r="O27" s="193"/>
-      <c r="P27" s="182"/>
-      <c r="Q27" s="183"/>
+      <c r="A27" s="191"/>
+      <c r="B27" s="184"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="192"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="193"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="184"/>
+      <c r="J27" s="193"/>
+      <c r="K27" s="184"/>
+      <c r="L27" s="194"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="184"/>
+      <c r="O27" s="194"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="184"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -10356,23 +10404,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="190"/>
-      <c r="B28" s="183"/>
-      <c r="C28" s="191"/>
-      <c r="D28" s="183"/>
-      <c r="E28" s="191"/>
-      <c r="F28" s="183"/>
-      <c r="G28" s="192"/>
-      <c r="H28" s="182"/>
-      <c r="I28" s="183"/>
-      <c r="J28" s="192"/>
-      <c r="K28" s="183"/>
-      <c r="L28" s="193"/>
-      <c r="M28" s="182"/>
-      <c r="N28" s="183"/>
-      <c r="O28" s="193"/>
-      <c r="P28" s="182"/>
-      <c r="Q28" s="183"/>
+      <c r="A28" s="191"/>
+      <c r="B28" s="184"/>
+      <c r="C28" s="192"/>
+      <c r="D28" s="184"/>
+      <c r="E28" s="192"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="193"/>
+      <c r="H28" s="183"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="193"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="194"/>
+      <c r="M28" s="183"/>
+      <c r="N28" s="184"/>
+      <c r="O28" s="194"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="184"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -10384,23 +10432,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="190"/>
-      <c r="B29" s="183"/>
-      <c r="C29" s="191"/>
-      <c r="D29" s="183"/>
-      <c r="E29" s="191"/>
-      <c r="F29" s="183"/>
-      <c r="G29" s="192"/>
-      <c r="H29" s="182"/>
-      <c r="I29" s="183"/>
-      <c r="J29" s="192"/>
-      <c r="K29" s="183"/>
-      <c r="L29" s="193"/>
-      <c r="M29" s="182"/>
-      <c r="N29" s="183"/>
-      <c r="O29" s="193"/>
-      <c r="P29" s="182"/>
-      <c r="Q29" s="183"/>
+      <c r="A29" s="191"/>
+      <c r="B29" s="184"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="192"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="193"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="193"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="194"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="184"/>
+      <c r="O29" s="194"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -10412,23 +10460,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="190"/>
-      <c r="B30" s="183"/>
-      <c r="C30" s="191"/>
-      <c r="D30" s="183"/>
-      <c r="E30" s="191"/>
-      <c r="F30" s="183"/>
-      <c r="G30" s="192"/>
-      <c r="H30" s="182"/>
-      <c r="I30" s="183"/>
-      <c r="J30" s="192"/>
-      <c r="K30" s="183"/>
-      <c r="L30" s="193"/>
-      <c r="M30" s="182"/>
-      <c r="N30" s="183"/>
-      <c r="O30" s="193"/>
-      <c r="P30" s="182"/>
-      <c r="Q30" s="183"/>
+      <c r="A30" s="191"/>
+      <c r="B30" s="184"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="184"/>
+      <c r="E30" s="192"/>
+      <c r="F30" s="184"/>
+      <c r="G30" s="193"/>
+      <c r="H30" s="183"/>
+      <c r="I30" s="184"/>
+      <c r="J30" s="193"/>
+      <c r="K30" s="184"/>
+      <c r="L30" s="194"/>
+      <c r="M30" s="183"/>
+      <c r="N30" s="184"/>
+      <c r="O30" s="194"/>
+      <c r="P30" s="183"/>
+      <c r="Q30" s="184"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -10440,23 +10488,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="198"/>
-      <c r="B31" s="197"/>
-      <c r="C31" s="199"/>
-      <c r="D31" s="197"/>
-      <c r="E31" s="199"/>
-      <c r="F31" s="197"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="196"/>
-      <c r="I31" s="197"/>
-      <c r="J31" s="200"/>
-      <c r="K31" s="197"/>
-      <c r="L31" s="195"/>
-      <c r="M31" s="196"/>
-      <c r="N31" s="197"/>
-      <c r="O31" s="195"/>
-      <c r="P31" s="196"/>
-      <c r="Q31" s="197"/>
+      <c r="A31" s="199"/>
+      <c r="B31" s="198"/>
+      <c r="C31" s="200"/>
+      <c r="D31" s="198"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="198"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="197"/>
+      <c r="I31" s="198"/>
+      <c r="J31" s="201"/>
+      <c r="K31" s="198"/>
+      <c r="L31" s="196"/>
+      <c r="M31" s="197"/>
+      <c r="N31" s="198"/>
+      <c r="O31" s="196"/>
+      <c r="P31" s="197"/>
+      <c r="Q31" s="198"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11612,64 +11660,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="211" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="211"/>
+      <c r="C1" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="210"/>
-      <c r="C1" s="211" t="s">
+      <c r="D1" s="213"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="215" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="217"/>
+      <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="212"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="215"/>
-      <c r="M1" s="216"/>
-      <c r="N1" s="52" t="s">
+      <c r="O1" s="215" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="214"/>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="52" t="s">
+      <c r="R1" s="215" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="214" t="s">
+      <c r="S1" s="217"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="211"/>
+      <c r="B2" s="211"/>
+      <c r="C2" s="212" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="216"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="210"/>
-      <c r="B2" s="210"/>
-      <c r="C2" s="211" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="215" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="216"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="216"/>
+      <c r="J2" s="216"/>
+      <c r="K2" s="216"/>
+      <c r="L2" s="216"/>
+      <c r="M2" s="217"/>
+      <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214"/>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
-      <c r="M2" s="216"/>
-      <c r="N2" s="52" t="s">
+      <c r="O2" s="218">
+        <v>45818</v>
+      </c>
+      <c r="P2" s="219"/>
+      <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="O2" s="217"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="R2" s="219">
-        <v>44771</v>
-      </c>
-      <c r="S2" s="220"/>
+      <c r="R2" s="220" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="221"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11694,1046 +11750,1058 @@
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
       <c r="A4" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="C4" s="202" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="202" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="201" t="s">
+      <c r="I4" s="203"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="203"/>
+      <c r="L4" s="203"/>
+      <c r="M4" s="204"/>
+      <c r="N4" s="202" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="202"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="202"/>
-      <c r="L4" s="202"/>
-      <c r="M4" s="203"/>
-      <c r="N4" s="201" t="s">
+      <c r="O4" s="203"/>
+      <c r="P4" s="204"/>
+      <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="O4" s="202"/>
-      <c r="P4" s="203"/>
-      <c r="Q4" s="57" t="s">
+      <c r="R4" s="202" t="s">
         <v>87</v>
       </c>
-      <c r="R4" s="201" t="s">
-        <v>88</v>
-      </c>
-      <c r="S4" s="203"/>
+      <c r="S4" s="204"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
-      <c r="A5" s="59"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="204"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="204"/>
-      <c r="M5" s="204"/>
-      <c r="N5" s="205"/>
-      <c r="O5" s="206"/>
-      <c r="P5" s="207"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="208"/>
-      <c r="S5" s="209"/>
+      <c r="A5" s="59">
+        <v>1</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="205" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="205"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="205"/>
+      <c r="L5" s="205"/>
+      <c r="M5" s="205"/>
+      <c r="N5" s="206" t="s">
+        <v>107</v>
+      </c>
+      <c r="O5" s="207"/>
+      <c r="P5" s="208"/>
+      <c r="Q5" s="64">
+        <v>45818</v>
+      </c>
+      <c r="R5" s="209"/>
+      <c r="S5" s="210"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="221"/>
-      <c r="D6" s="221"/>
-      <c r="E6" s="221"/>
-      <c r="F6" s="221"/>
-      <c r="G6" s="221"/>
-      <c r="H6" s="221"/>
-      <c r="I6" s="221"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="221"/>
-      <c r="L6" s="221"/>
-      <c r="M6" s="221"/>
-      <c r="N6" s="226"/>
-      <c r="O6" s="227"/>
-      <c r="P6" s="228"/>
+      <c r="C6" s="222"/>
+      <c r="D6" s="222"/>
+      <c r="E6" s="222"/>
+      <c r="F6" s="222"/>
+      <c r="G6" s="222"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="222"/>
+      <c r="J6" s="222"/>
+      <c r="K6" s="222"/>
+      <c r="L6" s="222"/>
+      <c r="M6" s="222"/>
+      <c r="N6" s="227"/>
+      <c r="O6" s="228"/>
+      <c r="P6" s="229"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="225"/>
-      <c r="S6" s="225"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="226"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="221"/>
-      <c r="D7" s="221"/>
-      <c r="E7" s="221"/>
-      <c r="F7" s="221"/>
-      <c r="G7" s="221"/>
-      <c r="H7" s="221"/>
-      <c r="I7" s="221"/>
-      <c r="J7" s="221"/>
-      <c r="K7" s="221"/>
-      <c r="L7" s="221"/>
-      <c r="M7" s="221"/>
-      <c r="N7" s="222"/>
-      <c r="O7" s="223"/>
-      <c r="P7" s="224"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="222"/>
+      <c r="L7" s="222"/>
+      <c r="M7" s="222"/>
+      <c r="N7" s="223"/>
+      <c r="O7" s="224"/>
+      <c r="P7" s="225"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="225"/>
-      <c r="S7" s="225"/>
+      <c r="R7" s="226"/>
+      <c r="S7" s="226"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="221"/>
-      <c r="D8" s="221"/>
-      <c r="E8" s="221"/>
-      <c r="F8" s="221"/>
-      <c r="G8" s="221"/>
-      <c r="H8" s="221"/>
-      <c r="I8" s="221"/>
-      <c r="J8" s="221"/>
-      <c r="K8" s="221"/>
-      <c r="L8" s="221"/>
-      <c r="M8" s="221"/>
-      <c r="N8" s="222"/>
-      <c r="O8" s="223"/>
-      <c r="P8" s="224"/>
+      <c r="C8" s="222"/>
+      <c r="D8" s="222"/>
+      <c r="E8" s="222"/>
+      <c r="F8" s="222"/>
+      <c r="G8" s="222"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="222"/>
+      <c r="J8" s="222"/>
+      <c r="K8" s="222"/>
+      <c r="L8" s="222"/>
+      <c r="M8" s="222"/>
+      <c r="N8" s="223"/>
+      <c r="O8" s="224"/>
+      <c r="P8" s="225"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="225"/>
-      <c r="S8" s="225"/>
+      <c r="R8" s="226"/>
+      <c r="S8" s="226"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="221"/>
-      <c r="D9" s="221"/>
-      <c r="E9" s="221"/>
-      <c r="F9" s="221"/>
-      <c r="G9" s="221"/>
-      <c r="H9" s="221"/>
-      <c r="I9" s="221"/>
-      <c r="J9" s="221"/>
-      <c r="K9" s="221"/>
-      <c r="L9" s="221"/>
-      <c r="M9" s="221"/>
-      <c r="N9" s="222"/>
-      <c r="O9" s="223"/>
-      <c r="P9" s="224"/>
+      <c r="C9" s="222"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="222"/>
+      <c r="K9" s="222"/>
+      <c r="L9" s="222"/>
+      <c r="M9" s="222"/>
+      <c r="N9" s="223"/>
+      <c r="O9" s="224"/>
+      <c r="P9" s="225"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="225"/>
-      <c r="S9" s="225"/>
+      <c r="R9" s="226"/>
+      <c r="S9" s="226"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="221"/>
-      <c r="D10" s="221"/>
-      <c r="E10" s="221"/>
-      <c r="F10" s="221"/>
-      <c r="G10" s="221"/>
-      <c r="H10" s="229"/>
-      <c r="I10" s="230"/>
-      <c r="J10" s="230"/>
-      <c r="K10" s="230"/>
-      <c r="L10" s="230"/>
-      <c r="M10" s="231"/>
-      <c r="N10" s="222"/>
-      <c r="O10" s="223"/>
-      <c r="P10" s="224"/>
+      <c r="C10" s="222"/>
+      <c r="D10" s="222"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="222"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="231"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="231"/>
+      <c r="M10" s="232"/>
+      <c r="N10" s="223"/>
+      <c r="O10" s="224"/>
+      <c r="P10" s="225"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="225"/>
-      <c r="S10" s="225"/>
+      <c r="R10" s="226"/>
+      <c r="S10" s="226"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="221"/>
-      <c r="D11" s="221"/>
-      <c r="E11" s="221"/>
-      <c r="F11" s="221"/>
-      <c r="G11" s="221"/>
-      <c r="H11" s="229"/>
-      <c r="I11" s="230"/>
-      <c r="J11" s="230"/>
-      <c r="K11" s="230"/>
-      <c r="L11" s="230"/>
-      <c r="M11" s="231"/>
-      <c r="N11" s="222"/>
-      <c r="O11" s="223"/>
-      <c r="P11" s="224"/>
+      <c r="C11" s="222"/>
+      <c r="D11" s="222"/>
+      <c r="E11" s="222"/>
+      <c r="F11" s="222"/>
+      <c r="G11" s="222"/>
+      <c r="H11" s="230"/>
+      <c r="I11" s="231"/>
+      <c r="J11" s="231"/>
+      <c r="K11" s="231"/>
+      <c r="L11" s="231"/>
+      <c r="M11" s="232"/>
+      <c r="N11" s="223"/>
+      <c r="O11" s="224"/>
+      <c r="P11" s="225"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="225"/>
-      <c r="S11" s="225"/>
+      <c r="R11" s="226"/>
+      <c r="S11" s="226"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="221"/>
-      <c r="D12" s="221"/>
-      <c r="E12" s="221"/>
-      <c r="F12" s="221"/>
-      <c r="G12" s="221"/>
-      <c r="H12" s="229"/>
-      <c r="I12" s="230"/>
-      <c r="J12" s="230"/>
-      <c r="K12" s="230"/>
-      <c r="L12" s="230"/>
-      <c r="M12" s="231"/>
-      <c r="N12" s="222"/>
-      <c r="O12" s="223"/>
-      <c r="P12" s="224"/>
+      <c r="C12" s="222"/>
+      <c r="D12" s="222"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="230"/>
+      <c r="I12" s="231"/>
+      <c r="J12" s="231"/>
+      <c r="K12" s="231"/>
+      <c r="L12" s="231"/>
+      <c r="M12" s="232"/>
+      <c r="N12" s="223"/>
+      <c r="O12" s="224"/>
+      <c r="P12" s="225"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="225"/>
-      <c r="S12" s="225"/>
+      <c r="R12" s="226"/>
+      <c r="S12" s="226"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="221"/>
-      <c r="D13" s="221"/>
-      <c r="E13" s="221"/>
-      <c r="F13" s="221"/>
-      <c r="G13" s="221"/>
-      <c r="H13" s="229"/>
-      <c r="I13" s="230"/>
-      <c r="J13" s="230"/>
-      <c r="K13" s="230"/>
-      <c r="L13" s="230"/>
-      <c r="M13" s="231"/>
-      <c r="N13" s="222"/>
-      <c r="O13" s="223"/>
-      <c r="P13" s="224"/>
+      <c r="C13" s="222"/>
+      <c r="D13" s="222"/>
+      <c r="E13" s="222"/>
+      <c r="F13" s="222"/>
+      <c r="G13" s="222"/>
+      <c r="H13" s="230"/>
+      <c r="I13" s="231"/>
+      <c r="J13" s="231"/>
+      <c r="K13" s="231"/>
+      <c r="L13" s="231"/>
+      <c r="M13" s="232"/>
+      <c r="N13" s="223"/>
+      <c r="O13" s="224"/>
+      <c r="P13" s="225"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="225"/>
-      <c r="S13" s="225"/>
+      <c r="R13" s="226"/>
+      <c r="S13" s="226"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="221"/>
-      <c r="D14" s="221"/>
-      <c r="E14" s="221"/>
-      <c r="F14" s="221"/>
-      <c r="G14" s="221"/>
-      <c r="H14" s="229"/>
-      <c r="I14" s="230"/>
-      <c r="J14" s="230"/>
-      <c r="K14" s="230"/>
-      <c r="L14" s="230"/>
-      <c r="M14" s="231"/>
-      <c r="N14" s="222"/>
-      <c r="O14" s="223"/>
-      <c r="P14" s="224"/>
+      <c r="C14" s="222"/>
+      <c r="D14" s="222"/>
+      <c r="E14" s="222"/>
+      <c r="F14" s="222"/>
+      <c r="G14" s="222"/>
+      <c r="H14" s="230"/>
+      <c r="I14" s="231"/>
+      <c r="J14" s="231"/>
+      <c r="K14" s="231"/>
+      <c r="L14" s="231"/>
+      <c r="M14" s="232"/>
+      <c r="N14" s="223"/>
+      <c r="O14" s="224"/>
+      <c r="P14" s="225"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="225"/>
-      <c r="S14" s="225"/>
+      <c r="R14" s="226"/>
+      <c r="S14" s="226"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="221"/>
-      <c r="D15" s="221"/>
-      <c r="E15" s="221"/>
-      <c r="F15" s="221"/>
-      <c r="G15" s="221"/>
-      <c r="H15" s="229"/>
-      <c r="I15" s="230"/>
-      <c r="J15" s="230"/>
-      <c r="K15" s="230"/>
-      <c r="L15" s="230"/>
-      <c r="M15" s="231"/>
-      <c r="N15" s="222"/>
-      <c r="O15" s="223"/>
-      <c r="P15" s="224"/>
+      <c r="C15" s="222"/>
+      <c r="D15" s="222"/>
+      <c r="E15" s="222"/>
+      <c r="F15" s="222"/>
+      <c r="G15" s="222"/>
+      <c r="H15" s="230"/>
+      <c r="I15" s="231"/>
+      <c r="J15" s="231"/>
+      <c r="K15" s="231"/>
+      <c r="L15" s="231"/>
+      <c r="M15" s="232"/>
+      <c r="N15" s="223"/>
+      <c r="O15" s="224"/>
+      <c r="P15" s="225"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="225"/>
-      <c r="S15" s="225"/>
+      <c r="R15" s="226"/>
+      <c r="S15" s="226"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="221"/>
-      <c r="D16" s="221"/>
-      <c r="E16" s="221"/>
-      <c r="F16" s="221"/>
-      <c r="G16" s="221"/>
-      <c r="H16" s="229"/>
-      <c r="I16" s="230"/>
-      <c r="J16" s="230"/>
-      <c r="K16" s="230"/>
-      <c r="L16" s="230"/>
-      <c r="M16" s="231"/>
-      <c r="N16" s="222"/>
-      <c r="O16" s="223"/>
-      <c r="P16" s="224"/>
+      <c r="C16" s="222"/>
+      <c r="D16" s="222"/>
+      <c r="E16" s="222"/>
+      <c r="F16" s="222"/>
+      <c r="G16" s="222"/>
+      <c r="H16" s="230"/>
+      <c r="I16" s="231"/>
+      <c r="J16" s="231"/>
+      <c r="K16" s="231"/>
+      <c r="L16" s="231"/>
+      <c r="M16" s="232"/>
+      <c r="N16" s="223"/>
+      <c r="O16" s="224"/>
+      <c r="P16" s="225"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="225"/>
-      <c r="S16" s="225"/>
+      <c r="R16" s="226"/>
+      <c r="S16" s="226"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="221"/>
-      <c r="D17" s="221"/>
-      <c r="E17" s="221"/>
-      <c r="F17" s="221"/>
-      <c r="G17" s="221"/>
-      <c r="H17" s="229"/>
-      <c r="I17" s="230"/>
-      <c r="J17" s="230"/>
-      <c r="K17" s="230"/>
-      <c r="L17" s="230"/>
-      <c r="M17" s="231"/>
-      <c r="N17" s="222"/>
-      <c r="O17" s="223"/>
-      <c r="P17" s="224"/>
+      <c r="C17" s="222"/>
+      <c r="D17" s="222"/>
+      <c r="E17" s="222"/>
+      <c r="F17" s="222"/>
+      <c r="G17" s="222"/>
+      <c r="H17" s="230"/>
+      <c r="I17" s="231"/>
+      <c r="J17" s="231"/>
+      <c r="K17" s="231"/>
+      <c r="L17" s="231"/>
+      <c r="M17" s="232"/>
+      <c r="N17" s="223"/>
+      <c r="O17" s="224"/>
+      <c r="P17" s="225"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="225"/>
-      <c r="S17" s="225"/>
+      <c r="R17" s="226"/>
+      <c r="S17" s="226"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="221"/>
-      <c r="D18" s="221"/>
-      <c r="E18" s="221"/>
-      <c r="F18" s="221"/>
-      <c r="G18" s="221"/>
-      <c r="H18" s="229"/>
-      <c r="I18" s="230"/>
-      <c r="J18" s="230"/>
-      <c r="K18" s="230"/>
-      <c r="L18" s="230"/>
-      <c r="M18" s="231"/>
-      <c r="N18" s="222"/>
-      <c r="O18" s="223"/>
-      <c r="P18" s="224"/>
+      <c r="C18" s="222"/>
+      <c r="D18" s="222"/>
+      <c r="E18" s="222"/>
+      <c r="F18" s="222"/>
+      <c r="G18" s="222"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="231"/>
+      <c r="J18" s="231"/>
+      <c r="K18" s="231"/>
+      <c r="L18" s="231"/>
+      <c r="M18" s="232"/>
+      <c r="N18" s="223"/>
+      <c r="O18" s="224"/>
+      <c r="P18" s="225"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="225"/>
-      <c r="S18" s="225"/>
+      <c r="R18" s="226"/>
+      <c r="S18" s="226"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="221"/>
-      <c r="D19" s="221"/>
-      <c r="E19" s="221"/>
-      <c r="F19" s="221"/>
-      <c r="G19" s="221"/>
-      <c r="H19" s="229"/>
-      <c r="I19" s="230"/>
-      <c r="J19" s="230"/>
-      <c r="K19" s="230"/>
-      <c r="L19" s="230"/>
-      <c r="M19" s="231"/>
-      <c r="N19" s="222"/>
-      <c r="O19" s="223"/>
-      <c r="P19" s="224"/>
+      <c r="C19" s="222"/>
+      <c r="D19" s="222"/>
+      <c r="E19" s="222"/>
+      <c r="F19" s="222"/>
+      <c r="G19" s="222"/>
+      <c r="H19" s="230"/>
+      <c r="I19" s="231"/>
+      <c r="J19" s="231"/>
+      <c r="K19" s="231"/>
+      <c r="L19" s="231"/>
+      <c r="M19" s="232"/>
+      <c r="N19" s="223"/>
+      <c r="O19" s="224"/>
+      <c r="P19" s="225"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="225"/>
-      <c r="S19" s="225"/>
+      <c r="R19" s="226"/>
+      <c r="S19" s="226"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="221"/>
-      <c r="D20" s="221"/>
-      <c r="E20" s="221"/>
-      <c r="F20" s="221"/>
-      <c r="G20" s="221"/>
-      <c r="H20" s="229"/>
-      <c r="I20" s="230"/>
-      <c r="J20" s="230"/>
-      <c r="K20" s="230"/>
-      <c r="L20" s="230"/>
-      <c r="M20" s="231"/>
-      <c r="N20" s="222"/>
-      <c r="O20" s="223"/>
-      <c r="P20" s="224"/>
+      <c r="C20" s="222"/>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="222"/>
+      <c r="G20" s="222"/>
+      <c r="H20" s="230"/>
+      <c r="I20" s="231"/>
+      <c r="J20" s="231"/>
+      <c r="K20" s="231"/>
+      <c r="L20" s="231"/>
+      <c r="M20" s="232"/>
+      <c r="N20" s="223"/>
+      <c r="O20" s="224"/>
+      <c r="P20" s="225"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="225"/>
-      <c r="S20" s="225"/>
+      <c r="R20" s="226"/>
+      <c r="S20" s="226"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="221"/>
-      <c r="D21" s="221"/>
-      <c r="E21" s="221"/>
-      <c r="F21" s="221"/>
-      <c r="G21" s="221"/>
-      <c r="H21" s="229"/>
-      <c r="I21" s="230"/>
-      <c r="J21" s="230"/>
-      <c r="K21" s="230"/>
-      <c r="L21" s="230"/>
-      <c r="M21" s="231"/>
-      <c r="N21" s="222"/>
-      <c r="O21" s="223"/>
-      <c r="P21" s="224"/>
+      <c r="C21" s="222"/>
+      <c r="D21" s="222"/>
+      <c r="E21" s="222"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="230"/>
+      <c r="I21" s="231"/>
+      <c r="J21" s="231"/>
+      <c r="K21" s="231"/>
+      <c r="L21" s="231"/>
+      <c r="M21" s="232"/>
+      <c r="N21" s="223"/>
+      <c r="O21" s="224"/>
+      <c r="P21" s="225"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="225"/>
-      <c r="S21" s="225"/>
+      <c r="R21" s="226"/>
+      <c r="S21" s="226"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="221"/>
-      <c r="D22" s="221"/>
-      <c r="E22" s="221"/>
-      <c r="F22" s="221"/>
-      <c r="G22" s="221"/>
-      <c r="H22" s="229"/>
-      <c r="I22" s="230"/>
-      <c r="J22" s="230"/>
-      <c r="K22" s="230"/>
-      <c r="L22" s="230"/>
-      <c r="M22" s="231"/>
-      <c r="N22" s="222"/>
-      <c r="O22" s="223"/>
-      <c r="P22" s="224"/>
+      <c r="C22" s="222"/>
+      <c r="D22" s="222"/>
+      <c r="E22" s="222"/>
+      <c r="F22" s="222"/>
+      <c r="G22" s="222"/>
+      <c r="H22" s="230"/>
+      <c r="I22" s="231"/>
+      <c r="J22" s="231"/>
+      <c r="K22" s="231"/>
+      <c r="L22" s="231"/>
+      <c r="M22" s="232"/>
+      <c r="N22" s="223"/>
+      <c r="O22" s="224"/>
+      <c r="P22" s="225"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="225"/>
-      <c r="S22" s="225"/>
+      <c r="R22" s="226"/>
+      <c r="S22" s="226"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="221"/>
-      <c r="D23" s="221"/>
-      <c r="E23" s="221"/>
-      <c r="F23" s="221"/>
-      <c r="G23" s="221"/>
-      <c r="H23" s="229"/>
-      <c r="I23" s="230"/>
-      <c r="J23" s="230"/>
-      <c r="K23" s="230"/>
-      <c r="L23" s="230"/>
-      <c r="M23" s="231"/>
-      <c r="N23" s="222"/>
-      <c r="O23" s="223"/>
-      <c r="P23" s="224"/>
+      <c r="C23" s="222"/>
+      <c r="D23" s="222"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="222"/>
+      <c r="G23" s="222"/>
+      <c r="H23" s="230"/>
+      <c r="I23" s="231"/>
+      <c r="J23" s="231"/>
+      <c r="K23" s="231"/>
+      <c r="L23" s="231"/>
+      <c r="M23" s="232"/>
+      <c r="N23" s="223"/>
+      <c r="O23" s="224"/>
+      <c r="P23" s="225"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="225"/>
-      <c r="S23" s="225"/>
+      <c r="R23" s="226"/>
+      <c r="S23" s="226"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="221"/>
-      <c r="D24" s="221"/>
-      <c r="E24" s="221"/>
-      <c r="F24" s="221"/>
-      <c r="G24" s="221"/>
-      <c r="H24" s="229"/>
-      <c r="I24" s="230"/>
-      <c r="J24" s="230"/>
-      <c r="K24" s="230"/>
-      <c r="L24" s="230"/>
-      <c r="M24" s="231"/>
-      <c r="N24" s="222"/>
-      <c r="O24" s="223"/>
-      <c r="P24" s="224"/>
+      <c r="C24" s="222"/>
+      <c r="D24" s="222"/>
+      <c r="E24" s="222"/>
+      <c r="F24" s="222"/>
+      <c r="G24" s="222"/>
+      <c r="H24" s="230"/>
+      <c r="I24" s="231"/>
+      <c r="J24" s="231"/>
+      <c r="K24" s="231"/>
+      <c r="L24" s="231"/>
+      <c r="M24" s="232"/>
+      <c r="N24" s="223"/>
+      <c r="O24" s="224"/>
+      <c r="P24" s="225"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="225"/>
-      <c r="S24" s="225"/>
+      <c r="R24" s="226"/>
+      <c r="S24" s="226"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="221"/>
-      <c r="D25" s="221"/>
-      <c r="E25" s="221"/>
-      <c r="F25" s="221"/>
-      <c r="G25" s="221"/>
-      <c r="H25" s="229"/>
-      <c r="I25" s="230"/>
-      <c r="J25" s="230"/>
-      <c r="K25" s="230"/>
-      <c r="L25" s="230"/>
-      <c r="M25" s="231"/>
-      <c r="N25" s="222"/>
-      <c r="O25" s="223"/>
-      <c r="P25" s="224"/>
+      <c r="C25" s="222"/>
+      <c r="D25" s="222"/>
+      <c r="E25" s="222"/>
+      <c r="F25" s="222"/>
+      <c r="G25" s="222"/>
+      <c r="H25" s="230"/>
+      <c r="I25" s="231"/>
+      <c r="J25" s="231"/>
+      <c r="K25" s="231"/>
+      <c r="L25" s="231"/>
+      <c r="M25" s="232"/>
+      <c r="N25" s="223"/>
+      <c r="O25" s="224"/>
+      <c r="P25" s="225"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="225"/>
-      <c r="S25" s="225"/>
+      <c r="R25" s="226"/>
+      <c r="S25" s="226"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="221"/>
-      <c r="D26" s="221"/>
-      <c r="E26" s="221"/>
-      <c r="F26" s="221"/>
-      <c r="G26" s="221"/>
-      <c r="H26" s="229"/>
-      <c r="I26" s="230"/>
-      <c r="J26" s="230"/>
-      <c r="K26" s="230"/>
-      <c r="L26" s="230"/>
-      <c r="M26" s="231"/>
-      <c r="N26" s="222"/>
-      <c r="O26" s="223"/>
-      <c r="P26" s="224"/>
+      <c r="C26" s="222"/>
+      <c r="D26" s="222"/>
+      <c r="E26" s="222"/>
+      <c r="F26" s="222"/>
+      <c r="G26" s="222"/>
+      <c r="H26" s="230"/>
+      <c r="I26" s="231"/>
+      <c r="J26" s="231"/>
+      <c r="K26" s="231"/>
+      <c r="L26" s="231"/>
+      <c r="M26" s="232"/>
+      <c r="N26" s="223"/>
+      <c r="O26" s="224"/>
+      <c r="P26" s="225"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="225"/>
-      <c r="S26" s="225"/>
+      <c r="R26" s="226"/>
+      <c r="S26" s="226"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="221"/>
-      <c r="D27" s="221"/>
-      <c r="E27" s="221"/>
-      <c r="F27" s="221"/>
-      <c r="G27" s="221"/>
-      <c r="H27" s="229"/>
-      <c r="I27" s="230"/>
-      <c r="J27" s="230"/>
-      <c r="K27" s="230"/>
-      <c r="L27" s="230"/>
-      <c r="M27" s="231"/>
-      <c r="N27" s="222"/>
-      <c r="O27" s="223"/>
-      <c r="P27" s="224"/>
+      <c r="C27" s="222"/>
+      <c r="D27" s="222"/>
+      <c r="E27" s="222"/>
+      <c r="F27" s="222"/>
+      <c r="G27" s="222"/>
+      <c r="H27" s="230"/>
+      <c r="I27" s="231"/>
+      <c r="J27" s="231"/>
+      <c r="K27" s="231"/>
+      <c r="L27" s="231"/>
+      <c r="M27" s="232"/>
+      <c r="N27" s="223"/>
+      <c r="O27" s="224"/>
+      <c r="P27" s="225"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="225"/>
-      <c r="S27" s="225"/>
+      <c r="R27" s="226"/>
+      <c r="S27" s="226"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="221"/>
-      <c r="D28" s="221"/>
-      <c r="E28" s="221"/>
-      <c r="F28" s="221"/>
-      <c r="G28" s="221"/>
-      <c r="H28" s="229"/>
-      <c r="I28" s="230"/>
-      <c r="J28" s="230"/>
-      <c r="K28" s="230"/>
-      <c r="L28" s="230"/>
-      <c r="M28" s="231"/>
-      <c r="N28" s="222"/>
-      <c r="O28" s="223"/>
-      <c r="P28" s="224"/>
+      <c r="C28" s="222"/>
+      <c r="D28" s="222"/>
+      <c r="E28" s="222"/>
+      <c r="F28" s="222"/>
+      <c r="G28" s="222"/>
+      <c r="H28" s="230"/>
+      <c r="I28" s="231"/>
+      <c r="J28" s="231"/>
+      <c r="K28" s="231"/>
+      <c r="L28" s="231"/>
+      <c r="M28" s="232"/>
+      <c r="N28" s="223"/>
+      <c r="O28" s="224"/>
+      <c r="P28" s="225"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="225"/>
-      <c r="S28" s="225"/>
+      <c r="R28" s="226"/>
+      <c r="S28" s="226"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="221"/>
-      <c r="D29" s="221"/>
-      <c r="E29" s="221"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="221"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="230"/>
-      <c r="J29" s="230"/>
-      <c r="K29" s="230"/>
-      <c r="L29" s="230"/>
-      <c r="M29" s="231"/>
-      <c r="N29" s="222"/>
-      <c r="O29" s="223"/>
-      <c r="P29" s="224"/>
+      <c r="C29" s="222"/>
+      <c r="D29" s="222"/>
+      <c r="E29" s="222"/>
+      <c r="F29" s="222"/>
+      <c r="G29" s="222"/>
+      <c r="H29" s="230"/>
+      <c r="I29" s="231"/>
+      <c r="J29" s="231"/>
+      <c r="K29" s="231"/>
+      <c r="L29" s="231"/>
+      <c r="M29" s="232"/>
+      <c r="N29" s="223"/>
+      <c r="O29" s="224"/>
+      <c r="P29" s="225"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="225"/>
-      <c r="S29" s="225"/>
+      <c r="R29" s="226"/>
+      <c r="S29" s="226"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="221"/>
-      <c r="D30" s="221"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="221"/>
-      <c r="G30" s="221"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="230"/>
-      <c r="J30" s="230"/>
-      <c r="K30" s="230"/>
-      <c r="L30" s="230"/>
-      <c r="M30" s="231"/>
-      <c r="N30" s="222"/>
-      <c r="O30" s="223"/>
-      <c r="P30" s="224"/>
+      <c r="C30" s="222"/>
+      <c r="D30" s="222"/>
+      <c r="E30" s="222"/>
+      <c r="F30" s="222"/>
+      <c r="G30" s="222"/>
+      <c r="H30" s="230"/>
+      <c r="I30" s="231"/>
+      <c r="J30" s="231"/>
+      <c r="K30" s="231"/>
+      <c r="L30" s="231"/>
+      <c r="M30" s="232"/>
+      <c r="N30" s="223"/>
+      <c r="O30" s="224"/>
+      <c r="P30" s="225"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="225"/>
-      <c r="S30" s="225"/>
+      <c r="R30" s="226"/>
+      <c r="S30" s="226"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="221"/>
-      <c r="D31" s="221"/>
-      <c r="E31" s="221"/>
-      <c r="F31" s="221"/>
-      <c r="G31" s="221"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="230"/>
-      <c r="J31" s="230"/>
-      <c r="K31" s="230"/>
-      <c r="L31" s="230"/>
-      <c r="M31" s="231"/>
-      <c r="N31" s="222"/>
-      <c r="O31" s="223"/>
-      <c r="P31" s="224"/>
+      <c r="C31" s="222"/>
+      <c r="D31" s="222"/>
+      <c r="E31" s="222"/>
+      <c r="F31" s="222"/>
+      <c r="G31" s="222"/>
+      <c r="H31" s="230"/>
+      <c r="I31" s="231"/>
+      <c r="J31" s="231"/>
+      <c r="K31" s="231"/>
+      <c r="L31" s="231"/>
+      <c r="M31" s="232"/>
+      <c r="N31" s="223"/>
+      <c r="O31" s="224"/>
+      <c r="P31" s="225"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="225"/>
-      <c r="S31" s="225"/>
+      <c r="R31" s="226"/>
+      <c r="S31" s="226"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="221"/>
-      <c r="D32" s="221"/>
-      <c r="E32" s="221"/>
-      <c r="F32" s="221"/>
-      <c r="G32" s="221"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="230"/>
-      <c r="J32" s="230"/>
-      <c r="K32" s="230"/>
-      <c r="L32" s="230"/>
-      <c r="M32" s="231"/>
-      <c r="N32" s="222"/>
-      <c r="O32" s="223"/>
-      <c r="P32" s="224"/>
+      <c r="C32" s="222"/>
+      <c r="D32" s="222"/>
+      <c r="E32" s="222"/>
+      <c r="F32" s="222"/>
+      <c r="G32" s="222"/>
+      <c r="H32" s="230"/>
+      <c r="I32" s="231"/>
+      <c r="J32" s="231"/>
+      <c r="K32" s="231"/>
+      <c r="L32" s="231"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="223"/>
+      <c r="O32" s="224"/>
+      <c r="P32" s="225"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="225"/>
-      <c r="S32" s="225"/>
+      <c r="R32" s="226"/>
+      <c r="S32" s="226"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="221"/>
-      <c r="D33" s="221"/>
-      <c r="E33" s="221"/>
-      <c r="F33" s="221"/>
-      <c r="G33" s="221"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="230"/>
-      <c r="J33" s="230"/>
-      <c r="K33" s="230"/>
-      <c r="L33" s="230"/>
-      <c r="M33" s="231"/>
-      <c r="N33" s="222"/>
-      <c r="O33" s="223"/>
-      <c r="P33" s="224"/>
+      <c r="C33" s="222"/>
+      <c r="D33" s="222"/>
+      <c r="E33" s="222"/>
+      <c r="F33" s="222"/>
+      <c r="G33" s="222"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="231"/>
+      <c r="J33" s="231"/>
+      <c r="K33" s="231"/>
+      <c r="L33" s="231"/>
+      <c r="M33" s="232"/>
+      <c r="N33" s="223"/>
+      <c r="O33" s="224"/>
+      <c r="P33" s="225"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="225"/>
-      <c r="S33" s="225"/>
+      <c r="R33" s="226"/>
+      <c r="S33" s="226"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="221"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="221"/>
-      <c r="F34" s="221"/>
-      <c r="G34" s="221"/>
-      <c r="H34" s="229"/>
-      <c r="I34" s="230"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="230"/>
-      <c r="L34" s="230"/>
-      <c r="M34" s="231"/>
-      <c r="N34" s="222"/>
-      <c r="O34" s="223"/>
-      <c r="P34" s="224"/>
+      <c r="C34" s="222"/>
+      <c r="D34" s="222"/>
+      <c r="E34" s="222"/>
+      <c r="F34" s="222"/>
+      <c r="G34" s="222"/>
+      <c r="H34" s="230"/>
+      <c r="I34" s="231"/>
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="232"/>
+      <c r="N34" s="223"/>
+      <c r="O34" s="224"/>
+      <c r="P34" s="225"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="225"/>
-      <c r="S34" s="225"/>
+      <c r="R34" s="226"/>
+      <c r="S34" s="226"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="221"/>
-      <c r="D35" s="221"/>
-      <c r="E35" s="221"/>
-      <c r="F35" s="221"/>
-      <c r="G35" s="221"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="230"/>
-      <c r="J35" s="230"/>
-      <c r="K35" s="230"/>
-      <c r="L35" s="230"/>
-      <c r="M35" s="231"/>
-      <c r="N35" s="222"/>
-      <c r="O35" s="223"/>
-      <c r="P35" s="224"/>
+      <c r="C35" s="222"/>
+      <c r="D35" s="222"/>
+      <c r="E35" s="222"/>
+      <c r="F35" s="222"/>
+      <c r="G35" s="222"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="231"/>
+      <c r="J35" s="231"/>
+      <c r="K35" s="231"/>
+      <c r="L35" s="231"/>
+      <c r="M35" s="232"/>
+      <c r="N35" s="223"/>
+      <c r="O35" s="224"/>
+      <c r="P35" s="225"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="225"/>
-      <c r="S35" s="225"/>
+      <c r="R35" s="226"/>
+      <c r="S35" s="226"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="221"/>
-      <c r="D36" s="221"/>
-      <c r="E36" s="221"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="221"/>
-      <c r="H36" s="229"/>
-      <c r="I36" s="230"/>
-      <c r="J36" s="230"/>
-      <c r="K36" s="230"/>
-      <c r="L36" s="230"/>
-      <c r="M36" s="231"/>
-      <c r="N36" s="222"/>
-      <c r="O36" s="223"/>
-      <c r="P36" s="224"/>
+      <c r="C36" s="222"/>
+      <c r="D36" s="222"/>
+      <c r="E36" s="222"/>
+      <c r="F36" s="222"/>
+      <c r="G36" s="222"/>
+      <c r="H36" s="230"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="231"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="232"/>
+      <c r="N36" s="223"/>
+      <c r="O36" s="224"/>
+      <c r="P36" s="225"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="225"/>
-      <c r="S36" s="225"/>
+      <c r="R36" s="226"/>
+      <c r="S36" s="226"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="221"/>
-      <c r="D37" s="221"/>
-      <c r="E37" s="221"/>
-      <c r="F37" s="221"/>
-      <c r="G37" s="221"/>
-      <c r="H37" s="229"/>
-      <c r="I37" s="230"/>
-      <c r="J37" s="230"/>
-      <c r="K37" s="230"/>
-      <c r="L37" s="230"/>
-      <c r="M37" s="231"/>
-      <c r="N37" s="222"/>
-      <c r="O37" s="223"/>
-      <c r="P37" s="224"/>
+      <c r="C37" s="222"/>
+      <c r="D37" s="222"/>
+      <c r="E37" s="222"/>
+      <c r="F37" s="222"/>
+      <c r="G37" s="222"/>
+      <c r="H37" s="230"/>
+      <c r="I37" s="231"/>
+      <c r="J37" s="231"/>
+      <c r="K37" s="231"/>
+      <c r="L37" s="231"/>
+      <c r="M37" s="232"/>
+      <c r="N37" s="223"/>
+      <c r="O37" s="224"/>
+      <c r="P37" s="225"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="225"/>
-      <c r="S37" s="225"/>
+      <c r="R37" s="226"/>
+      <c r="S37" s="226"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="221"/>
-      <c r="D38" s="221"/>
-      <c r="E38" s="221"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="221"/>
-      <c r="H38" s="229"/>
-      <c r="I38" s="230"/>
-      <c r="J38" s="230"/>
-      <c r="K38" s="230"/>
-      <c r="L38" s="230"/>
-      <c r="M38" s="231"/>
-      <c r="N38" s="222"/>
-      <c r="O38" s="223"/>
-      <c r="P38" s="224"/>
+      <c r="C38" s="222"/>
+      <c r="D38" s="222"/>
+      <c r="E38" s="222"/>
+      <c r="F38" s="222"/>
+      <c r="G38" s="222"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="231"/>
+      <c r="J38" s="231"/>
+      <c r="K38" s="231"/>
+      <c r="L38" s="231"/>
+      <c r="M38" s="232"/>
+      <c r="N38" s="223"/>
+      <c r="O38" s="224"/>
+      <c r="P38" s="225"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="225"/>
-      <c r="S38" s="225"/>
+      <c r="R38" s="226"/>
+      <c r="S38" s="226"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="221"/>
-      <c r="D39" s="221"/>
-      <c r="E39" s="221"/>
-      <c r="F39" s="221"/>
-      <c r="G39" s="221"/>
-      <c r="H39" s="229"/>
-      <c r="I39" s="230"/>
-      <c r="J39" s="230"/>
-      <c r="K39" s="230"/>
-      <c r="L39" s="230"/>
-      <c r="M39" s="231"/>
-      <c r="N39" s="222"/>
-      <c r="O39" s="223"/>
-      <c r="P39" s="224"/>
+      <c r="C39" s="222"/>
+      <c r="D39" s="222"/>
+      <c r="E39" s="222"/>
+      <c r="F39" s="222"/>
+      <c r="G39" s="222"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="232"/>
+      <c r="N39" s="223"/>
+      <c r="O39" s="224"/>
+      <c r="P39" s="225"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="225"/>
-      <c r="S39" s="225"/>
+      <c r="R39" s="226"/>
+      <c r="S39" s="226"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="221"/>
-      <c r="D40" s="221"/>
-      <c r="E40" s="221"/>
-      <c r="F40" s="221"/>
-      <c r="G40" s="221"/>
-      <c r="H40" s="229"/>
-      <c r="I40" s="230"/>
-      <c r="J40" s="230"/>
-      <c r="K40" s="230"/>
-      <c r="L40" s="230"/>
-      <c r="M40" s="231"/>
-      <c r="N40" s="222"/>
-      <c r="O40" s="223"/>
-      <c r="P40" s="224"/>
+      <c r="C40" s="222"/>
+      <c r="D40" s="222"/>
+      <c r="E40" s="222"/>
+      <c r="F40" s="222"/>
+      <c r="G40" s="222"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="223"/>
+      <c r="O40" s="224"/>
+      <c r="P40" s="225"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="225"/>
-      <c r="S40" s="225"/>
+      <c r="R40" s="226"/>
+      <c r="S40" s="226"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="221"/>
-      <c r="D41" s="221"/>
-      <c r="E41" s="221"/>
-      <c r="F41" s="221"/>
-      <c r="G41" s="221"/>
-      <c r="H41" s="229"/>
-      <c r="I41" s="230"/>
-      <c r="J41" s="230"/>
-      <c r="K41" s="230"/>
-      <c r="L41" s="230"/>
-      <c r="M41" s="231"/>
-      <c r="N41" s="222"/>
-      <c r="O41" s="223"/>
-      <c r="P41" s="224"/>
+      <c r="C41" s="222"/>
+      <c r="D41" s="222"/>
+      <c r="E41" s="222"/>
+      <c r="F41" s="222"/>
+      <c r="G41" s="222"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="231"/>
+      <c r="J41" s="231"/>
+      <c r="K41" s="231"/>
+      <c r="L41" s="231"/>
+      <c r="M41" s="232"/>
+      <c r="N41" s="223"/>
+      <c r="O41" s="224"/>
+      <c r="P41" s="225"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="225"/>
-      <c r="S41" s="225"/>
+      <c r="R41" s="226"/>
+      <c r="S41" s="226"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="221"/>
-      <c r="D42" s="221"/>
-      <c r="E42" s="221"/>
-      <c r="F42" s="221"/>
-      <c r="G42" s="221"/>
-      <c r="H42" s="229"/>
-      <c r="I42" s="230"/>
-      <c r="J42" s="230"/>
-      <c r="K42" s="230"/>
-      <c r="L42" s="230"/>
-      <c r="M42" s="231"/>
-      <c r="N42" s="222"/>
-      <c r="O42" s="223"/>
-      <c r="P42" s="224"/>
+      <c r="C42" s="222"/>
+      <c r="D42" s="222"/>
+      <c r="E42" s="222"/>
+      <c r="F42" s="222"/>
+      <c r="G42" s="222"/>
+      <c r="H42" s="230"/>
+      <c r="I42" s="231"/>
+      <c r="J42" s="231"/>
+      <c r="K42" s="231"/>
+      <c r="L42" s="231"/>
+      <c r="M42" s="232"/>
+      <c r="N42" s="223"/>
+      <c r="O42" s="224"/>
+      <c r="P42" s="225"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="225"/>
-      <c r="S42" s="225"/>
+      <c r="R42" s="226"/>
+      <c r="S42" s="226"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="221"/>
-      <c r="D43" s="221"/>
-      <c r="E43" s="221"/>
-      <c r="F43" s="221"/>
-      <c r="G43" s="221"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="230"/>
-      <c r="J43" s="230"/>
-      <c r="K43" s="230"/>
-      <c r="L43" s="230"/>
-      <c r="M43" s="231"/>
-      <c r="N43" s="222"/>
-      <c r="O43" s="223"/>
-      <c r="P43" s="224"/>
+      <c r="C43" s="222"/>
+      <c r="D43" s="222"/>
+      <c r="E43" s="222"/>
+      <c r="F43" s="222"/>
+      <c r="G43" s="222"/>
+      <c r="H43" s="230"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="231"/>
+      <c r="L43" s="231"/>
+      <c r="M43" s="232"/>
+      <c r="N43" s="223"/>
+      <c r="O43" s="224"/>
+      <c r="P43" s="225"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="225"/>
-      <c r="S43" s="225"/>
+      <c r="R43" s="226"/>
+      <c r="S43" s="226"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="221"/>
-      <c r="D44" s="221"/>
-      <c r="E44" s="221"/>
-      <c r="F44" s="221"/>
-      <c r="G44" s="221"/>
-      <c r="H44" s="229"/>
-      <c r="I44" s="230"/>
-      <c r="J44" s="230"/>
-      <c r="K44" s="230"/>
-      <c r="L44" s="230"/>
-      <c r="M44" s="231"/>
-      <c r="N44" s="222"/>
-      <c r="O44" s="223"/>
-      <c r="P44" s="224"/>
+      <c r="C44" s="222"/>
+      <c r="D44" s="222"/>
+      <c r="E44" s="222"/>
+      <c r="F44" s="222"/>
+      <c r="G44" s="222"/>
+      <c r="H44" s="230"/>
+      <c r="I44" s="231"/>
+      <c r="J44" s="231"/>
+      <c r="K44" s="231"/>
+      <c r="L44" s="231"/>
+      <c r="M44" s="232"/>
+      <c r="N44" s="223"/>
+      <c r="O44" s="224"/>
+      <c r="P44" s="225"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="225"/>
-      <c r="S44" s="225"/>
+      <c r="R44" s="226"/>
+      <c r="S44" s="226"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="221"/>
-      <c r="D45" s="221"/>
-      <c r="E45" s="221"/>
-      <c r="F45" s="221"/>
-      <c r="G45" s="221"/>
-      <c r="H45" s="229"/>
-      <c r="I45" s="230"/>
-      <c r="J45" s="230"/>
-      <c r="K45" s="230"/>
-      <c r="L45" s="230"/>
-      <c r="M45" s="231"/>
-      <c r="N45" s="222"/>
-      <c r="O45" s="223"/>
-      <c r="P45" s="224"/>
+      <c r="C45" s="222"/>
+      <c r="D45" s="222"/>
+      <c r="E45" s="222"/>
+      <c r="F45" s="222"/>
+      <c r="G45" s="222"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="231"/>
+      <c r="J45" s="231"/>
+      <c r="K45" s="231"/>
+      <c r="L45" s="231"/>
+      <c r="M45" s="232"/>
+      <c r="N45" s="223"/>
+      <c r="O45" s="224"/>
+      <c r="P45" s="225"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="225"/>
-      <c r="S45" s="225"/>
+      <c r="R45" s="226"/>
+      <c r="S45" s="226"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="221"/>
-      <c r="D46" s="221"/>
-      <c r="E46" s="221"/>
-      <c r="F46" s="221"/>
-      <c r="G46" s="221"/>
-      <c r="H46" s="229"/>
-      <c r="I46" s="230"/>
-      <c r="J46" s="230"/>
-      <c r="K46" s="230"/>
-      <c r="L46" s="230"/>
-      <c r="M46" s="231"/>
-      <c r="N46" s="222"/>
-      <c r="O46" s="223"/>
-      <c r="P46" s="224"/>
+      <c r="C46" s="222"/>
+      <c r="D46" s="222"/>
+      <c r="E46" s="222"/>
+      <c r="F46" s="222"/>
+      <c r="G46" s="222"/>
+      <c r="H46" s="230"/>
+      <c r="I46" s="231"/>
+      <c r="J46" s="231"/>
+      <c r="K46" s="231"/>
+      <c r="L46" s="231"/>
+      <c r="M46" s="232"/>
+      <c r="N46" s="223"/>
+      <c r="O46" s="224"/>
+      <c r="P46" s="225"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="225"/>
-      <c r="S46" s="225"/>
+      <c r="R46" s="226"/>
+      <c r="S46" s="226"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="221"/>
-      <c r="D47" s="221"/>
-      <c r="E47" s="221"/>
-      <c r="F47" s="221"/>
-      <c r="G47" s="221"/>
-      <c r="H47" s="229"/>
-      <c r="I47" s="230"/>
-      <c r="J47" s="230"/>
-      <c r="K47" s="230"/>
-      <c r="L47" s="230"/>
-      <c r="M47" s="231"/>
-      <c r="N47" s="222"/>
-      <c r="O47" s="223"/>
-      <c r="P47" s="224"/>
+      <c r="C47" s="222"/>
+      <c r="D47" s="222"/>
+      <c r="E47" s="222"/>
+      <c r="F47" s="222"/>
+      <c r="G47" s="222"/>
+      <c r="H47" s="230"/>
+      <c r="I47" s="231"/>
+      <c r="J47" s="231"/>
+      <c r="K47" s="231"/>
+      <c r="L47" s="231"/>
+      <c r="M47" s="232"/>
+      <c r="N47" s="223"/>
+      <c r="O47" s="224"/>
+      <c r="P47" s="225"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="225"/>
-      <c r="S47" s="225"/>
+      <c r="R47" s="226"/>
+      <c r="S47" s="226"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="230"/>
-      <c r="L48" s="230"/>
-      <c r="M48" s="231"/>
-      <c r="N48" s="222"/>
-      <c r="O48" s="223"/>
-      <c r="P48" s="224"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="231"/>
+      <c r="L48" s="231"/>
+      <c r="M48" s="232"/>
+      <c r="N48" s="223"/>
+      <c r="O48" s="224"/>
+      <c r="P48" s="225"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="225"/>
-      <c r="S48" s="225"/>
+      <c r="R48" s="226"/>
+      <c r="S48" s="226"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="221"/>
-      <c r="D49" s="221"/>
-      <c r="E49" s="221"/>
-      <c r="F49" s="221"/>
-      <c r="G49" s="221"/>
-      <c r="H49" s="229"/>
-      <c r="I49" s="230"/>
-      <c r="J49" s="230"/>
-      <c r="K49" s="230"/>
-      <c r="L49" s="230"/>
-      <c r="M49" s="231"/>
-      <c r="N49" s="222"/>
-      <c r="O49" s="223"/>
-      <c r="P49" s="224"/>
+      <c r="C49" s="222"/>
+      <c r="D49" s="222"/>
+      <c r="E49" s="222"/>
+      <c r="F49" s="222"/>
+      <c r="G49" s="222"/>
+      <c r="H49" s="230"/>
+      <c r="I49" s="231"/>
+      <c r="J49" s="231"/>
+      <c r="K49" s="231"/>
+      <c r="L49" s="231"/>
+      <c r="M49" s="232"/>
+      <c r="N49" s="223"/>
+      <c r="O49" s="224"/>
+      <c r="P49" s="225"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="225"/>
-      <c r="S49" s="225"/>
+      <c r="R49" s="226"/>
+      <c r="S49" s="226"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="221"/>
-      <c r="D50" s="221"/>
-      <c r="E50" s="221"/>
-      <c r="F50" s="221"/>
-      <c r="G50" s="221"/>
-      <c r="H50" s="229"/>
-      <c r="I50" s="230"/>
-      <c r="J50" s="230"/>
-      <c r="K50" s="230"/>
-      <c r="L50" s="230"/>
-      <c r="M50" s="231"/>
-      <c r="N50" s="222"/>
-      <c r="O50" s="223"/>
-      <c r="P50" s="224"/>
+      <c r="C50" s="222"/>
+      <c r="D50" s="222"/>
+      <c r="E50" s="222"/>
+      <c r="F50" s="222"/>
+      <c r="G50" s="222"/>
+      <c r="H50" s="230"/>
+      <c r="I50" s="231"/>
+      <c r="J50" s="231"/>
+      <c r="K50" s="231"/>
+      <c r="L50" s="231"/>
+      <c r="M50" s="232"/>
+      <c r="N50" s="223"/>
+      <c r="O50" s="224"/>
+      <c r="P50" s="225"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="225"/>
-      <c r="S50" s="225"/>
+      <c r="R50" s="226"/>
+      <c r="S50" s="226"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="221"/>
-      <c r="D51" s="221"/>
-      <c r="E51" s="221"/>
-      <c r="F51" s="221"/>
-      <c r="G51" s="221"/>
-      <c r="H51" s="229"/>
-      <c r="I51" s="230"/>
-      <c r="J51" s="230"/>
-      <c r="K51" s="230"/>
-      <c r="L51" s="230"/>
-      <c r="M51" s="231"/>
-      <c r="N51" s="222"/>
-      <c r="O51" s="223"/>
-      <c r="P51" s="224"/>
+      <c r="C51" s="222"/>
+      <c r="D51" s="222"/>
+      <c r="E51" s="222"/>
+      <c r="F51" s="222"/>
+      <c r="G51" s="222"/>
+      <c r="H51" s="230"/>
+      <c r="I51" s="231"/>
+      <c r="J51" s="231"/>
+      <c r="K51" s="231"/>
+      <c r="L51" s="231"/>
+      <c r="M51" s="232"/>
+      <c r="N51" s="223"/>
+      <c r="O51" s="224"/>
+      <c r="P51" s="225"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="225"/>
-      <c r="S51" s="225"/>
+      <c r="R51" s="226"/>
+      <c r="S51" s="226"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="221"/>
-      <c r="D52" s="221"/>
-      <c r="E52" s="221"/>
-      <c r="F52" s="221"/>
-      <c r="G52" s="221"/>
-      <c r="H52" s="229"/>
-      <c r="I52" s="230"/>
-      <c r="J52" s="230"/>
-      <c r="K52" s="230"/>
-      <c r="L52" s="230"/>
-      <c r="M52" s="231"/>
-      <c r="N52" s="222"/>
-      <c r="O52" s="223"/>
-      <c r="P52" s="224"/>
+      <c r="C52" s="222"/>
+      <c r="D52" s="222"/>
+      <c r="E52" s="222"/>
+      <c r="F52" s="222"/>
+      <c r="G52" s="222"/>
+      <c r="H52" s="230"/>
+      <c r="I52" s="231"/>
+      <c r="J52" s="231"/>
+      <c r="K52" s="231"/>
+      <c r="L52" s="231"/>
+      <c r="M52" s="232"/>
+      <c r="N52" s="223"/>
+      <c r="O52" s="224"/>
+      <c r="P52" s="225"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="225"/>
-      <c r="S52" s="225"/>
+      <c r="R52" s="226"/>
+      <c r="S52" s="226"/>
     </row>
   </sheetData>
   <mergeCells count="205">

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Desktop\プロ演最新\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49171F1E-DE71-492B-817D-15DB6F90474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49139972-3587-46B5-B4C4-BB3D536F34B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7470" yWindow="705" windowWidth="11475" windowHeight="9180" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="108">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -688,10 +688,6 @@
     <rPh sb="5" eb="6">
       <t>アタイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>〇</t>
     <phoneticPr fontId="7"/>
   </si>
 </sst>
@@ -1881,6 +1877,9 @@
     <xf numFmtId="56" fontId="15" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="10" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1905,6 +1904,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1938,21 +1982,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1998,36 +2027,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2091,51 +2090,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2211,6 +2210,51 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2232,15 +2276,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2256,40 +2291,37 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2351,42 +2383,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="10" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2938,85 +2934,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3036,46 +3032,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="65" t="s">
+      <c r="H13" s="68"/>
+      <c r="I13" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="66"/>
-      <c r="K13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="65"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="67"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="65"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="67"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3084,13 +3080,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4105,19 +4101,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="98" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="98" t="s">
+      <c r="E1" s="97"/>
+      <c r="F1" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="97"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4129,190 +4125,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="99" t="s">
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="99" t="s">
+      <c r="E2" s="111"/>
+      <c r="F2" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="103">
+      <c r="G2" s="111"/>
+      <c r="H2" s="114">
         <v>45805</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="93"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="82" t="s">
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="83"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="99"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="87" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="88"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="87" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="88"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="85"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="87" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="88"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="87" customHeight="1">
-      <c r="A9" s="110" t="s">
+      <c r="A9" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="104" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="88"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="113" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="88"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="86"/>
-      <c r="D11" s="104" t="s">
+      <c r="C11" s="76"/>
+      <c r="D11" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="88"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="78"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="85"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="104" t="s">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="88"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="105" t="s">
+      <c r="A13" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="109"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5303,6 +5299,18 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5318,18 +5326,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5348,19 +5344,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="123"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="130"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="131"/>
+      <c r="F1" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="130"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5372,48 +5368,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="125"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131" t="s">
+      <c r="E2" s="133"/>
+      <c r="F2" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="114">
+      <c r="G2" s="133"/>
+      <c r="H2" s="115">
         <v>45807</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="118"/>
+      <c r="J2" s="119"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="119"/>
+      <c r="A3" s="125"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="120"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="120"/>
+      <c r="A4" s="127"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6773,19 +6769,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="123"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="130"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="131"/>
+      <c r="F1" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="130"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6797,78 +6793,78 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="125"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131" t="s">
+      <c r="E2" s="133"/>
+      <c r="F2" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="114">
+      <c r="G2" s="133"/>
+      <c r="H2" s="115">
         <v>45810</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="118"/>
+      <c r="J2" s="119"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="119"/>
+      <c r="A3" s="125"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="120"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="124"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="119"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="138" t="s">
+      <c r="A5" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="144" t="s">
+      <c r="B5" s="137"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="139"/>
-      <c r="I5" s="139"/>
-      <c r="J5" s="145"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="143" t="s">
+      <c r="A6" s="141" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="136"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="145"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="146"/>
@@ -6883,104 +6879,104 @@
       <c r="J7" s="148"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="124"/>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
+      <c r="A8" s="125"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
       <c r="J8" s="149"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="124"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
+      <c r="A9" s="125"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
       <c r="J9" s="149"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="124"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
+      <c r="A10" s="125"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
       <c r="J10" s="149"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="124"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
+      <c r="A11" s="125"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
       <c r="J11" s="149"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="124"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
+      <c r="A12" s="125"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
       <c r="J12" s="149"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="124"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
+      <c r="A13" s="125"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
       <c r="J13" s="149"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="143" t="s">
+      <c r="A14" s="141" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="136"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="145"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="143" t="s">
+      <c r="A15" s="141" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="135" t="s">
+      <c r="B15" s="67"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="68"/>
       <c r="I15" s="13" t="s">
         <v>16</v>
       </c>
@@ -6989,11 +6985,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="143" t="s">
+      <c r="A16" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="67"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="68"/>
       <c r="D16" s="13" t="s">
         <v>18</v>
       </c>
@@ -7006,18 +7002,18 @@
       <c r="G16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="150" t="s">
+      <c r="H16" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="66"/>
-      <c r="J16" s="136"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="145"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="137">
+      <c r="A17" s="142">
         <v>1</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="68"/>
       <c r="D17" s="15" t="s">
         <v>62</v>
       </c>
@@ -7028,81 +7024,81 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="135"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="136"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="145"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="137"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="67"/>
+      <c r="A18" s="142"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="68"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="136"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="145"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="137"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
+      <c r="A19" s="142"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="68"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="136"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="145"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="137"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="67"/>
+      <c r="A20" s="142"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="68"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="136"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="145"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="137"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
+      <c r="A21" s="142"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="68"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="136"/>
+      <c r="H21" s="150"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="145"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="137"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="67"/>
+      <c r="A22" s="142"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="68"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="136"/>
+      <c r="H22" s="150"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="145"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="140"/>
-      <c r="B23" s="141"/>
-      <c r="C23" s="142"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="151"/>
-      <c r="I23" s="141"/>
-      <c r="J23" s="152"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="139"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8083,11 +8079,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8104,16 +8105,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8134,19 +8130,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="168" t="s">
+      <c r="B1" s="161"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="169"/>
-      <c r="F1" s="168" t="s">
+      <c r="E1" s="170"/>
+      <c r="F1" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="169"/>
+      <c r="G1" s="170"/>
       <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
@@ -8158,48 +8154,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="162"/>
-      <c r="B2" s="163"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="170" t="s">
+      <c r="A2" s="163"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="171"/>
-      <c r="F2" s="170" t="s">
+      <c r="E2" s="172"/>
+      <c r="F2" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="174">
+      <c r="G2" s="172"/>
+      <c r="H2" s="175">
         <v>45810</v>
       </c>
-      <c r="I2" s="153" t="s">
+      <c r="I2" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="156"/>
+      <c r="J2" s="157"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="162"/>
-      <c r="B3" s="163"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="157"/>
+      <c r="A3" s="163"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="158"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="165"/>
-      <c r="B4" s="166"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="158"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="168"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="159"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="26"/>
@@ -9548,141 +9544,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="168" t="s">
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="168" t="s">
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="168" t="s">
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="168" t="s">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="169"/>
-      <c r="S1" s="168" t="s">
+      <c r="R1" s="170"/>
+      <c r="S1" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="181"/>
+      <c r="T1" s="197"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="162"/>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="170" t="s">
+      <c r="A2" s="163"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="188"/>
-      <c r="I2" s="188"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="170" t="s">
+      <c r="H2" s="201"/>
+      <c r="I2" s="201"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="188"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="171"/>
-      <c r="O2" s="189">
+      <c r="L2" s="201"/>
+      <c r="M2" s="201"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="202">
         <v>45817</v>
       </c>
-      <c r="P2" s="171"/>
-      <c r="Q2" s="170" t="s">
+      <c r="P2" s="172"/>
+      <c r="Q2" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="171"/>
-      <c r="S2" s="170"/>
-      <c r="T2" s="175"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="171"/>
+      <c r="T2" s="191"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="162"/>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="172"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="172"/>
-      <c r="P3" s="164"/>
-      <c r="Q3" s="172"/>
-      <c r="R3" s="164"/>
-      <c r="S3" s="172"/>
-      <c r="T3" s="176"/>
+      <c r="A3" s="163"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="173"/>
+      <c r="L3" s="164"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="165"/>
+      <c r="O3" s="173"/>
+      <c r="P3" s="165"/>
+      <c r="Q3" s="173"/>
+      <c r="R3" s="165"/>
+      <c r="S3" s="173"/>
+      <c r="T3" s="192"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="165"/>
-      <c r="B4" s="166"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="166"/>
-      <c r="M4" s="166"/>
-      <c r="N4" s="167"/>
-      <c r="O4" s="173"/>
-      <c r="P4" s="167"/>
-      <c r="Q4" s="173"/>
-      <c r="R4" s="167"/>
-      <c r="S4" s="173"/>
-      <c r="T4" s="177"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+      <c r="J4" s="168"/>
+      <c r="K4" s="174"/>
+      <c r="L4" s="167"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="168"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="168"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="168"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="193"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="178" t="s">
+      <c r="A5" s="194" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="179"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="180" t="s">
+      <c r="B5" s="195"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="196" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="179"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
-      <c r="L5" s="179"/>
-      <c r="M5" s="179"/>
-      <c r="N5" s="179"/>
-      <c r="O5" s="179"/>
-      <c r="P5" s="179"/>
-      <c r="Q5" s="179"/>
-      <c r="R5" s="179"/>
-      <c r="S5" s="179"/>
-      <c r="T5" s="181"/>
+      <c r="H5" s="195"/>
+      <c r="I5" s="195"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="195"/>
+      <c r="L5" s="195"/>
+      <c r="M5" s="195"/>
+      <c r="N5" s="195"/>
+      <c r="O5" s="195"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="195"/>
+      <c r="T5" s="197"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="189" t="s">
         <v>42</v>
       </c>
       <c r="B6" s="183"/>
@@ -9690,7 +9686,7 @@
       <c r="D6" s="183"/>
       <c r="E6" s="183"/>
       <c r="F6" s="184"/>
-      <c r="G6" s="185" t="s">
+      <c r="G6" s="198" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="183"/>
@@ -9705,10 +9701,10 @@
       <c r="Q6" s="183"/>
       <c r="R6" s="183"/>
       <c r="S6" s="183"/>
-      <c r="T6" s="186"/>
+      <c r="T6" s="199"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="189" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="183"/>
@@ -9716,7 +9712,7 @@
       <c r="D7" s="183"/>
       <c r="E7" s="183"/>
       <c r="F7" s="184"/>
-      <c r="G7" s="185" t="s">
+      <c r="G7" s="198" t="s">
         <v>72</v>
       </c>
       <c r="H7" s="183"/>
@@ -9731,7 +9727,7 @@
       <c r="Q7" s="183"/>
       <c r="R7" s="183"/>
       <c r="S7" s="183"/>
-      <c r="T7" s="186"/>
+      <c r="T7" s="199"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9930,33 +9926,33 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="182" t="s">
+      <c r="A15" s="189" t="s">
         <v>50</v>
       </c>
       <c r="B15" s="184"/>
-      <c r="C15" s="195" t="s">
+      <c r="C15" s="190" t="s">
         <v>44</v>
       </c>
       <c r="D15" s="184"/>
-      <c r="E15" s="190" t="s">
+      <c r="E15" s="188" t="s">
         <v>51</v>
       </c>
       <c r="F15" s="184"/>
-      <c r="G15" s="190" t="s">
+      <c r="G15" s="188" t="s">
         <v>52</v>
       </c>
       <c r="H15" s="183"/>
       <c r="I15" s="184"/>
-      <c r="J15" s="190" t="s">
+      <c r="J15" s="188" t="s">
         <v>53</v>
       </c>
       <c r="K15" s="184"/>
-      <c r="L15" s="190" t="s">
+      <c r="L15" s="188" t="s">
         <v>54</v>
       </c>
       <c r="M15" s="183"/>
       <c r="N15" s="184"/>
-      <c r="O15" s="190" t="s">
+      <c r="O15" s="188" t="s">
         <v>55</v>
       </c>
       <c r="P15" s="183"/>
@@ -9972,46 +9968,40 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="191">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
       <c r="B16" s="184"/>
-      <c r="C16" s="192" t="s">
+      <c r="C16" s="186" t="s">
         <v>59</v>
       </c>
       <c r="D16" s="184"/>
-      <c r="E16" s="192" t="s">
+      <c r="E16" s="186" t="s">
         <v>60</v>
       </c>
       <c r="F16" s="184"/>
-      <c r="G16" s="193" t="s">
+      <c r="G16" s="187" t="s">
         <v>88</v>
       </c>
       <c r="H16" s="183"/>
       <c r="I16" s="184"/>
-      <c r="J16" s="193" t="s">
+      <c r="J16" s="187" t="s">
         <v>91</v>
       </c>
       <c r="K16" s="184"/>
-      <c r="L16" s="194" t="s">
+      <c r="L16" s="182" t="s">
         <v>89</v>
       </c>
       <c r="M16" s="183"/>
       <c r="N16" s="184"/>
-      <c r="O16" s="194" t="s">
+      <c r="O16" s="182" t="s">
         <v>90</v>
       </c>
       <c r="P16" s="183"/>
       <c r="Q16" s="184"/>
-      <c r="R16" s="233">
-        <v>45818</v>
-      </c>
-      <c r="S16" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="T16" s="47" t="s">
-        <v>108</v>
-      </c>
+      <c r="R16" s="65"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="47"/>
       <c r="U16" s="48"/>
       <c r="V16" s="48"/>
       <c r="W16" s="48"/>
@@ -10020,46 +10010,40 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="191">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
       <c r="B17" s="184"/>
-      <c r="C17" s="192" t="s">
+      <c r="C17" s="186" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="184"/>
-      <c r="E17" s="192" t="s">
+      <c r="E17" s="186" t="s">
         <v>60</v>
       </c>
       <c r="F17" s="184"/>
-      <c r="G17" s="193" t="s">
+      <c r="G17" s="187" t="s">
         <v>97</v>
       </c>
       <c r="H17" s="183"/>
       <c r="I17" s="184"/>
-      <c r="J17" s="193" t="s">
+      <c r="J17" s="187" t="s">
         <v>91</v>
       </c>
       <c r="K17" s="184"/>
-      <c r="L17" s="194" t="s">
+      <c r="L17" s="182" t="s">
         <v>89</v>
       </c>
       <c r="M17" s="183"/>
       <c r="N17" s="184"/>
-      <c r="O17" s="194" t="s">
+      <c r="O17" s="182" t="s">
         <v>98</v>
       </c>
       <c r="P17" s="183"/>
       <c r="Q17" s="184"/>
-      <c r="R17" s="233">
-        <v>45818</v>
-      </c>
-      <c r="S17" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="T17" s="47" t="s">
-        <v>108</v>
-      </c>
+      <c r="R17" s="65"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="47"/>
       <c r="U17" s="48"/>
       <c r="V17" s="48"/>
       <c r="W17" s="48"/>
@@ -10068,33 +10052,33 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="191">
+      <c r="A18" s="185">
         <v>3</v>
       </c>
       <c r="B18" s="184"/>
-      <c r="C18" s="192" t="s">
+      <c r="C18" s="186" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="184"/>
-      <c r="E18" s="192" t="s">
+      <c r="E18" s="186" t="s">
         <v>61</v>
       </c>
       <c r="F18" s="184"/>
-      <c r="G18" s="193" t="s">
+      <c r="G18" s="187" t="s">
         <v>92</v>
       </c>
       <c r="H18" s="183"/>
       <c r="I18" s="184"/>
-      <c r="J18" s="193" t="s">
+      <c r="J18" s="187" t="s">
         <v>91</v>
       </c>
       <c r="K18" s="184"/>
-      <c r="L18" s="194" t="s">
+      <c r="L18" s="182" t="s">
         <v>89</v>
       </c>
       <c r="M18" s="183"/>
       <c r="N18" s="184"/>
-      <c r="O18" s="194" t="s">
+      <c r="O18" s="182" t="s">
         <v>93</v>
       </c>
       <c r="P18" s="183"/>
@@ -10110,33 +10094,33 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A19" s="191">
+      <c r="A19" s="185">
         <v>4</v>
       </c>
       <c r="B19" s="184"/>
-      <c r="C19" s="192" t="s">
+      <c r="C19" s="186" t="s">
         <v>59</v>
       </c>
       <c r="D19" s="184"/>
-      <c r="E19" s="192" t="s">
+      <c r="E19" s="186" t="s">
         <v>94</v>
       </c>
       <c r="F19" s="184"/>
-      <c r="G19" s="193" t="s">
+      <c r="G19" s="187" t="s">
         <v>96</v>
       </c>
       <c r="H19" s="183"/>
       <c r="I19" s="184"/>
-      <c r="J19" s="193" t="s">
+      <c r="J19" s="187" t="s">
         <v>91</v>
       </c>
       <c r="K19" s="184"/>
-      <c r="L19" s="194" t="s">
+      <c r="L19" s="182" t="s">
         <v>89</v>
       </c>
       <c r="M19" s="183"/>
       <c r="N19" s="184"/>
-      <c r="O19" s="194" t="s">
+      <c r="O19" s="182" t="s">
         <v>95</v>
       </c>
       <c r="P19" s="183"/>
@@ -10152,33 +10136,33 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A20" s="191">
+      <c r="A20" s="185">
         <v>5</v>
       </c>
       <c r="B20" s="184"/>
-      <c r="C20" s="192" t="s">
+      <c r="C20" s="186" t="s">
         <v>59</v>
       </c>
       <c r="D20" s="184"/>
-      <c r="E20" s="192" t="s">
+      <c r="E20" s="186" t="s">
         <v>94</v>
       </c>
       <c r="F20" s="184"/>
-      <c r="G20" s="193" t="s">
+      <c r="G20" s="187" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="183"/>
       <c r="I20" s="184"/>
-      <c r="J20" s="193" t="s">
+      <c r="J20" s="187" t="s">
         <v>91</v>
       </c>
       <c r="K20" s="184"/>
-      <c r="L20" s="194" t="s">
+      <c r="L20" s="182" t="s">
         <v>89</v>
       </c>
       <c r="M20" s="183"/>
       <c r="N20" s="184"/>
-      <c r="O20" s="194" t="s">
+      <c r="O20" s="182" t="s">
         <v>99</v>
       </c>
       <c r="P20" s="183"/>
@@ -10194,33 +10178,33 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A21" s="191">
+      <c r="A21" s="185">
         <v>6</v>
       </c>
       <c r="B21" s="184"/>
-      <c r="C21" s="192" t="s">
+      <c r="C21" s="186" t="s">
         <v>59</v>
       </c>
       <c r="D21" s="184"/>
-      <c r="E21" s="192" t="s">
+      <c r="E21" s="186" t="s">
         <v>94</v>
       </c>
       <c r="F21" s="184"/>
-      <c r="G21" s="193" t="s">
+      <c r="G21" s="187" t="s">
         <v>101</v>
       </c>
       <c r="H21" s="183"/>
       <c r="I21" s="184"/>
-      <c r="J21" s="193" t="s">
+      <c r="J21" s="187" t="s">
         <v>91</v>
       </c>
       <c r="K21" s="184"/>
-      <c r="L21" s="194" t="s">
+      <c r="L21" s="182" t="s">
         <v>89</v>
       </c>
       <c r="M21" s="183"/>
       <c r="N21" s="184"/>
-      <c r="O21" s="194" t="s">
+      <c r="O21" s="182" t="s">
         <v>102</v>
       </c>
       <c r="P21" s="183"/>
@@ -10236,21 +10220,21 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A22" s="191"/>
+      <c r="A22" s="185"/>
       <c r="B22" s="184"/>
-      <c r="C22" s="192"/>
+      <c r="C22" s="186"/>
       <c r="D22" s="184"/>
-      <c r="E22" s="192"/>
+      <c r="E22" s="186"/>
       <c r="F22" s="184"/>
-      <c r="G22" s="193"/>
+      <c r="G22" s="187"/>
       <c r="H22" s="183"/>
       <c r="I22" s="184"/>
-      <c r="J22" s="193"/>
+      <c r="J22" s="187"/>
       <c r="K22" s="184"/>
-      <c r="L22" s="194"/>
+      <c r="L22" s="182"/>
       <c r="M22" s="183"/>
       <c r="N22" s="184"/>
-      <c r="O22" s="194"/>
+      <c r="O22" s="182"/>
       <c r="P22" s="183"/>
       <c r="Q22" s="184"/>
       <c r="R22" s="46"/>
@@ -10264,21 +10248,21 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="191"/>
+      <c r="A23" s="185"/>
       <c r="B23" s="184"/>
-      <c r="C23" s="192"/>
+      <c r="C23" s="186"/>
       <c r="D23" s="184"/>
-      <c r="E23" s="192"/>
+      <c r="E23" s="186"/>
       <c r="F23" s="184"/>
-      <c r="G23" s="193"/>
+      <c r="G23" s="187"/>
       <c r="H23" s="183"/>
       <c r="I23" s="184"/>
-      <c r="J23" s="193"/>
+      <c r="J23" s="187"/>
       <c r="K23" s="184"/>
-      <c r="L23" s="194"/>
+      <c r="L23" s="182"/>
       <c r="M23" s="183"/>
       <c r="N23" s="184"/>
-      <c r="O23" s="194"/>
+      <c r="O23" s="182"/>
       <c r="P23" s="183"/>
       <c r="Q23" s="184"/>
       <c r="R23" s="46"/>
@@ -10292,21 +10276,21 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="191"/>
+      <c r="A24" s="185"/>
       <c r="B24" s="184"/>
-      <c r="C24" s="192"/>
+      <c r="C24" s="186"/>
       <c r="D24" s="184"/>
-      <c r="E24" s="192"/>
+      <c r="E24" s="186"/>
       <c r="F24" s="184"/>
-      <c r="G24" s="193"/>
+      <c r="G24" s="187"/>
       <c r="H24" s="183"/>
       <c r="I24" s="184"/>
-      <c r="J24" s="193"/>
+      <c r="J24" s="187"/>
       <c r="K24" s="184"/>
-      <c r="L24" s="194"/>
+      <c r="L24" s="182"/>
       <c r="M24" s="183"/>
       <c r="N24" s="184"/>
-      <c r="O24" s="194"/>
+      <c r="O24" s="182"/>
       <c r="P24" s="183"/>
       <c r="Q24" s="184"/>
       <c r="R24" s="46"/>
@@ -10320,21 +10304,21 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="191"/>
+      <c r="A25" s="185"/>
       <c r="B25" s="184"/>
-      <c r="C25" s="192"/>
+      <c r="C25" s="186"/>
       <c r="D25" s="184"/>
-      <c r="E25" s="192"/>
+      <c r="E25" s="186"/>
       <c r="F25" s="184"/>
-      <c r="G25" s="193"/>
+      <c r="G25" s="187"/>
       <c r="H25" s="183"/>
       <c r="I25" s="184"/>
-      <c r="J25" s="193"/>
+      <c r="J25" s="187"/>
       <c r="K25" s="184"/>
-      <c r="L25" s="194"/>
+      <c r="L25" s="182"/>
       <c r="M25" s="183"/>
       <c r="N25" s="184"/>
-      <c r="O25" s="194"/>
+      <c r="O25" s="182"/>
       <c r="P25" s="183"/>
       <c r="Q25" s="184"/>
       <c r="R25" s="46"/>
@@ -10348,21 +10332,21 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="191"/>
+      <c r="A26" s="185"/>
       <c r="B26" s="184"/>
-      <c r="C26" s="192"/>
+      <c r="C26" s="186"/>
       <c r="D26" s="184"/>
-      <c r="E26" s="192"/>
+      <c r="E26" s="186"/>
       <c r="F26" s="184"/>
-      <c r="G26" s="193"/>
+      <c r="G26" s="187"/>
       <c r="H26" s="183"/>
       <c r="I26" s="184"/>
-      <c r="J26" s="193"/>
+      <c r="J26" s="187"/>
       <c r="K26" s="184"/>
-      <c r="L26" s="194"/>
+      <c r="L26" s="182"/>
       <c r="M26" s="183"/>
       <c r="N26" s="184"/>
-      <c r="O26" s="194"/>
+      <c r="O26" s="182"/>
       <c r="P26" s="183"/>
       <c r="Q26" s="184"/>
       <c r="R26" s="46"/>
@@ -10376,21 +10360,21 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="191"/>
+      <c r="A27" s="185"/>
       <c r="B27" s="184"/>
-      <c r="C27" s="192"/>
+      <c r="C27" s="186"/>
       <c r="D27" s="184"/>
-      <c r="E27" s="192"/>
+      <c r="E27" s="186"/>
       <c r="F27" s="184"/>
-      <c r="G27" s="193"/>
+      <c r="G27" s="187"/>
       <c r="H27" s="183"/>
       <c r="I27" s="184"/>
-      <c r="J27" s="193"/>
+      <c r="J27" s="187"/>
       <c r="K27" s="184"/>
-      <c r="L27" s="194"/>
+      <c r="L27" s="182"/>
       <c r="M27" s="183"/>
       <c r="N27" s="184"/>
-      <c r="O27" s="194"/>
+      <c r="O27" s="182"/>
       <c r="P27" s="183"/>
       <c r="Q27" s="184"/>
       <c r="R27" s="46"/>
@@ -10404,21 +10388,21 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="191"/>
+      <c r="A28" s="185"/>
       <c r="B28" s="184"/>
-      <c r="C28" s="192"/>
+      <c r="C28" s="186"/>
       <c r="D28" s="184"/>
-      <c r="E28" s="192"/>
+      <c r="E28" s="186"/>
       <c r="F28" s="184"/>
-      <c r="G28" s="193"/>
+      <c r="G28" s="187"/>
       <c r="H28" s="183"/>
       <c r="I28" s="184"/>
-      <c r="J28" s="193"/>
+      <c r="J28" s="187"/>
       <c r="K28" s="184"/>
-      <c r="L28" s="194"/>
+      <c r="L28" s="182"/>
       <c r="M28" s="183"/>
       <c r="N28" s="184"/>
-      <c r="O28" s="194"/>
+      <c r="O28" s="182"/>
       <c r="P28" s="183"/>
       <c r="Q28" s="184"/>
       <c r="R28" s="46"/>
@@ -10432,21 +10416,21 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="191"/>
+      <c r="A29" s="185"/>
       <c r="B29" s="184"/>
-      <c r="C29" s="192"/>
+      <c r="C29" s="186"/>
       <c r="D29" s="184"/>
-      <c r="E29" s="192"/>
+      <c r="E29" s="186"/>
       <c r="F29" s="184"/>
-      <c r="G29" s="193"/>
+      <c r="G29" s="187"/>
       <c r="H29" s="183"/>
       <c r="I29" s="184"/>
-      <c r="J29" s="193"/>
+      <c r="J29" s="187"/>
       <c r="K29" s="184"/>
-      <c r="L29" s="194"/>
+      <c r="L29" s="182"/>
       <c r="M29" s="183"/>
       <c r="N29" s="184"/>
-      <c r="O29" s="194"/>
+      <c r="O29" s="182"/>
       <c r="P29" s="183"/>
       <c r="Q29" s="184"/>
       <c r="R29" s="46"/>
@@ -10460,21 +10444,21 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="191"/>
+      <c r="A30" s="185"/>
       <c r="B30" s="184"/>
-      <c r="C30" s="192"/>
+      <c r="C30" s="186"/>
       <c r="D30" s="184"/>
-      <c r="E30" s="192"/>
+      <c r="E30" s="186"/>
       <c r="F30" s="184"/>
-      <c r="G30" s="193"/>
+      <c r="G30" s="187"/>
       <c r="H30" s="183"/>
       <c r="I30" s="184"/>
-      <c r="J30" s="193"/>
+      <c r="J30" s="187"/>
       <c r="K30" s="184"/>
-      <c r="L30" s="194"/>
+      <c r="L30" s="182"/>
       <c r="M30" s="183"/>
       <c r="N30" s="184"/>
-      <c r="O30" s="194"/>
+      <c r="O30" s="182"/>
       <c r="P30" s="183"/>
       <c r="Q30" s="184"/>
       <c r="R30" s="46"/>
@@ -10488,23 +10472,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="199"/>
-      <c r="B31" s="198"/>
-      <c r="C31" s="200"/>
-      <c r="D31" s="198"/>
-      <c r="E31" s="200"/>
-      <c r="F31" s="198"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="197"/>
-      <c r="I31" s="198"/>
-      <c r="J31" s="201"/>
-      <c r="K31" s="198"/>
-      <c r="L31" s="196"/>
-      <c r="M31" s="197"/>
-      <c r="N31" s="198"/>
-      <c r="O31" s="196"/>
-      <c r="P31" s="197"/>
-      <c r="Q31" s="198"/>
+      <c r="A31" s="179"/>
+      <c r="B31" s="178"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="178"/>
+      <c r="E31" s="180"/>
+      <c r="F31" s="178"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="176"/>
+      <c r="M31" s="177"/>
+      <c r="N31" s="178"/>
+      <c r="O31" s="176"/>
+      <c r="P31" s="177"/>
+      <c r="Q31" s="178"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11502,6 +11486,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -11523,121 +11622,6 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11660,72 +11644,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="223" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="212" t="s">
+      <c r="B1" s="223"/>
+      <c r="C1" s="224" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="213"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="215" t="s">
+      <c r="D1" s="225"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="227" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="216"/>
-      <c r="J1" s="216"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="216"/>
-      <c r="M1" s="217"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="229"/>
       <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="215" t="s">
+      <c r="O1" s="227" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="217"/>
+      <c r="P1" s="229"/>
       <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="215" t="s">
+      <c r="R1" s="227" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="217"/>
+      <c r="S1" s="229"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="211"/>
-      <c r="B2" s="211"/>
-      <c r="C2" s="212" t="s">
+      <c r="A2" s="223"/>
+      <c r="B2" s="223"/>
+      <c r="C2" s="224" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="D2" s="225"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="227" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="216"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="216"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="216"/>
-      <c r="M2" s="217"/>
+      <c r="G2" s="228"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="228"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
+      <c r="M2" s="229"/>
       <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="218">
+      <c r="O2" s="230">
         <v>45818</v>
       </c>
-      <c r="P2" s="219"/>
+      <c r="P2" s="231"/>
       <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="220" t="s">
+      <c r="R2" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="221"/>
+      <c r="S2" s="233"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11755,33 +11739,33 @@
       <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="202" t="s">
+      <c r="C4" s="214" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="203"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204"/>
-      <c r="H4" s="202" t="s">
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="203"/>
-      <c r="J4" s="203"/>
-      <c r="K4" s="203"/>
-      <c r="L4" s="203"/>
-      <c r="M4" s="204"/>
-      <c r="N4" s="202" t="s">
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
+      <c r="L4" s="215"/>
+      <c r="M4" s="216"/>
+      <c r="N4" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="203"/>
-      <c r="P4" s="204"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="216"/>
       <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="202" t="s">
+      <c r="R4" s="214" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="204"/>
+      <c r="S4" s="216"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59">
@@ -11790,1209 +11774,1021 @@
       <c r="B5" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="205" t="s">
+      <c r="C5" s="217" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205" t="s">
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="217" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="205"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="205"/>
-      <c r="L5" s="205"/>
-      <c r="M5" s="205"/>
-      <c r="N5" s="206" t="s">
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="217"/>
+      <c r="M5" s="217"/>
+      <c r="N5" s="218" t="s">
         <v>107</v>
       </c>
-      <c r="O5" s="207"/>
-      <c r="P5" s="208"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="220"/>
       <c r="Q5" s="64">
         <v>45818</v>
       </c>
-      <c r="R5" s="209"/>
-      <c r="S5" s="210"/>
+      <c r="R5" s="221"/>
+      <c r="S5" s="222"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="222"/>
-      <c r="D6" s="222"/>
-      <c r="E6" s="222"/>
-      <c r="F6" s="222"/>
-      <c r="G6" s="222"/>
-      <c r="H6" s="222"/>
-      <c r="I6" s="222"/>
-      <c r="J6" s="222"/>
-      <c r="K6" s="222"/>
-      <c r="L6" s="222"/>
-      <c r="M6" s="222"/>
-      <c r="N6" s="227"/>
-      <c r="O6" s="228"/>
-      <c r="P6" s="229"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="203"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
+      <c r="G6" s="203"/>
+      <c r="H6" s="203"/>
+      <c r="I6" s="203"/>
+      <c r="J6" s="203"/>
+      <c r="K6" s="203"/>
+      <c r="L6" s="203"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="211"/>
+      <c r="O6" s="212"/>
+      <c r="P6" s="213"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="226"/>
+      <c r="R6" s="210"/>
+      <c r="S6" s="210"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="222"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="222"/>
-      <c r="H7" s="222"/>
-      <c r="I7" s="222"/>
-      <c r="J7" s="222"/>
-      <c r="K7" s="222"/>
-      <c r="L7" s="222"/>
-      <c r="M7" s="222"/>
-      <c r="N7" s="223"/>
-      <c r="O7" s="224"/>
-      <c r="P7" s="225"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="203"/>
+      <c r="F7" s="203"/>
+      <c r="G7" s="203"/>
+      <c r="H7" s="203"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="203"/>
+      <c r="K7" s="203"/>
+      <c r="L7" s="203"/>
+      <c r="M7" s="203"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="208"/>
+      <c r="P7" s="209"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="226"/>
-      <c r="S7" s="226"/>
+      <c r="R7" s="210"/>
+      <c r="S7" s="210"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="222"/>
-      <c r="D8" s="222"/>
-      <c r="E8" s="222"/>
-      <c r="F8" s="222"/>
-      <c r="G8" s="222"/>
-      <c r="H8" s="222"/>
-      <c r="I8" s="222"/>
-      <c r="J8" s="222"/>
-      <c r="K8" s="222"/>
-      <c r="L8" s="222"/>
-      <c r="M8" s="222"/>
-      <c r="N8" s="223"/>
-      <c r="O8" s="224"/>
-      <c r="P8" s="225"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="203"/>
+      <c r="H8" s="203"/>
+      <c r="I8" s="203"/>
+      <c r="J8" s="203"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="203"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="208"/>
+      <c r="P8" s="209"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="226"/>
-      <c r="S8" s="226"/>
+      <c r="R8" s="210"/>
+      <c r="S8" s="210"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="222"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="222"/>
-      <c r="K9" s="222"/>
-      <c r="L9" s="222"/>
-      <c r="M9" s="222"/>
-      <c r="N9" s="223"/>
-      <c r="O9" s="224"/>
-      <c r="P9" s="225"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="203"/>
+      <c r="H9" s="203"/>
+      <c r="I9" s="203"/>
+      <c r="J9" s="203"/>
+      <c r="K9" s="203"/>
+      <c r="L9" s="203"/>
+      <c r="M9" s="203"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="208"/>
+      <c r="P9" s="209"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="226"/>
-      <c r="S9" s="226"/>
+      <c r="R9" s="210"/>
+      <c r="S9" s="210"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="222"/>
-      <c r="D10" s="222"/>
-      <c r="E10" s="222"/>
-      <c r="F10" s="222"/>
-      <c r="G10" s="222"/>
-      <c r="H10" s="230"/>
-      <c r="I10" s="231"/>
-      <c r="J10" s="231"/>
-      <c r="K10" s="231"/>
-      <c r="L10" s="231"/>
-      <c r="M10" s="232"/>
-      <c r="N10" s="223"/>
-      <c r="O10" s="224"/>
-      <c r="P10" s="225"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="203"/>
+      <c r="H10" s="204"/>
+      <c r="I10" s="205"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="205"/>
+      <c r="L10" s="205"/>
+      <c r="M10" s="206"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="208"/>
+      <c r="P10" s="209"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="226"/>
-      <c r="S10" s="226"/>
+      <c r="R10" s="210"/>
+      <c r="S10" s="210"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="222"/>
-      <c r="D11" s="222"/>
-      <c r="E11" s="222"/>
-      <c r="F11" s="222"/>
-      <c r="G11" s="222"/>
-      <c r="H11" s="230"/>
-      <c r="I11" s="231"/>
-      <c r="J11" s="231"/>
-      <c r="K11" s="231"/>
-      <c r="L11" s="231"/>
-      <c r="M11" s="232"/>
-      <c r="N11" s="223"/>
-      <c r="O11" s="224"/>
-      <c r="P11" s="225"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="203"/>
+      <c r="H11" s="204"/>
+      <c r="I11" s="205"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="205"/>
+      <c r="L11" s="205"/>
+      <c r="M11" s="206"/>
+      <c r="N11" s="207"/>
+      <c r="O11" s="208"/>
+      <c r="P11" s="209"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="226"/>
-      <c r="S11" s="226"/>
+      <c r="R11" s="210"/>
+      <c r="S11" s="210"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="222"/>
-      <c r="D12" s="222"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="230"/>
-      <c r="I12" s="231"/>
-      <c r="J12" s="231"/>
-      <c r="K12" s="231"/>
-      <c r="L12" s="231"/>
-      <c r="M12" s="232"/>
-      <c r="N12" s="223"/>
-      <c r="O12" s="224"/>
-      <c r="P12" s="225"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="204"/>
+      <c r="I12" s="205"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="205"/>
+      <c r="M12" s="206"/>
+      <c r="N12" s="207"/>
+      <c r="O12" s="208"/>
+      <c r="P12" s="209"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="226"/>
-      <c r="S12" s="226"/>
+      <c r="R12" s="210"/>
+      <c r="S12" s="210"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="222"/>
-      <c r="D13" s="222"/>
-      <c r="E13" s="222"/>
-      <c r="F13" s="222"/>
-      <c r="G13" s="222"/>
-      <c r="H13" s="230"/>
-      <c r="I13" s="231"/>
-      <c r="J13" s="231"/>
-      <c r="K13" s="231"/>
-      <c r="L13" s="231"/>
-      <c r="M13" s="232"/>
-      <c r="N13" s="223"/>
-      <c r="O13" s="224"/>
-      <c r="P13" s="225"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="204"/>
+      <c r="I13" s="205"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="205"/>
+      <c r="L13" s="205"/>
+      <c r="M13" s="206"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="208"/>
+      <c r="P13" s="209"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="226"/>
-      <c r="S13" s="226"/>
+      <c r="R13" s="210"/>
+      <c r="S13" s="210"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="222"/>
-      <c r="D14" s="222"/>
-      <c r="E14" s="222"/>
-      <c r="F14" s="222"/>
-      <c r="G14" s="222"/>
-      <c r="H14" s="230"/>
-      <c r="I14" s="231"/>
-      <c r="J14" s="231"/>
-      <c r="K14" s="231"/>
-      <c r="L14" s="231"/>
-      <c r="M14" s="232"/>
-      <c r="N14" s="223"/>
-      <c r="O14" s="224"/>
-      <c r="P14" s="225"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="204"/>
+      <c r="I14" s="205"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="205"/>
+      <c r="L14" s="205"/>
+      <c r="M14" s="206"/>
+      <c r="N14" s="207"/>
+      <c r="O14" s="208"/>
+      <c r="P14" s="209"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="226"/>
-      <c r="S14" s="226"/>
+      <c r="R14" s="210"/>
+      <c r="S14" s="210"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="222"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="222"/>
-      <c r="F15" s="222"/>
-      <c r="G15" s="222"/>
-      <c r="H15" s="230"/>
-      <c r="I15" s="231"/>
-      <c r="J15" s="231"/>
-      <c r="K15" s="231"/>
-      <c r="L15" s="231"/>
-      <c r="M15" s="232"/>
-      <c r="N15" s="223"/>
-      <c r="O15" s="224"/>
-      <c r="P15" s="225"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="204"/>
+      <c r="I15" s="205"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="205"/>
+      <c r="L15" s="205"/>
+      <c r="M15" s="206"/>
+      <c r="N15" s="207"/>
+      <c r="O15" s="208"/>
+      <c r="P15" s="209"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="226"/>
-      <c r="S15" s="226"/>
+      <c r="R15" s="210"/>
+      <c r="S15" s="210"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
-      <c r="F16" s="222"/>
-      <c r="G16" s="222"/>
-      <c r="H16" s="230"/>
-      <c r="I16" s="231"/>
-      <c r="J16" s="231"/>
-      <c r="K16" s="231"/>
-      <c r="L16" s="231"/>
-      <c r="M16" s="232"/>
-      <c r="N16" s="223"/>
-      <c r="O16" s="224"/>
-      <c r="P16" s="225"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="203"/>
+      <c r="H16" s="204"/>
+      <c r="I16" s="205"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="205"/>
+      <c r="M16" s="206"/>
+      <c r="N16" s="207"/>
+      <c r="O16" s="208"/>
+      <c r="P16" s="209"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="226"/>
-      <c r="S16" s="226"/>
+      <c r="R16" s="210"/>
+      <c r="S16" s="210"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="222"/>
-      <c r="D17" s="222"/>
-      <c r="E17" s="222"/>
-      <c r="F17" s="222"/>
-      <c r="G17" s="222"/>
-      <c r="H17" s="230"/>
-      <c r="I17" s="231"/>
-      <c r="J17" s="231"/>
-      <c r="K17" s="231"/>
-      <c r="L17" s="231"/>
-      <c r="M17" s="232"/>
-      <c r="N17" s="223"/>
-      <c r="O17" s="224"/>
-      <c r="P17" s="225"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="203"/>
+      <c r="H17" s="204"/>
+      <c r="I17" s="205"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="205"/>
+      <c r="L17" s="205"/>
+      <c r="M17" s="206"/>
+      <c r="N17" s="207"/>
+      <c r="O17" s="208"/>
+      <c r="P17" s="209"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="226"/>
-      <c r="S17" s="226"/>
+      <c r="R17" s="210"/>
+      <c r="S17" s="210"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="222"/>
-      <c r="D18" s="222"/>
-      <c r="E18" s="222"/>
-      <c r="F18" s="222"/>
-      <c r="G18" s="222"/>
-      <c r="H18" s="230"/>
-      <c r="I18" s="231"/>
-      <c r="J18" s="231"/>
-      <c r="K18" s="231"/>
-      <c r="L18" s="231"/>
-      <c r="M18" s="232"/>
-      <c r="N18" s="223"/>
-      <c r="O18" s="224"/>
-      <c r="P18" s="225"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="204"/>
+      <c r="I18" s="205"/>
+      <c r="J18" s="205"/>
+      <c r="K18" s="205"/>
+      <c r="L18" s="205"/>
+      <c r="M18" s="206"/>
+      <c r="N18" s="207"/>
+      <c r="O18" s="208"/>
+      <c r="P18" s="209"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="226"/>
-      <c r="S18" s="226"/>
+      <c r="R18" s="210"/>
+      <c r="S18" s="210"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="222"/>
-      <c r="D19" s="222"/>
-      <c r="E19" s="222"/>
-      <c r="F19" s="222"/>
-      <c r="G19" s="222"/>
-      <c r="H19" s="230"/>
-      <c r="I19" s="231"/>
-      <c r="J19" s="231"/>
-      <c r="K19" s="231"/>
-      <c r="L19" s="231"/>
-      <c r="M19" s="232"/>
-      <c r="N19" s="223"/>
-      <c r="O19" s="224"/>
-      <c r="P19" s="225"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="203"/>
+      <c r="H19" s="204"/>
+      <c r="I19" s="205"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="205"/>
+      <c r="L19" s="205"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="207"/>
+      <c r="O19" s="208"/>
+      <c r="P19" s="209"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="226"/>
-      <c r="S19" s="226"/>
+      <c r="R19" s="210"/>
+      <c r="S19" s="210"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="222"/>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="230"/>
-      <c r="I20" s="231"/>
-      <c r="J20" s="231"/>
-      <c r="K20" s="231"/>
-      <c r="L20" s="231"/>
-      <c r="M20" s="232"/>
-      <c r="N20" s="223"/>
-      <c r="O20" s="224"/>
-      <c r="P20" s="225"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="203"/>
+      <c r="H20" s="204"/>
+      <c r="I20" s="205"/>
+      <c r="J20" s="205"/>
+      <c r="K20" s="205"/>
+      <c r="L20" s="205"/>
+      <c r="M20" s="206"/>
+      <c r="N20" s="207"/>
+      <c r="O20" s="208"/>
+      <c r="P20" s="209"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="226"/>
-      <c r="S20" s="226"/>
+      <c r="R20" s="210"/>
+      <c r="S20" s="210"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="222"/>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="222"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="230"/>
-      <c r="I21" s="231"/>
-      <c r="J21" s="231"/>
-      <c r="K21" s="231"/>
-      <c r="L21" s="231"/>
-      <c r="M21" s="232"/>
-      <c r="N21" s="223"/>
-      <c r="O21" s="224"/>
-      <c r="P21" s="225"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="203"/>
+      <c r="H21" s="204"/>
+      <c r="I21" s="205"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="205"/>
+      <c r="L21" s="205"/>
+      <c r="M21" s="206"/>
+      <c r="N21" s="207"/>
+      <c r="O21" s="208"/>
+      <c r="P21" s="209"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="226"/>
-      <c r="S21" s="226"/>
+      <c r="R21" s="210"/>
+      <c r="S21" s="210"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="222"/>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="222"/>
-      <c r="G22" s="222"/>
-      <c r="H22" s="230"/>
-      <c r="I22" s="231"/>
-      <c r="J22" s="231"/>
-      <c r="K22" s="231"/>
-      <c r="L22" s="231"/>
-      <c r="M22" s="232"/>
-      <c r="N22" s="223"/>
-      <c r="O22" s="224"/>
-      <c r="P22" s="225"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="204"/>
+      <c r="I22" s="205"/>
+      <c r="J22" s="205"/>
+      <c r="K22" s="205"/>
+      <c r="L22" s="205"/>
+      <c r="M22" s="206"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="208"/>
+      <c r="P22" s="209"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="226"/>
-      <c r="S22" s="226"/>
+      <c r="R22" s="210"/>
+      <c r="S22" s="210"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="222"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
-      <c r="G23" s="222"/>
-      <c r="H23" s="230"/>
-      <c r="I23" s="231"/>
-      <c r="J23" s="231"/>
-      <c r="K23" s="231"/>
-      <c r="L23" s="231"/>
-      <c r="M23" s="232"/>
-      <c r="N23" s="223"/>
-      <c r="O23" s="224"/>
-      <c r="P23" s="225"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="203"/>
+      <c r="H23" s="204"/>
+      <c r="I23" s="205"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="205"/>
+      <c r="L23" s="205"/>
+      <c r="M23" s="206"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="208"/>
+      <c r="P23" s="209"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="226"/>
-      <c r="S23" s="226"/>
+      <c r="R23" s="210"/>
+      <c r="S23" s="210"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="222"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
-      <c r="G24" s="222"/>
-      <c r="H24" s="230"/>
-      <c r="I24" s="231"/>
-      <c r="J24" s="231"/>
-      <c r="K24" s="231"/>
-      <c r="L24" s="231"/>
-      <c r="M24" s="232"/>
-      <c r="N24" s="223"/>
-      <c r="O24" s="224"/>
-      <c r="P24" s="225"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="203"/>
+      <c r="H24" s="204"/>
+      <c r="I24" s="205"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="205"/>
+      <c r="L24" s="205"/>
+      <c r="M24" s="206"/>
+      <c r="N24" s="207"/>
+      <c r="O24" s="208"/>
+      <c r="P24" s="209"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="226"/>
-      <c r="S24" s="226"/>
+      <c r="R24" s="210"/>
+      <c r="S24" s="210"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="222"/>
-      <c r="D25" s="222"/>
-      <c r="E25" s="222"/>
-      <c r="F25" s="222"/>
-      <c r="G25" s="222"/>
-      <c r="H25" s="230"/>
-      <c r="I25" s="231"/>
-      <c r="J25" s="231"/>
-      <c r="K25" s="231"/>
-      <c r="L25" s="231"/>
-      <c r="M25" s="232"/>
-      <c r="N25" s="223"/>
-      <c r="O25" s="224"/>
-      <c r="P25" s="225"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="203"/>
+      <c r="H25" s="204"/>
+      <c r="I25" s="205"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="205"/>
+      <c r="L25" s="205"/>
+      <c r="M25" s="206"/>
+      <c r="N25" s="207"/>
+      <c r="O25" s="208"/>
+      <c r="P25" s="209"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="226"/>
-      <c r="S25" s="226"/>
+      <c r="R25" s="210"/>
+      <c r="S25" s="210"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="222"/>
-      <c r="D26" s="222"/>
-      <c r="E26" s="222"/>
-      <c r="F26" s="222"/>
-      <c r="G26" s="222"/>
-      <c r="H26" s="230"/>
-      <c r="I26" s="231"/>
-      <c r="J26" s="231"/>
-      <c r="K26" s="231"/>
-      <c r="L26" s="231"/>
-      <c r="M26" s="232"/>
-      <c r="N26" s="223"/>
-      <c r="O26" s="224"/>
-      <c r="P26" s="225"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="205"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="205"/>
+      <c r="L26" s="205"/>
+      <c r="M26" s="206"/>
+      <c r="N26" s="207"/>
+      <c r="O26" s="208"/>
+      <c r="P26" s="209"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="226"/>
-      <c r="S26" s="226"/>
+      <c r="R26" s="210"/>
+      <c r="S26" s="210"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="222"/>
-      <c r="D27" s="222"/>
-      <c r="E27" s="222"/>
-      <c r="F27" s="222"/>
-      <c r="G27" s="222"/>
-      <c r="H27" s="230"/>
-      <c r="I27" s="231"/>
-      <c r="J27" s="231"/>
-      <c r="K27" s="231"/>
-      <c r="L27" s="231"/>
-      <c r="M27" s="232"/>
-      <c r="N27" s="223"/>
-      <c r="O27" s="224"/>
-      <c r="P27" s="225"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="203"/>
+      <c r="H27" s="204"/>
+      <c r="I27" s="205"/>
+      <c r="J27" s="205"/>
+      <c r="K27" s="205"/>
+      <c r="L27" s="205"/>
+      <c r="M27" s="206"/>
+      <c r="N27" s="207"/>
+      <c r="O27" s="208"/>
+      <c r="P27" s="209"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="226"/>
-      <c r="S27" s="226"/>
+      <c r="R27" s="210"/>
+      <c r="S27" s="210"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="222"/>
-      <c r="D28" s="222"/>
-      <c r="E28" s="222"/>
-      <c r="F28" s="222"/>
-      <c r="G28" s="222"/>
-      <c r="H28" s="230"/>
-      <c r="I28" s="231"/>
-      <c r="J28" s="231"/>
-      <c r="K28" s="231"/>
-      <c r="L28" s="231"/>
-      <c r="M28" s="232"/>
-      <c r="N28" s="223"/>
-      <c r="O28" s="224"/>
-      <c r="P28" s="225"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="203"/>
+      <c r="H28" s="204"/>
+      <c r="I28" s="205"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="205"/>
+      <c r="L28" s="205"/>
+      <c r="M28" s="206"/>
+      <c r="N28" s="207"/>
+      <c r="O28" s="208"/>
+      <c r="P28" s="209"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="226"/>
-      <c r="S28" s="226"/>
+      <c r="R28" s="210"/>
+      <c r="S28" s="210"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="222"/>
-      <c r="D29" s="222"/>
-      <c r="E29" s="222"/>
-      <c r="F29" s="222"/>
-      <c r="G29" s="222"/>
-      <c r="H29" s="230"/>
-      <c r="I29" s="231"/>
-      <c r="J29" s="231"/>
-      <c r="K29" s="231"/>
-      <c r="L29" s="231"/>
-      <c r="M29" s="232"/>
-      <c r="N29" s="223"/>
-      <c r="O29" s="224"/>
-      <c r="P29" s="225"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="204"/>
+      <c r="I29" s="205"/>
+      <c r="J29" s="205"/>
+      <c r="K29" s="205"/>
+      <c r="L29" s="205"/>
+      <c r="M29" s="206"/>
+      <c r="N29" s="207"/>
+      <c r="O29" s="208"/>
+      <c r="P29" s="209"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="226"/>
-      <c r="S29" s="226"/>
+      <c r="R29" s="210"/>
+      <c r="S29" s="210"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="222"/>
-      <c r="D30" s="222"/>
-      <c r="E30" s="222"/>
-      <c r="F30" s="222"/>
-      <c r="G30" s="222"/>
-      <c r="H30" s="230"/>
-      <c r="I30" s="231"/>
-      <c r="J30" s="231"/>
-      <c r="K30" s="231"/>
-      <c r="L30" s="231"/>
-      <c r="M30" s="232"/>
-      <c r="N30" s="223"/>
-      <c r="O30" s="224"/>
-      <c r="P30" s="225"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="203"/>
+      <c r="H30" s="204"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="205"/>
+      <c r="L30" s="205"/>
+      <c r="M30" s="206"/>
+      <c r="N30" s="207"/>
+      <c r="O30" s="208"/>
+      <c r="P30" s="209"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="226"/>
-      <c r="S30" s="226"/>
+      <c r="R30" s="210"/>
+      <c r="S30" s="210"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="222"/>
-      <c r="D31" s="222"/>
-      <c r="E31" s="222"/>
-      <c r="F31" s="222"/>
-      <c r="G31" s="222"/>
-      <c r="H31" s="230"/>
-      <c r="I31" s="231"/>
-      <c r="J31" s="231"/>
-      <c r="K31" s="231"/>
-      <c r="L31" s="231"/>
-      <c r="M31" s="232"/>
-      <c r="N31" s="223"/>
-      <c r="O31" s="224"/>
-      <c r="P31" s="225"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="203"/>
+      <c r="H31" s="204"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="205"/>
+      <c r="L31" s="205"/>
+      <c r="M31" s="206"/>
+      <c r="N31" s="207"/>
+      <c r="O31" s="208"/>
+      <c r="P31" s="209"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="226"/>
-      <c r="S31" s="226"/>
+      <c r="R31" s="210"/>
+      <c r="S31" s="210"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="222"/>
-      <c r="D32" s="222"/>
-      <c r="E32" s="222"/>
-      <c r="F32" s="222"/>
-      <c r="G32" s="222"/>
-      <c r="H32" s="230"/>
-      <c r="I32" s="231"/>
-      <c r="J32" s="231"/>
-      <c r="K32" s="231"/>
-      <c r="L32" s="231"/>
-      <c r="M32" s="232"/>
-      <c r="N32" s="223"/>
-      <c r="O32" s="224"/>
-      <c r="P32" s="225"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="203"/>
+      <c r="H32" s="204"/>
+      <c r="I32" s="205"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="205"/>
+      <c r="L32" s="205"/>
+      <c r="M32" s="206"/>
+      <c r="N32" s="207"/>
+      <c r="O32" s="208"/>
+      <c r="P32" s="209"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="226"/>
-      <c r="S32" s="226"/>
+      <c r="R32" s="210"/>
+      <c r="S32" s="210"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="222"/>
-      <c r="D33" s="222"/>
-      <c r="E33" s="222"/>
-      <c r="F33" s="222"/>
-      <c r="G33" s="222"/>
-      <c r="H33" s="230"/>
-      <c r="I33" s="231"/>
-      <c r="J33" s="231"/>
-      <c r="K33" s="231"/>
-      <c r="L33" s="231"/>
-      <c r="M33" s="232"/>
-      <c r="N33" s="223"/>
-      <c r="O33" s="224"/>
-      <c r="P33" s="225"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="204"/>
+      <c r="I33" s="205"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="205"/>
+      <c r="L33" s="205"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="207"/>
+      <c r="O33" s="208"/>
+      <c r="P33" s="209"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="226"/>
-      <c r="S33" s="226"/>
+      <c r="R33" s="210"/>
+      <c r="S33" s="210"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="222"/>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="222"/>
-      <c r="G34" s="222"/>
-      <c r="H34" s="230"/>
-      <c r="I34" s="231"/>
-      <c r="J34" s="231"/>
-      <c r="K34" s="231"/>
-      <c r="L34" s="231"/>
-      <c r="M34" s="232"/>
-      <c r="N34" s="223"/>
-      <c r="O34" s="224"/>
-      <c r="P34" s="225"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="203"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="204"/>
+      <c r="I34" s="205"/>
+      <c r="J34" s="205"/>
+      <c r="K34" s="205"/>
+      <c r="L34" s="205"/>
+      <c r="M34" s="206"/>
+      <c r="N34" s="207"/>
+      <c r="O34" s="208"/>
+      <c r="P34" s="209"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="226"/>
-      <c r="S34" s="226"/>
+      <c r="R34" s="210"/>
+      <c r="S34" s="210"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="222"/>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="230"/>
-      <c r="I35" s="231"/>
-      <c r="J35" s="231"/>
-      <c r="K35" s="231"/>
-      <c r="L35" s="231"/>
-      <c r="M35" s="232"/>
-      <c r="N35" s="223"/>
-      <c r="O35" s="224"/>
-      <c r="P35" s="225"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="204"/>
+      <c r="I35" s="205"/>
+      <c r="J35" s="205"/>
+      <c r="K35" s="205"/>
+      <c r="L35" s="205"/>
+      <c r="M35" s="206"/>
+      <c r="N35" s="207"/>
+      <c r="O35" s="208"/>
+      <c r="P35" s="209"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="226"/>
-      <c r="S35" s="226"/>
+      <c r="R35" s="210"/>
+      <c r="S35" s="210"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="222"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="222"/>
-      <c r="G36" s="222"/>
-      <c r="H36" s="230"/>
-      <c r="I36" s="231"/>
-      <c r="J36" s="231"/>
-      <c r="K36" s="231"/>
-      <c r="L36" s="231"/>
-      <c r="M36" s="232"/>
-      <c r="N36" s="223"/>
-      <c r="O36" s="224"/>
-      <c r="P36" s="225"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="203"/>
+      <c r="F36" s="203"/>
+      <c r="G36" s="203"/>
+      <c r="H36" s="204"/>
+      <c r="I36" s="205"/>
+      <c r="J36" s="205"/>
+      <c r="K36" s="205"/>
+      <c r="L36" s="205"/>
+      <c r="M36" s="206"/>
+      <c r="N36" s="207"/>
+      <c r="O36" s="208"/>
+      <c r="P36" s="209"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="226"/>
-      <c r="S36" s="226"/>
+      <c r="R36" s="210"/>
+      <c r="S36" s="210"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="222"/>
-      <c r="D37" s="222"/>
-      <c r="E37" s="222"/>
-      <c r="F37" s="222"/>
-      <c r="G37" s="222"/>
-      <c r="H37" s="230"/>
-      <c r="I37" s="231"/>
-      <c r="J37" s="231"/>
-      <c r="K37" s="231"/>
-      <c r="L37" s="231"/>
-      <c r="M37" s="232"/>
-      <c r="N37" s="223"/>
-      <c r="O37" s="224"/>
-      <c r="P37" s="225"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="203"/>
+      <c r="H37" s="204"/>
+      <c r="I37" s="205"/>
+      <c r="J37" s="205"/>
+      <c r="K37" s="205"/>
+      <c r="L37" s="205"/>
+      <c r="M37" s="206"/>
+      <c r="N37" s="207"/>
+      <c r="O37" s="208"/>
+      <c r="P37" s="209"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="226"/>
-      <c r="S37" s="226"/>
+      <c r="R37" s="210"/>
+      <c r="S37" s="210"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="222"/>
-      <c r="D38" s="222"/>
-      <c r="E38" s="222"/>
-      <c r="F38" s="222"/>
-      <c r="G38" s="222"/>
-      <c r="H38" s="230"/>
-      <c r="I38" s="231"/>
-      <c r="J38" s="231"/>
-      <c r="K38" s="231"/>
-      <c r="L38" s="231"/>
-      <c r="M38" s="232"/>
-      <c r="N38" s="223"/>
-      <c r="O38" s="224"/>
-      <c r="P38" s="225"/>
+      <c r="C38" s="203"/>
+      <c r="D38" s="203"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="203"/>
+      <c r="H38" s="204"/>
+      <c r="I38" s="205"/>
+      <c r="J38" s="205"/>
+      <c r="K38" s="205"/>
+      <c r="L38" s="205"/>
+      <c r="M38" s="206"/>
+      <c r="N38" s="207"/>
+      <c r="O38" s="208"/>
+      <c r="P38" s="209"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="226"/>
-      <c r="S38" s="226"/>
+      <c r="R38" s="210"/>
+      <c r="S38" s="210"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="222"/>
-      <c r="D39" s="222"/>
-      <c r="E39" s="222"/>
-      <c r="F39" s="222"/>
-      <c r="G39" s="222"/>
-      <c r="H39" s="230"/>
-      <c r="I39" s="231"/>
-      <c r="J39" s="231"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="231"/>
-      <c r="M39" s="232"/>
-      <c r="N39" s="223"/>
-      <c r="O39" s="224"/>
-      <c r="P39" s="225"/>
+      <c r="C39" s="203"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="203"/>
+      <c r="F39" s="203"/>
+      <c r="G39" s="203"/>
+      <c r="H39" s="204"/>
+      <c r="I39" s="205"/>
+      <c r="J39" s="205"/>
+      <c r="K39" s="205"/>
+      <c r="L39" s="205"/>
+      <c r="M39" s="206"/>
+      <c r="N39" s="207"/>
+      <c r="O39" s="208"/>
+      <c r="P39" s="209"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="226"/>
-      <c r="S39" s="226"/>
+      <c r="R39" s="210"/>
+      <c r="S39" s="210"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="222"/>
-      <c r="D40" s="222"/>
-      <c r="E40" s="222"/>
-      <c r="F40" s="222"/>
-      <c r="G40" s="222"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="231"/>
-      <c r="J40" s="231"/>
-      <c r="K40" s="231"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="223"/>
-      <c r="O40" s="224"/>
-      <c r="P40" s="225"/>
+      <c r="C40" s="203"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="204"/>
+      <c r="I40" s="205"/>
+      <c r="J40" s="205"/>
+      <c r="K40" s="205"/>
+      <c r="L40" s="205"/>
+      <c r="M40" s="206"/>
+      <c r="N40" s="207"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="209"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="226"/>
-      <c r="S40" s="226"/>
+      <c r="R40" s="210"/>
+      <c r="S40" s="210"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="222"/>
-      <c r="D41" s="222"/>
-      <c r="E41" s="222"/>
-      <c r="F41" s="222"/>
-      <c r="G41" s="222"/>
-      <c r="H41" s="230"/>
-      <c r="I41" s="231"/>
-      <c r="J41" s="231"/>
-      <c r="K41" s="231"/>
-      <c r="L41" s="231"/>
-      <c r="M41" s="232"/>
-      <c r="N41" s="223"/>
-      <c r="O41" s="224"/>
-      <c r="P41" s="225"/>
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+      <c r="G41" s="203"/>
+      <c r="H41" s="204"/>
+      <c r="I41" s="205"/>
+      <c r="J41" s="205"/>
+      <c r="K41" s="205"/>
+      <c r="L41" s="205"/>
+      <c r="M41" s="206"/>
+      <c r="N41" s="207"/>
+      <c r="O41" s="208"/>
+      <c r="P41" s="209"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="226"/>
-      <c r="S41" s="226"/>
+      <c r="R41" s="210"/>
+      <c r="S41" s="210"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="222"/>
-      <c r="D42" s="222"/>
-      <c r="E42" s="222"/>
-      <c r="F42" s="222"/>
-      <c r="G42" s="222"/>
-      <c r="H42" s="230"/>
-      <c r="I42" s="231"/>
-      <c r="J42" s="231"/>
-      <c r="K42" s="231"/>
-      <c r="L42" s="231"/>
-      <c r="M42" s="232"/>
-      <c r="N42" s="223"/>
-      <c r="O42" s="224"/>
-      <c r="P42" s="225"/>
+      <c r="C42" s="203"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="203"/>
+      <c r="G42" s="203"/>
+      <c r="H42" s="204"/>
+      <c r="I42" s="205"/>
+      <c r="J42" s="205"/>
+      <c r="K42" s="205"/>
+      <c r="L42" s="205"/>
+      <c r="M42" s="206"/>
+      <c r="N42" s="207"/>
+      <c r="O42" s="208"/>
+      <c r="P42" s="209"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="226"/>
-      <c r="S42" s="226"/>
+      <c r="R42" s="210"/>
+      <c r="S42" s="210"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="222"/>
-      <c r="D43" s="222"/>
-      <c r="E43" s="222"/>
-      <c r="F43" s="222"/>
-      <c r="G43" s="222"/>
-      <c r="H43" s="230"/>
-      <c r="I43" s="231"/>
-      <c r="J43" s="231"/>
-      <c r="K43" s="231"/>
-      <c r="L43" s="231"/>
-      <c r="M43" s="232"/>
-      <c r="N43" s="223"/>
-      <c r="O43" s="224"/>
-      <c r="P43" s="225"/>
+      <c r="C43" s="203"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="203"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
+      <c r="H43" s="204"/>
+      <c r="I43" s="205"/>
+      <c r="J43" s="205"/>
+      <c r="K43" s="205"/>
+      <c r="L43" s="205"/>
+      <c r="M43" s="206"/>
+      <c r="N43" s="207"/>
+      <c r="O43" s="208"/>
+      <c r="P43" s="209"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="226"/>
-      <c r="S43" s="226"/>
+      <c r="R43" s="210"/>
+      <c r="S43" s="210"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="222"/>
-      <c r="D44" s="222"/>
-      <c r="E44" s="222"/>
-      <c r="F44" s="222"/>
-      <c r="G44" s="222"/>
-      <c r="H44" s="230"/>
-      <c r="I44" s="231"/>
-      <c r="J44" s="231"/>
-      <c r="K44" s="231"/>
-      <c r="L44" s="231"/>
-      <c r="M44" s="232"/>
-      <c r="N44" s="223"/>
-      <c r="O44" s="224"/>
-      <c r="P44" s="225"/>
+      <c r="C44" s="203"/>
+      <c r="D44" s="203"/>
+      <c r="E44" s="203"/>
+      <c r="F44" s="203"/>
+      <c r="G44" s="203"/>
+      <c r="H44" s="204"/>
+      <c r="I44" s="205"/>
+      <c r="J44" s="205"/>
+      <c r="K44" s="205"/>
+      <c r="L44" s="205"/>
+      <c r="M44" s="206"/>
+      <c r="N44" s="207"/>
+      <c r="O44" s="208"/>
+      <c r="P44" s="209"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="226"/>
-      <c r="S44" s="226"/>
+      <c r="R44" s="210"/>
+      <c r="S44" s="210"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="222"/>
-      <c r="D45" s="222"/>
-      <c r="E45" s="222"/>
-      <c r="F45" s="222"/>
-      <c r="G45" s="222"/>
-      <c r="H45" s="230"/>
-      <c r="I45" s="231"/>
-      <c r="J45" s="231"/>
-      <c r="K45" s="231"/>
-      <c r="L45" s="231"/>
-      <c r="M45" s="232"/>
-      <c r="N45" s="223"/>
-      <c r="O45" s="224"/>
-      <c r="P45" s="225"/>
+      <c r="C45" s="203"/>
+      <c r="D45" s="203"/>
+      <c r="E45" s="203"/>
+      <c r="F45" s="203"/>
+      <c r="G45" s="203"/>
+      <c r="H45" s="204"/>
+      <c r="I45" s="205"/>
+      <c r="J45" s="205"/>
+      <c r="K45" s="205"/>
+      <c r="L45" s="205"/>
+      <c r="M45" s="206"/>
+      <c r="N45" s="207"/>
+      <c r="O45" s="208"/>
+      <c r="P45" s="209"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="226"/>
-      <c r="S45" s="226"/>
+      <c r="R45" s="210"/>
+      <c r="S45" s="210"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="222"/>
-      <c r="D46" s="222"/>
-      <c r="E46" s="222"/>
-      <c r="F46" s="222"/>
-      <c r="G46" s="222"/>
-      <c r="H46" s="230"/>
-      <c r="I46" s="231"/>
-      <c r="J46" s="231"/>
-      <c r="K46" s="231"/>
-      <c r="L46" s="231"/>
-      <c r="M46" s="232"/>
-      <c r="N46" s="223"/>
-      <c r="O46" s="224"/>
-      <c r="P46" s="225"/>
+      <c r="C46" s="203"/>
+      <c r="D46" s="203"/>
+      <c r="E46" s="203"/>
+      <c r="F46" s="203"/>
+      <c r="G46" s="203"/>
+      <c r="H46" s="204"/>
+      <c r="I46" s="205"/>
+      <c r="J46" s="205"/>
+      <c r="K46" s="205"/>
+      <c r="L46" s="205"/>
+      <c r="M46" s="206"/>
+      <c r="N46" s="207"/>
+      <c r="O46" s="208"/>
+      <c r="P46" s="209"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="226"/>
-      <c r="S46" s="226"/>
+      <c r="R46" s="210"/>
+      <c r="S46" s="210"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="222"/>
-      <c r="D47" s="222"/>
-      <c r="E47" s="222"/>
-      <c r="F47" s="222"/>
-      <c r="G47" s="222"/>
-      <c r="H47" s="230"/>
-      <c r="I47" s="231"/>
-      <c r="J47" s="231"/>
-      <c r="K47" s="231"/>
-      <c r="L47" s="231"/>
-      <c r="M47" s="232"/>
-      <c r="N47" s="223"/>
-      <c r="O47" s="224"/>
-      <c r="P47" s="225"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="203"/>
+      <c r="E47" s="203"/>
+      <c r="F47" s="203"/>
+      <c r="G47" s="203"/>
+      <c r="H47" s="204"/>
+      <c r="I47" s="205"/>
+      <c r="J47" s="205"/>
+      <c r="K47" s="205"/>
+      <c r="L47" s="205"/>
+      <c r="M47" s="206"/>
+      <c r="N47" s="207"/>
+      <c r="O47" s="208"/>
+      <c r="P47" s="209"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="226"/>
-      <c r="S47" s="226"/>
+      <c r="R47" s="210"/>
+      <c r="S47" s="210"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="231"/>
-      <c r="L48" s="231"/>
-      <c r="M48" s="232"/>
-      <c r="N48" s="223"/>
-      <c r="O48" s="224"/>
-      <c r="P48" s="225"/>
+      <c r="C48" s="203"/>
+      <c r="D48" s="203"/>
+      <c r="E48" s="203"/>
+      <c r="F48" s="203"/>
+      <c r="G48" s="203"/>
+      <c r="H48" s="204"/>
+      <c r="I48" s="205"/>
+      <c r="J48" s="205"/>
+      <c r="K48" s="205"/>
+      <c r="L48" s="205"/>
+      <c r="M48" s="206"/>
+      <c r="N48" s="207"/>
+      <c r="O48" s="208"/>
+      <c r="P48" s="209"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="226"/>
-      <c r="S48" s="226"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="210"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="222"/>
-      <c r="D49" s="222"/>
-      <c r="E49" s="222"/>
-      <c r="F49" s="222"/>
-      <c r="G49" s="222"/>
-      <c r="H49" s="230"/>
-      <c r="I49" s="231"/>
-      <c r="J49" s="231"/>
-      <c r="K49" s="231"/>
-      <c r="L49" s="231"/>
-      <c r="M49" s="232"/>
-      <c r="N49" s="223"/>
-      <c r="O49" s="224"/>
-      <c r="P49" s="225"/>
+      <c r="C49" s="203"/>
+      <c r="D49" s="203"/>
+      <c r="E49" s="203"/>
+      <c r="F49" s="203"/>
+      <c r="G49" s="203"/>
+      <c r="H49" s="204"/>
+      <c r="I49" s="205"/>
+      <c r="J49" s="205"/>
+      <c r="K49" s="205"/>
+      <c r="L49" s="205"/>
+      <c r="M49" s="206"/>
+      <c r="N49" s="207"/>
+      <c r="O49" s="208"/>
+      <c r="P49" s="209"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="226"/>
-      <c r="S49" s="226"/>
+      <c r="R49" s="210"/>
+      <c r="S49" s="210"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="222"/>
-      <c r="D50" s="222"/>
-      <c r="E50" s="222"/>
-      <c r="F50" s="222"/>
-      <c r="G50" s="222"/>
-      <c r="H50" s="230"/>
-      <c r="I50" s="231"/>
-      <c r="J50" s="231"/>
-      <c r="K50" s="231"/>
-      <c r="L50" s="231"/>
-      <c r="M50" s="232"/>
-      <c r="N50" s="223"/>
-      <c r="O50" s="224"/>
-      <c r="P50" s="225"/>
+      <c r="C50" s="203"/>
+      <c r="D50" s="203"/>
+      <c r="E50" s="203"/>
+      <c r="F50" s="203"/>
+      <c r="G50" s="203"/>
+      <c r="H50" s="204"/>
+      <c r="I50" s="205"/>
+      <c r="J50" s="205"/>
+      <c r="K50" s="205"/>
+      <c r="L50" s="205"/>
+      <c r="M50" s="206"/>
+      <c r="N50" s="207"/>
+      <c r="O50" s="208"/>
+      <c r="P50" s="209"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="226"/>
-      <c r="S50" s="226"/>
+      <c r="R50" s="210"/>
+      <c r="S50" s="210"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="222"/>
-      <c r="D51" s="222"/>
-      <c r="E51" s="222"/>
-      <c r="F51" s="222"/>
-      <c r="G51" s="222"/>
-      <c r="H51" s="230"/>
-      <c r="I51" s="231"/>
-      <c r="J51" s="231"/>
-      <c r="K51" s="231"/>
-      <c r="L51" s="231"/>
-      <c r="M51" s="232"/>
-      <c r="N51" s="223"/>
-      <c r="O51" s="224"/>
-      <c r="P51" s="225"/>
+      <c r="C51" s="203"/>
+      <c r="D51" s="203"/>
+      <c r="E51" s="203"/>
+      <c r="F51" s="203"/>
+      <c r="G51" s="203"/>
+      <c r="H51" s="204"/>
+      <c r="I51" s="205"/>
+      <c r="J51" s="205"/>
+      <c r="K51" s="205"/>
+      <c r="L51" s="205"/>
+      <c r="M51" s="206"/>
+      <c r="N51" s="207"/>
+      <c r="O51" s="208"/>
+      <c r="P51" s="209"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="226"/>
-      <c r="S51" s="226"/>
+      <c r="R51" s="210"/>
+      <c r="S51" s="210"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="222"/>
-      <c r="D52" s="222"/>
-      <c r="E52" s="222"/>
-      <c r="F52" s="222"/>
-      <c r="G52" s="222"/>
-      <c r="H52" s="230"/>
-      <c r="I52" s="231"/>
-      <c r="J52" s="231"/>
-      <c r="K52" s="231"/>
-      <c r="L52" s="231"/>
-      <c r="M52" s="232"/>
-      <c r="N52" s="223"/>
-      <c r="O52" s="224"/>
-      <c r="P52" s="225"/>
+      <c r="C52" s="203"/>
+      <c r="D52" s="203"/>
+      <c r="E52" s="203"/>
+      <c r="F52" s="203"/>
+      <c r="G52" s="203"/>
+      <c r="H52" s="204"/>
+      <c r="I52" s="205"/>
+      <c r="J52" s="205"/>
+      <c r="K52" s="205"/>
+      <c r="L52" s="205"/>
+      <c r="M52" s="206"/>
+      <c r="N52" s="207"/>
+      <c r="O52" s="208"/>
+      <c r="P52" s="209"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="226"/>
-      <c r="S52" s="226"/>
+      <c r="R52" s="210"/>
+      <c r="S52" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -13010,6 +12806,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49139972-3587-46B5-B4C4-BB3D536F34B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF9DA33-68CC-4411-A4B9-D21FFCCD1191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9000" yWindow="780" windowWidth="11415" windowHeight="8955" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -688,6 +688,10 @@
     <rPh sb="5" eb="6">
       <t>アタイ</t>
     </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="7"/>
   </si>
 </sst>
@@ -1904,6 +1908,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1914,11 +1951,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1934,9 +2019,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1949,84 +2031,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2090,6 +2094,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2108,18 +2121,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2132,9 +2139,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2210,6 +2214,69 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2228,73 +2295,91 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2302,87 +2387,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4101,19 +4105,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="109" t="s">
+      <c r="B1" s="91"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="97"/>
-      <c r="F1" s="109" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="97"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4125,190 +4129,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="103"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="110" t="s">
+      <c r="A2" s="93"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="111"/>
-      <c r="F2" s="110" t="s">
+      <c r="E2" s="101"/>
+      <c r="F2" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="114">
+      <c r="G2" s="101"/>
+      <c r="H2" s="104">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="92"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="103"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="93"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="96"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="95" t="s">
+      <c r="A5" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="99"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="84" t="s">
+      <c r="B6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="78"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="84" t="s">
+      <c r="B7" s="86"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="78"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="84" t="s">
+      <c r="B8" s="86"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="78"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="87" customHeight="1">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="88" t="s">
+      <c r="B9" s="114" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="77" t="s">
+      <c r="C9" s="87"/>
+      <c r="D9" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="78"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="89"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="88" t="s">
+      <c r="A10" s="112"/>
+      <c r="B10" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="78"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88" t="s">
+      <c r="A11" s="113"/>
+      <c r="B11" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77" t="s">
+      <c r="C11" s="87"/>
+      <c r="D11" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="78"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="89"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="77" t="s">
+      <c r="B12" s="86"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="78"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="89"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="83"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="110"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5299,18 +5303,6 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5326,6 +5318,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6837,23 +6841,23 @@
       <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="137"/>
+      <c r="B5" s="140"/>
       <c r="C5" s="131"/>
-      <c r="D5" s="143" t="s">
+      <c r="D5" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
-      <c r="J5" s="144"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="146"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="141" t="s">
+      <c r="A6" s="144" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="67"/>
@@ -6864,19 +6868,19 @@
       <c r="G6" s="67"/>
       <c r="H6" s="67"/>
       <c r="I6" s="67"/>
-      <c r="J6" s="145"/>
+      <c r="J6" s="137"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="146"/>
-      <c r="B7" s="147"/>
-      <c r="C7" s="147"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="148"/>
+      <c r="A7" s="147"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="149"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="125"/>
@@ -6888,7 +6892,7 @@
       <c r="G8" s="70"/>
       <c r="H8" s="70"/>
       <c r="I8" s="70"/>
-      <c r="J8" s="149"/>
+      <c r="J8" s="150"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="125"/>
@@ -6900,7 +6904,7 @@
       <c r="G9" s="70"/>
       <c r="H9" s="70"/>
       <c r="I9" s="70"/>
-      <c r="J9" s="149"/>
+      <c r="J9" s="150"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="125"/>
@@ -6912,7 +6916,7 @@
       <c r="G10" s="70"/>
       <c r="H10" s="70"/>
       <c r="I10" s="70"/>
-      <c r="J10" s="149"/>
+      <c r="J10" s="150"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="125"/>
@@ -6924,7 +6928,7 @@
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
-      <c r="J11" s="149"/>
+      <c r="J11" s="150"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="125"/>
@@ -6936,7 +6940,7 @@
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
       <c r="I12" s="70"/>
-      <c r="J12" s="149"/>
+      <c r="J12" s="150"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="125"/>
@@ -6948,10 +6952,10 @@
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
       <c r="I13" s="70"/>
-      <c r="J13" s="149"/>
+      <c r="J13" s="150"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="141" t="s">
+      <c r="A14" s="144" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="67"/>
@@ -6962,15 +6966,15 @@
       <c r="G14" s="67"/>
       <c r="H14" s="67"/>
       <c r="I14" s="67"/>
-      <c r="J14" s="145"/>
+      <c r="J14" s="137"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="141" t="s">
+      <c r="A15" s="144" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="67"/>
       <c r="C15" s="68"/>
-      <c r="D15" s="150" t="s">
+      <c r="D15" s="136" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="67"/>
@@ -6985,7 +6989,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="144" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="67"/>
@@ -7006,10 +7010,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="67"/>
-      <c r="J16" s="145"/>
+      <c r="J16" s="137"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="138">
         <v>1</v>
       </c>
       <c r="B17" s="67"/>
@@ -7024,80 +7028,80 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="150"/>
+      <c r="H17" s="136"/>
       <c r="I17" s="67"/>
-      <c r="J17" s="145"/>
+      <c r="J17" s="137"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142"/>
+      <c r="A18" s="138"/>
       <c r="B18" s="67"/>
       <c r="C18" s="68"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="150"/>
+      <c r="H18" s="136"/>
       <c r="I18" s="67"/>
-      <c r="J18" s="145"/>
+      <c r="J18" s="137"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142"/>
+      <c r="A19" s="138"/>
       <c r="B19" s="67"/>
       <c r="C19" s="68"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="150"/>
+      <c r="H19" s="136"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="145"/>
+      <c r="J19" s="137"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142"/>
+      <c r="A20" s="138"/>
       <c r="B20" s="67"/>
       <c r="C20" s="68"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="150"/>
+      <c r="H20" s="136"/>
       <c r="I20" s="67"/>
-      <c r="J20" s="145"/>
+      <c r="J20" s="137"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142"/>
+      <c r="A21" s="138"/>
       <c r="B21" s="67"/>
       <c r="C21" s="68"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="150"/>
+      <c r="H21" s="136"/>
       <c r="I21" s="67"/>
-      <c r="J21" s="145"/>
+      <c r="J21" s="137"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142"/>
+      <c r="A22" s="138"/>
       <c r="B22" s="67"/>
       <c r="C22" s="68"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="150"/>
+      <c r="H22" s="136"/>
       <c r="I22" s="67"/>
-      <c r="J22" s="145"/>
+      <c r="J22" s="137"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="138"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="142"/>
+      <c r="C23" s="143"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="152"/>
-      <c r="I23" s="139"/>
+      <c r="I23" s="142"/>
       <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8079,16 +8083,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8105,11 +8104,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9544,7 +9548,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="188" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="161"/>
@@ -9555,14 +9559,14 @@
       <c r="G1" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
       <c r="J1" s="170"/>
       <c r="K1" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
+      <c r="L1" s="180"/>
+      <c r="M1" s="180"/>
       <c r="N1" s="170"/>
       <c r="O1" s="169" t="s">
         <v>7</v>
@@ -9575,7 +9579,7 @@
       <c r="S1" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="197"/>
+      <c r="T1" s="182"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="163"/>
@@ -9587,16 +9591,16 @@
       <c r="G2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="201"/>
-      <c r="I2" s="201"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
       <c r="J2" s="172"/>
       <c r="K2" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="201"/>
-      <c r="M2" s="201"/>
+      <c r="L2" s="189"/>
+      <c r="M2" s="189"/>
       <c r="N2" s="172"/>
-      <c r="O2" s="202">
+      <c r="O2" s="190">
         <v>45817</v>
       </c>
       <c r="P2" s="172"/>
@@ -9605,7 +9609,7 @@
       </c>
       <c r="R2" s="172"/>
       <c r="S2" s="171"/>
-      <c r="T2" s="191"/>
+      <c r="T2" s="176"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="163"/>
@@ -9627,7 +9631,7 @@
       <c r="Q3" s="173"/>
       <c r="R3" s="165"/>
       <c r="S3" s="173"/>
-      <c r="T3" s="192"/>
+      <c r="T3" s="177"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="166"/>
@@ -9649,85 +9653,85 @@
       <c r="Q4" s="174"/>
       <c r="R4" s="168"/>
       <c r="S4" s="174"/>
-      <c r="T4" s="193"/>
+      <c r="T4" s="178"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="194" t="s">
+      <c r="A5" s="179" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="195"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
+      <c r="B5" s="180"/>
+      <c r="C5" s="180"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="180"/>
       <c r="F5" s="170"/>
-      <c r="G5" s="196" t="s">
+      <c r="G5" s="181" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="195"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
-      <c r="L5" s="195"/>
-      <c r="M5" s="195"/>
-      <c r="N5" s="195"/>
-      <c r="O5" s="195"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="195"/>
-      <c r="T5" s="197"/>
+      <c r="H5" s="180"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="180"/>
+      <c r="Q5" s="180"/>
+      <c r="R5" s="180"/>
+      <c r="S5" s="180"/>
+      <c r="T5" s="182"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="183" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="183"/>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="198" t="s">
+      <c r="B6" s="184"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="183"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="183"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="183"/>
-      <c r="Q6" s="183"/>
-      <c r="R6" s="183"/>
-      <c r="S6" s="183"/>
-      <c r="T6" s="199"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="184"/>
+      <c r="L6" s="184"/>
+      <c r="M6" s="184"/>
+      <c r="N6" s="184"/>
+      <c r="O6" s="184"/>
+      <c r="P6" s="184"/>
+      <c r="Q6" s="184"/>
+      <c r="R6" s="184"/>
+      <c r="S6" s="184"/>
+      <c r="T6" s="187"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="183" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="184"/>
-      <c r="G7" s="198" t="s">
+      <c r="B7" s="184"/>
+      <c r="C7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="185"/>
+      <c r="G7" s="186" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="183"/>
-      <c r="K7" s="183"/>
-      <c r="L7" s="183"/>
-      <c r="M7" s="183"/>
-      <c r="N7" s="183"/>
-      <c r="O7" s="183"/>
-      <c r="P7" s="183"/>
-      <c r="Q7" s="183"/>
-      <c r="R7" s="183"/>
-      <c r="S7" s="183"/>
-      <c r="T7" s="199"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="184"/>
+      <c r="K7" s="184"/>
+      <c r="L7" s="184"/>
+      <c r="M7" s="184"/>
+      <c r="N7" s="184"/>
+      <c r="O7" s="184"/>
+      <c r="P7" s="184"/>
+      <c r="Q7" s="184"/>
+      <c r="R7" s="184"/>
+      <c r="S7" s="184"/>
+      <c r="T7" s="187"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9926,37 +9930,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="184"/>
-      <c r="C15" s="190" t="s">
+      <c r="B15" s="185"/>
+      <c r="C15" s="196" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="184"/>
-      <c r="E15" s="188" t="s">
+      <c r="D15" s="185"/>
+      <c r="E15" s="191" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="184"/>
-      <c r="G15" s="188" t="s">
+      <c r="F15" s="185"/>
+      <c r="G15" s="191" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="183"/>
-      <c r="I15" s="184"/>
-      <c r="J15" s="188" t="s">
+      <c r="H15" s="184"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="191" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="184"/>
-      <c r="L15" s="188" t="s">
+      <c r="K15" s="185"/>
+      <c r="L15" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="183"/>
-      <c r="N15" s="184"/>
-      <c r="O15" s="188" t="s">
+      <c r="M15" s="184"/>
+      <c r="N15" s="185"/>
+      <c r="O15" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="184"/>
+      <c r="P15" s="184"/>
+      <c r="Q15" s="185"/>
       <c r="R15" s="44" t="s">
         <v>56</v>
       </c>
@@ -9968,40 +9972,46 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="192">
         <v>1</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="186" t="s">
+      <c r="B16" s="185"/>
+      <c r="C16" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="184"/>
-      <c r="E16" s="186" t="s">
+      <c r="D16" s="185"/>
+      <c r="E16" s="193" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="184"/>
-      <c r="G16" s="187" t="s">
+      <c r="F16" s="185"/>
+      <c r="G16" s="194" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="183"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="187" t="s">
+      <c r="H16" s="184"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="184"/>
-      <c r="L16" s="182" t="s">
+      <c r="K16" s="185"/>
+      <c r="L16" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="183"/>
-      <c r="N16" s="184"/>
-      <c r="O16" s="182" t="s">
+      <c r="M16" s="184"/>
+      <c r="N16" s="185"/>
+      <c r="O16" s="195" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="184"/>
-      <c r="R16" s="65"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="47"/>
+      <c r="P16" s="184"/>
+      <c r="Q16" s="185"/>
+      <c r="R16" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S16" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T16" s="47" t="s">
+        <v>108</v>
+      </c>
       <c r="U16" s="48"/>
       <c r="V16" s="48"/>
       <c r="W16" s="48"/>
@@ -10010,40 +10020,46 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="192">
         <v>2</v>
       </c>
-      <c r="B17" s="184"/>
-      <c r="C17" s="186" t="s">
+      <c r="B17" s="185"/>
+      <c r="C17" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="184"/>
-      <c r="E17" s="186" t="s">
+      <c r="D17" s="185"/>
+      <c r="E17" s="193" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="184"/>
-      <c r="G17" s="187" t="s">
+      <c r="F17" s="185"/>
+      <c r="G17" s="194" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="183"/>
-      <c r="I17" s="184"/>
-      <c r="J17" s="187" t="s">
+      <c r="H17" s="184"/>
+      <c r="I17" s="185"/>
+      <c r="J17" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="184"/>
-      <c r="L17" s="182" t="s">
+      <c r="K17" s="185"/>
+      <c r="L17" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M17" s="183"/>
-      <c r="N17" s="184"/>
-      <c r="O17" s="182" t="s">
+      <c r="M17" s="184"/>
+      <c r="N17" s="185"/>
+      <c r="O17" s="195" t="s">
         <v>98</v>
       </c>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="184"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="47"/>
+      <c r="P17" s="184"/>
+      <c r="Q17" s="185"/>
+      <c r="R17" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S17" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T17" s="47" t="s">
+        <v>108</v>
+      </c>
       <c r="U17" s="48"/>
       <c r="V17" s="48"/>
       <c r="W17" s="48"/>
@@ -10052,40 +10068,46 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="185">
+      <c r="A18" s="192">
         <v>3</v>
       </c>
-      <c r="B18" s="184"/>
-      <c r="C18" s="186" t="s">
+      <c r="B18" s="185"/>
+      <c r="C18" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="184"/>
-      <c r="E18" s="186" t="s">
+      <c r="D18" s="185"/>
+      <c r="E18" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="184"/>
-      <c r="G18" s="187" t="s">
+      <c r="F18" s="185"/>
+      <c r="G18" s="194" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="183"/>
-      <c r="I18" s="184"/>
-      <c r="J18" s="187" t="s">
+      <c r="H18" s="184"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="184"/>
-      <c r="L18" s="182" t="s">
+      <c r="K18" s="185"/>
+      <c r="L18" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M18" s="183"/>
-      <c r="N18" s="184"/>
-      <c r="O18" s="182" t="s">
+      <c r="M18" s="184"/>
+      <c r="N18" s="185"/>
+      <c r="O18" s="195" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="184"/>
-      <c r="R18" s="46"/>
-      <c r="S18" s="46"/>
-      <c r="T18" s="47"/>
+      <c r="P18" s="184"/>
+      <c r="Q18" s="185"/>
+      <c r="R18" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S18" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T18" s="47" t="s">
+        <v>108</v>
+      </c>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
@@ -10094,37 +10116,37 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A19" s="185">
+      <c r="A19" s="192">
         <v>4</v>
       </c>
-      <c r="B19" s="184"/>
-      <c r="C19" s="186" t="s">
+      <c r="B19" s="185"/>
+      <c r="C19" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="184"/>
-      <c r="E19" s="186" t="s">
+      <c r="D19" s="185"/>
+      <c r="E19" s="193" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="184"/>
-      <c r="G19" s="187" t="s">
+      <c r="F19" s="185"/>
+      <c r="G19" s="194" t="s">
         <v>96</v>
       </c>
-      <c r="H19" s="183"/>
-      <c r="I19" s="184"/>
-      <c r="J19" s="187" t="s">
+      <c r="H19" s="184"/>
+      <c r="I19" s="185"/>
+      <c r="J19" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="184"/>
-      <c r="L19" s="182" t="s">
+      <c r="K19" s="185"/>
+      <c r="L19" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M19" s="183"/>
-      <c r="N19" s="184"/>
-      <c r="O19" s="182" t="s">
+      <c r="M19" s="184"/>
+      <c r="N19" s="185"/>
+      <c r="O19" s="195" t="s">
         <v>95</v>
       </c>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="184"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="185"/>
       <c r="R19" s="46"/>
       <c r="S19" s="46"/>
       <c r="T19" s="47"/>
@@ -10136,37 +10158,37 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A20" s="185">
+      <c r="A20" s="192">
         <v>5</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="186" t="s">
+      <c r="B20" s="185"/>
+      <c r="C20" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="184"/>
-      <c r="E20" s="186" t="s">
+      <c r="D20" s="185"/>
+      <c r="E20" s="193" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="184"/>
-      <c r="G20" s="187" t="s">
+      <c r="F20" s="185"/>
+      <c r="G20" s="194" t="s">
         <v>100</v>
       </c>
-      <c r="H20" s="183"/>
-      <c r="I20" s="184"/>
-      <c r="J20" s="187" t="s">
+      <c r="H20" s="184"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="184"/>
-      <c r="L20" s="182" t="s">
+      <c r="K20" s="185"/>
+      <c r="L20" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M20" s="183"/>
-      <c r="N20" s="184"/>
-      <c r="O20" s="182" t="s">
+      <c r="M20" s="184"/>
+      <c r="N20" s="185"/>
+      <c r="O20" s="195" t="s">
         <v>99</v>
       </c>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="184"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="185"/>
       <c r="R20" s="46"/>
       <c r="S20" s="46"/>
       <c r="T20" s="47"/>
@@ -10178,40 +10200,46 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A21" s="185">
+      <c r="A21" s="192">
         <v>6</v>
       </c>
-      <c r="B21" s="184"/>
-      <c r="C21" s="186" t="s">
+      <c r="B21" s="185"/>
+      <c r="C21" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="184"/>
-      <c r="E21" s="186" t="s">
+      <c r="D21" s="185"/>
+      <c r="E21" s="193" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="184"/>
-      <c r="G21" s="187" t="s">
+      <c r="F21" s="185"/>
+      <c r="G21" s="194" t="s">
         <v>101</v>
       </c>
-      <c r="H21" s="183"/>
-      <c r="I21" s="184"/>
-      <c r="J21" s="187" t="s">
+      <c r="H21" s="184"/>
+      <c r="I21" s="185"/>
+      <c r="J21" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K21" s="184"/>
-      <c r="L21" s="182" t="s">
+      <c r="K21" s="185"/>
+      <c r="L21" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M21" s="183"/>
-      <c r="N21" s="184"/>
-      <c r="O21" s="182" t="s">
+      <c r="M21" s="184"/>
+      <c r="N21" s="185"/>
+      <c r="O21" s="195" t="s">
         <v>102</v>
       </c>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="184"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="47"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="185"/>
+      <c r="R21" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S21" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T21" s="47" t="s">
+        <v>108</v>
+      </c>
       <c r="U21" s="48"/>
       <c r="V21" s="48"/>
       <c r="W21" s="48"/>
@@ -10220,23 +10248,23 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A22" s="185"/>
-      <c r="B22" s="184"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="184"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="184"/>
-      <c r="G22" s="187"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="184"/>
-      <c r="J22" s="187"/>
-      <c r="K22" s="184"/>
-      <c r="L22" s="182"/>
-      <c r="M22" s="183"/>
-      <c r="N22" s="184"/>
-      <c r="O22" s="182"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="184"/>
+      <c r="A22" s="192"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="185"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="185"/>
+      <c r="G22" s="194"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="185"/>
+      <c r="J22" s="194"/>
+      <c r="K22" s="185"/>
+      <c r="L22" s="195"/>
+      <c r="M22" s="184"/>
+      <c r="N22" s="185"/>
+      <c r="O22" s="195"/>
+      <c r="P22" s="184"/>
+      <c r="Q22" s="185"/>
       <c r="R22" s="46"/>
       <c r="S22" s="46"/>
       <c r="T22" s="47"/>
@@ -10248,23 +10276,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
-      <c r="B23" s="184"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="184"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="184"/>
-      <c r="G23" s="187"/>
-      <c r="H23" s="183"/>
-      <c r="I23" s="184"/>
-      <c r="J23" s="187"/>
-      <c r="K23" s="184"/>
-      <c r="L23" s="182"/>
-      <c r="M23" s="183"/>
-      <c r="N23" s="184"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="183"/>
-      <c r="Q23" s="184"/>
+      <c r="A23" s="192"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="193"/>
+      <c r="D23" s="185"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="185"/>
+      <c r="G23" s="194"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="185"/>
+      <c r="J23" s="194"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="195"/>
+      <c r="M23" s="184"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="195"/>
+      <c r="P23" s="184"/>
+      <c r="Q23" s="185"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -10276,23 +10304,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
-      <c r="B24" s="184"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="184"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="184"/>
-      <c r="G24" s="187"/>
-      <c r="H24" s="183"/>
-      <c r="I24" s="184"/>
-      <c r="J24" s="187"/>
-      <c r="K24" s="184"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="183"/>
-      <c r="N24" s="184"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="184"/>
+      <c r="A24" s="192"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="193"/>
+      <c r="D24" s="185"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="185"/>
+      <c r="G24" s="194"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="185"/>
+      <c r="J24" s="194"/>
+      <c r="K24" s="185"/>
+      <c r="L24" s="195"/>
+      <c r="M24" s="184"/>
+      <c r="N24" s="185"/>
+      <c r="O24" s="195"/>
+      <c r="P24" s="184"/>
+      <c r="Q24" s="185"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -10304,23 +10332,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
-      <c r="B25" s="184"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="184"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="187"/>
-      <c r="H25" s="183"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="187"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="183"/>
-      <c r="N25" s="184"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="184"/>
+      <c r="A25" s="192"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="193"/>
+      <c r="D25" s="185"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="185"/>
+      <c r="G25" s="194"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="194"/>
+      <c r="K25" s="185"/>
+      <c r="L25" s="195"/>
+      <c r="M25" s="184"/>
+      <c r="N25" s="185"/>
+      <c r="O25" s="195"/>
+      <c r="P25" s="184"/>
+      <c r="Q25" s="185"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -10332,23 +10360,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
-      <c r="B26" s="184"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="184"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="187"/>
-      <c r="H26" s="183"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="187"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="182"/>
-      <c r="M26" s="183"/>
-      <c r="N26" s="184"/>
-      <c r="O26" s="182"/>
-      <c r="P26" s="183"/>
-      <c r="Q26" s="184"/>
+      <c r="A26" s="192"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="193"/>
+      <c r="D26" s="185"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="185"/>
+      <c r="G26" s="194"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="194"/>
+      <c r="K26" s="185"/>
+      <c r="L26" s="195"/>
+      <c r="M26" s="184"/>
+      <c r="N26" s="185"/>
+      <c r="O26" s="195"/>
+      <c r="P26" s="184"/>
+      <c r="Q26" s="185"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -10360,23 +10388,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="184"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="184"/>
-      <c r="G27" s="187"/>
-      <c r="H27" s="183"/>
-      <c r="I27" s="184"/>
-      <c r="J27" s="187"/>
-      <c r="K27" s="184"/>
-      <c r="L27" s="182"/>
-      <c r="M27" s="183"/>
-      <c r="N27" s="184"/>
-      <c r="O27" s="182"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="184"/>
+      <c r="A27" s="192"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="193"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="195"/>
+      <c r="M27" s="184"/>
+      <c r="N27" s="185"/>
+      <c r="O27" s="195"/>
+      <c r="P27" s="184"/>
+      <c r="Q27" s="185"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -10388,23 +10416,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="184"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="184"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="184"/>
-      <c r="G28" s="187"/>
-      <c r="H28" s="183"/>
-      <c r="I28" s="184"/>
-      <c r="J28" s="187"/>
-      <c r="K28" s="184"/>
-      <c r="L28" s="182"/>
-      <c r="M28" s="183"/>
-      <c r="N28" s="184"/>
-      <c r="O28" s="182"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="184"/>
+      <c r="A28" s="192"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="185"/>
+      <c r="E28" s="193"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="194"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="194"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="195"/>
+      <c r="M28" s="184"/>
+      <c r="N28" s="185"/>
+      <c r="O28" s="195"/>
+      <c r="P28" s="184"/>
+      <c r="Q28" s="185"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -10416,23 +10444,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
-      <c r="B29" s="184"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="187"/>
-      <c r="H29" s="183"/>
-      <c r="I29" s="184"/>
-      <c r="J29" s="187"/>
-      <c r="K29" s="184"/>
-      <c r="L29" s="182"/>
-      <c r="M29" s="183"/>
-      <c r="N29" s="184"/>
-      <c r="O29" s="182"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="184"/>
+      <c r="A29" s="192"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="193"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="193"/>
+      <c r="F29" s="185"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="194"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="195"/>
+      <c r="M29" s="184"/>
+      <c r="N29" s="185"/>
+      <c r="O29" s="195"/>
+      <c r="P29" s="184"/>
+      <c r="Q29" s="185"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -10444,23 +10472,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
-      <c r="B30" s="184"/>
-      <c r="C30" s="186"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="187"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="184"/>
-      <c r="J30" s="187"/>
-      <c r="K30" s="184"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="183"/>
-      <c r="N30" s="184"/>
-      <c r="O30" s="182"/>
-      <c r="P30" s="183"/>
-      <c r="Q30" s="184"/>
+      <c r="A30" s="192"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="193"/>
+      <c r="D30" s="185"/>
+      <c r="E30" s="193"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="194"/>
+      <c r="H30" s="184"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="194"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="195"/>
+      <c r="M30" s="184"/>
+      <c r="N30" s="185"/>
+      <c r="O30" s="195"/>
+      <c r="P30" s="184"/>
+      <c r="Q30" s="185"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -10472,23 +10500,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="179"/>
-      <c r="B31" s="178"/>
-      <c r="C31" s="180"/>
-      <c r="D31" s="178"/>
-      <c r="E31" s="180"/>
-      <c r="F31" s="178"/>
-      <c r="G31" s="181"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="176"/>
-      <c r="M31" s="177"/>
-      <c r="N31" s="178"/>
-      <c r="O31" s="176"/>
-      <c r="P31" s="177"/>
-      <c r="Q31" s="178"/>
+      <c r="A31" s="200"/>
+      <c r="B31" s="199"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="199"/>
+      <c r="E31" s="201"/>
+      <c r="F31" s="199"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="198"/>
+      <c r="I31" s="199"/>
+      <c r="J31" s="202"/>
+      <c r="K31" s="199"/>
+      <c r="L31" s="197"/>
+      <c r="M31" s="198"/>
+      <c r="N31" s="199"/>
+      <c r="O31" s="197"/>
+      <c r="P31" s="198"/>
+      <c r="Q31" s="199"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11486,121 +11514,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -11622,6 +11535,121 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11644,72 +11672,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="224" t="s">
+      <c r="B1" s="212"/>
+      <c r="C1" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="225"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="227" t="s">
+      <c r="D1" s="214"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="228"/>
-      <c r="H1" s="228"/>
-      <c r="I1" s="228"/>
-      <c r="J1" s="228"/>
-      <c r="K1" s="228"/>
-      <c r="L1" s="228"/>
-      <c r="M1" s="229"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="218"/>
       <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="227" t="s">
+      <c r="O1" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="229"/>
+      <c r="P1" s="218"/>
       <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="227" t="s">
+      <c r="R1" s="216" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="229"/>
+      <c r="S1" s="218"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="223"/>
-      <c r="B2" s="223"/>
-      <c r="C2" s="224" t="s">
+      <c r="A2" s="212"/>
+      <c r="B2" s="212"/>
+      <c r="C2" s="213" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="225"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="227" t="s">
+      <c r="D2" s="214"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="228"/>
-      <c r="H2" s="228"/>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="228"/>
-      <c r="M2" s="229"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="217"/>
+      <c r="J2" s="217"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="217"/>
+      <c r="M2" s="218"/>
       <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="230">
+      <c r="O2" s="219">
         <v>45818</v>
       </c>
-      <c r="P2" s="231"/>
+      <c r="P2" s="220"/>
       <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="232" t="s">
+      <c r="R2" s="221" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="233"/>
+      <c r="S2" s="222"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11739,33 +11767,33 @@
       <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="203" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="215"/>
-      <c r="E4" s="215"/>
-      <c r="F4" s="215"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="214" t="s">
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="203" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="215"/>
-      <c r="J4" s="215"/>
-      <c r="K4" s="215"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="216"/>
-      <c r="N4" s="214" t="s">
+      <c r="I4" s="204"/>
+      <c r="J4" s="204"/>
+      <c r="K4" s="204"/>
+      <c r="L4" s="204"/>
+      <c r="M4" s="205"/>
+      <c r="N4" s="203" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="215"/>
-      <c r="P4" s="216"/>
+      <c r="O4" s="204"/>
+      <c r="P4" s="205"/>
       <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="214" t="s">
+      <c r="R4" s="203" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="216"/>
+      <c r="S4" s="205"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59">
@@ -11774,1021 +11802,1209 @@
       <c r="B5" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="C5" s="206" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="217"/>
-      <c r="E5" s="217"/>
-      <c r="F5" s="217"/>
-      <c r="G5" s="217"/>
-      <c r="H5" s="217" t="s">
+      <c r="D5" s="206"/>
+      <c r="E5" s="206"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="206" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
-      <c r="L5" s="217"/>
-      <c r="M5" s="217"/>
-      <c r="N5" s="218" t="s">
+      <c r="I5" s="206"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="206"/>
+      <c r="L5" s="206"/>
+      <c r="M5" s="206"/>
+      <c r="N5" s="207" t="s">
         <v>107</v>
       </c>
-      <c r="O5" s="219"/>
-      <c r="P5" s="220"/>
+      <c r="O5" s="208"/>
+      <c r="P5" s="209"/>
       <c r="Q5" s="64">
         <v>45818</v>
       </c>
-      <c r="R5" s="221"/>
-      <c r="S5" s="222"/>
+      <c r="R5" s="210"/>
+      <c r="S5" s="211"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="203"/>
-      <c r="D6" s="203"/>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="203"/>
-      <c r="J6" s="203"/>
-      <c r="K6" s="203"/>
-      <c r="L6" s="203"/>
-      <c r="M6" s="203"/>
-      <c r="N6" s="211"/>
-      <c r="O6" s="212"/>
-      <c r="P6" s="213"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="228"/>
+      <c r="O6" s="229"/>
+      <c r="P6" s="230"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="210"/>
-      <c r="S6" s="210"/>
+      <c r="R6" s="227"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="203"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="203"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="203"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="203"/>
-      <c r="K7" s="203"/>
-      <c r="L7" s="203"/>
-      <c r="M7" s="203"/>
-      <c r="N7" s="207"/>
-      <c r="O7" s="208"/>
-      <c r="P7" s="209"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="223"/>
+      <c r="G7" s="223"/>
+      <c r="H7" s="223"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="223"/>
+      <c r="K7" s="223"/>
+      <c r="L7" s="223"/>
+      <c r="M7" s="223"/>
+      <c r="N7" s="224"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="226"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="210"/>
-      <c r="S7" s="210"/>
+      <c r="R7" s="227"/>
+      <c r="S7" s="227"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="203"/>
-      <c r="H8" s="203"/>
-      <c r="I8" s="203"/>
-      <c r="J8" s="203"/>
-      <c r="K8" s="203"/>
-      <c r="L8" s="203"/>
-      <c r="M8" s="203"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="208"/>
-      <c r="P8" s="209"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="224"/>
+      <c r="O8" s="225"/>
+      <c r="P8" s="226"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="210"/>
-      <c r="S8" s="210"/>
+      <c r="R8" s="227"/>
+      <c r="S8" s="227"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="203"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="203"/>
-      <c r="H9" s="203"/>
-      <c r="I9" s="203"/>
-      <c r="J9" s="203"/>
-      <c r="K9" s="203"/>
-      <c r="L9" s="203"/>
-      <c r="M9" s="203"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="208"/>
-      <c r="P9" s="209"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="223"/>
+      <c r="H9" s="223"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="223"/>
+      <c r="K9" s="223"/>
+      <c r="L9" s="223"/>
+      <c r="M9" s="223"/>
+      <c r="N9" s="224"/>
+      <c r="O9" s="225"/>
+      <c r="P9" s="226"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="210"/>
-      <c r="S9" s="210"/>
+      <c r="R9" s="227"/>
+      <c r="S9" s="227"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="203"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="203"/>
-      <c r="H10" s="204"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
-      <c r="L10" s="205"/>
-      <c r="M10" s="206"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="208"/>
-      <c r="P10" s="209"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="223"/>
+      <c r="F10" s="223"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="231"/>
+      <c r="I10" s="232"/>
+      <c r="J10" s="232"/>
+      <c r="K10" s="232"/>
+      <c r="L10" s="232"/>
+      <c r="M10" s="233"/>
+      <c r="N10" s="224"/>
+      <c r="O10" s="225"/>
+      <c r="P10" s="226"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="210"/>
-      <c r="S10" s="210"/>
+      <c r="R10" s="227"/>
+      <c r="S10" s="227"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="203"/>
-      <c r="D11" s="203"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="203"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="204"/>
-      <c r="I11" s="205"/>
-      <c r="J11" s="205"/>
-      <c r="K11" s="205"/>
-      <c r="L11" s="205"/>
-      <c r="M11" s="206"/>
-      <c r="N11" s="207"/>
-      <c r="O11" s="208"/>
-      <c r="P11" s="209"/>
+      <c r="C11" s="223"/>
+      <c r="D11" s="223"/>
+      <c r="E11" s="223"/>
+      <c r="F11" s="223"/>
+      <c r="G11" s="223"/>
+      <c r="H11" s="231"/>
+      <c r="I11" s="232"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="232"/>
+      <c r="L11" s="232"/>
+      <c r="M11" s="233"/>
+      <c r="N11" s="224"/>
+      <c r="O11" s="225"/>
+      <c r="P11" s="226"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="210"/>
-      <c r="S11" s="210"/>
+      <c r="R11" s="227"/>
+      <c r="S11" s="227"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="204"/>
-      <c r="I12" s="205"/>
-      <c r="J12" s="205"/>
-      <c r="K12" s="205"/>
-      <c r="L12" s="205"/>
-      <c r="M12" s="206"/>
-      <c r="N12" s="207"/>
-      <c r="O12" s="208"/>
-      <c r="P12" s="209"/>
+      <c r="C12" s="223"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="223"/>
+      <c r="F12" s="223"/>
+      <c r="G12" s="223"/>
+      <c r="H12" s="231"/>
+      <c r="I12" s="232"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="232"/>
+      <c r="M12" s="233"/>
+      <c r="N12" s="224"/>
+      <c r="O12" s="225"/>
+      <c r="P12" s="226"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="210"/>
-      <c r="S12" s="210"/>
+      <c r="R12" s="227"/>
+      <c r="S12" s="227"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="203"/>
-      <c r="G13" s="203"/>
-      <c r="H13" s="204"/>
-      <c r="I13" s="205"/>
-      <c r="J13" s="205"/>
-      <c r="K13" s="205"/>
-      <c r="L13" s="205"/>
-      <c r="M13" s="206"/>
-      <c r="N13" s="207"/>
-      <c r="O13" s="208"/>
-      <c r="P13" s="209"/>
+      <c r="C13" s="223"/>
+      <c r="D13" s="223"/>
+      <c r="E13" s="223"/>
+      <c r="F13" s="223"/>
+      <c r="G13" s="223"/>
+      <c r="H13" s="231"/>
+      <c r="I13" s="232"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="232"/>
+      <c r="L13" s="232"/>
+      <c r="M13" s="233"/>
+      <c r="N13" s="224"/>
+      <c r="O13" s="225"/>
+      <c r="P13" s="226"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="210"/>
-      <c r="S13" s="210"/>
+      <c r="R13" s="227"/>
+      <c r="S13" s="227"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="204"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="205"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="205"/>
-      <c r="M14" s="206"/>
-      <c r="N14" s="207"/>
-      <c r="O14" s="208"/>
-      <c r="P14" s="209"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="223"/>
+      <c r="E14" s="223"/>
+      <c r="F14" s="223"/>
+      <c r="G14" s="223"/>
+      <c r="H14" s="231"/>
+      <c r="I14" s="232"/>
+      <c r="J14" s="232"/>
+      <c r="K14" s="232"/>
+      <c r="L14" s="232"/>
+      <c r="M14" s="233"/>
+      <c r="N14" s="224"/>
+      <c r="O14" s="225"/>
+      <c r="P14" s="226"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
+      <c r="R14" s="227"/>
+      <c r="S14" s="227"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="203"/>
-      <c r="H15" s="204"/>
-      <c r="I15" s="205"/>
-      <c r="J15" s="205"/>
-      <c r="K15" s="205"/>
-      <c r="L15" s="205"/>
-      <c r="M15" s="206"/>
-      <c r="N15" s="207"/>
-      <c r="O15" s="208"/>
-      <c r="P15" s="209"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="223"/>
+      <c r="E15" s="223"/>
+      <c r="F15" s="223"/>
+      <c r="G15" s="223"/>
+      <c r="H15" s="231"/>
+      <c r="I15" s="232"/>
+      <c r="J15" s="232"/>
+      <c r="K15" s="232"/>
+      <c r="L15" s="232"/>
+      <c r="M15" s="233"/>
+      <c r="N15" s="224"/>
+      <c r="O15" s="225"/>
+      <c r="P15" s="226"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="210"/>
-      <c r="S15" s="210"/>
+      <c r="R15" s="227"/>
+      <c r="S15" s="227"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="203"/>
-      <c r="G16" s="203"/>
-      <c r="H16" s="204"/>
-      <c r="I16" s="205"/>
-      <c r="J16" s="205"/>
-      <c r="K16" s="205"/>
-      <c r="L16" s="205"/>
-      <c r="M16" s="206"/>
-      <c r="N16" s="207"/>
-      <c r="O16" s="208"/>
-      <c r="P16" s="209"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="223"/>
+      <c r="H16" s="231"/>
+      <c r="I16" s="232"/>
+      <c r="J16" s="232"/>
+      <c r="K16" s="232"/>
+      <c r="L16" s="232"/>
+      <c r="M16" s="233"/>
+      <c r="N16" s="224"/>
+      <c r="O16" s="225"/>
+      <c r="P16" s="226"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="210"/>
-      <c r="S16" s="210"/>
+      <c r="R16" s="227"/>
+      <c r="S16" s="227"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="203"/>
-      <c r="H17" s="204"/>
-      <c r="I17" s="205"/>
-      <c r="J17" s="205"/>
-      <c r="K17" s="205"/>
-      <c r="L17" s="205"/>
-      <c r="M17" s="206"/>
-      <c r="N17" s="207"/>
-      <c r="O17" s="208"/>
-      <c r="P17" s="209"/>
+      <c r="C17" s="223"/>
+      <c r="D17" s="223"/>
+      <c r="E17" s="223"/>
+      <c r="F17" s="223"/>
+      <c r="G17" s="223"/>
+      <c r="H17" s="231"/>
+      <c r="I17" s="232"/>
+      <c r="J17" s="232"/>
+      <c r="K17" s="232"/>
+      <c r="L17" s="232"/>
+      <c r="M17" s="233"/>
+      <c r="N17" s="224"/>
+      <c r="O17" s="225"/>
+      <c r="P17" s="226"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="210"/>
-      <c r="S17" s="210"/>
+      <c r="R17" s="227"/>
+      <c r="S17" s="227"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="203"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="203"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="204"/>
-      <c r="I18" s="205"/>
-      <c r="J18" s="205"/>
-      <c r="K18" s="205"/>
-      <c r="L18" s="205"/>
-      <c r="M18" s="206"/>
-      <c r="N18" s="207"/>
-      <c r="O18" s="208"/>
-      <c r="P18" s="209"/>
+      <c r="C18" s="223"/>
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="231"/>
+      <c r="I18" s="232"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="232"/>
+      <c r="L18" s="232"/>
+      <c r="M18" s="233"/>
+      <c r="N18" s="224"/>
+      <c r="O18" s="225"/>
+      <c r="P18" s="226"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="210"/>
-      <c r="S18" s="210"/>
+      <c r="R18" s="227"/>
+      <c r="S18" s="227"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="203"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="203"/>
-      <c r="H19" s="204"/>
-      <c r="I19" s="205"/>
-      <c r="J19" s="205"/>
-      <c r="K19" s="205"/>
-      <c r="L19" s="205"/>
-      <c r="M19" s="206"/>
-      <c r="N19" s="207"/>
-      <c r="O19" s="208"/>
-      <c r="P19" s="209"/>
+      <c r="C19" s="223"/>
+      <c r="D19" s="223"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="223"/>
+      <c r="G19" s="223"/>
+      <c r="H19" s="231"/>
+      <c r="I19" s="232"/>
+      <c r="J19" s="232"/>
+      <c r="K19" s="232"/>
+      <c r="L19" s="232"/>
+      <c r="M19" s="233"/>
+      <c r="N19" s="224"/>
+      <c r="O19" s="225"/>
+      <c r="P19" s="226"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="210"/>
-      <c r="S19" s="210"/>
+      <c r="R19" s="227"/>
+      <c r="S19" s="227"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="203"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="203"/>
-      <c r="G20" s="203"/>
-      <c r="H20" s="204"/>
-      <c r="I20" s="205"/>
-      <c r="J20" s="205"/>
-      <c r="K20" s="205"/>
-      <c r="L20" s="205"/>
-      <c r="M20" s="206"/>
-      <c r="N20" s="207"/>
-      <c r="O20" s="208"/>
-      <c r="P20" s="209"/>
+      <c r="C20" s="223"/>
+      <c r="D20" s="223"/>
+      <c r="E20" s="223"/>
+      <c r="F20" s="223"/>
+      <c r="G20" s="223"/>
+      <c r="H20" s="231"/>
+      <c r="I20" s="232"/>
+      <c r="J20" s="232"/>
+      <c r="K20" s="232"/>
+      <c r="L20" s="232"/>
+      <c r="M20" s="233"/>
+      <c r="N20" s="224"/>
+      <c r="O20" s="225"/>
+      <c r="P20" s="226"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="210"/>
-      <c r="S20" s="210"/>
+      <c r="R20" s="227"/>
+      <c r="S20" s="227"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="203"/>
-      <c r="D21" s="203"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="203"/>
-      <c r="H21" s="204"/>
-      <c r="I21" s="205"/>
-      <c r="J21" s="205"/>
-      <c r="K21" s="205"/>
-      <c r="L21" s="205"/>
-      <c r="M21" s="206"/>
-      <c r="N21" s="207"/>
-      <c r="O21" s="208"/>
-      <c r="P21" s="209"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="231"/>
+      <c r="I21" s="232"/>
+      <c r="J21" s="232"/>
+      <c r="K21" s="232"/>
+      <c r="L21" s="232"/>
+      <c r="M21" s="233"/>
+      <c r="N21" s="224"/>
+      <c r="O21" s="225"/>
+      <c r="P21" s="226"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="210"/>
-      <c r="S21" s="210"/>
+      <c r="R21" s="227"/>
+      <c r="S21" s="227"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="204"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="205"/>
-      <c r="K22" s="205"/>
-      <c r="L22" s="205"/>
-      <c r="M22" s="206"/>
-      <c r="N22" s="207"/>
-      <c r="O22" s="208"/>
-      <c r="P22" s="209"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="231"/>
+      <c r="I22" s="232"/>
+      <c r="J22" s="232"/>
+      <c r="K22" s="232"/>
+      <c r="L22" s="232"/>
+      <c r="M22" s="233"/>
+      <c r="N22" s="224"/>
+      <c r="O22" s="225"/>
+      <c r="P22" s="226"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="210"/>
-      <c r="S22" s="210"/>
+      <c r="R22" s="227"/>
+      <c r="S22" s="227"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="203"/>
-      <c r="D23" s="203"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="203"/>
-      <c r="G23" s="203"/>
-      <c r="H23" s="204"/>
-      <c r="I23" s="205"/>
-      <c r="J23" s="205"/>
-      <c r="K23" s="205"/>
-      <c r="L23" s="205"/>
-      <c r="M23" s="206"/>
-      <c r="N23" s="207"/>
-      <c r="O23" s="208"/>
-      <c r="P23" s="209"/>
+      <c r="C23" s="223"/>
+      <c r="D23" s="223"/>
+      <c r="E23" s="223"/>
+      <c r="F23" s="223"/>
+      <c r="G23" s="223"/>
+      <c r="H23" s="231"/>
+      <c r="I23" s="232"/>
+      <c r="J23" s="232"/>
+      <c r="K23" s="232"/>
+      <c r="L23" s="232"/>
+      <c r="M23" s="233"/>
+      <c r="N23" s="224"/>
+      <c r="O23" s="225"/>
+      <c r="P23" s="226"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="210"/>
-      <c r="S23" s="210"/>
+      <c r="R23" s="227"/>
+      <c r="S23" s="227"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="203"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="203"/>
-      <c r="G24" s="203"/>
-      <c r="H24" s="204"/>
-      <c r="I24" s="205"/>
-      <c r="J24" s="205"/>
-      <c r="K24" s="205"/>
-      <c r="L24" s="205"/>
-      <c r="M24" s="206"/>
-      <c r="N24" s="207"/>
-      <c r="O24" s="208"/>
-      <c r="P24" s="209"/>
+      <c r="C24" s="223"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="223"/>
+      <c r="H24" s="231"/>
+      <c r="I24" s="232"/>
+      <c r="J24" s="232"/>
+      <c r="K24" s="232"/>
+      <c r="L24" s="232"/>
+      <c r="M24" s="233"/>
+      <c r="N24" s="224"/>
+      <c r="O24" s="225"/>
+      <c r="P24" s="226"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="210"/>
-      <c r="S24" s="210"/>
+      <c r="R24" s="227"/>
+      <c r="S24" s="227"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="203"/>
-      <c r="D25" s="203"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="203"/>
-      <c r="G25" s="203"/>
-      <c r="H25" s="204"/>
-      <c r="I25" s="205"/>
-      <c r="J25" s="205"/>
-      <c r="K25" s="205"/>
-      <c r="L25" s="205"/>
-      <c r="M25" s="206"/>
-      <c r="N25" s="207"/>
-      <c r="O25" s="208"/>
-      <c r="P25" s="209"/>
+      <c r="C25" s="223"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="231"/>
+      <c r="I25" s="232"/>
+      <c r="J25" s="232"/>
+      <c r="K25" s="232"/>
+      <c r="L25" s="232"/>
+      <c r="M25" s="233"/>
+      <c r="N25" s="224"/>
+      <c r="O25" s="225"/>
+      <c r="P25" s="226"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="210"/>
-      <c r="S25" s="210"/>
+      <c r="R25" s="227"/>
+      <c r="S25" s="227"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="203"/>
-      <c r="D26" s="203"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="203"/>
-      <c r="G26" s="203"/>
-      <c r="H26" s="204"/>
-      <c r="I26" s="205"/>
-      <c r="J26" s="205"/>
-      <c r="K26" s="205"/>
-      <c r="L26" s="205"/>
-      <c r="M26" s="206"/>
-      <c r="N26" s="207"/>
-      <c r="O26" s="208"/>
-      <c r="P26" s="209"/>
+      <c r="C26" s="223"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="223"/>
+      <c r="F26" s="223"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="231"/>
+      <c r="I26" s="232"/>
+      <c r="J26" s="232"/>
+      <c r="K26" s="232"/>
+      <c r="L26" s="232"/>
+      <c r="M26" s="233"/>
+      <c r="N26" s="224"/>
+      <c r="O26" s="225"/>
+      <c r="P26" s="226"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="210"/>
-      <c r="S26" s="210"/>
+      <c r="R26" s="227"/>
+      <c r="S26" s="227"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="203"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="204"/>
-      <c r="I27" s="205"/>
-      <c r="J27" s="205"/>
-      <c r="K27" s="205"/>
-      <c r="L27" s="205"/>
-      <c r="M27" s="206"/>
-      <c r="N27" s="207"/>
-      <c r="O27" s="208"/>
-      <c r="P27" s="209"/>
+      <c r="C27" s="223"/>
+      <c r="D27" s="223"/>
+      <c r="E27" s="223"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="223"/>
+      <c r="H27" s="231"/>
+      <c r="I27" s="232"/>
+      <c r="J27" s="232"/>
+      <c r="K27" s="232"/>
+      <c r="L27" s="232"/>
+      <c r="M27" s="233"/>
+      <c r="N27" s="224"/>
+      <c r="O27" s="225"/>
+      <c r="P27" s="226"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="210"/>
-      <c r="S27" s="210"/>
+      <c r="R27" s="227"/>
+      <c r="S27" s="227"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="203"/>
-      <c r="D28" s="203"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="203"/>
-      <c r="G28" s="203"/>
-      <c r="H28" s="204"/>
-      <c r="I28" s="205"/>
-      <c r="J28" s="205"/>
-      <c r="K28" s="205"/>
-      <c r="L28" s="205"/>
-      <c r="M28" s="206"/>
-      <c r="N28" s="207"/>
-      <c r="O28" s="208"/>
-      <c r="P28" s="209"/>
+      <c r="C28" s="223"/>
+      <c r="D28" s="223"/>
+      <c r="E28" s="223"/>
+      <c r="F28" s="223"/>
+      <c r="G28" s="223"/>
+      <c r="H28" s="231"/>
+      <c r="I28" s="232"/>
+      <c r="J28" s="232"/>
+      <c r="K28" s="232"/>
+      <c r="L28" s="232"/>
+      <c r="M28" s="233"/>
+      <c r="N28" s="224"/>
+      <c r="O28" s="225"/>
+      <c r="P28" s="226"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="210"/>
-      <c r="S28" s="210"/>
+      <c r="R28" s="227"/>
+      <c r="S28" s="227"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="203"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="203"/>
-      <c r="G29" s="203"/>
-      <c r="H29" s="204"/>
-      <c r="I29" s="205"/>
-      <c r="J29" s="205"/>
-      <c r="K29" s="205"/>
-      <c r="L29" s="205"/>
-      <c r="M29" s="206"/>
-      <c r="N29" s="207"/>
-      <c r="O29" s="208"/>
-      <c r="P29" s="209"/>
+      <c r="C29" s="223"/>
+      <c r="D29" s="223"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="223"/>
+      <c r="G29" s="223"/>
+      <c r="H29" s="231"/>
+      <c r="I29" s="232"/>
+      <c r="J29" s="232"/>
+      <c r="K29" s="232"/>
+      <c r="L29" s="232"/>
+      <c r="M29" s="233"/>
+      <c r="N29" s="224"/>
+      <c r="O29" s="225"/>
+      <c r="P29" s="226"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="210"/>
-      <c r="S29" s="210"/>
+      <c r="R29" s="227"/>
+      <c r="S29" s="227"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="203"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="203"/>
-      <c r="G30" s="203"/>
-      <c r="H30" s="204"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="205"/>
-      <c r="K30" s="205"/>
-      <c r="L30" s="205"/>
-      <c r="M30" s="206"/>
-      <c r="N30" s="207"/>
-      <c r="O30" s="208"/>
-      <c r="P30" s="209"/>
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="231"/>
+      <c r="I30" s="232"/>
+      <c r="J30" s="232"/>
+      <c r="K30" s="232"/>
+      <c r="L30" s="232"/>
+      <c r="M30" s="233"/>
+      <c r="N30" s="224"/>
+      <c r="O30" s="225"/>
+      <c r="P30" s="226"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="210"/>
-      <c r="S30" s="210"/>
+      <c r="R30" s="227"/>
+      <c r="S30" s="227"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="203"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="203"/>
-      <c r="H31" s="204"/>
-      <c r="I31" s="205"/>
-      <c r="J31" s="205"/>
-      <c r="K31" s="205"/>
-      <c r="L31" s="205"/>
-      <c r="M31" s="206"/>
-      <c r="N31" s="207"/>
-      <c r="O31" s="208"/>
-      <c r="P31" s="209"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="231"/>
+      <c r="I31" s="232"/>
+      <c r="J31" s="232"/>
+      <c r="K31" s="232"/>
+      <c r="L31" s="232"/>
+      <c r="M31" s="233"/>
+      <c r="N31" s="224"/>
+      <c r="O31" s="225"/>
+      <c r="P31" s="226"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
+      <c r="R31" s="227"/>
+      <c r="S31" s="227"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="203"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="203"/>
-      <c r="G32" s="203"/>
-      <c r="H32" s="204"/>
-      <c r="I32" s="205"/>
-      <c r="J32" s="205"/>
-      <c r="K32" s="205"/>
-      <c r="L32" s="205"/>
-      <c r="M32" s="206"/>
-      <c r="N32" s="207"/>
-      <c r="O32" s="208"/>
-      <c r="P32" s="209"/>
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="231"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="232"/>
+      <c r="L32" s="232"/>
+      <c r="M32" s="233"/>
+      <c r="N32" s="224"/>
+      <c r="O32" s="225"/>
+      <c r="P32" s="226"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="210"/>
-      <c r="S32" s="210"/>
+      <c r="R32" s="227"/>
+      <c r="S32" s="227"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="203"/>
-      <c r="H33" s="204"/>
-      <c r="I33" s="205"/>
-      <c r="J33" s="205"/>
-      <c r="K33" s="205"/>
-      <c r="L33" s="205"/>
-      <c r="M33" s="206"/>
-      <c r="N33" s="207"/>
-      <c r="O33" s="208"/>
-      <c r="P33" s="209"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="231"/>
+      <c r="I33" s="232"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="232"/>
+      <c r="M33" s="233"/>
+      <c r="N33" s="224"/>
+      <c r="O33" s="225"/>
+      <c r="P33" s="226"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="210"/>
-      <c r="S33" s="210"/>
+      <c r="R33" s="227"/>
+      <c r="S33" s="227"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="203"/>
-      <c r="D34" s="203"/>
-      <c r="E34" s="203"/>
-      <c r="F34" s="203"/>
-      <c r="G34" s="203"/>
-      <c r="H34" s="204"/>
-      <c r="I34" s="205"/>
-      <c r="J34" s="205"/>
-      <c r="K34" s="205"/>
-      <c r="L34" s="205"/>
-      <c r="M34" s="206"/>
-      <c r="N34" s="207"/>
-      <c r="O34" s="208"/>
-      <c r="P34" s="209"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="231"/>
+      <c r="I34" s="232"/>
+      <c r="J34" s="232"/>
+      <c r="K34" s="232"/>
+      <c r="L34" s="232"/>
+      <c r="M34" s="233"/>
+      <c r="N34" s="224"/>
+      <c r="O34" s="225"/>
+      <c r="P34" s="226"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="210"/>
-      <c r="S34" s="210"/>
+      <c r="R34" s="227"/>
+      <c r="S34" s="227"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="203"/>
-      <c r="D35" s="203"/>
-      <c r="E35" s="203"/>
-      <c r="F35" s="203"/>
-      <c r="G35" s="203"/>
-      <c r="H35" s="204"/>
-      <c r="I35" s="205"/>
-      <c r="J35" s="205"/>
-      <c r="K35" s="205"/>
-      <c r="L35" s="205"/>
-      <c r="M35" s="206"/>
-      <c r="N35" s="207"/>
-      <c r="O35" s="208"/>
-      <c r="P35" s="209"/>
+      <c r="C35" s="223"/>
+      <c r="D35" s="223"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="231"/>
+      <c r="I35" s="232"/>
+      <c r="J35" s="232"/>
+      <c r="K35" s="232"/>
+      <c r="L35" s="232"/>
+      <c r="M35" s="233"/>
+      <c r="N35" s="224"/>
+      <c r="O35" s="225"/>
+      <c r="P35" s="226"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="210"/>
-      <c r="S35" s="210"/>
+      <c r="R35" s="227"/>
+      <c r="S35" s="227"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="203"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="203"/>
-      <c r="F36" s="203"/>
-      <c r="G36" s="203"/>
-      <c r="H36" s="204"/>
-      <c r="I36" s="205"/>
-      <c r="J36" s="205"/>
-      <c r="K36" s="205"/>
-      <c r="L36" s="205"/>
-      <c r="M36" s="206"/>
-      <c r="N36" s="207"/>
-      <c r="O36" s="208"/>
-      <c r="P36" s="209"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="231"/>
+      <c r="I36" s="232"/>
+      <c r="J36" s="232"/>
+      <c r="K36" s="232"/>
+      <c r="L36" s="232"/>
+      <c r="M36" s="233"/>
+      <c r="N36" s="224"/>
+      <c r="O36" s="225"/>
+      <c r="P36" s="226"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="210"/>
-      <c r="S36" s="210"/>
+      <c r="R36" s="227"/>
+      <c r="S36" s="227"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="203"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="204"/>
-      <c r="I37" s="205"/>
-      <c r="J37" s="205"/>
-      <c r="K37" s="205"/>
-      <c r="L37" s="205"/>
-      <c r="M37" s="206"/>
-      <c r="N37" s="207"/>
-      <c r="O37" s="208"/>
-      <c r="P37" s="209"/>
+      <c r="C37" s="223"/>
+      <c r="D37" s="223"/>
+      <c r="E37" s="223"/>
+      <c r="F37" s="223"/>
+      <c r="G37" s="223"/>
+      <c r="H37" s="231"/>
+      <c r="I37" s="232"/>
+      <c r="J37" s="232"/>
+      <c r="K37" s="232"/>
+      <c r="L37" s="232"/>
+      <c r="M37" s="233"/>
+      <c r="N37" s="224"/>
+      <c r="O37" s="225"/>
+      <c r="P37" s="226"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="210"/>
-      <c r="S37" s="210"/>
+      <c r="R37" s="227"/>
+      <c r="S37" s="227"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="203"/>
-      <c r="D38" s="203"/>
-      <c r="E38" s="203"/>
-      <c r="F38" s="203"/>
-      <c r="G38" s="203"/>
-      <c r="H38" s="204"/>
-      <c r="I38" s="205"/>
-      <c r="J38" s="205"/>
-      <c r="K38" s="205"/>
-      <c r="L38" s="205"/>
-      <c r="M38" s="206"/>
-      <c r="N38" s="207"/>
-      <c r="O38" s="208"/>
-      <c r="P38" s="209"/>
+      <c r="C38" s="223"/>
+      <c r="D38" s="223"/>
+      <c r="E38" s="223"/>
+      <c r="F38" s="223"/>
+      <c r="G38" s="223"/>
+      <c r="H38" s="231"/>
+      <c r="I38" s="232"/>
+      <c r="J38" s="232"/>
+      <c r="K38" s="232"/>
+      <c r="L38" s="232"/>
+      <c r="M38" s="233"/>
+      <c r="N38" s="224"/>
+      <c r="O38" s="225"/>
+      <c r="P38" s="226"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="210"/>
-      <c r="S38" s="210"/>
+      <c r="R38" s="227"/>
+      <c r="S38" s="227"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="203"/>
-      <c r="D39" s="203"/>
-      <c r="E39" s="203"/>
-      <c r="F39" s="203"/>
-      <c r="G39" s="203"/>
-      <c r="H39" s="204"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="205"/>
-      <c r="K39" s="205"/>
-      <c r="L39" s="205"/>
-      <c r="M39" s="206"/>
-      <c r="N39" s="207"/>
-      <c r="O39" s="208"/>
-      <c r="P39" s="209"/>
+      <c r="C39" s="223"/>
+      <c r="D39" s="223"/>
+      <c r="E39" s="223"/>
+      <c r="F39" s="223"/>
+      <c r="G39" s="223"/>
+      <c r="H39" s="231"/>
+      <c r="I39" s="232"/>
+      <c r="J39" s="232"/>
+      <c r="K39" s="232"/>
+      <c r="L39" s="232"/>
+      <c r="M39" s="233"/>
+      <c r="N39" s="224"/>
+      <c r="O39" s="225"/>
+      <c r="P39" s="226"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="210"/>
-      <c r="S39" s="210"/>
+      <c r="R39" s="227"/>
+      <c r="S39" s="227"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="203"/>
-      <c r="D40" s="203"/>
-      <c r="E40" s="203"/>
-      <c r="F40" s="203"/>
-      <c r="G40" s="203"/>
-      <c r="H40" s="204"/>
-      <c r="I40" s="205"/>
-      <c r="J40" s="205"/>
-      <c r="K40" s="205"/>
-      <c r="L40" s="205"/>
-      <c r="M40" s="206"/>
-      <c r="N40" s="207"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="209"/>
+      <c r="C40" s="223"/>
+      <c r="D40" s="223"/>
+      <c r="E40" s="223"/>
+      <c r="F40" s="223"/>
+      <c r="G40" s="223"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="233"/>
+      <c r="N40" s="224"/>
+      <c r="O40" s="225"/>
+      <c r="P40" s="226"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="210"/>
-      <c r="S40" s="210"/>
+      <c r="R40" s="227"/>
+      <c r="S40" s="227"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="203"/>
-      <c r="D41" s="203"/>
-      <c r="E41" s="203"/>
-      <c r="F41" s="203"/>
-      <c r="G41" s="203"/>
-      <c r="H41" s="204"/>
-      <c r="I41" s="205"/>
-      <c r="J41" s="205"/>
-      <c r="K41" s="205"/>
-      <c r="L41" s="205"/>
-      <c r="M41" s="206"/>
-      <c r="N41" s="207"/>
-      <c r="O41" s="208"/>
-      <c r="P41" s="209"/>
+      <c r="C41" s="223"/>
+      <c r="D41" s="223"/>
+      <c r="E41" s="223"/>
+      <c r="F41" s="223"/>
+      <c r="G41" s="223"/>
+      <c r="H41" s="231"/>
+      <c r="I41" s="232"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="232"/>
+      <c r="M41" s="233"/>
+      <c r="N41" s="224"/>
+      <c r="O41" s="225"/>
+      <c r="P41" s="226"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="210"/>
-      <c r="S41" s="210"/>
+      <c r="R41" s="227"/>
+      <c r="S41" s="227"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="203"/>
-      <c r="D42" s="203"/>
-      <c r="E42" s="203"/>
-      <c r="F42" s="203"/>
-      <c r="G42" s="203"/>
-      <c r="H42" s="204"/>
-      <c r="I42" s="205"/>
-      <c r="J42" s="205"/>
-      <c r="K42" s="205"/>
-      <c r="L42" s="205"/>
-      <c r="M42" s="206"/>
-      <c r="N42" s="207"/>
-      <c r="O42" s="208"/>
-      <c r="P42" s="209"/>
+      <c r="C42" s="223"/>
+      <c r="D42" s="223"/>
+      <c r="E42" s="223"/>
+      <c r="F42" s="223"/>
+      <c r="G42" s="223"/>
+      <c r="H42" s="231"/>
+      <c r="I42" s="232"/>
+      <c r="J42" s="232"/>
+      <c r="K42" s="232"/>
+      <c r="L42" s="232"/>
+      <c r="M42" s="233"/>
+      <c r="N42" s="224"/>
+      <c r="O42" s="225"/>
+      <c r="P42" s="226"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="210"/>
-      <c r="S42" s="210"/>
+      <c r="R42" s="227"/>
+      <c r="S42" s="227"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="203"/>
-      <c r="D43" s="203"/>
-      <c r="E43" s="203"/>
-      <c r="F43" s="203"/>
-      <c r="G43" s="203"/>
-      <c r="H43" s="204"/>
-      <c r="I43" s="205"/>
-      <c r="J43" s="205"/>
-      <c r="K43" s="205"/>
-      <c r="L43" s="205"/>
-      <c r="M43" s="206"/>
-      <c r="N43" s="207"/>
-      <c r="O43" s="208"/>
-      <c r="P43" s="209"/>
+      <c r="C43" s="223"/>
+      <c r="D43" s="223"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="231"/>
+      <c r="I43" s="232"/>
+      <c r="J43" s="232"/>
+      <c r="K43" s="232"/>
+      <c r="L43" s="232"/>
+      <c r="M43" s="233"/>
+      <c r="N43" s="224"/>
+      <c r="O43" s="225"/>
+      <c r="P43" s="226"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="210"/>
-      <c r="S43" s="210"/>
+      <c r="R43" s="227"/>
+      <c r="S43" s="227"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="203"/>
-      <c r="D44" s="203"/>
-      <c r="E44" s="203"/>
-      <c r="F44" s="203"/>
-      <c r="G44" s="203"/>
-      <c r="H44" s="204"/>
-      <c r="I44" s="205"/>
-      <c r="J44" s="205"/>
-      <c r="K44" s="205"/>
-      <c r="L44" s="205"/>
-      <c r="M44" s="206"/>
-      <c r="N44" s="207"/>
-      <c r="O44" s="208"/>
-      <c r="P44" s="209"/>
+      <c r="C44" s="223"/>
+      <c r="D44" s="223"/>
+      <c r="E44" s="223"/>
+      <c r="F44" s="223"/>
+      <c r="G44" s="223"/>
+      <c r="H44" s="231"/>
+      <c r="I44" s="232"/>
+      <c r="J44" s="232"/>
+      <c r="K44" s="232"/>
+      <c r="L44" s="232"/>
+      <c r="M44" s="233"/>
+      <c r="N44" s="224"/>
+      <c r="O44" s="225"/>
+      <c r="P44" s="226"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="210"/>
-      <c r="S44" s="210"/>
+      <c r="R44" s="227"/>
+      <c r="S44" s="227"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="203"/>
-      <c r="D45" s="203"/>
-      <c r="E45" s="203"/>
-      <c r="F45" s="203"/>
-      <c r="G45" s="203"/>
-      <c r="H45" s="204"/>
-      <c r="I45" s="205"/>
-      <c r="J45" s="205"/>
-      <c r="K45" s="205"/>
-      <c r="L45" s="205"/>
-      <c r="M45" s="206"/>
-      <c r="N45" s="207"/>
-      <c r="O45" s="208"/>
-      <c r="P45" s="209"/>
+      <c r="C45" s="223"/>
+      <c r="D45" s="223"/>
+      <c r="E45" s="223"/>
+      <c r="F45" s="223"/>
+      <c r="G45" s="223"/>
+      <c r="H45" s="231"/>
+      <c r="I45" s="232"/>
+      <c r="J45" s="232"/>
+      <c r="K45" s="232"/>
+      <c r="L45" s="232"/>
+      <c r="M45" s="233"/>
+      <c r="N45" s="224"/>
+      <c r="O45" s="225"/>
+      <c r="P45" s="226"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="210"/>
-      <c r="S45" s="210"/>
+      <c r="R45" s="227"/>
+      <c r="S45" s="227"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="203"/>
-      <c r="D46" s="203"/>
-      <c r="E46" s="203"/>
-      <c r="F46" s="203"/>
-      <c r="G46" s="203"/>
-      <c r="H46" s="204"/>
-      <c r="I46" s="205"/>
-      <c r="J46" s="205"/>
-      <c r="K46" s="205"/>
-      <c r="L46" s="205"/>
-      <c r="M46" s="206"/>
-      <c r="N46" s="207"/>
-      <c r="O46" s="208"/>
-      <c r="P46" s="209"/>
+      <c r="C46" s="223"/>
+      <c r="D46" s="223"/>
+      <c r="E46" s="223"/>
+      <c r="F46" s="223"/>
+      <c r="G46" s="223"/>
+      <c r="H46" s="231"/>
+      <c r="I46" s="232"/>
+      <c r="J46" s="232"/>
+      <c r="K46" s="232"/>
+      <c r="L46" s="232"/>
+      <c r="M46" s="233"/>
+      <c r="N46" s="224"/>
+      <c r="O46" s="225"/>
+      <c r="P46" s="226"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="210"/>
-      <c r="S46" s="210"/>
+      <c r="R46" s="227"/>
+      <c r="S46" s="227"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="203"/>
-      <c r="D47" s="203"/>
-      <c r="E47" s="203"/>
-      <c r="F47" s="203"/>
-      <c r="G47" s="203"/>
-      <c r="H47" s="204"/>
-      <c r="I47" s="205"/>
-      <c r="J47" s="205"/>
-      <c r="K47" s="205"/>
-      <c r="L47" s="205"/>
-      <c r="M47" s="206"/>
-      <c r="N47" s="207"/>
-      <c r="O47" s="208"/>
-      <c r="P47" s="209"/>
+      <c r="C47" s="223"/>
+      <c r="D47" s="223"/>
+      <c r="E47" s="223"/>
+      <c r="F47" s="223"/>
+      <c r="G47" s="223"/>
+      <c r="H47" s="231"/>
+      <c r="I47" s="232"/>
+      <c r="J47" s="232"/>
+      <c r="K47" s="232"/>
+      <c r="L47" s="232"/>
+      <c r="M47" s="233"/>
+      <c r="N47" s="224"/>
+      <c r="O47" s="225"/>
+      <c r="P47" s="226"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="210"/>
-      <c r="S47" s="210"/>
+      <c r="R47" s="227"/>
+      <c r="S47" s="227"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="203"/>
-      <c r="D48" s="203"/>
-      <c r="E48" s="203"/>
-      <c r="F48" s="203"/>
-      <c r="G48" s="203"/>
-      <c r="H48" s="204"/>
-      <c r="I48" s="205"/>
-      <c r="J48" s="205"/>
-      <c r="K48" s="205"/>
-      <c r="L48" s="205"/>
-      <c r="M48" s="206"/>
-      <c r="N48" s="207"/>
-      <c r="O48" s="208"/>
-      <c r="P48" s="209"/>
+      <c r="C48" s="223"/>
+      <c r="D48" s="223"/>
+      <c r="E48" s="223"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="223"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="232"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="232"/>
+      <c r="L48" s="232"/>
+      <c r="M48" s="233"/>
+      <c r="N48" s="224"/>
+      <c r="O48" s="225"/>
+      <c r="P48" s="226"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="210"/>
-      <c r="S48" s="210"/>
+      <c r="R48" s="227"/>
+      <c r="S48" s="227"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="203"/>
-      <c r="D49" s="203"/>
-      <c r="E49" s="203"/>
-      <c r="F49" s="203"/>
-      <c r="G49" s="203"/>
-      <c r="H49" s="204"/>
-      <c r="I49" s="205"/>
-      <c r="J49" s="205"/>
-      <c r="K49" s="205"/>
-      <c r="L49" s="205"/>
-      <c r="M49" s="206"/>
-      <c r="N49" s="207"/>
-      <c r="O49" s="208"/>
-      <c r="P49" s="209"/>
+      <c r="C49" s="223"/>
+      <c r="D49" s="223"/>
+      <c r="E49" s="223"/>
+      <c r="F49" s="223"/>
+      <c r="G49" s="223"/>
+      <c r="H49" s="231"/>
+      <c r="I49" s="232"/>
+      <c r="J49" s="232"/>
+      <c r="K49" s="232"/>
+      <c r="L49" s="232"/>
+      <c r="M49" s="233"/>
+      <c r="N49" s="224"/>
+      <c r="O49" s="225"/>
+      <c r="P49" s="226"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="210"/>
-      <c r="S49" s="210"/>
+      <c r="R49" s="227"/>
+      <c r="S49" s="227"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="203"/>
-      <c r="D50" s="203"/>
-      <c r="E50" s="203"/>
-      <c r="F50" s="203"/>
-      <c r="G50" s="203"/>
-      <c r="H50" s="204"/>
-      <c r="I50" s="205"/>
-      <c r="J50" s="205"/>
-      <c r="K50" s="205"/>
-      <c r="L50" s="205"/>
-      <c r="M50" s="206"/>
-      <c r="N50" s="207"/>
-      <c r="O50" s="208"/>
-      <c r="P50" s="209"/>
+      <c r="C50" s="223"/>
+      <c r="D50" s="223"/>
+      <c r="E50" s="223"/>
+      <c r="F50" s="223"/>
+      <c r="G50" s="223"/>
+      <c r="H50" s="231"/>
+      <c r="I50" s="232"/>
+      <c r="J50" s="232"/>
+      <c r="K50" s="232"/>
+      <c r="L50" s="232"/>
+      <c r="M50" s="233"/>
+      <c r="N50" s="224"/>
+      <c r="O50" s="225"/>
+      <c r="P50" s="226"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="210"/>
-      <c r="S50" s="210"/>
+      <c r="R50" s="227"/>
+      <c r="S50" s="227"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="203"/>
-      <c r="D51" s="203"/>
-      <c r="E51" s="203"/>
-      <c r="F51" s="203"/>
-      <c r="G51" s="203"/>
-      <c r="H51" s="204"/>
-      <c r="I51" s="205"/>
-      <c r="J51" s="205"/>
-      <c r="K51" s="205"/>
-      <c r="L51" s="205"/>
-      <c r="M51" s="206"/>
-      <c r="N51" s="207"/>
-      <c r="O51" s="208"/>
-      <c r="P51" s="209"/>
+      <c r="C51" s="223"/>
+      <c r="D51" s="223"/>
+      <c r="E51" s="223"/>
+      <c r="F51" s="223"/>
+      <c r="G51" s="223"/>
+      <c r="H51" s="231"/>
+      <c r="I51" s="232"/>
+      <c r="J51" s="232"/>
+      <c r="K51" s="232"/>
+      <c r="L51" s="232"/>
+      <c r="M51" s="233"/>
+      <c r="N51" s="224"/>
+      <c r="O51" s="225"/>
+      <c r="P51" s="226"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="210"/>
-      <c r="S51" s="210"/>
+      <c r="R51" s="227"/>
+      <c r="S51" s="227"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="203"/>
-      <c r="D52" s="203"/>
-      <c r="E52" s="203"/>
-      <c r="F52" s="203"/>
-      <c r="G52" s="203"/>
-      <c r="H52" s="204"/>
-      <c r="I52" s="205"/>
-      <c r="J52" s="205"/>
-      <c r="K52" s="205"/>
-      <c r="L52" s="205"/>
-      <c r="M52" s="206"/>
-      <c r="N52" s="207"/>
-      <c r="O52" s="208"/>
-      <c r="P52" s="209"/>
+      <c r="C52" s="223"/>
+      <c r="D52" s="223"/>
+      <c r="E52" s="223"/>
+      <c r="F52" s="223"/>
+      <c r="G52" s="223"/>
+      <c r="H52" s="231"/>
+      <c r="I52" s="232"/>
+      <c r="J52" s="232"/>
+      <c r="K52" s="232"/>
+      <c r="L52" s="232"/>
+      <c r="M52" s="233"/>
+      <c r="N52" s="224"/>
+      <c r="O52" s="225"/>
+      <c r="P52" s="226"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="210"/>
-      <c r="S52" s="210"/>
+      <c r="R52" s="227"/>
+      <c r="S52" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -12806,194 +13022,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF9DA33-68CC-4411-A4B9-D21FFCCD1191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82A8AA3-74BF-43A3-96F4-A3BAF12C3493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="780" windowWidth="11415" windowHeight="8955" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="114">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -694,6 +694,50 @@
     <t>〇</t>
     <phoneticPr fontId="7"/>
   </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>ログアウト状態でのページ表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-list.jsp</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
 </sst>
 </file>
 
@@ -702,7 +746,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -817,6 +861,14 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1678,14 +1730,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1908,6 +1961,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1941,21 +2039,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2001,36 +2084,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2094,51 +2147,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2214,6 +2267,51 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2235,15 +2333,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2259,40 +2348,37 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2355,41 +2441,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="ハイパーリンク" xfId="5" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{6F8E72F5-98DE-405A-B9D4-A66D21EFE385}"/>
     <cellStyle name="標準 2 2" xfId="1" xr:uid="{79379184-E0E4-48AE-9057-633A6B8D7415}"/>
@@ -4105,19 +4164,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="97"/>
+      <c r="F1" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="82"/>
+      <c r="G1" s="97"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4129,190 +4188,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="100" t="s">
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="101"/>
-      <c r="F2" s="100" t="s">
+      <c r="E2" s="111"/>
+      <c r="F2" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="104">
+      <c r="G2" s="111"/>
+      <c r="H2" s="114">
         <v>45805</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="77"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="93"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="96"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="83" t="s">
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="84"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="99"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="89"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="89"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="88" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="89"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="87" customHeight="1">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="87"/>
-      <c r="D9" s="105" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="89"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="112"/>
-      <c r="B10" s="114" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="89"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="113"/>
-      <c r="B11" s="114" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="105" t="s">
+      <c r="C11" s="76"/>
+      <c r="D11" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="89"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="78"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="105" t="s">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="89"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="107"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="110"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5303,6 +5362,18 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5318,18 +5389,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6841,23 +6900,23 @@
       <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="140"/>
+      <c r="B5" s="137"/>
       <c r="C5" s="131"/>
-      <c r="D5" s="145" t="s">
+      <c r="D5" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="146"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="144" t="s">
+      <c r="A6" s="141" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="67"/>
@@ -6868,19 +6927,19 @@
       <c r="G6" s="67"/>
       <c r="H6" s="67"/>
       <c r="I6" s="67"/>
-      <c r="J6" s="137"/>
+      <c r="J6" s="145"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="147"/>
-      <c r="B7" s="148"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="148"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="149"/>
+      <c r="A7" s="146"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="148"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="125"/>
@@ -6892,7 +6951,7 @@
       <c r="G8" s="70"/>
       <c r="H8" s="70"/>
       <c r="I8" s="70"/>
-      <c r="J8" s="150"/>
+      <c r="J8" s="149"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="125"/>
@@ -6904,7 +6963,7 @@
       <c r="G9" s="70"/>
       <c r="H9" s="70"/>
       <c r="I9" s="70"/>
-      <c r="J9" s="150"/>
+      <c r="J9" s="149"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="125"/>
@@ -6916,7 +6975,7 @@
       <c r="G10" s="70"/>
       <c r="H10" s="70"/>
       <c r="I10" s="70"/>
-      <c r="J10" s="150"/>
+      <c r="J10" s="149"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="125"/>
@@ -6928,7 +6987,7 @@
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
-      <c r="J11" s="150"/>
+      <c r="J11" s="149"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="125"/>
@@ -6940,7 +6999,7 @@
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
       <c r="I12" s="70"/>
-      <c r="J12" s="150"/>
+      <c r="J12" s="149"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="125"/>
@@ -6952,10 +7011,10 @@
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
       <c r="I13" s="70"/>
-      <c r="J13" s="150"/>
+      <c r="J13" s="149"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="144" t="s">
+      <c r="A14" s="141" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="67"/>
@@ -6966,15 +7025,15 @@
       <c r="G14" s="67"/>
       <c r="H14" s="67"/>
       <c r="I14" s="67"/>
-      <c r="J14" s="137"/>
+      <c r="J14" s="145"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="144" t="s">
+      <c r="A15" s="141" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="67"/>
       <c r="C15" s="68"/>
-      <c r="D15" s="136" t="s">
+      <c r="D15" s="150" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="67"/>
@@ -6989,7 +7048,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="144" t="s">
+      <c r="A16" s="141" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="67"/>
@@ -7010,10 +7069,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="67"/>
-      <c r="J16" s="137"/>
+      <c r="J16" s="145"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="138">
+      <c r="A17" s="142">
         <v>1</v>
       </c>
       <c r="B17" s="67"/>
@@ -7028,80 +7087,80 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="136"/>
+      <c r="H17" s="150"/>
       <c r="I17" s="67"/>
-      <c r="J17" s="137"/>
+      <c r="J17" s="145"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="138"/>
+      <c r="A18" s="142"/>
       <c r="B18" s="67"/>
       <c r="C18" s="68"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="136"/>
+      <c r="H18" s="150"/>
       <c r="I18" s="67"/>
-      <c r="J18" s="137"/>
+      <c r="J18" s="145"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="138"/>
+      <c r="A19" s="142"/>
       <c r="B19" s="67"/>
       <c r="C19" s="68"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="136"/>
+      <c r="H19" s="150"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="137"/>
+      <c r="J19" s="145"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="138"/>
+      <c r="A20" s="142"/>
       <c r="B20" s="67"/>
       <c r="C20" s="68"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="136"/>
+      <c r="H20" s="150"/>
       <c r="I20" s="67"/>
-      <c r="J20" s="137"/>
+      <c r="J20" s="145"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="138"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="67"/>
       <c r="C21" s="68"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="136"/>
+      <c r="H21" s="150"/>
       <c r="I21" s="67"/>
-      <c r="J21" s="137"/>
+      <c r="J21" s="145"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="138"/>
+      <c r="A22" s="142"/>
       <c r="B22" s="67"/>
       <c r="C22" s="68"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="136"/>
+      <c r="H22" s="150"/>
       <c r="I22" s="67"/>
-      <c r="J22" s="137"/>
+      <c r="J22" s="145"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="143"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="152"/>
-      <c r="I23" s="142"/>
+      <c r="I23" s="139"/>
       <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8083,11 +8142,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8104,16 +8168,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9548,7 +9607,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="200" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="161"/>
@@ -9559,14 +9618,14 @@
       <c r="G1" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
       <c r="J1" s="170"/>
       <c r="K1" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
       <c r="N1" s="170"/>
       <c r="O1" s="169" t="s">
         <v>7</v>
@@ -9579,7 +9638,7 @@
       <c r="S1" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="182"/>
+      <c r="T1" s="197"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="163"/>
@@ -9591,16 +9650,16 @@
       <c r="G2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
+      <c r="H2" s="201"/>
+      <c r="I2" s="201"/>
       <c r="J2" s="172"/>
       <c r="K2" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="189"/>
-      <c r="M2" s="189"/>
+      <c r="L2" s="201"/>
+      <c r="M2" s="201"/>
       <c r="N2" s="172"/>
-      <c r="O2" s="190">
+      <c r="O2" s="202">
         <v>45817</v>
       </c>
       <c r="P2" s="172"/>
@@ -9609,7 +9668,7 @@
       </c>
       <c r="R2" s="172"/>
       <c r="S2" s="171"/>
-      <c r="T2" s="176"/>
+      <c r="T2" s="191"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="163"/>
@@ -9631,7 +9690,7 @@
       <c r="Q3" s="173"/>
       <c r="R3" s="165"/>
       <c r="S3" s="173"/>
-      <c r="T3" s="177"/>
+      <c r="T3" s="192"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="166"/>
@@ -9653,85 +9712,85 @@
       <c r="Q4" s="174"/>
       <c r="R4" s="168"/>
       <c r="S4" s="174"/>
-      <c r="T4" s="178"/>
+      <c r="T4" s="193"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="179" t="s">
+      <c r="A5" s="194" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
+      <c r="B5" s="195"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
       <c r="F5" s="170"/>
-      <c r="G5" s="181" t="s">
+      <c r="G5" s="196" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="180"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="180"/>
-      <c r="T5" s="182"/>
+      <c r="H5" s="195"/>
+      <c r="I5" s="195"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="195"/>
+      <c r="L5" s="195"/>
+      <c r="M5" s="195"/>
+      <c r="N5" s="195"/>
+      <c r="O5" s="195"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="195"/>
+      <c r="T5" s="197"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="183" t="s">
+      <c r="A6" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="186" t="s">
+      <c r="B6" s="183"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="184"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
-      <c r="K6" s="184"/>
-      <c r="L6" s="184"/>
-      <c r="M6" s="184"/>
-      <c r="N6" s="184"/>
-      <c r="O6" s="184"/>
-      <c r="P6" s="184"/>
-      <c r="Q6" s="184"/>
-      <c r="R6" s="184"/>
-      <c r="S6" s="184"/>
-      <c r="T6" s="187"/>
+      <c r="H6" s="183"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="183"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="183"/>
+      <c r="Q6" s="183"/>
+      <c r="R6" s="183"/>
+      <c r="S6" s="183"/>
+      <c r="T6" s="199"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="183" t="s">
+      <c r="A7" s="189" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="184"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="184"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="186" t="s">
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="198" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="184"/>
-      <c r="I7" s="184"/>
-      <c r="J7" s="184"/>
-      <c r="K7" s="184"/>
-      <c r="L7" s="184"/>
-      <c r="M7" s="184"/>
-      <c r="N7" s="184"/>
-      <c r="O7" s="184"/>
-      <c r="P7" s="184"/>
-      <c r="Q7" s="184"/>
-      <c r="R7" s="184"/>
-      <c r="S7" s="184"/>
-      <c r="T7" s="187"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="183"/>
+      <c r="M7" s="183"/>
+      <c r="N7" s="183"/>
+      <c r="O7" s="183"/>
+      <c r="P7" s="183"/>
+      <c r="Q7" s="183"/>
+      <c r="R7" s="183"/>
+      <c r="S7" s="183"/>
+      <c r="T7" s="199"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9930,37 +9989,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="183" t="s">
+      <c r="A15" s="189" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="185"/>
-      <c r="C15" s="196" t="s">
+      <c r="B15" s="184"/>
+      <c r="C15" s="190" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="185"/>
-      <c r="E15" s="191" t="s">
+      <c r="D15" s="184"/>
+      <c r="E15" s="188" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="185"/>
-      <c r="G15" s="191" t="s">
+      <c r="F15" s="184"/>
+      <c r="G15" s="188" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="184"/>
-      <c r="I15" s="185"/>
-      <c r="J15" s="191" t="s">
+      <c r="H15" s="183"/>
+      <c r="I15" s="184"/>
+      <c r="J15" s="188" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="185"/>
-      <c r="L15" s="191" t="s">
+      <c r="K15" s="184"/>
+      <c r="L15" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="184"/>
-      <c r="N15" s="185"/>
-      <c r="O15" s="191" t="s">
+      <c r="M15" s="183"/>
+      <c r="N15" s="184"/>
+      <c r="O15" s="188" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="184"/>
-      <c r="Q15" s="185"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="184"/>
       <c r="R15" s="44" t="s">
         <v>56</v>
       </c>
@@ -9972,37 +10031,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="192">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="193" t="s">
+      <c r="B16" s="184"/>
+      <c r="C16" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="185"/>
-      <c r="E16" s="193" t="s">
+      <c r="D16" s="184"/>
+      <c r="E16" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="185"/>
-      <c r="G16" s="194" t="s">
+      <c r="F16" s="184"/>
+      <c r="G16" s="187" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="184"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="194" t="s">
+      <c r="H16" s="183"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="185"/>
-      <c r="L16" s="195" t="s">
+      <c r="K16" s="184"/>
+      <c r="L16" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="184"/>
-      <c r="N16" s="185"/>
-      <c r="O16" s="195" t="s">
+      <c r="M16" s="183"/>
+      <c r="N16" s="184"/>
+      <c r="O16" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="184"/>
-      <c r="Q16" s="185"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="184"/>
       <c r="R16" s="65">
         <v>45825</v>
       </c>
@@ -10020,37 +10079,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="192">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="185"/>
-      <c r="C17" s="193" t="s">
+      <c r="B17" s="184"/>
+      <c r="C17" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="185"/>
-      <c r="E17" s="193" t="s">
+      <c r="D17" s="184"/>
+      <c r="E17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="185"/>
-      <c r="G17" s="194" t="s">
+      <c r="F17" s="184"/>
+      <c r="G17" s="187" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="184"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="194" t="s">
+      <c r="H17" s="183"/>
+      <c r="I17" s="184"/>
+      <c r="J17" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="185"/>
-      <c r="L17" s="195" t="s">
+      <c r="K17" s="184"/>
+      <c r="L17" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M17" s="184"/>
-      <c r="N17" s="185"/>
-      <c r="O17" s="195" t="s">
+      <c r="M17" s="183"/>
+      <c r="N17" s="184"/>
+      <c r="O17" s="182" t="s">
         <v>98</v>
       </c>
-      <c r="P17" s="184"/>
-      <c r="Q17" s="185"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="184"/>
       <c r="R17" s="65">
         <v>45825</v>
       </c>
@@ -10068,37 +10127,37 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="192">
+      <c r="A18" s="185">
         <v>3</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="193" t="s">
+      <c r="B18" s="184"/>
+      <c r="C18" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="185"/>
-      <c r="E18" s="193" t="s">
+      <c r="D18" s="184"/>
+      <c r="E18" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="185"/>
-      <c r="G18" s="194" t="s">
+      <c r="F18" s="184"/>
+      <c r="G18" s="187" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="184"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="194" t="s">
+      <c r="H18" s="183"/>
+      <c r="I18" s="184"/>
+      <c r="J18" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="185"/>
-      <c r="L18" s="195" t="s">
+      <c r="K18" s="184"/>
+      <c r="L18" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M18" s="184"/>
-      <c r="N18" s="185"/>
-      <c r="O18" s="195" t="s">
+      <c r="M18" s="183"/>
+      <c r="N18" s="184"/>
+      <c r="O18" s="182" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="184"/>
-      <c r="Q18" s="185"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="184"/>
       <c r="R18" s="65">
         <v>45825</v>
       </c>
@@ -10116,37 +10175,37 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A19" s="192">
+      <c r="A19" s="185">
         <v>4</v>
       </c>
-      <c r="B19" s="185"/>
-      <c r="C19" s="193" t="s">
+      <c r="B19" s="184"/>
+      <c r="C19" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="185"/>
-      <c r="E19" s="193" t="s">
+      <c r="D19" s="184"/>
+      <c r="E19" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="185"/>
-      <c r="G19" s="194" t="s">
+      <c r="F19" s="184"/>
+      <c r="G19" s="187" t="s">
         <v>96</v>
       </c>
-      <c r="H19" s="184"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="194" t="s">
+      <c r="H19" s="183"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="185"/>
-      <c r="L19" s="195" t="s">
+      <c r="K19" s="184"/>
+      <c r="L19" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M19" s="184"/>
-      <c r="N19" s="185"/>
-      <c r="O19" s="195" t="s">
+      <c r="M19" s="183"/>
+      <c r="N19" s="184"/>
+      <c r="O19" s="182" t="s">
         <v>95</v>
       </c>
-      <c r="P19" s="184"/>
-      <c r="Q19" s="185"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="184"/>
       <c r="R19" s="46"/>
       <c r="S19" s="46"/>
       <c r="T19" s="47"/>
@@ -10158,37 +10217,37 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A20" s="192">
+      <c r="A20" s="185">
         <v>5</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="193" t="s">
+      <c r="B20" s="184"/>
+      <c r="C20" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="185"/>
-      <c r="E20" s="193" t="s">
+      <c r="D20" s="184"/>
+      <c r="E20" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="185"/>
-      <c r="G20" s="194" t="s">
+      <c r="F20" s="184"/>
+      <c r="G20" s="187" t="s">
         <v>100</v>
       </c>
-      <c r="H20" s="184"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="194" t="s">
+      <c r="H20" s="183"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="185"/>
-      <c r="L20" s="195" t="s">
+      <c r="K20" s="184"/>
+      <c r="L20" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M20" s="184"/>
-      <c r="N20" s="185"/>
-      <c r="O20" s="195" t="s">
+      <c r="M20" s="183"/>
+      <c r="N20" s="184"/>
+      <c r="O20" s="182" t="s">
         <v>99</v>
       </c>
-      <c r="P20" s="184"/>
-      <c r="Q20" s="185"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="184"/>
       <c r="R20" s="46"/>
       <c r="S20" s="46"/>
       <c r="T20" s="47"/>
@@ -10200,37 +10259,37 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A21" s="192">
+      <c r="A21" s="185">
         <v>6</v>
       </c>
-      <c r="B21" s="185"/>
-      <c r="C21" s="193" t="s">
+      <c r="B21" s="184"/>
+      <c r="C21" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="185"/>
-      <c r="E21" s="193" t="s">
+      <c r="D21" s="184"/>
+      <c r="E21" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="185"/>
-      <c r="G21" s="194" t="s">
+      <c r="F21" s="184"/>
+      <c r="G21" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="H21" s="184"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="194" t="s">
+      <c r="H21" s="183"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K21" s="185"/>
-      <c r="L21" s="195" t="s">
+      <c r="K21" s="184"/>
+      <c r="L21" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M21" s="184"/>
-      <c r="N21" s="185"/>
-      <c r="O21" s="195" t="s">
+      <c r="M21" s="183"/>
+      <c r="N21" s="184"/>
+      <c r="O21" s="182" t="s">
         <v>102</v>
       </c>
-      <c r="P21" s="184"/>
-      <c r="Q21" s="185"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="184"/>
       <c r="R21" s="65">
         <v>45825</v>
       </c>
@@ -10248,23 +10307,37 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A22" s="192"/>
-      <c r="B22" s="185"/>
-      <c r="C22" s="193"/>
-      <c r="D22" s="185"/>
-      <c r="E22" s="193"/>
-      <c r="F22" s="185"/>
-      <c r="G22" s="194"/>
-      <c r="H22" s="184"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="194"/>
-      <c r="K22" s="185"/>
-      <c r="L22" s="195"/>
-      <c r="M22" s="184"/>
-      <c r="N22" s="185"/>
-      <c r="O22" s="195"/>
-      <c r="P22" s="184"/>
-      <c r="Q22" s="185"/>
+      <c r="A22" s="185">
+        <v>7</v>
+      </c>
+      <c r="B22" s="184"/>
+      <c r="C22" s="186" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="184"/>
+      <c r="E22" s="186" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="184"/>
+      <c r="G22" s="187" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="183"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="187" t="s">
+        <v>111</v>
+      </c>
+      <c r="K22" s="184"/>
+      <c r="L22" s="234" t="s">
+        <v>112</v>
+      </c>
+      <c r="M22" s="235"/>
+      <c r="N22" s="235"/>
+      <c r="O22" s="236" t="s">
+        <v>113</v>
+      </c>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="68"/>
       <c r="R22" s="46"/>
       <c r="S22" s="46"/>
       <c r="T22" s="47"/>
@@ -10276,23 +10349,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="192"/>
-      <c r="B23" s="185"/>
-      <c r="C23" s="193"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="193"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="194"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="194"/>
-      <c r="K23" s="185"/>
-      <c r="L23" s="195"/>
-      <c r="M23" s="184"/>
-      <c r="N23" s="185"/>
-      <c r="O23" s="195"/>
-      <c r="P23" s="184"/>
-      <c r="Q23" s="185"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="184"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="187"/>
+      <c r="H23" s="183"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="187"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="183"/>
+      <c r="N23" s="184"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="184"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -10304,23 +10377,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="192"/>
-      <c r="B24" s="185"/>
-      <c r="C24" s="193"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="193"/>
-      <c r="F24" s="185"/>
-      <c r="G24" s="194"/>
-      <c r="H24" s="184"/>
-      <c r="I24" s="185"/>
-      <c r="J24" s="194"/>
-      <c r="K24" s="185"/>
-      <c r="L24" s="195"/>
-      <c r="M24" s="184"/>
-      <c r="N24" s="185"/>
-      <c r="O24" s="195"/>
-      <c r="P24" s="184"/>
-      <c r="Q24" s="185"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="184"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="187"/>
+      <c r="H24" s="183"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="187"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="183"/>
+      <c r="N24" s="184"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="184"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -10332,23 +10405,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="192"/>
-      <c r="B25" s="185"/>
-      <c r="C25" s="193"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="193"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="194"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="194"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="195"/>
-      <c r="M25" s="184"/>
-      <c r="N25" s="185"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="184"/>
-      <c r="Q25" s="185"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="184"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="184"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="187"/>
+      <c r="H25" s="183"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="187"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="183"/>
+      <c r="N25" s="184"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="184"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -10360,23 +10433,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="192"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="193"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="193"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="194"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="194"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="195"/>
-      <c r="M26" s="184"/>
-      <c r="N26" s="185"/>
-      <c r="O26" s="195"/>
-      <c r="P26" s="184"/>
-      <c r="Q26" s="185"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="184"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="184"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="187"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="183"/>
+      <c r="N26" s="184"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="184"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -10388,23 +10461,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="192"/>
-      <c r="B27" s="185"/>
-      <c r="C27" s="193"/>
-      <c r="D27" s="185"/>
-      <c r="E27" s="193"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="194"/>
-      <c r="H27" s="184"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="194"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="195"/>
-      <c r="M27" s="184"/>
-      <c r="N27" s="185"/>
-      <c r="O27" s="195"/>
-      <c r="P27" s="184"/>
-      <c r="Q27" s="185"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="184"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="187"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="184"/>
+      <c r="J27" s="187"/>
+      <c r="K27" s="184"/>
+      <c r="L27" s="182"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="184"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="184"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -10416,23 +10489,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="192"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="193"/>
-      <c r="D28" s="185"/>
-      <c r="E28" s="193"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="194"/>
-      <c r="H28" s="184"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="194"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="195"/>
-      <c r="M28" s="184"/>
-      <c r="N28" s="185"/>
-      <c r="O28" s="195"/>
-      <c r="P28" s="184"/>
-      <c r="Q28" s="185"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="184"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="184"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="187"/>
+      <c r="H28" s="183"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="187"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="183"/>
+      <c r="N28" s="184"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="184"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -10444,23 +10517,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="192"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="193"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="193"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="184"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="194"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="195"/>
-      <c r="M29" s="184"/>
-      <c r="N29" s="185"/>
-      <c r="O29" s="195"/>
-      <c r="P29" s="184"/>
-      <c r="Q29" s="185"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="184"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="187"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="187"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="184"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -10472,23 +10545,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="192"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="193"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="193"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="194"/>
-      <c r="H30" s="184"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="194"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="195"/>
-      <c r="M30" s="184"/>
-      <c r="N30" s="185"/>
-      <c r="O30" s="195"/>
-      <c r="P30" s="184"/>
-      <c r="Q30" s="185"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="184"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="184"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="184"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="183"/>
+      <c r="I30" s="184"/>
+      <c r="J30" s="187"/>
+      <c r="K30" s="184"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="183"/>
+      <c r="N30" s="184"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="183"/>
+      <c r="Q30" s="184"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -10500,23 +10573,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="200"/>
-      <c r="B31" s="199"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="199"/>
-      <c r="E31" s="201"/>
-      <c r="F31" s="199"/>
-      <c r="G31" s="202"/>
-      <c r="H31" s="198"/>
-      <c r="I31" s="199"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="199"/>
-      <c r="L31" s="197"/>
-      <c r="M31" s="198"/>
-      <c r="N31" s="199"/>
-      <c r="O31" s="197"/>
-      <c r="P31" s="198"/>
-      <c r="Q31" s="199"/>
+      <c r="A31" s="179"/>
+      <c r="B31" s="178"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="178"/>
+      <c r="E31" s="180"/>
+      <c r="F31" s="178"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="176"/>
+      <c r="M31" s="177"/>
+      <c r="N31" s="178"/>
+      <c r="O31" s="176"/>
+      <c r="P31" s="177"/>
+      <c r="Q31" s="178"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11514,6 +11587,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -11535,123 +11723,11 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
+  <hyperlinks>
+    <hyperlink ref="L22" r:id="rId1" xr:uid="{70F16E29-4C19-40D6-A6FE-AC67A8668308}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -11672,72 +11748,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="212" t="s">
+      <c r="A1" s="223" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="213" t="s">
+      <c r="B1" s="223"/>
+      <c r="C1" s="224" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="214"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="216" t="s">
+      <c r="D1" s="225"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="227" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="218"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="229"/>
       <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="216" t="s">
+      <c r="O1" s="227" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="218"/>
+      <c r="P1" s="229"/>
       <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="216" t="s">
+      <c r="R1" s="227" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="218"/>
+      <c r="S1" s="229"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="212"/>
-      <c r="B2" s="212"/>
-      <c r="C2" s="213" t="s">
+      <c r="A2" s="223"/>
+      <c r="B2" s="223"/>
+      <c r="C2" s="224" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="216" t="s">
+      <c r="D2" s="225"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="227" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="217"/>
-      <c r="I2" s="217"/>
-      <c r="J2" s="217"/>
-      <c r="K2" s="217"/>
-      <c r="L2" s="217"/>
-      <c r="M2" s="218"/>
+      <c r="G2" s="228"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="228"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
+      <c r="M2" s="229"/>
       <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="219">
+      <c r="O2" s="230">
         <v>45818</v>
       </c>
-      <c r="P2" s="220"/>
+      <c r="P2" s="231"/>
       <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="221" t="s">
+      <c r="R2" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="222"/>
+      <c r="S2" s="233"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11767,33 +11843,33 @@
       <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="214" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="203" t="s">
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="204"/>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
-      <c r="M4" s="205"/>
-      <c r="N4" s="203" t="s">
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
+      <c r="L4" s="215"/>
+      <c r="M4" s="216"/>
+      <c r="N4" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="204"/>
-      <c r="P4" s="205"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="216"/>
       <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="203" t="s">
+      <c r="R4" s="214" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="205"/>
+      <c r="S4" s="216"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59">
@@ -11802,1209 +11878,1021 @@
       <c r="B5" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="206" t="s">
+      <c r="C5" s="217" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="206"/>
-      <c r="E5" s="206"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="206"/>
-      <c r="H5" s="206" t="s">
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="217" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="206"/>
-      <c r="J5" s="206"/>
-      <c r="K5" s="206"/>
-      <c r="L5" s="206"/>
-      <c r="M5" s="206"/>
-      <c r="N5" s="207" t="s">
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="217"/>
+      <c r="M5" s="217"/>
+      <c r="N5" s="218" t="s">
         <v>107</v>
       </c>
-      <c r="O5" s="208"/>
-      <c r="P5" s="209"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="220"/>
       <c r="Q5" s="64">
         <v>45818</v>
       </c>
-      <c r="R5" s="210"/>
-      <c r="S5" s="211"/>
+      <c r="R5" s="221"/>
+      <c r="S5" s="222"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="228"/>
-      <c r="O6" s="229"/>
-      <c r="P6" s="230"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="203"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
+      <c r="G6" s="203"/>
+      <c r="H6" s="203"/>
+      <c r="I6" s="203"/>
+      <c r="J6" s="203"/>
+      <c r="K6" s="203"/>
+      <c r="L6" s="203"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="211"/>
+      <c r="O6" s="212"/>
+      <c r="P6" s="213"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="227"/>
-      <c r="S6" s="227"/>
+      <c r="R6" s="210"/>
+      <c r="S6" s="210"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="223"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="224"/>
-      <c r="O7" s="225"/>
-      <c r="P7" s="226"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="203"/>
+      <c r="F7" s="203"/>
+      <c r="G7" s="203"/>
+      <c r="H7" s="203"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="203"/>
+      <c r="K7" s="203"/>
+      <c r="L7" s="203"/>
+      <c r="M7" s="203"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="208"/>
+      <c r="P7" s="209"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="227"/>
-      <c r="S7" s="227"/>
+      <c r="R7" s="210"/>
+      <c r="S7" s="210"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="223"/>
-      <c r="H8" s="223"/>
-      <c r="I8" s="223"/>
-      <c r="J8" s="223"/>
-      <c r="K8" s="223"/>
-      <c r="L8" s="223"/>
-      <c r="M8" s="223"/>
-      <c r="N8" s="224"/>
-      <c r="O8" s="225"/>
-      <c r="P8" s="226"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="203"/>
+      <c r="H8" s="203"/>
+      <c r="I8" s="203"/>
+      <c r="J8" s="203"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="203"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="208"/>
+      <c r="P8" s="209"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="227"/>
-      <c r="S8" s="227"/>
+      <c r="R8" s="210"/>
+      <c r="S8" s="210"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="223"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="223"/>
-      <c r="K9" s="223"/>
-      <c r="L9" s="223"/>
-      <c r="M9" s="223"/>
-      <c r="N9" s="224"/>
-      <c r="O9" s="225"/>
-      <c r="P9" s="226"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="203"/>
+      <c r="H9" s="203"/>
+      <c r="I9" s="203"/>
+      <c r="J9" s="203"/>
+      <c r="K9" s="203"/>
+      <c r="L9" s="203"/>
+      <c r="M9" s="203"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="208"/>
+      <c r="P9" s="209"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="227"/>
-      <c r="S9" s="227"/>
+      <c r="R9" s="210"/>
+      <c r="S9" s="210"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="231"/>
-      <c r="I10" s="232"/>
-      <c r="J10" s="232"/>
-      <c r="K10" s="232"/>
-      <c r="L10" s="232"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="224"/>
-      <c r="O10" s="225"/>
-      <c r="P10" s="226"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="203"/>
+      <c r="H10" s="204"/>
+      <c r="I10" s="205"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="205"/>
+      <c r="L10" s="205"/>
+      <c r="M10" s="206"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="208"/>
+      <c r="P10" s="209"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="227"/>
-      <c r="S10" s="227"/>
+      <c r="R10" s="210"/>
+      <c r="S10" s="210"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="223"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="223"/>
-      <c r="F11" s="223"/>
-      <c r="G11" s="223"/>
-      <c r="H11" s="231"/>
-      <c r="I11" s="232"/>
-      <c r="J11" s="232"/>
-      <c r="K11" s="232"/>
-      <c r="L11" s="232"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="224"/>
-      <c r="O11" s="225"/>
-      <c r="P11" s="226"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="203"/>
+      <c r="H11" s="204"/>
+      <c r="I11" s="205"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="205"/>
+      <c r="L11" s="205"/>
+      <c r="M11" s="206"/>
+      <c r="N11" s="207"/>
+      <c r="O11" s="208"/>
+      <c r="P11" s="209"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="227"/>
-      <c r="S11" s="227"/>
+      <c r="R11" s="210"/>
+      <c r="S11" s="210"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="223"/>
-      <c r="D12" s="223"/>
-      <c r="E12" s="223"/>
-      <c r="F12" s="223"/>
-      <c r="G12" s="223"/>
-      <c r="H12" s="231"/>
-      <c r="I12" s="232"/>
-      <c r="J12" s="232"/>
-      <c r="K12" s="232"/>
-      <c r="L12" s="232"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="224"/>
-      <c r="O12" s="225"/>
-      <c r="P12" s="226"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="204"/>
+      <c r="I12" s="205"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="205"/>
+      <c r="M12" s="206"/>
+      <c r="N12" s="207"/>
+      <c r="O12" s="208"/>
+      <c r="P12" s="209"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="227"/>
-      <c r="S12" s="227"/>
+      <c r="R12" s="210"/>
+      <c r="S12" s="210"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="223"/>
-      <c r="D13" s="223"/>
-      <c r="E13" s="223"/>
-      <c r="F13" s="223"/>
-      <c r="G13" s="223"/>
-      <c r="H13" s="231"/>
-      <c r="I13" s="232"/>
-      <c r="J13" s="232"/>
-      <c r="K13" s="232"/>
-      <c r="L13" s="232"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="224"/>
-      <c r="O13" s="225"/>
-      <c r="P13" s="226"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="204"/>
+      <c r="I13" s="205"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="205"/>
+      <c r="L13" s="205"/>
+      <c r="M13" s="206"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="208"/>
+      <c r="P13" s="209"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="227"/>
-      <c r="S13" s="227"/>
+      <c r="R13" s="210"/>
+      <c r="S13" s="210"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="223"/>
-      <c r="G14" s="223"/>
-      <c r="H14" s="231"/>
-      <c r="I14" s="232"/>
-      <c r="J14" s="232"/>
-      <c r="K14" s="232"/>
-      <c r="L14" s="232"/>
-      <c r="M14" s="233"/>
-      <c r="N14" s="224"/>
-      <c r="O14" s="225"/>
-      <c r="P14" s="226"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="204"/>
+      <c r="I14" s="205"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="205"/>
+      <c r="L14" s="205"/>
+      <c r="M14" s="206"/>
+      <c r="N14" s="207"/>
+      <c r="O14" s="208"/>
+      <c r="P14" s="209"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="227"/>
-      <c r="S14" s="227"/>
+      <c r="R14" s="210"/>
+      <c r="S14" s="210"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="223"/>
-      <c r="D15" s="223"/>
-      <c r="E15" s="223"/>
-      <c r="F15" s="223"/>
-      <c r="G15" s="223"/>
-      <c r="H15" s="231"/>
-      <c r="I15" s="232"/>
-      <c r="J15" s="232"/>
-      <c r="K15" s="232"/>
-      <c r="L15" s="232"/>
-      <c r="M15" s="233"/>
-      <c r="N15" s="224"/>
-      <c r="O15" s="225"/>
-      <c r="P15" s="226"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="204"/>
+      <c r="I15" s="205"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="205"/>
+      <c r="L15" s="205"/>
+      <c r="M15" s="206"/>
+      <c r="N15" s="207"/>
+      <c r="O15" s="208"/>
+      <c r="P15" s="209"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="227"/>
-      <c r="S15" s="227"/>
+      <c r="R15" s="210"/>
+      <c r="S15" s="210"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="223"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="231"/>
-      <c r="I16" s="232"/>
-      <c r="J16" s="232"/>
-      <c r="K16" s="232"/>
-      <c r="L16" s="232"/>
-      <c r="M16" s="233"/>
-      <c r="N16" s="224"/>
-      <c r="O16" s="225"/>
-      <c r="P16" s="226"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="203"/>
+      <c r="H16" s="204"/>
+      <c r="I16" s="205"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="205"/>
+      <c r="M16" s="206"/>
+      <c r="N16" s="207"/>
+      <c r="O16" s="208"/>
+      <c r="P16" s="209"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="227"/>
-      <c r="S16" s="227"/>
+      <c r="R16" s="210"/>
+      <c r="S16" s="210"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="223"/>
-      <c r="D17" s="223"/>
-      <c r="E17" s="223"/>
-      <c r="F17" s="223"/>
-      <c r="G17" s="223"/>
-      <c r="H17" s="231"/>
-      <c r="I17" s="232"/>
-      <c r="J17" s="232"/>
-      <c r="K17" s="232"/>
-      <c r="L17" s="232"/>
-      <c r="M17" s="233"/>
-      <c r="N17" s="224"/>
-      <c r="O17" s="225"/>
-      <c r="P17" s="226"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="203"/>
+      <c r="H17" s="204"/>
+      <c r="I17" s="205"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="205"/>
+      <c r="L17" s="205"/>
+      <c r="M17" s="206"/>
+      <c r="N17" s="207"/>
+      <c r="O17" s="208"/>
+      <c r="P17" s="209"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="227"/>
-      <c r="S17" s="227"/>
+      <c r="R17" s="210"/>
+      <c r="S17" s="210"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="223"/>
-      <c r="E18" s="223"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="231"/>
-      <c r="I18" s="232"/>
-      <c r="J18" s="232"/>
-      <c r="K18" s="232"/>
-      <c r="L18" s="232"/>
-      <c r="M18" s="233"/>
-      <c r="N18" s="224"/>
-      <c r="O18" s="225"/>
-      <c r="P18" s="226"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="204"/>
+      <c r="I18" s="205"/>
+      <c r="J18" s="205"/>
+      <c r="K18" s="205"/>
+      <c r="L18" s="205"/>
+      <c r="M18" s="206"/>
+      <c r="N18" s="207"/>
+      <c r="O18" s="208"/>
+      <c r="P18" s="209"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="227"/>
-      <c r="S18" s="227"/>
+      <c r="R18" s="210"/>
+      <c r="S18" s="210"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="223"/>
-      <c r="D19" s="223"/>
-      <c r="E19" s="223"/>
-      <c r="F19" s="223"/>
-      <c r="G19" s="223"/>
-      <c r="H19" s="231"/>
-      <c r="I19" s="232"/>
-      <c r="J19" s="232"/>
-      <c r="K19" s="232"/>
-      <c r="L19" s="232"/>
-      <c r="M19" s="233"/>
-      <c r="N19" s="224"/>
-      <c r="O19" s="225"/>
-      <c r="P19" s="226"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="203"/>
+      <c r="H19" s="204"/>
+      <c r="I19" s="205"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="205"/>
+      <c r="L19" s="205"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="207"/>
+      <c r="O19" s="208"/>
+      <c r="P19" s="209"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="227"/>
-      <c r="S19" s="227"/>
+      <c r="R19" s="210"/>
+      <c r="S19" s="210"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="223"/>
-      <c r="D20" s="223"/>
-      <c r="E20" s="223"/>
-      <c r="F20" s="223"/>
-      <c r="G20" s="223"/>
-      <c r="H20" s="231"/>
-      <c r="I20" s="232"/>
-      <c r="J20" s="232"/>
-      <c r="K20" s="232"/>
-      <c r="L20" s="232"/>
-      <c r="M20" s="233"/>
-      <c r="N20" s="224"/>
-      <c r="O20" s="225"/>
-      <c r="P20" s="226"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="203"/>
+      <c r="H20" s="204"/>
+      <c r="I20" s="205"/>
+      <c r="J20" s="205"/>
+      <c r="K20" s="205"/>
+      <c r="L20" s="205"/>
+      <c r="M20" s="206"/>
+      <c r="N20" s="207"/>
+      <c r="O20" s="208"/>
+      <c r="P20" s="209"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="227"/>
-      <c r="S20" s="227"/>
+      <c r="R20" s="210"/>
+      <c r="S20" s="210"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="223"/>
-      <c r="D21" s="223"/>
-      <c r="E21" s="223"/>
-      <c r="F21" s="223"/>
-      <c r="G21" s="223"/>
-      <c r="H21" s="231"/>
-      <c r="I21" s="232"/>
-      <c r="J21" s="232"/>
-      <c r="K21" s="232"/>
-      <c r="L21" s="232"/>
-      <c r="M21" s="233"/>
-      <c r="N21" s="224"/>
-      <c r="O21" s="225"/>
-      <c r="P21" s="226"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="203"/>
+      <c r="H21" s="204"/>
+      <c r="I21" s="205"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="205"/>
+      <c r="L21" s="205"/>
+      <c r="M21" s="206"/>
+      <c r="N21" s="207"/>
+      <c r="O21" s="208"/>
+      <c r="P21" s="209"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="227"/>
-      <c r="S21" s="227"/>
+      <c r="R21" s="210"/>
+      <c r="S21" s="210"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="223"/>
-      <c r="D22" s="223"/>
-      <c r="E22" s="223"/>
-      <c r="F22" s="223"/>
-      <c r="G22" s="223"/>
-      <c r="H22" s="231"/>
-      <c r="I22" s="232"/>
-      <c r="J22" s="232"/>
-      <c r="K22" s="232"/>
-      <c r="L22" s="232"/>
-      <c r="M22" s="233"/>
-      <c r="N22" s="224"/>
-      <c r="O22" s="225"/>
-      <c r="P22" s="226"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="204"/>
+      <c r="I22" s="205"/>
+      <c r="J22" s="205"/>
+      <c r="K22" s="205"/>
+      <c r="L22" s="205"/>
+      <c r="M22" s="206"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="208"/>
+      <c r="P22" s="209"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="227"/>
-      <c r="S22" s="227"/>
+      <c r="R22" s="210"/>
+      <c r="S22" s="210"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="223"/>
-      <c r="D23" s="223"/>
-      <c r="E23" s="223"/>
-      <c r="F23" s="223"/>
-      <c r="G23" s="223"/>
-      <c r="H23" s="231"/>
-      <c r="I23" s="232"/>
-      <c r="J23" s="232"/>
-      <c r="K23" s="232"/>
-      <c r="L23" s="232"/>
-      <c r="M23" s="233"/>
-      <c r="N23" s="224"/>
-      <c r="O23" s="225"/>
-      <c r="P23" s="226"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="203"/>
+      <c r="H23" s="204"/>
+      <c r="I23" s="205"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="205"/>
+      <c r="L23" s="205"/>
+      <c r="M23" s="206"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="208"/>
+      <c r="P23" s="209"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="227"/>
-      <c r="S23" s="227"/>
+      <c r="R23" s="210"/>
+      <c r="S23" s="210"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="223"/>
-      <c r="D24" s="223"/>
-      <c r="E24" s="223"/>
-      <c r="F24" s="223"/>
-      <c r="G24" s="223"/>
-      <c r="H24" s="231"/>
-      <c r="I24" s="232"/>
-      <c r="J24" s="232"/>
-      <c r="K24" s="232"/>
-      <c r="L24" s="232"/>
-      <c r="M24" s="233"/>
-      <c r="N24" s="224"/>
-      <c r="O24" s="225"/>
-      <c r="P24" s="226"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="203"/>
+      <c r="H24" s="204"/>
+      <c r="I24" s="205"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="205"/>
+      <c r="L24" s="205"/>
+      <c r="M24" s="206"/>
+      <c r="N24" s="207"/>
+      <c r="O24" s="208"/>
+      <c r="P24" s="209"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="227"/>
-      <c r="S24" s="227"/>
+      <c r="R24" s="210"/>
+      <c r="S24" s="210"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="223"/>
-      <c r="D25" s="223"/>
-      <c r="E25" s="223"/>
-      <c r="F25" s="223"/>
-      <c r="G25" s="223"/>
-      <c r="H25" s="231"/>
-      <c r="I25" s="232"/>
-      <c r="J25" s="232"/>
-      <c r="K25" s="232"/>
-      <c r="L25" s="232"/>
-      <c r="M25" s="233"/>
-      <c r="N25" s="224"/>
-      <c r="O25" s="225"/>
-      <c r="P25" s="226"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="203"/>
+      <c r="H25" s="204"/>
+      <c r="I25" s="205"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="205"/>
+      <c r="L25" s="205"/>
+      <c r="M25" s="206"/>
+      <c r="N25" s="207"/>
+      <c r="O25" s="208"/>
+      <c r="P25" s="209"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="227"/>
-      <c r="S25" s="227"/>
+      <c r="R25" s="210"/>
+      <c r="S25" s="210"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="223"/>
-      <c r="D26" s="223"/>
-      <c r="E26" s="223"/>
-      <c r="F26" s="223"/>
-      <c r="G26" s="223"/>
-      <c r="H26" s="231"/>
-      <c r="I26" s="232"/>
-      <c r="J26" s="232"/>
-      <c r="K26" s="232"/>
-      <c r="L26" s="232"/>
-      <c r="M26" s="233"/>
-      <c r="N26" s="224"/>
-      <c r="O26" s="225"/>
-      <c r="P26" s="226"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="205"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="205"/>
+      <c r="L26" s="205"/>
+      <c r="M26" s="206"/>
+      <c r="N26" s="207"/>
+      <c r="O26" s="208"/>
+      <c r="P26" s="209"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="227"/>
-      <c r="S26" s="227"/>
+      <c r="R26" s="210"/>
+      <c r="S26" s="210"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="223"/>
-      <c r="D27" s="223"/>
-      <c r="E27" s="223"/>
-      <c r="F27" s="223"/>
-      <c r="G27" s="223"/>
-      <c r="H27" s="231"/>
-      <c r="I27" s="232"/>
-      <c r="J27" s="232"/>
-      <c r="K27" s="232"/>
-      <c r="L27" s="232"/>
-      <c r="M27" s="233"/>
-      <c r="N27" s="224"/>
-      <c r="O27" s="225"/>
-      <c r="P27" s="226"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="203"/>
+      <c r="H27" s="204"/>
+      <c r="I27" s="205"/>
+      <c r="J27" s="205"/>
+      <c r="K27" s="205"/>
+      <c r="L27" s="205"/>
+      <c r="M27" s="206"/>
+      <c r="N27" s="207"/>
+      <c r="O27" s="208"/>
+      <c r="P27" s="209"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="227"/>
-      <c r="S27" s="227"/>
+      <c r="R27" s="210"/>
+      <c r="S27" s="210"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="223"/>
-      <c r="D28" s="223"/>
-      <c r="E28" s="223"/>
-      <c r="F28" s="223"/>
-      <c r="G28" s="223"/>
-      <c r="H28" s="231"/>
-      <c r="I28" s="232"/>
-      <c r="J28" s="232"/>
-      <c r="K28" s="232"/>
-      <c r="L28" s="232"/>
-      <c r="M28" s="233"/>
-      <c r="N28" s="224"/>
-      <c r="O28" s="225"/>
-      <c r="P28" s="226"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="203"/>
+      <c r="H28" s="204"/>
+      <c r="I28" s="205"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="205"/>
+      <c r="L28" s="205"/>
+      <c r="M28" s="206"/>
+      <c r="N28" s="207"/>
+      <c r="O28" s="208"/>
+      <c r="P28" s="209"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="227"/>
-      <c r="S28" s="227"/>
+      <c r="R28" s="210"/>
+      <c r="S28" s="210"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="223"/>
-      <c r="D29" s="223"/>
-      <c r="E29" s="223"/>
-      <c r="F29" s="223"/>
-      <c r="G29" s="223"/>
-      <c r="H29" s="231"/>
-      <c r="I29" s="232"/>
-      <c r="J29" s="232"/>
-      <c r="K29" s="232"/>
-      <c r="L29" s="232"/>
-      <c r="M29" s="233"/>
-      <c r="N29" s="224"/>
-      <c r="O29" s="225"/>
-      <c r="P29" s="226"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="204"/>
+      <c r="I29" s="205"/>
+      <c r="J29" s="205"/>
+      <c r="K29" s="205"/>
+      <c r="L29" s="205"/>
+      <c r="M29" s="206"/>
+      <c r="N29" s="207"/>
+      <c r="O29" s="208"/>
+      <c r="P29" s="209"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="227"/>
-      <c r="S29" s="227"/>
+      <c r="R29" s="210"/>
+      <c r="S29" s="210"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="223"/>
-      <c r="D30" s="223"/>
-      <c r="E30" s="223"/>
-      <c r="F30" s="223"/>
-      <c r="G30" s="223"/>
-      <c r="H30" s="231"/>
-      <c r="I30" s="232"/>
-      <c r="J30" s="232"/>
-      <c r="K30" s="232"/>
-      <c r="L30" s="232"/>
-      <c r="M30" s="233"/>
-      <c r="N30" s="224"/>
-      <c r="O30" s="225"/>
-      <c r="P30" s="226"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="203"/>
+      <c r="H30" s="204"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="205"/>
+      <c r="L30" s="205"/>
+      <c r="M30" s="206"/>
+      <c r="N30" s="207"/>
+      <c r="O30" s="208"/>
+      <c r="P30" s="209"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="227"/>
-      <c r="S30" s="227"/>
+      <c r="R30" s="210"/>
+      <c r="S30" s="210"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="223"/>
-      <c r="D31" s="223"/>
-      <c r="E31" s="223"/>
-      <c r="F31" s="223"/>
-      <c r="G31" s="223"/>
-      <c r="H31" s="231"/>
-      <c r="I31" s="232"/>
-      <c r="J31" s="232"/>
-      <c r="K31" s="232"/>
-      <c r="L31" s="232"/>
-      <c r="M31" s="233"/>
-      <c r="N31" s="224"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="226"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="203"/>
+      <c r="H31" s="204"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="205"/>
+      <c r="L31" s="205"/>
+      <c r="M31" s="206"/>
+      <c r="N31" s="207"/>
+      <c r="O31" s="208"/>
+      <c r="P31" s="209"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="227"/>
-      <c r="S31" s="227"/>
+      <c r="R31" s="210"/>
+      <c r="S31" s="210"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="223"/>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="223"/>
-      <c r="G32" s="223"/>
-      <c r="H32" s="231"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="232"/>
-      <c r="K32" s="232"/>
-      <c r="L32" s="232"/>
-      <c r="M32" s="233"/>
-      <c r="N32" s="224"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="226"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="203"/>
+      <c r="H32" s="204"/>
+      <c r="I32" s="205"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="205"/>
+      <c r="L32" s="205"/>
+      <c r="M32" s="206"/>
+      <c r="N32" s="207"/>
+      <c r="O32" s="208"/>
+      <c r="P32" s="209"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="227"/>
-      <c r="S32" s="227"/>
+      <c r="R32" s="210"/>
+      <c r="S32" s="210"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="223"/>
-      <c r="F33" s="223"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="231"/>
-      <c r="I33" s="232"/>
-      <c r="J33" s="232"/>
-      <c r="K33" s="232"/>
-      <c r="L33" s="232"/>
-      <c r="M33" s="233"/>
-      <c r="N33" s="224"/>
-      <c r="O33" s="225"/>
-      <c r="P33" s="226"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="204"/>
+      <c r="I33" s="205"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="205"/>
+      <c r="L33" s="205"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="207"/>
+      <c r="O33" s="208"/>
+      <c r="P33" s="209"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="227"/>
-      <c r="S33" s="227"/>
+      <c r="R33" s="210"/>
+      <c r="S33" s="210"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="223"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="223"/>
-      <c r="F34" s="223"/>
-      <c r="G34" s="223"/>
-      <c r="H34" s="231"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="232"/>
-      <c r="M34" s="233"/>
-      <c r="N34" s="224"/>
-      <c r="O34" s="225"/>
-      <c r="P34" s="226"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="203"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="204"/>
+      <c r="I34" s="205"/>
+      <c r="J34" s="205"/>
+      <c r="K34" s="205"/>
+      <c r="L34" s="205"/>
+      <c r="M34" s="206"/>
+      <c r="N34" s="207"/>
+      <c r="O34" s="208"/>
+      <c r="P34" s="209"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="227"/>
-      <c r="S34" s="227"/>
+      <c r="R34" s="210"/>
+      <c r="S34" s="210"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="223"/>
-      <c r="E35" s="223"/>
-      <c r="F35" s="223"/>
-      <c r="G35" s="223"/>
-      <c r="H35" s="231"/>
-      <c r="I35" s="232"/>
-      <c r="J35" s="232"/>
-      <c r="K35" s="232"/>
-      <c r="L35" s="232"/>
-      <c r="M35" s="233"/>
-      <c r="N35" s="224"/>
-      <c r="O35" s="225"/>
-      <c r="P35" s="226"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="204"/>
+      <c r="I35" s="205"/>
+      <c r="J35" s="205"/>
+      <c r="K35" s="205"/>
+      <c r="L35" s="205"/>
+      <c r="M35" s="206"/>
+      <c r="N35" s="207"/>
+      <c r="O35" s="208"/>
+      <c r="P35" s="209"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="227"/>
-      <c r="S35" s="227"/>
+      <c r="R35" s="210"/>
+      <c r="S35" s="210"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="231"/>
-      <c r="I36" s="232"/>
-      <c r="J36" s="232"/>
-      <c r="K36" s="232"/>
-      <c r="L36" s="232"/>
-      <c r="M36" s="233"/>
-      <c r="N36" s="224"/>
-      <c r="O36" s="225"/>
-      <c r="P36" s="226"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="203"/>
+      <c r="F36" s="203"/>
+      <c r="G36" s="203"/>
+      <c r="H36" s="204"/>
+      <c r="I36" s="205"/>
+      <c r="J36" s="205"/>
+      <c r="K36" s="205"/>
+      <c r="L36" s="205"/>
+      <c r="M36" s="206"/>
+      <c r="N36" s="207"/>
+      <c r="O36" s="208"/>
+      <c r="P36" s="209"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="227"/>
-      <c r="S36" s="227"/>
+      <c r="R36" s="210"/>
+      <c r="S36" s="210"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="223"/>
-      <c r="D37" s="223"/>
-      <c r="E37" s="223"/>
-      <c r="F37" s="223"/>
-      <c r="G37" s="223"/>
-      <c r="H37" s="231"/>
-      <c r="I37" s="232"/>
-      <c r="J37" s="232"/>
-      <c r="K37" s="232"/>
-      <c r="L37" s="232"/>
-      <c r="M37" s="233"/>
-      <c r="N37" s="224"/>
-      <c r="O37" s="225"/>
-      <c r="P37" s="226"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="203"/>
+      <c r="H37" s="204"/>
+      <c r="I37" s="205"/>
+      <c r="J37" s="205"/>
+      <c r="K37" s="205"/>
+      <c r="L37" s="205"/>
+      <c r="M37" s="206"/>
+      <c r="N37" s="207"/>
+      <c r="O37" s="208"/>
+      <c r="P37" s="209"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="227"/>
-      <c r="S37" s="227"/>
+      <c r="R37" s="210"/>
+      <c r="S37" s="210"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="223"/>
-      <c r="D38" s="223"/>
-      <c r="E38" s="223"/>
-      <c r="F38" s="223"/>
-      <c r="G38" s="223"/>
-      <c r="H38" s="231"/>
-      <c r="I38" s="232"/>
-      <c r="J38" s="232"/>
-      <c r="K38" s="232"/>
-      <c r="L38" s="232"/>
-      <c r="M38" s="233"/>
-      <c r="N38" s="224"/>
-      <c r="O38" s="225"/>
-      <c r="P38" s="226"/>
+      <c r="C38" s="203"/>
+      <c r="D38" s="203"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="203"/>
+      <c r="H38" s="204"/>
+      <c r="I38" s="205"/>
+      <c r="J38" s="205"/>
+      <c r="K38" s="205"/>
+      <c r="L38" s="205"/>
+      <c r="M38" s="206"/>
+      <c r="N38" s="207"/>
+      <c r="O38" s="208"/>
+      <c r="P38" s="209"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="227"/>
-      <c r="S38" s="227"/>
+      <c r="R38" s="210"/>
+      <c r="S38" s="210"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="223"/>
-      <c r="D39" s="223"/>
-      <c r="E39" s="223"/>
-      <c r="F39" s="223"/>
-      <c r="G39" s="223"/>
-      <c r="H39" s="231"/>
-      <c r="I39" s="232"/>
-      <c r="J39" s="232"/>
-      <c r="K39" s="232"/>
-      <c r="L39" s="232"/>
-      <c r="M39" s="233"/>
-      <c r="N39" s="224"/>
-      <c r="O39" s="225"/>
-      <c r="P39" s="226"/>
+      <c r="C39" s="203"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="203"/>
+      <c r="F39" s="203"/>
+      <c r="G39" s="203"/>
+      <c r="H39" s="204"/>
+      <c r="I39" s="205"/>
+      <c r="J39" s="205"/>
+      <c r="K39" s="205"/>
+      <c r="L39" s="205"/>
+      <c r="M39" s="206"/>
+      <c r="N39" s="207"/>
+      <c r="O39" s="208"/>
+      <c r="P39" s="209"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="227"/>
-      <c r="S39" s="227"/>
+      <c r="R39" s="210"/>
+      <c r="S39" s="210"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="223"/>
-      <c r="D40" s="223"/>
-      <c r="E40" s="223"/>
-      <c r="F40" s="223"/>
-      <c r="G40" s="223"/>
-      <c r="H40" s="231"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="233"/>
-      <c r="N40" s="224"/>
-      <c r="O40" s="225"/>
-      <c r="P40" s="226"/>
+      <c r="C40" s="203"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="204"/>
+      <c r="I40" s="205"/>
+      <c r="J40" s="205"/>
+      <c r="K40" s="205"/>
+      <c r="L40" s="205"/>
+      <c r="M40" s="206"/>
+      <c r="N40" s="207"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="209"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="227"/>
-      <c r="S40" s="227"/>
+      <c r="R40" s="210"/>
+      <c r="S40" s="210"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="223"/>
-      <c r="D41" s="223"/>
-      <c r="E41" s="223"/>
-      <c r="F41" s="223"/>
-      <c r="G41" s="223"/>
-      <c r="H41" s="231"/>
-      <c r="I41" s="232"/>
-      <c r="J41" s="232"/>
-      <c r="K41" s="232"/>
-      <c r="L41" s="232"/>
-      <c r="M41" s="233"/>
-      <c r="N41" s="224"/>
-      <c r="O41" s="225"/>
-      <c r="P41" s="226"/>
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+      <c r="G41" s="203"/>
+      <c r="H41" s="204"/>
+      <c r="I41" s="205"/>
+      <c r="J41" s="205"/>
+      <c r="K41" s="205"/>
+      <c r="L41" s="205"/>
+      <c r="M41" s="206"/>
+      <c r="N41" s="207"/>
+      <c r="O41" s="208"/>
+      <c r="P41" s="209"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="227"/>
-      <c r="S41" s="227"/>
+      <c r="R41" s="210"/>
+      <c r="S41" s="210"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="223"/>
-      <c r="D42" s="223"/>
-      <c r="E42" s="223"/>
-      <c r="F42" s="223"/>
-      <c r="G42" s="223"/>
-      <c r="H42" s="231"/>
-      <c r="I42" s="232"/>
-      <c r="J42" s="232"/>
-      <c r="K42" s="232"/>
-      <c r="L42" s="232"/>
-      <c r="M42" s="233"/>
-      <c r="N42" s="224"/>
-      <c r="O42" s="225"/>
-      <c r="P42" s="226"/>
+      <c r="C42" s="203"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="203"/>
+      <c r="G42" s="203"/>
+      <c r="H42" s="204"/>
+      <c r="I42" s="205"/>
+      <c r="J42" s="205"/>
+      <c r="K42" s="205"/>
+      <c r="L42" s="205"/>
+      <c r="M42" s="206"/>
+      <c r="N42" s="207"/>
+      <c r="O42" s="208"/>
+      <c r="P42" s="209"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="227"/>
-      <c r="S42" s="227"/>
+      <c r="R42" s="210"/>
+      <c r="S42" s="210"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="223"/>
-      <c r="D43" s="223"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="231"/>
-      <c r="I43" s="232"/>
-      <c r="J43" s="232"/>
-      <c r="K43" s="232"/>
-      <c r="L43" s="232"/>
-      <c r="M43" s="233"/>
-      <c r="N43" s="224"/>
-      <c r="O43" s="225"/>
-      <c r="P43" s="226"/>
+      <c r="C43" s="203"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="203"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
+      <c r="H43" s="204"/>
+      <c r="I43" s="205"/>
+      <c r="J43" s="205"/>
+      <c r="K43" s="205"/>
+      <c r="L43" s="205"/>
+      <c r="M43" s="206"/>
+      <c r="N43" s="207"/>
+      <c r="O43" s="208"/>
+      <c r="P43" s="209"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="227"/>
-      <c r="S43" s="227"/>
+      <c r="R43" s="210"/>
+      <c r="S43" s="210"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="223"/>
-      <c r="D44" s="223"/>
-      <c r="E44" s="223"/>
-      <c r="F44" s="223"/>
-      <c r="G44" s="223"/>
-      <c r="H44" s="231"/>
-      <c r="I44" s="232"/>
-      <c r="J44" s="232"/>
-      <c r="K44" s="232"/>
-      <c r="L44" s="232"/>
-      <c r="M44" s="233"/>
-      <c r="N44" s="224"/>
-      <c r="O44" s="225"/>
-      <c r="P44" s="226"/>
+      <c r="C44" s="203"/>
+      <c r="D44" s="203"/>
+      <c r="E44" s="203"/>
+      <c r="F44" s="203"/>
+      <c r="G44" s="203"/>
+      <c r="H44" s="204"/>
+      <c r="I44" s="205"/>
+      <c r="J44" s="205"/>
+      <c r="K44" s="205"/>
+      <c r="L44" s="205"/>
+      <c r="M44" s="206"/>
+      <c r="N44" s="207"/>
+      <c r="O44" s="208"/>
+      <c r="P44" s="209"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="227"/>
-      <c r="S44" s="227"/>
+      <c r="R44" s="210"/>
+      <c r="S44" s="210"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="223"/>
-      <c r="D45" s="223"/>
-      <c r="E45" s="223"/>
-      <c r="F45" s="223"/>
-      <c r="G45" s="223"/>
-      <c r="H45" s="231"/>
-      <c r="I45" s="232"/>
-      <c r="J45" s="232"/>
-      <c r="K45" s="232"/>
-      <c r="L45" s="232"/>
-      <c r="M45" s="233"/>
-      <c r="N45" s="224"/>
-      <c r="O45" s="225"/>
-      <c r="P45" s="226"/>
+      <c r="C45" s="203"/>
+      <c r="D45" s="203"/>
+      <c r="E45" s="203"/>
+      <c r="F45" s="203"/>
+      <c r="G45" s="203"/>
+      <c r="H45" s="204"/>
+      <c r="I45" s="205"/>
+      <c r="J45" s="205"/>
+      <c r="K45" s="205"/>
+      <c r="L45" s="205"/>
+      <c r="M45" s="206"/>
+      <c r="N45" s="207"/>
+      <c r="O45" s="208"/>
+      <c r="P45" s="209"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="227"/>
-      <c r="S45" s="227"/>
+      <c r="R45" s="210"/>
+      <c r="S45" s="210"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="223"/>
-      <c r="D46" s="223"/>
-      <c r="E46" s="223"/>
-      <c r="F46" s="223"/>
-      <c r="G46" s="223"/>
-      <c r="H46" s="231"/>
-      <c r="I46" s="232"/>
-      <c r="J46" s="232"/>
-      <c r="K46" s="232"/>
-      <c r="L46" s="232"/>
-      <c r="M46" s="233"/>
-      <c r="N46" s="224"/>
-      <c r="O46" s="225"/>
-      <c r="P46" s="226"/>
+      <c r="C46" s="203"/>
+      <c r="D46" s="203"/>
+      <c r="E46" s="203"/>
+      <c r="F46" s="203"/>
+      <c r="G46" s="203"/>
+      <c r="H46" s="204"/>
+      <c r="I46" s="205"/>
+      <c r="J46" s="205"/>
+      <c r="K46" s="205"/>
+      <c r="L46" s="205"/>
+      <c r="M46" s="206"/>
+      <c r="N46" s="207"/>
+      <c r="O46" s="208"/>
+      <c r="P46" s="209"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="227"/>
-      <c r="S46" s="227"/>
+      <c r="R46" s="210"/>
+      <c r="S46" s="210"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="223"/>
-      <c r="D47" s="223"/>
-      <c r="E47" s="223"/>
-      <c r="F47" s="223"/>
-      <c r="G47" s="223"/>
-      <c r="H47" s="231"/>
-      <c r="I47" s="232"/>
-      <c r="J47" s="232"/>
-      <c r="K47" s="232"/>
-      <c r="L47" s="232"/>
-      <c r="M47" s="233"/>
-      <c r="N47" s="224"/>
-      <c r="O47" s="225"/>
-      <c r="P47" s="226"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="203"/>
+      <c r="E47" s="203"/>
+      <c r="F47" s="203"/>
+      <c r="G47" s="203"/>
+      <c r="H47" s="204"/>
+      <c r="I47" s="205"/>
+      <c r="J47" s="205"/>
+      <c r="K47" s="205"/>
+      <c r="L47" s="205"/>
+      <c r="M47" s="206"/>
+      <c r="N47" s="207"/>
+      <c r="O47" s="208"/>
+      <c r="P47" s="209"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="227"/>
-      <c r="S47" s="227"/>
+      <c r="R47" s="210"/>
+      <c r="S47" s="210"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="223"/>
-      <c r="D48" s="223"/>
-      <c r="E48" s="223"/>
-      <c r="F48" s="223"/>
-      <c r="G48" s="223"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="232"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="232"/>
-      <c r="L48" s="232"/>
-      <c r="M48" s="233"/>
-      <c r="N48" s="224"/>
-      <c r="O48" s="225"/>
-      <c r="P48" s="226"/>
+      <c r="C48" s="203"/>
+      <c r="D48" s="203"/>
+      <c r="E48" s="203"/>
+      <c r="F48" s="203"/>
+      <c r="G48" s="203"/>
+      <c r="H48" s="204"/>
+      <c r="I48" s="205"/>
+      <c r="J48" s="205"/>
+      <c r="K48" s="205"/>
+      <c r="L48" s="205"/>
+      <c r="M48" s="206"/>
+      <c r="N48" s="207"/>
+      <c r="O48" s="208"/>
+      <c r="P48" s="209"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="227"/>
-      <c r="S48" s="227"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="210"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="223"/>
-      <c r="D49" s="223"/>
-      <c r="E49" s="223"/>
-      <c r="F49" s="223"/>
-      <c r="G49" s="223"/>
-      <c r="H49" s="231"/>
-      <c r="I49" s="232"/>
-      <c r="J49" s="232"/>
-      <c r="K49" s="232"/>
-      <c r="L49" s="232"/>
-      <c r="M49" s="233"/>
-      <c r="N49" s="224"/>
-      <c r="O49" s="225"/>
-      <c r="P49" s="226"/>
+      <c r="C49" s="203"/>
+      <c r="D49" s="203"/>
+      <c r="E49" s="203"/>
+      <c r="F49" s="203"/>
+      <c r="G49" s="203"/>
+      <c r="H49" s="204"/>
+      <c r="I49" s="205"/>
+      <c r="J49" s="205"/>
+      <c r="K49" s="205"/>
+      <c r="L49" s="205"/>
+      <c r="M49" s="206"/>
+      <c r="N49" s="207"/>
+      <c r="O49" s="208"/>
+      <c r="P49" s="209"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="227"/>
-      <c r="S49" s="227"/>
+      <c r="R49" s="210"/>
+      <c r="S49" s="210"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="223"/>
-      <c r="D50" s="223"/>
-      <c r="E50" s="223"/>
-      <c r="F50" s="223"/>
-      <c r="G50" s="223"/>
-      <c r="H50" s="231"/>
-      <c r="I50" s="232"/>
-      <c r="J50" s="232"/>
-      <c r="K50" s="232"/>
-      <c r="L50" s="232"/>
-      <c r="M50" s="233"/>
-      <c r="N50" s="224"/>
-      <c r="O50" s="225"/>
-      <c r="P50" s="226"/>
+      <c r="C50" s="203"/>
+      <c r="D50" s="203"/>
+      <c r="E50" s="203"/>
+      <c r="F50" s="203"/>
+      <c r="G50" s="203"/>
+      <c r="H50" s="204"/>
+      <c r="I50" s="205"/>
+      <c r="J50" s="205"/>
+      <c r="K50" s="205"/>
+      <c r="L50" s="205"/>
+      <c r="M50" s="206"/>
+      <c r="N50" s="207"/>
+      <c r="O50" s="208"/>
+      <c r="P50" s="209"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="227"/>
-      <c r="S50" s="227"/>
+      <c r="R50" s="210"/>
+      <c r="S50" s="210"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="223"/>
-      <c r="D51" s="223"/>
-      <c r="E51" s="223"/>
-      <c r="F51" s="223"/>
-      <c r="G51" s="223"/>
-      <c r="H51" s="231"/>
-      <c r="I51" s="232"/>
-      <c r="J51" s="232"/>
-      <c r="K51" s="232"/>
-      <c r="L51" s="232"/>
-      <c r="M51" s="233"/>
-      <c r="N51" s="224"/>
-      <c r="O51" s="225"/>
-      <c r="P51" s="226"/>
+      <c r="C51" s="203"/>
+      <c r="D51" s="203"/>
+      <c r="E51" s="203"/>
+      <c r="F51" s="203"/>
+      <c r="G51" s="203"/>
+      <c r="H51" s="204"/>
+      <c r="I51" s="205"/>
+      <c r="J51" s="205"/>
+      <c r="K51" s="205"/>
+      <c r="L51" s="205"/>
+      <c r="M51" s="206"/>
+      <c r="N51" s="207"/>
+      <c r="O51" s="208"/>
+      <c r="P51" s="209"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="227"/>
-      <c r="S51" s="227"/>
+      <c r="R51" s="210"/>
+      <c r="S51" s="210"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="223"/>
-      <c r="D52" s="223"/>
-      <c r="E52" s="223"/>
-      <c r="F52" s="223"/>
-      <c r="G52" s="223"/>
-      <c r="H52" s="231"/>
-      <c r="I52" s="232"/>
-      <c r="J52" s="232"/>
-      <c r="K52" s="232"/>
-      <c r="L52" s="232"/>
-      <c r="M52" s="233"/>
-      <c r="N52" s="224"/>
-      <c r="O52" s="225"/>
-      <c r="P52" s="226"/>
+      <c r="C52" s="203"/>
+      <c r="D52" s="203"/>
+      <c r="E52" s="203"/>
+      <c r="F52" s="203"/>
+      <c r="G52" s="203"/>
+      <c r="H52" s="204"/>
+      <c r="I52" s="205"/>
+      <c r="J52" s="205"/>
+      <c r="K52" s="205"/>
+      <c r="L52" s="205"/>
+      <c r="M52" s="206"/>
+      <c r="N52" s="207"/>
+      <c r="O52" s="208"/>
+      <c r="P52" s="209"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="227"/>
-      <c r="S52" s="227"/>
+      <c r="R52" s="210"/>
+      <c r="S52" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -13022,6 +12910,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82A8AA3-74BF-43A3-96F4-A3BAF12C3493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D351F8-CB54-4746-9B54-EA68144AC375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="114">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -588,16 +588,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>「未入力」と表示される</t>
-    <rPh sb="1" eb="4">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>期限、メモが未入力の場合のタスク一覧表示</t>
     <rPh sb="0" eb="2">
       <t>キゲン</t>
@@ -734,6 +724,25 @@
       <t>ユウドウ</t>
     </rPh>
     <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>期限は「未入力」と表示され、メモは元のメモが表示される</t>
+    <rPh sb="0" eb="2">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="22" eb="24">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="7"/>
@@ -1961,6 +1970,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1971,11 +2013,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1991,9 +2081,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2006,84 +2093,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2147,6 +2156,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2165,18 +2183,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2189,9 +2201,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2267,184 +2276,184 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4164,19 +4173,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="109" t="s">
+      <c r="B1" s="91"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="97"/>
-      <c r="F1" s="109" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="97"/>
+      <c r="G1" s="82"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4188,190 +4197,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="103"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="110" t="s">
+      <c r="A2" s="93"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="111"/>
-      <c r="F2" s="110" t="s">
+      <c r="E2" s="101"/>
+      <c r="F2" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="114">
+      <c r="G2" s="101"/>
+      <c r="H2" s="104">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="92"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="103"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="93"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="96"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="95" t="s">
+      <c r="A5" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="99"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="84" t="s">
+      <c r="B6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="78"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="84" t="s">
+      <c r="B7" s="86"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="78"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="84" t="s">
+      <c r="B8" s="86"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="78"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="87" customHeight="1">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="88" t="s">
+      <c r="B9" s="114" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="77" t="s">
+      <c r="C9" s="87"/>
+      <c r="D9" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="78"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="89"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="88" t="s">
+      <c r="A10" s="112"/>
+      <c r="B10" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="78"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88" t="s">
+      <c r="A11" s="113"/>
+      <c r="B11" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77" t="s">
+      <c r="C11" s="87"/>
+      <c r="D11" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="78"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="89"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="78"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="105" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="89"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="83"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="110"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5362,18 +5371,6 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5389,6 +5386,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6900,23 +6909,23 @@
       <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="137"/>
+      <c r="B5" s="140"/>
       <c r="C5" s="131"/>
-      <c r="D5" s="143" t="s">
+      <c r="D5" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
-      <c r="J5" s="144"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="146"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="141" t="s">
+      <c r="A6" s="144" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="67"/>
@@ -6927,19 +6936,19 @@
       <c r="G6" s="67"/>
       <c r="H6" s="67"/>
       <c r="I6" s="67"/>
-      <c r="J6" s="145"/>
+      <c r="J6" s="137"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="146"/>
-      <c r="B7" s="147"/>
-      <c r="C7" s="147"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="148"/>
+      <c r="A7" s="147"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="149"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="125"/>
@@ -6951,7 +6960,7 @@
       <c r="G8" s="70"/>
       <c r="H8" s="70"/>
       <c r="I8" s="70"/>
-      <c r="J8" s="149"/>
+      <c r="J8" s="150"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="125"/>
@@ -6963,7 +6972,7 @@
       <c r="G9" s="70"/>
       <c r="H9" s="70"/>
       <c r="I9" s="70"/>
-      <c r="J9" s="149"/>
+      <c r="J9" s="150"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="125"/>
@@ -6975,7 +6984,7 @@
       <c r="G10" s="70"/>
       <c r="H10" s="70"/>
       <c r="I10" s="70"/>
-      <c r="J10" s="149"/>
+      <c r="J10" s="150"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="125"/>
@@ -6987,7 +6996,7 @@
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
-      <c r="J11" s="149"/>
+      <c r="J11" s="150"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="125"/>
@@ -6999,7 +7008,7 @@
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
       <c r="I12" s="70"/>
-      <c r="J12" s="149"/>
+      <c r="J12" s="150"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="125"/>
@@ -7011,10 +7020,10 @@
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
       <c r="I13" s="70"/>
-      <c r="J13" s="149"/>
+      <c r="J13" s="150"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="141" t="s">
+      <c r="A14" s="144" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="67"/>
@@ -7025,15 +7034,15 @@
       <c r="G14" s="67"/>
       <c r="H14" s="67"/>
       <c r="I14" s="67"/>
-      <c r="J14" s="145"/>
+      <c r="J14" s="137"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="141" t="s">
+      <c r="A15" s="144" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="67"/>
       <c r="C15" s="68"/>
-      <c r="D15" s="150" t="s">
+      <c r="D15" s="136" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="67"/>
@@ -7048,7 +7057,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="144" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="67"/>
@@ -7069,10 +7078,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="67"/>
-      <c r="J16" s="145"/>
+      <c r="J16" s="137"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="138">
         <v>1</v>
       </c>
       <c r="B17" s="67"/>
@@ -7087,80 +7096,80 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="150"/>
+      <c r="H17" s="136"/>
       <c r="I17" s="67"/>
-      <c r="J17" s="145"/>
+      <c r="J17" s="137"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142"/>
+      <c r="A18" s="138"/>
       <c r="B18" s="67"/>
       <c r="C18" s="68"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="150"/>
+      <c r="H18" s="136"/>
       <c r="I18" s="67"/>
-      <c r="J18" s="145"/>
+      <c r="J18" s="137"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142"/>
+      <c r="A19" s="138"/>
       <c r="B19" s="67"/>
       <c r="C19" s="68"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="150"/>
+      <c r="H19" s="136"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="145"/>
+      <c r="J19" s="137"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142"/>
+      <c r="A20" s="138"/>
       <c r="B20" s="67"/>
       <c r="C20" s="68"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="150"/>
+      <c r="H20" s="136"/>
       <c r="I20" s="67"/>
-      <c r="J20" s="145"/>
+      <c r="J20" s="137"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142"/>
+      <c r="A21" s="138"/>
       <c r="B21" s="67"/>
       <c r="C21" s="68"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="150"/>
+      <c r="H21" s="136"/>
       <c r="I21" s="67"/>
-      <c r="J21" s="145"/>
+      <c r="J21" s="137"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142"/>
+      <c r="A22" s="138"/>
       <c r="B22" s="67"/>
       <c r="C22" s="68"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="150"/>
+      <c r="H22" s="136"/>
       <c r="I22" s="67"/>
-      <c r="J22" s="145"/>
+      <c r="J22" s="137"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="138"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="142"/>
+      <c r="C23" s="143"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="152"/>
-      <c r="I23" s="139"/>
+      <c r="I23" s="142"/>
       <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8142,16 +8151,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8168,11 +8172,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9607,7 +9616,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="188" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="161"/>
@@ -9618,14 +9627,14 @@
       <c r="G1" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
       <c r="J1" s="170"/>
       <c r="K1" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
+      <c r="L1" s="180"/>
+      <c r="M1" s="180"/>
       <c r="N1" s="170"/>
       <c r="O1" s="169" t="s">
         <v>7</v>
@@ -9638,7 +9647,7 @@
       <c r="S1" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="197"/>
+      <c r="T1" s="182"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="163"/>
@@ -9650,16 +9659,16 @@
       <c r="G2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="201"/>
-      <c r="I2" s="201"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
       <c r="J2" s="172"/>
       <c r="K2" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="201"/>
-      <c r="M2" s="201"/>
+      <c r="L2" s="189"/>
+      <c r="M2" s="189"/>
       <c r="N2" s="172"/>
-      <c r="O2" s="202">
+      <c r="O2" s="190">
         <v>45817</v>
       </c>
       <c r="P2" s="172"/>
@@ -9668,7 +9677,7 @@
       </c>
       <c r="R2" s="172"/>
       <c r="S2" s="171"/>
-      <c r="T2" s="191"/>
+      <c r="T2" s="176"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="163"/>
@@ -9690,7 +9699,7 @@
       <c r="Q3" s="173"/>
       <c r="R3" s="165"/>
       <c r="S3" s="173"/>
-      <c r="T3" s="192"/>
+      <c r="T3" s="177"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="166"/>
@@ -9712,85 +9721,85 @@
       <c r="Q4" s="174"/>
       <c r="R4" s="168"/>
       <c r="S4" s="174"/>
-      <c r="T4" s="193"/>
+      <c r="T4" s="178"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="194" t="s">
+      <c r="A5" s="179" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="195"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
+      <c r="B5" s="180"/>
+      <c r="C5" s="180"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="180"/>
       <c r="F5" s="170"/>
-      <c r="G5" s="196" t="s">
+      <c r="G5" s="181" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="195"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="195"/>
-      <c r="L5" s="195"/>
-      <c r="M5" s="195"/>
-      <c r="N5" s="195"/>
-      <c r="O5" s="195"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="195"/>
-      <c r="T5" s="197"/>
+      <c r="H5" s="180"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="180"/>
+      <c r="Q5" s="180"/>
+      <c r="R5" s="180"/>
+      <c r="S5" s="180"/>
+      <c r="T5" s="182"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="183" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="183"/>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="198" t="s">
+      <c r="B6" s="184"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="183"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="183"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="183"/>
-      <c r="Q6" s="183"/>
-      <c r="R6" s="183"/>
-      <c r="S6" s="183"/>
-      <c r="T6" s="199"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="184"/>
+      <c r="L6" s="184"/>
+      <c r="M6" s="184"/>
+      <c r="N6" s="184"/>
+      <c r="O6" s="184"/>
+      <c r="P6" s="184"/>
+      <c r="Q6" s="184"/>
+      <c r="R6" s="184"/>
+      <c r="S6" s="184"/>
+      <c r="T6" s="187"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="183" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="184"/>
-      <c r="G7" s="198" t="s">
+      <c r="B7" s="184"/>
+      <c r="C7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="185"/>
+      <c r="G7" s="186" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="183"/>
-      <c r="K7" s="183"/>
-      <c r="L7" s="183"/>
-      <c r="M7" s="183"/>
-      <c r="N7" s="183"/>
-      <c r="O7" s="183"/>
-      <c r="P7" s="183"/>
-      <c r="Q7" s="183"/>
-      <c r="R7" s="183"/>
-      <c r="S7" s="183"/>
-      <c r="T7" s="199"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="184"/>
+      <c r="K7" s="184"/>
+      <c r="L7" s="184"/>
+      <c r="M7" s="184"/>
+      <c r="N7" s="184"/>
+      <c r="O7" s="184"/>
+      <c r="P7" s="184"/>
+      <c r="Q7" s="184"/>
+      <c r="R7" s="184"/>
+      <c r="S7" s="184"/>
+      <c r="T7" s="187"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9989,37 +9998,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="184"/>
-      <c r="C15" s="190" t="s">
+      <c r="B15" s="185"/>
+      <c r="C15" s="196" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="184"/>
-      <c r="E15" s="188" t="s">
+      <c r="D15" s="185"/>
+      <c r="E15" s="191" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="184"/>
-      <c r="G15" s="188" t="s">
+      <c r="F15" s="185"/>
+      <c r="G15" s="191" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="183"/>
-      <c r="I15" s="184"/>
-      <c r="J15" s="188" t="s">
+      <c r="H15" s="184"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="191" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="184"/>
-      <c r="L15" s="188" t="s">
+      <c r="K15" s="185"/>
+      <c r="L15" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="183"/>
-      <c r="N15" s="184"/>
-      <c r="O15" s="188" t="s">
+      <c r="M15" s="184"/>
+      <c r="N15" s="185"/>
+      <c r="O15" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="184"/>
+      <c r="P15" s="184"/>
+      <c r="Q15" s="185"/>
       <c r="R15" s="44" t="s">
         <v>56</v>
       </c>
@@ -10031,37 +10040,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="192">
         <v>1</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="186" t="s">
+      <c r="B16" s="185"/>
+      <c r="C16" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="184"/>
-      <c r="E16" s="186" t="s">
+      <c r="D16" s="185"/>
+      <c r="E16" s="193" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="184"/>
-      <c r="G16" s="187" t="s">
+      <c r="F16" s="185"/>
+      <c r="G16" s="194" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="183"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="187" t="s">
+      <c r="H16" s="184"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="184"/>
-      <c r="L16" s="182" t="s">
+      <c r="K16" s="185"/>
+      <c r="L16" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="183"/>
-      <c r="N16" s="184"/>
-      <c r="O16" s="182" t="s">
+      <c r="M16" s="184"/>
+      <c r="N16" s="185"/>
+      <c r="O16" s="195" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="184"/>
+      <c r="P16" s="184"/>
+      <c r="Q16" s="185"/>
       <c r="R16" s="65">
         <v>45825</v>
       </c>
@@ -10069,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="T16" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U16" s="48"/>
       <c r="V16" s="48"/>
@@ -10079,37 +10088,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="192">
         <v>2</v>
       </c>
-      <c r="B17" s="184"/>
-      <c r="C17" s="186" t="s">
+      <c r="B17" s="185"/>
+      <c r="C17" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="184"/>
-      <c r="E17" s="186" t="s">
+      <c r="D17" s="185"/>
+      <c r="E17" s="193" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="184"/>
-      <c r="G17" s="187" t="s">
+      <c r="F17" s="185"/>
+      <c r="G17" s="194" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="183"/>
-      <c r="I17" s="184"/>
-      <c r="J17" s="187" t="s">
+      <c r="H17" s="184"/>
+      <c r="I17" s="185"/>
+      <c r="J17" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="184"/>
-      <c r="L17" s="182" t="s">
+      <c r="K17" s="185"/>
+      <c r="L17" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M17" s="183"/>
-      <c r="N17" s="184"/>
-      <c r="O17" s="182" t="s">
+      <c r="M17" s="184"/>
+      <c r="N17" s="185"/>
+      <c r="O17" s="195" t="s">
         <v>98</v>
       </c>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="184"/>
+      <c r="P17" s="184"/>
+      <c r="Q17" s="185"/>
       <c r="R17" s="65">
         <v>45825</v>
       </c>
@@ -10117,7 +10126,7 @@
         <v>27</v>
       </c>
       <c r="T17" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U17" s="48"/>
       <c r="V17" s="48"/>
@@ -10127,37 +10136,37 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="185">
+      <c r="A18" s="192">
         <v>3</v>
       </c>
-      <c r="B18" s="184"/>
-      <c r="C18" s="186" t="s">
+      <c r="B18" s="185"/>
+      <c r="C18" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="184"/>
-      <c r="E18" s="186" t="s">
+      <c r="D18" s="185"/>
+      <c r="E18" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="184"/>
-      <c r="G18" s="187" t="s">
+      <c r="F18" s="185"/>
+      <c r="G18" s="194" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="183"/>
-      <c r="I18" s="184"/>
-      <c r="J18" s="187" t="s">
+      <c r="H18" s="184"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="184"/>
-      <c r="L18" s="182" t="s">
+      <c r="K18" s="185"/>
+      <c r="L18" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M18" s="183"/>
-      <c r="N18" s="184"/>
-      <c r="O18" s="182" t="s">
+      <c r="M18" s="184"/>
+      <c r="N18" s="185"/>
+      <c r="O18" s="195" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="184"/>
+      <c r="P18" s="184"/>
+      <c r="Q18" s="185"/>
       <c r="R18" s="65">
         <v>45825</v>
       </c>
@@ -10165,7 +10174,7 @@
         <v>27</v>
       </c>
       <c r="T18" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
@@ -10175,40 +10184,46 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A19" s="185">
+      <c r="A19" s="192">
         <v>4</v>
       </c>
-      <c r="B19" s="184"/>
-      <c r="C19" s="186" t="s">
+      <c r="B19" s="185"/>
+      <c r="C19" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="184"/>
-      <c r="E19" s="186" t="s">
+      <c r="D19" s="185"/>
+      <c r="E19" s="193" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="184"/>
-      <c r="G19" s="187" t="s">
+      <c r="F19" s="185"/>
+      <c r="G19" s="194" t="s">
         <v>96</v>
       </c>
-      <c r="H19" s="183"/>
-      <c r="I19" s="184"/>
-      <c r="J19" s="187" t="s">
+      <c r="H19" s="184"/>
+      <c r="I19" s="185"/>
+      <c r="J19" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="184"/>
-      <c r="L19" s="182" t="s">
+      <c r="K19" s="185"/>
+      <c r="L19" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M19" s="183"/>
-      <c r="N19" s="184"/>
-      <c r="O19" s="182" t="s">
+      <c r="M19" s="184"/>
+      <c r="N19" s="185"/>
+      <c r="O19" s="195" t="s">
         <v>95</v>
       </c>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="184"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="47"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="185"/>
+      <c r="R19" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S19" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T19" s="47" t="s">
+        <v>107</v>
+      </c>
       <c r="U19" s="48"/>
       <c r="V19" s="48"/>
       <c r="W19" s="48"/>
@@ -10217,40 +10232,46 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A20" s="185">
+      <c r="A20" s="192">
         <v>5</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="186" t="s">
+      <c r="B20" s="185"/>
+      <c r="C20" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="184"/>
-      <c r="E20" s="186" t="s">
+      <c r="D20" s="185"/>
+      <c r="E20" s="193" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="184"/>
-      <c r="G20" s="187" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="183"/>
-      <c r="I20" s="184"/>
-      <c r="J20" s="187" t="s">
+      <c r="F20" s="185"/>
+      <c r="G20" s="194" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="184"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="184"/>
-      <c r="L20" s="182" t="s">
+      <c r="K20" s="185"/>
+      <c r="L20" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="M20" s="183"/>
-      <c r="N20" s="184"/>
-      <c r="O20" s="182" t="s">
-        <v>99</v>
-      </c>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="184"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46"/>
-      <c r="T20" s="47"/>
+      <c r="M20" s="184"/>
+      <c r="N20" s="185"/>
+      <c r="O20" s="195" t="s">
+        <v>113</v>
+      </c>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="185"/>
+      <c r="R20" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S20" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T20" s="47" t="s">
+        <v>107</v>
+      </c>
       <c r="U20" s="48"/>
       <c r="V20" s="48"/>
       <c r="W20" s="48"/>
@@ -10259,37 +10280,37 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A21" s="185">
+      <c r="A21" s="192">
         <v>6</v>
       </c>
-      <c r="B21" s="184"/>
-      <c r="C21" s="186" t="s">
+      <c r="B21" s="185"/>
+      <c r="C21" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="184"/>
-      <c r="E21" s="186" t="s">
+      <c r="D21" s="185"/>
+      <c r="E21" s="193" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="184"/>
-      <c r="G21" s="187" t="s">
+      <c r="F21" s="185"/>
+      <c r="G21" s="194" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" s="184"/>
+      <c r="I21" s="185"/>
+      <c r="J21" s="194" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="185"/>
+      <c r="L21" s="195" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" s="184"/>
+      <c r="N21" s="185"/>
+      <c r="O21" s="195" t="s">
         <v>101</v>
       </c>
-      <c r="H21" s="183"/>
-      <c r="I21" s="184"/>
-      <c r="J21" s="187" t="s">
-        <v>91</v>
-      </c>
-      <c r="K21" s="184"/>
-      <c r="L21" s="182" t="s">
-        <v>89</v>
-      </c>
-      <c r="M21" s="183"/>
-      <c r="N21" s="184"/>
-      <c r="O21" s="182" t="s">
-        <v>102</v>
-      </c>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="184"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="185"/>
       <c r="R21" s="65">
         <v>45825</v>
       </c>
@@ -10297,7 +10318,7 @@
         <v>27</v>
       </c>
       <c r="T21" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U21" s="48"/>
       <c r="V21" s="48"/>
@@ -10307,40 +10328,46 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A22" s="185">
+      <c r="A22" s="192">
         <v>7</v>
       </c>
-      <c r="B22" s="184"/>
-      <c r="C22" s="186" t="s">
+      <c r="B22" s="185"/>
+      <c r="C22" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="184"/>
-      <c r="E22" s="186" t="s">
+      <c r="D22" s="185"/>
+      <c r="E22" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="185"/>
+      <c r="G22" s="194" t="s">
         <v>109</v>
       </c>
-      <c r="F22" s="184"/>
-      <c r="G22" s="187" t="s">
+      <c r="H22" s="184"/>
+      <c r="I22" s="185"/>
+      <c r="J22" s="194" t="s">
         <v>110</v>
       </c>
-      <c r="H22" s="183"/>
-      <c r="I22" s="184"/>
-      <c r="J22" s="187" t="s">
+      <c r="K22" s="185"/>
+      <c r="L22" s="197" t="s">
         <v>111</v>
       </c>
-      <c r="K22" s="184"/>
-      <c r="L22" s="234" t="s">
+      <c r="M22" s="198"/>
+      <c r="N22" s="198"/>
+      <c r="O22" s="199" t="s">
         <v>112</v>
-      </c>
-      <c r="M22" s="235"/>
-      <c r="N22" s="235"/>
-      <c r="O22" s="236" t="s">
-        <v>113</v>
       </c>
       <c r="P22" s="67"/>
       <c r="Q22" s="68"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="47"/>
+      <c r="R22" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S22" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T22" s="47" t="s">
+        <v>107</v>
+      </c>
       <c r="U22" s="48"/>
       <c r="V22" s="48"/>
       <c r="W22" s="48"/>
@@ -10349,23 +10376,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
-      <c r="B23" s="184"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="184"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="184"/>
-      <c r="G23" s="187"/>
-      <c r="H23" s="183"/>
-      <c r="I23" s="184"/>
-      <c r="J23" s="187"/>
-      <c r="K23" s="184"/>
-      <c r="L23" s="182"/>
-      <c r="M23" s="183"/>
-      <c r="N23" s="184"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="183"/>
-      <c r="Q23" s="184"/>
+      <c r="A23" s="192"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="193"/>
+      <c r="D23" s="185"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="185"/>
+      <c r="G23" s="194"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="185"/>
+      <c r="J23" s="194"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="195"/>
+      <c r="M23" s="184"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="195"/>
+      <c r="P23" s="184"/>
+      <c r="Q23" s="185"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -10377,23 +10404,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
-      <c r="B24" s="184"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="184"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="184"/>
-      <c r="G24" s="187"/>
-      <c r="H24" s="183"/>
-      <c r="I24" s="184"/>
-      <c r="J24" s="187"/>
-      <c r="K24" s="184"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="183"/>
-      <c r="N24" s="184"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="184"/>
+      <c r="A24" s="192"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="193"/>
+      <c r="D24" s="185"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="185"/>
+      <c r="G24" s="194"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="185"/>
+      <c r="J24" s="194"/>
+      <c r="K24" s="185"/>
+      <c r="L24" s="195"/>
+      <c r="M24" s="184"/>
+      <c r="N24" s="185"/>
+      <c r="O24" s="195"/>
+      <c r="P24" s="184"/>
+      <c r="Q24" s="185"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -10405,23 +10432,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
-      <c r="B25" s="184"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="184"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="187"/>
-      <c r="H25" s="183"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="187"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="183"/>
-      <c r="N25" s="184"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="184"/>
+      <c r="A25" s="192"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="193"/>
+      <c r="D25" s="185"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="185"/>
+      <c r="G25" s="194"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="194"/>
+      <c r="K25" s="185"/>
+      <c r="L25" s="195"/>
+      <c r="M25" s="184"/>
+      <c r="N25" s="185"/>
+      <c r="O25" s="195"/>
+      <c r="P25" s="184"/>
+      <c r="Q25" s="185"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -10433,23 +10460,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
-      <c r="B26" s="184"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="184"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="187"/>
-      <c r="H26" s="183"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="187"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="182"/>
-      <c r="M26" s="183"/>
-      <c r="N26" s="184"/>
-      <c r="O26" s="182"/>
-      <c r="P26" s="183"/>
-      <c r="Q26" s="184"/>
+      <c r="A26" s="192"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="193"/>
+      <c r="D26" s="185"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="185"/>
+      <c r="G26" s="194"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="194"/>
+      <c r="K26" s="185"/>
+      <c r="L26" s="195"/>
+      <c r="M26" s="184"/>
+      <c r="N26" s="185"/>
+      <c r="O26" s="195"/>
+      <c r="P26" s="184"/>
+      <c r="Q26" s="185"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -10461,23 +10488,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="184"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="184"/>
-      <c r="G27" s="187"/>
-      <c r="H27" s="183"/>
-      <c r="I27" s="184"/>
-      <c r="J27" s="187"/>
-      <c r="K27" s="184"/>
-      <c r="L27" s="182"/>
-      <c r="M27" s="183"/>
-      <c r="N27" s="184"/>
-      <c r="O27" s="182"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="184"/>
+      <c r="A27" s="192"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="193"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="195"/>
+      <c r="M27" s="184"/>
+      <c r="N27" s="185"/>
+      <c r="O27" s="195"/>
+      <c r="P27" s="184"/>
+      <c r="Q27" s="185"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -10489,23 +10516,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="184"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="184"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="184"/>
-      <c r="G28" s="187"/>
-      <c r="H28" s="183"/>
-      <c r="I28" s="184"/>
-      <c r="J28" s="187"/>
-      <c r="K28" s="184"/>
-      <c r="L28" s="182"/>
-      <c r="M28" s="183"/>
-      <c r="N28" s="184"/>
-      <c r="O28" s="182"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="184"/>
+      <c r="A28" s="192"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="185"/>
+      <c r="E28" s="193"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="194"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="194"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="195"/>
+      <c r="M28" s="184"/>
+      <c r="N28" s="185"/>
+      <c r="O28" s="195"/>
+      <c r="P28" s="184"/>
+      <c r="Q28" s="185"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -10517,23 +10544,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
-      <c r="B29" s="184"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="187"/>
-      <c r="H29" s="183"/>
-      <c r="I29" s="184"/>
-      <c r="J29" s="187"/>
-      <c r="K29" s="184"/>
-      <c r="L29" s="182"/>
-      <c r="M29" s="183"/>
-      <c r="N29" s="184"/>
-      <c r="O29" s="182"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="184"/>
+      <c r="A29" s="192"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="193"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="193"/>
+      <c r="F29" s="185"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="194"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="195"/>
+      <c r="M29" s="184"/>
+      <c r="N29" s="185"/>
+      <c r="O29" s="195"/>
+      <c r="P29" s="184"/>
+      <c r="Q29" s="185"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -10545,23 +10572,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
-      <c r="B30" s="184"/>
-      <c r="C30" s="186"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="187"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="184"/>
-      <c r="J30" s="187"/>
-      <c r="K30" s="184"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="183"/>
-      <c r="N30" s="184"/>
-      <c r="O30" s="182"/>
-      <c r="P30" s="183"/>
-      <c r="Q30" s="184"/>
+      <c r="A30" s="192"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="193"/>
+      <c r="D30" s="185"/>
+      <c r="E30" s="193"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="194"/>
+      <c r="H30" s="184"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="194"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="195"/>
+      <c r="M30" s="184"/>
+      <c r="N30" s="185"/>
+      <c r="O30" s="195"/>
+      <c r="P30" s="184"/>
+      <c r="Q30" s="185"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -10573,23 +10600,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="179"/>
-      <c r="B31" s="178"/>
-      <c r="C31" s="180"/>
-      <c r="D31" s="178"/>
-      <c r="E31" s="180"/>
-      <c r="F31" s="178"/>
-      <c r="G31" s="181"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="176"/>
-      <c r="M31" s="177"/>
-      <c r="N31" s="178"/>
-      <c r="O31" s="176"/>
-      <c r="P31" s="177"/>
-      <c r="Q31" s="178"/>
+      <c r="A31" s="203"/>
+      <c r="B31" s="202"/>
+      <c r="C31" s="204"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="205"/>
+      <c r="H31" s="201"/>
+      <c r="I31" s="202"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="202"/>
+      <c r="L31" s="200"/>
+      <c r="M31" s="201"/>
+      <c r="N31" s="202"/>
+      <c r="O31" s="200"/>
+      <c r="P31" s="201"/>
+      <c r="Q31" s="202"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11587,121 +11614,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -11723,6 +11635,121 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <hyperlinks>
@@ -11748,72 +11775,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="224" t="s">
+      <c r="B1" s="215"/>
+      <c r="C1" s="216" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="225"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="227" t="s">
+      <c r="D1" s="217"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="219" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="228"/>
-      <c r="H1" s="228"/>
-      <c r="I1" s="228"/>
-      <c r="J1" s="228"/>
-      <c r="K1" s="228"/>
-      <c r="L1" s="228"/>
-      <c r="M1" s="229"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="221"/>
       <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="227" t="s">
+      <c r="O1" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="229"/>
+      <c r="P1" s="221"/>
       <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="227" t="s">
+      <c r="R1" s="219" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="229"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="223"/>
-      <c r="B2" s="223"/>
-      <c r="C2" s="224" t="s">
+      <c r="A2" s="215"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="216" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="225"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="227" t="s">
+      <c r="D2" s="217"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="219" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="228"/>
-      <c r="H2" s="228"/>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="228"/>
-      <c r="M2" s="229"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="220"/>
+      <c r="J2" s="220"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="221"/>
       <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="230">
+      <c r="O2" s="222">
         <v>45818</v>
       </c>
-      <c r="P2" s="231"/>
+      <c r="P2" s="223"/>
       <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="232" t="s">
+      <c r="R2" s="224" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="233"/>
+      <c r="S2" s="225"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11843,1056 +11870,1244 @@
       <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="206" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="215"/>
-      <c r="E4" s="215"/>
-      <c r="F4" s="215"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="214" t="s">
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="215"/>
-      <c r="J4" s="215"/>
-      <c r="K4" s="215"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="216"/>
-      <c r="N4" s="214" t="s">
+      <c r="I4" s="207"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="206" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="215"/>
-      <c r="P4" s="216"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="208"/>
       <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="214" t="s">
+      <c r="R4" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="216"/>
+      <c r="S4" s="208"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59">
         <v>1</v>
       </c>
       <c r="B5" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="217"/>
-      <c r="E5" s="217"/>
-      <c r="F5" s="217"/>
-      <c r="G5" s="217"/>
-      <c r="H5" s="217" t="s">
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
+      <c r="M5" s="209"/>
+      <c r="N5" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="217"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="217"/>
-      <c r="L5" s="217"/>
-      <c r="M5" s="217"/>
-      <c r="N5" s="218" t="s">
-        <v>107</v>
-      </c>
-      <c r="O5" s="219"/>
-      <c r="P5" s="220"/>
+      <c r="O5" s="211"/>
+      <c r="P5" s="212"/>
       <c r="Q5" s="64">
         <v>45818</v>
       </c>
-      <c r="R5" s="221"/>
-      <c r="S5" s="222"/>
+      <c r="R5" s="213"/>
+      <c r="S5" s="214"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="203"/>
-      <c r="D6" s="203"/>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="203"/>
-      <c r="J6" s="203"/>
-      <c r="K6" s="203"/>
-      <c r="L6" s="203"/>
-      <c r="M6" s="203"/>
-      <c r="N6" s="211"/>
-      <c r="O6" s="212"/>
-      <c r="P6" s="213"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="231"/>
+      <c r="O6" s="232"/>
+      <c r="P6" s="233"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="210"/>
-      <c r="S6" s="210"/>
+      <c r="R6" s="230"/>
+      <c r="S6" s="230"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="203"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="203"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="203"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="203"/>
-      <c r="K7" s="203"/>
-      <c r="L7" s="203"/>
-      <c r="M7" s="203"/>
-      <c r="N7" s="207"/>
-      <c r="O7" s="208"/>
-      <c r="P7" s="209"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="227"/>
+      <c r="O7" s="228"/>
+      <c r="P7" s="229"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="210"/>
-      <c r="S7" s="210"/>
+      <c r="R7" s="230"/>
+      <c r="S7" s="230"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="203"/>
-      <c r="H8" s="203"/>
-      <c r="I8" s="203"/>
-      <c r="J8" s="203"/>
-      <c r="K8" s="203"/>
-      <c r="L8" s="203"/>
-      <c r="M8" s="203"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="208"/>
-      <c r="P8" s="209"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
+      <c r="G8" s="226"/>
+      <c r="H8" s="226"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="226"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="227"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="229"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="210"/>
-      <c r="S8" s="210"/>
+      <c r="R8" s="230"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="203"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="203"/>
-      <c r="H9" s="203"/>
-      <c r="I9" s="203"/>
-      <c r="J9" s="203"/>
-      <c r="K9" s="203"/>
-      <c r="L9" s="203"/>
-      <c r="M9" s="203"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="208"/>
-      <c r="P9" s="209"/>
+      <c r="C9" s="226"/>
+      <c r="D9" s="226"/>
+      <c r="E9" s="226"/>
+      <c r="F9" s="226"/>
+      <c r="G9" s="226"/>
+      <c r="H9" s="226"/>
+      <c r="I9" s="226"/>
+      <c r="J9" s="226"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="227"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="229"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="210"/>
-      <c r="S9" s="210"/>
+      <c r="R9" s="230"/>
+      <c r="S9" s="230"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="203"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="203"/>
-      <c r="H10" s="204"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
-      <c r="L10" s="205"/>
-      <c r="M10" s="206"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="208"/>
-      <c r="P10" s="209"/>
+      <c r="C10" s="226"/>
+      <c r="D10" s="226"/>
+      <c r="E10" s="226"/>
+      <c r="F10" s="226"/>
+      <c r="G10" s="226"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="227"/>
+      <c r="O10" s="228"/>
+      <c r="P10" s="229"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="210"/>
-      <c r="S10" s="210"/>
+      <c r="R10" s="230"/>
+      <c r="S10" s="230"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="203"/>
-      <c r="D11" s="203"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="203"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="204"/>
-      <c r="I11" s="205"/>
-      <c r="J11" s="205"/>
-      <c r="K11" s="205"/>
-      <c r="L11" s="205"/>
-      <c r="M11" s="206"/>
-      <c r="N11" s="207"/>
-      <c r="O11" s="208"/>
-      <c r="P11" s="209"/>
+      <c r="C11" s="226"/>
+      <c r="D11" s="226"/>
+      <c r="E11" s="226"/>
+      <c r="F11" s="226"/>
+      <c r="G11" s="226"/>
+      <c r="H11" s="234"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235"/>
+      <c r="L11" s="235"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="227"/>
+      <c r="O11" s="228"/>
+      <c r="P11" s="229"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="210"/>
-      <c r="S11" s="210"/>
+      <c r="R11" s="230"/>
+      <c r="S11" s="230"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="204"/>
-      <c r="I12" s="205"/>
-      <c r="J12" s="205"/>
-      <c r="K12" s="205"/>
-      <c r="L12" s="205"/>
-      <c r="M12" s="206"/>
-      <c r="N12" s="207"/>
-      <c r="O12" s="208"/>
-      <c r="P12" s="209"/>
+      <c r="C12" s="226"/>
+      <c r="D12" s="226"/>
+      <c r="E12" s="226"/>
+      <c r="F12" s="226"/>
+      <c r="G12" s="226"/>
+      <c r="H12" s="234"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="235"/>
+      <c r="L12" s="235"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="228"/>
+      <c r="P12" s="229"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="210"/>
-      <c r="S12" s="210"/>
+      <c r="R12" s="230"/>
+      <c r="S12" s="230"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="203"/>
-      <c r="G13" s="203"/>
-      <c r="H13" s="204"/>
-      <c r="I13" s="205"/>
-      <c r="J13" s="205"/>
-      <c r="K13" s="205"/>
-      <c r="L13" s="205"/>
-      <c r="M13" s="206"/>
-      <c r="N13" s="207"/>
-      <c r="O13" s="208"/>
-      <c r="P13" s="209"/>
+      <c r="C13" s="226"/>
+      <c r="D13" s="226"/>
+      <c r="E13" s="226"/>
+      <c r="F13" s="226"/>
+      <c r="G13" s="226"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="235"/>
+      <c r="L13" s="235"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="227"/>
+      <c r="O13" s="228"/>
+      <c r="P13" s="229"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="210"/>
-      <c r="S13" s="210"/>
+      <c r="R13" s="230"/>
+      <c r="S13" s="230"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="204"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="205"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="205"/>
-      <c r="M14" s="206"/>
-      <c r="N14" s="207"/>
-      <c r="O14" s="208"/>
-      <c r="P14" s="209"/>
+      <c r="C14" s="226"/>
+      <c r="D14" s="226"/>
+      <c r="E14" s="226"/>
+      <c r="F14" s="226"/>
+      <c r="G14" s="226"/>
+      <c r="H14" s="234"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235"/>
+      <c r="L14" s="235"/>
+      <c r="M14" s="236"/>
+      <c r="N14" s="227"/>
+      <c r="O14" s="228"/>
+      <c r="P14" s="229"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
+      <c r="R14" s="230"/>
+      <c r="S14" s="230"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="203"/>
-      <c r="H15" s="204"/>
-      <c r="I15" s="205"/>
-      <c r="J15" s="205"/>
-      <c r="K15" s="205"/>
-      <c r="L15" s="205"/>
-      <c r="M15" s="206"/>
-      <c r="N15" s="207"/>
-      <c r="O15" s="208"/>
-      <c r="P15" s="209"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="226"/>
+      <c r="E15" s="226"/>
+      <c r="F15" s="226"/>
+      <c r="G15" s="226"/>
+      <c r="H15" s="234"/>
+      <c r="I15" s="235"/>
+      <c r="J15" s="235"/>
+      <c r="K15" s="235"/>
+      <c r="L15" s="235"/>
+      <c r="M15" s="236"/>
+      <c r="N15" s="227"/>
+      <c r="O15" s="228"/>
+      <c r="P15" s="229"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="210"/>
-      <c r="S15" s="210"/>
+      <c r="R15" s="230"/>
+      <c r="S15" s="230"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="203"/>
-      <c r="G16" s="203"/>
-      <c r="H16" s="204"/>
-      <c r="I16" s="205"/>
-      <c r="J16" s="205"/>
-      <c r="K16" s="205"/>
-      <c r="L16" s="205"/>
-      <c r="M16" s="206"/>
-      <c r="N16" s="207"/>
-      <c r="O16" s="208"/>
-      <c r="P16" s="209"/>
+      <c r="C16" s="226"/>
+      <c r="D16" s="226"/>
+      <c r="E16" s="226"/>
+      <c r="F16" s="226"/>
+      <c r="G16" s="226"/>
+      <c r="H16" s="234"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235"/>
+      <c r="L16" s="235"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="227"/>
+      <c r="O16" s="228"/>
+      <c r="P16" s="229"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="210"/>
-      <c r="S16" s="210"/>
+      <c r="R16" s="230"/>
+      <c r="S16" s="230"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="203"/>
-      <c r="H17" s="204"/>
-      <c r="I17" s="205"/>
-      <c r="J17" s="205"/>
-      <c r="K17" s="205"/>
-      <c r="L17" s="205"/>
-      <c r="M17" s="206"/>
-      <c r="N17" s="207"/>
-      <c r="O17" s="208"/>
-      <c r="P17" s="209"/>
+      <c r="C17" s="226"/>
+      <c r="D17" s="226"/>
+      <c r="E17" s="226"/>
+      <c r="F17" s="226"/>
+      <c r="G17" s="226"/>
+      <c r="H17" s="234"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="235"/>
+      <c r="L17" s="235"/>
+      <c r="M17" s="236"/>
+      <c r="N17" s="227"/>
+      <c r="O17" s="228"/>
+      <c r="P17" s="229"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="210"/>
-      <c r="S17" s="210"/>
+      <c r="R17" s="230"/>
+      <c r="S17" s="230"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="203"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="203"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="204"/>
-      <c r="I18" s="205"/>
-      <c r="J18" s="205"/>
-      <c r="K18" s="205"/>
-      <c r="L18" s="205"/>
-      <c r="M18" s="206"/>
-      <c r="N18" s="207"/>
-      <c r="O18" s="208"/>
-      <c r="P18" s="209"/>
+      <c r="C18" s="226"/>
+      <c r="D18" s="226"/>
+      <c r="E18" s="226"/>
+      <c r="F18" s="226"/>
+      <c r="G18" s="226"/>
+      <c r="H18" s="234"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
+      <c r="M18" s="236"/>
+      <c r="N18" s="227"/>
+      <c r="O18" s="228"/>
+      <c r="P18" s="229"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="210"/>
-      <c r="S18" s="210"/>
+      <c r="R18" s="230"/>
+      <c r="S18" s="230"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="203"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="203"/>
-      <c r="H19" s="204"/>
-      <c r="I19" s="205"/>
-      <c r="J19" s="205"/>
-      <c r="K19" s="205"/>
-      <c r="L19" s="205"/>
-      <c r="M19" s="206"/>
-      <c r="N19" s="207"/>
-      <c r="O19" s="208"/>
-      <c r="P19" s="209"/>
+      <c r="C19" s="226"/>
+      <c r="D19" s="226"/>
+      <c r="E19" s="226"/>
+      <c r="F19" s="226"/>
+      <c r="G19" s="226"/>
+      <c r="H19" s="234"/>
+      <c r="I19" s="235"/>
+      <c r="J19" s="235"/>
+      <c r="K19" s="235"/>
+      <c r="L19" s="235"/>
+      <c r="M19" s="236"/>
+      <c r="N19" s="227"/>
+      <c r="O19" s="228"/>
+      <c r="P19" s="229"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="210"/>
-      <c r="S19" s="210"/>
+      <c r="R19" s="230"/>
+      <c r="S19" s="230"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="203"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="203"/>
-      <c r="G20" s="203"/>
-      <c r="H20" s="204"/>
-      <c r="I20" s="205"/>
-      <c r="J20" s="205"/>
-      <c r="K20" s="205"/>
-      <c r="L20" s="205"/>
-      <c r="M20" s="206"/>
-      <c r="N20" s="207"/>
-      <c r="O20" s="208"/>
-      <c r="P20" s="209"/>
+      <c r="C20" s="226"/>
+      <c r="D20" s="226"/>
+      <c r="E20" s="226"/>
+      <c r="F20" s="226"/>
+      <c r="G20" s="226"/>
+      <c r="H20" s="234"/>
+      <c r="I20" s="235"/>
+      <c r="J20" s="235"/>
+      <c r="K20" s="235"/>
+      <c r="L20" s="235"/>
+      <c r="M20" s="236"/>
+      <c r="N20" s="227"/>
+      <c r="O20" s="228"/>
+      <c r="P20" s="229"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="210"/>
-      <c r="S20" s="210"/>
+      <c r="R20" s="230"/>
+      <c r="S20" s="230"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="203"/>
-      <c r="D21" s="203"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="203"/>
-      <c r="H21" s="204"/>
-      <c r="I21" s="205"/>
-      <c r="J21" s="205"/>
-      <c r="K21" s="205"/>
-      <c r="L21" s="205"/>
-      <c r="M21" s="206"/>
-      <c r="N21" s="207"/>
-      <c r="O21" s="208"/>
-      <c r="P21" s="209"/>
+      <c r="C21" s="226"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="226"/>
+      <c r="F21" s="226"/>
+      <c r="G21" s="226"/>
+      <c r="H21" s="234"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
+      <c r="M21" s="236"/>
+      <c r="N21" s="227"/>
+      <c r="O21" s="228"/>
+      <c r="P21" s="229"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="210"/>
-      <c r="S21" s="210"/>
+      <c r="R21" s="230"/>
+      <c r="S21" s="230"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="204"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="205"/>
-      <c r="K22" s="205"/>
-      <c r="L22" s="205"/>
-      <c r="M22" s="206"/>
-      <c r="N22" s="207"/>
-      <c r="O22" s="208"/>
-      <c r="P22" s="209"/>
+      <c r="C22" s="226"/>
+      <c r="D22" s="226"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="226"/>
+      <c r="G22" s="226"/>
+      <c r="H22" s="234"/>
+      <c r="I22" s="235"/>
+      <c r="J22" s="235"/>
+      <c r="K22" s="235"/>
+      <c r="L22" s="235"/>
+      <c r="M22" s="236"/>
+      <c r="N22" s="227"/>
+      <c r="O22" s="228"/>
+      <c r="P22" s="229"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="210"/>
-      <c r="S22" s="210"/>
+      <c r="R22" s="230"/>
+      <c r="S22" s="230"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="203"/>
-      <c r="D23" s="203"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="203"/>
-      <c r="G23" s="203"/>
-      <c r="H23" s="204"/>
-      <c r="I23" s="205"/>
-      <c r="J23" s="205"/>
-      <c r="K23" s="205"/>
-      <c r="L23" s="205"/>
-      <c r="M23" s="206"/>
-      <c r="N23" s="207"/>
-      <c r="O23" s="208"/>
-      <c r="P23" s="209"/>
+      <c r="C23" s="226"/>
+      <c r="D23" s="226"/>
+      <c r="E23" s="226"/>
+      <c r="F23" s="226"/>
+      <c r="G23" s="226"/>
+      <c r="H23" s="234"/>
+      <c r="I23" s="235"/>
+      <c r="J23" s="235"/>
+      <c r="K23" s="235"/>
+      <c r="L23" s="235"/>
+      <c r="M23" s="236"/>
+      <c r="N23" s="227"/>
+      <c r="O23" s="228"/>
+      <c r="P23" s="229"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="210"/>
-      <c r="S23" s="210"/>
+      <c r="R23" s="230"/>
+      <c r="S23" s="230"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="203"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="203"/>
-      <c r="G24" s="203"/>
-      <c r="H24" s="204"/>
-      <c r="I24" s="205"/>
-      <c r="J24" s="205"/>
-      <c r="K24" s="205"/>
-      <c r="L24" s="205"/>
-      <c r="M24" s="206"/>
-      <c r="N24" s="207"/>
-      <c r="O24" s="208"/>
-      <c r="P24" s="209"/>
+      <c r="C24" s="226"/>
+      <c r="D24" s="226"/>
+      <c r="E24" s="226"/>
+      <c r="F24" s="226"/>
+      <c r="G24" s="226"/>
+      <c r="H24" s="234"/>
+      <c r="I24" s="235"/>
+      <c r="J24" s="235"/>
+      <c r="K24" s="235"/>
+      <c r="L24" s="235"/>
+      <c r="M24" s="236"/>
+      <c r="N24" s="227"/>
+      <c r="O24" s="228"/>
+      <c r="P24" s="229"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="210"/>
-      <c r="S24" s="210"/>
+      <c r="R24" s="230"/>
+      <c r="S24" s="230"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="203"/>
-      <c r="D25" s="203"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="203"/>
-      <c r="G25" s="203"/>
-      <c r="H25" s="204"/>
-      <c r="I25" s="205"/>
-      <c r="J25" s="205"/>
-      <c r="K25" s="205"/>
-      <c r="L25" s="205"/>
-      <c r="M25" s="206"/>
-      <c r="N25" s="207"/>
-      <c r="O25" s="208"/>
-      <c r="P25" s="209"/>
+      <c r="C25" s="226"/>
+      <c r="D25" s="226"/>
+      <c r="E25" s="226"/>
+      <c r="F25" s="226"/>
+      <c r="G25" s="226"/>
+      <c r="H25" s="234"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
+      <c r="M25" s="236"/>
+      <c r="N25" s="227"/>
+      <c r="O25" s="228"/>
+      <c r="P25" s="229"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="210"/>
-      <c r="S25" s="210"/>
+      <c r="R25" s="230"/>
+      <c r="S25" s="230"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="203"/>
-      <c r="D26" s="203"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="203"/>
-      <c r="G26" s="203"/>
-      <c r="H26" s="204"/>
-      <c r="I26" s="205"/>
-      <c r="J26" s="205"/>
-      <c r="K26" s="205"/>
-      <c r="L26" s="205"/>
-      <c r="M26" s="206"/>
-      <c r="N26" s="207"/>
-      <c r="O26" s="208"/>
-      <c r="P26" s="209"/>
+      <c r="C26" s="226"/>
+      <c r="D26" s="226"/>
+      <c r="E26" s="226"/>
+      <c r="F26" s="226"/>
+      <c r="G26" s="226"/>
+      <c r="H26" s="234"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
+      <c r="M26" s="236"/>
+      <c r="N26" s="227"/>
+      <c r="O26" s="228"/>
+      <c r="P26" s="229"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="210"/>
-      <c r="S26" s="210"/>
+      <c r="R26" s="230"/>
+      <c r="S26" s="230"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="203"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="204"/>
-      <c r="I27" s="205"/>
-      <c r="J27" s="205"/>
-      <c r="K27" s="205"/>
-      <c r="L27" s="205"/>
-      <c r="M27" s="206"/>
-      <c r="N27" s="207"/>
-      <c r="O27" s="208"/>
-      <c r="P27" s="209"/>
+      <c r="C27" s="226"/>
+      <c r="D27" s="226"/>
+      <c r="E27" s="226"/>
+      <c r="F27" s="226"/>
+      <c r="G27" s="226"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="235"/>
+      <c r="J27" s="235"/>
+      <c r="K27" s="235"/>
+      <c r="L27" s="235"/>
+      <c r="M27" s="236"/>
+      <c r="N27" s="227"/>
+      <c r="O27" s="228"/>
+      <c r="P27" s="229"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="210"/>
-      <c r="S27" s="210"/>
+      <c r="R27" s="230"/>
+      <c r="S27" s="230"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="203"/>
-      <c r="D28" s="203"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="203"/>
-      <c r="G28" s="203"/>
-      <c r="H28" s="204"/>
-      <c r="I28" s="205"/>
-      <c r="J28" s="205"/>
-      <c r="K28" s="205"/>
-      <c r="L28" s="205"/>
-      <c r="M28" s="206"/>
-      <c r="N28" s="207"/>
-      <c r="O28" s="208"/>
-      <c r="P28" s="209"/>
+      <c r="C28" s="226"/>
+      <c r="D28" s="226"/>
+      <c r="E28" s="226"/>
+      <c r="F28" s="226"/>
+      <c r="G28" s="226"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="235"/>
+      <c r="J28" s="235"/>
+      <c r="K28" s="235"/>
+      <c r="L28" s="235"/>
+      <c r="M28" s="236"/>
+      <c r="N28" s="227"/>
+      <c r="O28" s="228"/>
+      <c r="P28" s="229"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="210"/>
-      <c r="S28" s="210"/>
+      <c r="R28" s="230"/>
+      <c r="S28" s="230"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="203"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="203"/>
-      <c r="G29" s="203"/>
-      <c r="H29" s="204"/>
-      <c r="I29" s="205"/>
-      <c r="J29" s="205"/>
-      <c r="K29" s="205"/>
-      <c r="L29" s="205"/>
-      <c r="M29" s="206"/>
-      <c r="N29" s="207"/>
-      <c r="O29" s="208"/>
-      <c r="P29" s="209"/>
+      <c r="C29" s="226"/>
+      <c r="D29" s="226"/>
+      <c r="E29" s="226"/>
+      <c r="F29" s="226"/>
+      <c r="G29" s="226"/>
+      <c r="H29" s="234"/>
+      <c r="I29" s="235"/>
+      <c r="J29" s="235"/>
+      <c r="K29" s="235"/>
+      <c r="L29" s="235"/>
+      <c r="M29" s="236"/>
+      <c r="N29" s="227"/>
+      <c r="O29" s="228"/>
+      <c r="P29" s="229"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="210"/>
-      <c r="S29" s="210"/>
+      <c r="R29" s="230"/>
+      <c r="S29" s="230"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="203"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="203"/>
-      <c r="G30" s="203"/>
-      <c r="H30" s="204"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="205"/>
-      <c r="K30" s="205"/>
-      <c r="L30" s="205"/>
-      <c r="M30" s="206"/>
-      <c r="N30" s="207"/>
-      <c r="O30" s="208"/>
-      <c r="P30" s="209"/>
+      <c r="C30" s="226"/>
+      <c r="D30" s="226"/>
+      <c r="E30" s="226"/>
+      <c r="F30" s="226"/>
+      <c r="G30" s="226"/>
+      <c r="H30" s="234"/>
+      <c r="I30" s="235"/>
+      <c r="J30" s="235"/>
+      <c r="K30" s="235"/>
+      <c r="L30" s="235"/>
+      <c r="M30" s="236"/>
+      <c r="N30" s="227"/>
+      <c r="O30" s="228"/>
+      <c r="P30" s="229"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="210"/>
-      <c r="S30" s="210"/>
+      <c r="R30" s="230"/>
+      <c r="S30" s="230"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="203"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="203"/>
-      <c r="H31" s="204"/>
-      <c r="I31" s="205"/>
-      <c r="J31" s="205"/>
-      <c r="K31" s="205"/>
-      <c r="L31" s="205"/>
-      <c r="M31" s="206"/>
-      <c r="N31" s="207"/>
-      <c r="O31" s="208"/>
-      <c r="P31" s="209"/>
+      <c r="C31" s="226"/>
+      <c r="D31" s="226"/>
+      <c r="E31" s="226"/>
+      <c r="F31" s="226"/>
+      <c r="G31" s="226"/>
+      <c r="H31" s="234"/>
+      <c r="I31" s="235"/>
+      <c r="J31" s="235"/>
+      <c r="K31" s="235"/>
+      <c r="L31" s="235"/>
+      <c r="M31" s="236"/>
+      <c r="N31" s="227"/>
+      <c r="O31" s="228"/>
+      <c r="P31" s="229"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
+      <c r="R31" s="230"/>
+      <c r="S31" s="230"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="203"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="203"/>
-      <c r="G32" s="203"/>
-      <c r="H32" s="204"/>
-      <c r="I32" s="205"/>
-      <c r="J32" s="205"/>
-      <c r="K32" s="205"/>
-      <c r="L32" s="205"/>
-      <c r="M32" s="206"/>
-      <c r="N32" s="207"/>
-      <c r="O32" s="208"/>
-      <c r="P32" s="209"/>
+      <c r="C32" s="226"/>
+      <c r="D32" s="226"/>
+      <c r="E32" s="226"/>
+      <c r="F32" s="226"/>
+      <c r="G32" s="226"/>
+      <c r="H32" s="234"/>
+      <c r="I32" s="235"/>
+      <c r="J32" s="235"/>
+      <c r="K32" s="235"/>
+      <c r="L32" s="235"/>
+      <c r="M32" s="236"/>
+      <c r="N32" s="227"/>
+      <c r="O32" s="228"/>
+      <c r="P32" s="229"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="210"/>
-      <c r="S32" s="210"/>
+      <c r="R32" s="230"/>
+      <c r="S32" s="230"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="203"/>
-      <c r="H33" s="204"/>
-      <c r="I33" s="205"/>
-      <c r="J33" s="205"/>
-      <c r="K33" s="205"/>
-      <c r="L33" s="205"/>
-      <c r="M33" s="206"/>
-      <c r="N33" s="207"/>
-      <c r="O33" s="208"/>
-      <c r="P33" s="209"/>
+      <c r="C33" s="226"/>
+      <c r="D33" s="226"/>
+      <c r="E33" s="226"/>
+      <c r="F33" s="226"/>
+      <c r="G33" s="226"/>
+      <c r="H33" s="234"/>
+      <c r="I33" s="235"/>
+      <c r="J33" s="235"/>
+      <c r="K33" s="235"/>
+      <c r="L33" s="235"/>
+      <c r="M33" s="236"/>
+      <c r="N33" s="227"/>
+      <c r="O33" s="228"/>
+      <c r="P33" s="229"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="210"/>
-      <c r="S33" s="210"/>
+      <c r="R33" s="230"/>
+      <c r="S33" s="230"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="203"/>
-      <c r="D34" s="203"/>
-      <c r="E34" s="203"/>
-      <c r="F34" s="203"/>
-      <c r="G34" s="203"/>
-      <c r="H34" s="204"/>
-      <c r="I34" s="205"/>
-      <c r="J34" s="205"/>
-      <c r="K34" s="205"/>
-      <c r="L34" s="205"/>
-      <c r="M34" s="206"/>
-      <c r="N34" s="207"/>
-      <c r="O34" s="208"/>
-      <c r="P34" s="209"/>
+      <c r="C34" s="226"/>
+      <c r="D34" s="226"/>
+      <c r="E34" s="226"/>
+      <c r="F34" s="226"/>
+      <c r="G34" s="226"/>
+      <c r="H34" s="234"/>
+      <c r="I34" s="235"/>
+      <c r="J34" s="235"/>
+      <c r="K34" s="235"/>
+      <c r="L34" s="235"/>
+      <c r="M34" s="236"/>
+      <c r="N34" s="227"/>
+      <c r="O34" s="228"/>
+      <c r="P34" s="229"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="210"/>
-      <c r="S34" s="210"/>
+      <c r="R34" s="230"/>
+      <c r="S34" s="230"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="203"/>
-      <c r="D35" s="203"/>
-      <c r="E35" s="203"/>
-      <c r="F35" s="203"/>
-      <c r="G35" s="203"/>
-      <c r="H35" s="204"/>
-      <c r="I35" s="205"/>
-      <c r="J35" s="205"/>
-      <c r="K35" s="205"/>
-      <c r="L35" s="205"/>
-      <c r="M35" s="206"/>
-      <c r="N35" s="207"/>
-      <c r="O35" s="208"/>
-      <c r="P35" s="209"/>
+      <c r="C35" s="226"/>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="226"/>
+      <c r="G35" s="226"/>
+      <c r="H35" s="234"/>
+      <c r="I35" s="235"/>
+      <c r="J35" s="235"/>
+      <c r="K35" s="235"/>
+      <c r="L35" s="235"/>
+      <c r="M35" s="236"/>
+      <c r="N35" s="227"/>
+      <c r="O35" s="228"/>
+      <c r="P35" s="229"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="210"/>
-      <c r="S35" s="210"/>
+      <c r="R35" s="230"/>
+      <c r="S35" s="230"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="203"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="203"/>
-      <c r="F36" s="203"/>
-      <c r="G36" s="203"/>
-      <c r="H36" s="204"/>
-      <c r="I36" s="205"/>
-      <c r="J36" s="205"/>
-      <c r="K36" s="205"/>
-      <c r="L36" s="205"/>
-      <c r="M36" s="206"/>
-      <c r="N36" s="207"/>
-      <c r="O36" s="208"/>
-      <c r="P36" s="209"/>
+      <c r="C36" s="226"/>
+      <c r="D36" s="226"/>
+      <c r="E36" s="226"/>
+      <c r="F36" s="226"/>
+      <c r="G36" s="226"/>
+      <c r="H36" s="234"/>
+      <c r="I36" s="235"/>
+      <c r="J36" s="235"/>
+      <c r="K36" s="235"/>
+      <c r="L36" s="235"/>
+      <c r="M36" s="236"/>
+      <c r="N36" s="227"/>
+      <c r="O36" s="228"/>
+      <c r="P36" s="229"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="210"/>
-      <c r="S36" s="210"/>
+      <c r="R36" s="230"/>
+      <c r="S36" s="230"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="203"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="204"/>
-      <c r="I37" s="205"/>
-      <c r="J37" s="205"/>
-      <c r="K37" s="205"/>
-      <c r="L37" s="205"/>
-      <c r="M37" s="206"/>
-      <c r="N37" s="207"/>
-      <c r="O37" s="208"/>
-      <c r="P37" s="209"/>
+      <c r="C37" s="226"/>
+      <c r="D37" s="226"/>
+      <c r="E37" s="226"/>
+      <c r="F37" s="226"/>
+      <c r="G37" s="226"/>
+      <c r="H37" s="234"/>
+      <c r="I37" s="235"/>
+      <c r="J37" s="235"/>
+      <c r="K37" s="235"/>
+      <c r="L37" s="235"/>
+      <c r="M37" s="236"/>
+      <c r="N37" s="227"/>
+      <c r="O37" s="228"/>
+      <c r="P37" s="229"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="210"/>
-      <c r="S37" s="210"/>
+      <c r="R37" s="230"/>
+      <c r="S37" s="230"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="203"/>
-      <c r="D38" s="203"/>
-      <c r="E38" s="203"/>
-      <c r="F38" s="203"/>
-      <c r="G38" s="203"/>
-      <c r="H38" s="204"/>
-      <c r="I38" s="205"/>
-      <c r="J38" s="205"/>
-      <c r="K38" s="205"/>
-      <c r="L38" s="205"/>
-      <c r="M38" s="206"/>
-      <c r="N38" s="207"/>
-      <c r="O38" s="208"/>
-      <c r="P38" s="209"/>
+      <c r="C38" s="226"/>
+      <c r="D38" s="226"/>
+      <c r="E38" s="226"/>
+      <c r="F38" s="226"/>
+      <c r="G38" s="226"/>
+      <c r="H38" s="234"/>
+      <c r="I38" s="235"/>
+      <c r="J38" s="235"/>
+      <c r="K38" s="235"/>
+      <c r="L38" s="235"/>
+      <c r="M38" s="236"/>
+      <c r="N38" s="227"/>
+      <c r="O38" s="228"/>
+      <c r="P38" s="229"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="210"/>
-      <c r="S38" s="210"/>
+      <c r="R38" s="230"/>
+      <c r="S38" s="230"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="203"/>
-      <c r="D39" s="203"/>
-      <c r="E39" s="203"/>
-      <c r="F39" s="203"/>
-      <c r="G39" s="203"/>
-      <c r="H39" s="204"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="205"/>
-      <c r="K39" s="205"/>
-      <c r="L39" s="205"/>
-      <c r="M39" s="206"/>
-      <c r="N39" s="207"/>
-      <c r="O39" s="208"/>
-      <c r="P39" s="209"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="226"/>
+      <c r="E39" s="226"/>
+      <c r="F39" s="226"/>
+      <c r="G39" s="226"/>
+      <c r="H39" s="234"/>
+      <c r="I39" s="235"/>
+      <c r="J39" s="235"/>
+      <c r="K39" s="235"/>
+      <c r="L39" s="235"/>
+      <c r="M39" s="236"/>
+      <c r="N39" s="227"/>
+      <c r="O39" s="228"/>
+      <c r="P39" s="229"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="210"/>
-      <c r="S39" s="210"/>
+      <c r="R39" s="230"/>
+      <c r="S39" s="230"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="203"/>
-      <c r="D40" s="203"/>
-      <c r="E40" s="203"/>
-      <c r="F40" s="203"/>
-      <c r="G40" s="203"/>
-      <c r="H40" s="204"/>
-      <c r="I40" s="205"/>
-      <c r="J40" s="205"/>
-      <c r="K40" s="205"/>
-      <c r="L40" s="205"/>
-      <c r="M40" s="206"/>
-      <c r="N40" s="207"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="209"/>
+      <c r="C40" s="226"/>
+      <c r="D40" s="226"/>
+      <c r="E40" s="226"/>
+      <c r="F40" s="226"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="235"/>
+      <c r="J40" s="235"/>
+      <c r="K40" s="235"/>
+      <c r="L40" s="235"/>
+      <c r="M40" s="236"/>
+      <c r="N40" s="227"/>
+      <c r="O40" s="228"/>
+      <c r="P40" s="229"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="210"/>
-      <c r="S40" s="210"/>
+      <c r="R40" s="230"/>
+      <c r="S40" s="230"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="203"/>
-      <c r="D41" s="203"/>
-      <c r="E41" s="203"/>
-      <c r="F41" s="203"/>
-      <c r="G41" s="203"/>
-      <c r="H41" s="204"/>
-      <c r="I41" s="205"/>
-      <c r="J41" s="205"/>
-      <c r="K41" s="205"/>
-      <c r="L41" s="205"/>
-      <c r="M41" s="206"/>
-      <c r="N41" s="207"/>
-      <c r="O41" s="208"/>
-      <c r="P41" s="209"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="226"/>
+      <c r="E41" s="226"/>
+      <c r="F41" s="226"/>
+      <c r="G41" s="226"/>
+      <c r="H41" s="234"/>
+      <c r="I41" s="235"/>
+      <c r="J41" s="235"/>
+      <c r="K41" s="235"/>
+      <c r="L41" s="235"/>
+      <c r="M41" s="236"/>
+      <c r="N41" s="227"/>
+      <c r="O41" s="228"/>
+      <c r="P41" s="229"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="210"/>
-      <c r="S41" s="210"/>
+      <c r="R41" s="230"/>
+      <c r="S41" s="230"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="203"/>
-      <c r="D42" s="203"/>
-      <c r="E42" s="203"/>
-      <c r="F42" s="203"/>
-      <c r="G42" s="203"/>
-      <c r="H42" s="204"/>
-      <c r="I42" s="205"/>
-      <c r="J42" s="205"/>
-      <c r="K42" s="205"/>
-      <c r="L42" s="205"/>
-      <c r="M42" s="206"/>
-      <c r="N42" s="207"/>
-      <c r="O42" s="208"/>
-      <c r="P42" s="209"/>
+      <c r="C42" s="226"/>
+      <c r="D42" s="226"/>
+      <c r="E42" s="226"/>
+      <c r="F42" s="226"/>
+      <c r="G42" s="226"/>
+      <c r="H42" s="234"/>
+      <c r="I42" s="235"/>
+      <c r="J42" s="235"/>
+      <c r="K42" s="235"/>
+      <c r="L42" s="235"/>
+      <c r="M42" s="236"/>
+      <c r="N42" s="227"/>
+      <c r="O42" s="228"/>
+      <c r="P42" s="229"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="210"/>
-      <c r="S42" s="210"/>
+      <c r="R42" s="230"/>
+      <c r="S42" s="230"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="203"/>
-      <c r="D43" s="203"/>
-      <c r="E43" s="203"/>
-      <c r="F43" s="203"/>
-      <c r="G43" s="203"/>
-      <c r="H43" s="204"/>
-      <c r="I43" s="205"/>
-      <c r="J43" s="205"/>
-      <c r="K43" s="205"/>
-      <c r="L43" s="205"/>
-      <c r="M43" s="206"/>
-      <c r="N43" s="207"/>
-      <c r="O43" s="208"/>
-      <c r="P43" s="209"/>
+      <c r="C43" s="226"/>
+      <c r="D43" s="226"/>
+      <c r="E43" s="226"/>
+      <c r="F43" s="226"/>
+      <c r="G43" s="226"/>
+      <c r="H43" s="234"/>
+      <c r="I43" s="235"/>
+      <c r="J43" s="235"/>
+      <c r="K43" s="235"/>
+      <c r="L43" s="235"/>
+      <c r="M43" s="236"/>
+      <c r="N43" s="227"/>
+      <c r="O43" s="228"/>
+      <c r="P43" s="229"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="210"/>
-      <c r="S43" s="210"/>
+      <c r="R43" s="230"/>
+      <c r="S43" s="230"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="203"/>
-      <c r="D44" s="203"/>
-      <c r="E44" s="203"/>
-      <c r="F44" s="203"/>
-      <c r="G44" s="203"/>
-      <c r="H44" s="204"/>
-      <c r="I44" s="205"/>
-      <c r="J44" s="205"/>
-      <c r="K44" s="205"/>
-      <c r="L44" s="205"/>
-      <c r="M44" s="206"/>
-      <c r="N44" s="207"/>
-      <c r="O44" s="208"/>
-      <c r="P44" s="209"/>
+      <c r="C44" s="226"/>
+      <c r="D44" s="226"/>
+      <c r="E44" s="226"/>
+      <c r="F44" s="226"/>
+      <c r="G44" s="226"/>
+      <c r="H44" s="234"/>
+      <c r="I44" s="235"/>
+      <c r="J44" s="235"/>
+      <c r="K44" s="235"/>
+      <c r="L44" s="235"/>
+      <c r="M44" s="236"/>
+      <c r="N44" s="227"/>
+      <c r="O44" s="228"/>
+      <c r="P44" s="229"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="210"/>
-      <c r="S44" s="210"/>
+      <c r="R44" s="230"/>
+      <c r="S44" s="230"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="203"/>
-      <c r="D45" s="203"/>
-      <c r="E45" s="203"/>
-      <c r="F45" s="203"/>
-      <c r="G45" s="203"/>
-      <c r="H45" s="204"/>
-      <c r="I45" s="205"/>
-      <c r="J45" s="205"/>
-      <c r="K45" s="205"/>
-      <c r="L45" s="205"/>
-      <c r="M45" s="206"/>
-      <c r="N45" s="207"/>
-      <c r="O45" s="208"/>
-      <c r="P45" s="209"/>
+      <c r="C45" s="226"/>
+      <c r="D45" s="226"/>
+      <c r="E45" s="226"/>
+      <c r="F45" s="226"/>
+      <c r="G45" s="226"/>
+      <c r="H45" s="234"/>
+      <c r="I45" s="235"/>
+      <c r="J45" s="235"/>
+      <c r="K45" s="235"/>
+      <c r="L45" s="235"/>
+      <c r="M45" s="236"/>
+      <c r="N45" s="227"/>
+      <c r="O45" s="228"/>
+      <c r="P45" s="229"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="210"/>
-      <c r="S45" s="210"/>
+      <c r="R45" s="230"/>
+      <c r="S45" s="230"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="203"/>
-      <c r="D46" s="203"/>
-      <c r="E46" s="203"/>
-      <c r="F46" s="203"/>
-      <c r="G46" s="203"/>
-      <c r="H46" s="204"/>
-      <c r="I46" s="205"/>
-      <c r="J46" s="205"/>
-      <c r="K46" s="205"/>
-      <c r="L46" s="205"/>
-      <c r="M46" s="206"/>
-      <c r="N46" s="207"/>
-      <c r="O46" s="208"/>
-      <c r="P46" s="209"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="226"/>
+      <c r="H46" s="234"/>
+      <c r="I46" s="235"/>
+      <c r="J46" s="235"/>
+      <c r="K46" s="235"/>
+      <c r="L46" s="235"/>
+      <c r="M46" s="236"/>
+      <c r="N46" s="227"/>
+      <c r="O46" s="228"/>
+      <c r="P46" s="229"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="210"/>
-      <c r="S46" s="210"/>
+      <c r="R46" s="230"/>
+      <c r="S46" s="230"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="203"/>
-      <c r="D47" s="203"/>
-      <c r="E47" s="203"/>
-      <c r="F47" s="203"/>
-      <c r="G47" s="203"/>
-      <c r="H47" s="204"/>
-      <c r="I47" s="205"/>
-      <c r="J47" s="205"/>
-      <c r="K47" s="205"/>
-      <c r="L47" s="205"/>
-      <c r="M47" s="206"/>
-      <c r="N47" s="207"/>
-      <c r="O47" s="208"/>
-      <c r="P47" s="209"/>
+      <c r="C47" s="226"/>
+      <c r="D47" s="226"/>
+      <c r="E47" s="226"/>
+      <c r="F47" s="226"/>
+      <c r="G47" s="226"/>
+      <c r="H47" s="234"/>
+      <c r="I47" s="235"/>
+      <c r="J47" s="235"/>
+      <c r="K47" s="235"/>
+      <c r="L47" s="235"/>
+      <c r="M47" s="236"/>
+      <c r="N47" s="227"/>
+      <c r="O47" s="228"/>
+      <c r="P47" s="229"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="210"/>
-      <c r="S47" s="210"/>
+      <c r="R47" s="230"/>
+      <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="203"/>
-      <c r="D48" s="203"/>
-      <c r="E48" s="203"/>
-      <c r="F48" s="203"/>
-      <c r="G48" s="203"/>
-      <c r="H48" s="204"/>
-      <c r="I48" s="205"/>
-      <c r="J48" s="205"/>
-      <c r="K48" s="205"/>
-      <c r="L48" s="205"/>
-      <c r="M48" s="206"/>
-      <c r="N48" s="207"/>
-      <c r="O48" s="208"/>
-      <c r="P48" s="209"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="234"/>
+      <c r="I48" s="235"/>
+      <c r="J48" s="235"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="236"/>
+      <c r="N48" s="227"/>
+      <c r="O48" s="228"/>
+      <c r="P48" s="229"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="210"/>
-      <c r="S48" s="210"/>
+      <c r="R48" s="230"/>
+      <c r="S48" s="230"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="203"/>
-      <c r="D49" s="203"/>
-      <c r="E49" s="203"/>
-      <c r="F49" s="203"/>
-      <c r="G49" s="203"/>
-      <c r="H49" s="204"/>
-      <c r="I49" s="205"/>
-      <c r="J49" s="205"/>
-      <c r="K49" s="205"/>
-      <c r="L49" s="205"/>
-      <c r="M49" s="206"/>
-      <c r="N49" s="207"/>
-      <c r="O49" s="208"/>
-      <c r="P49" s="209"/>
+      <c r="C49" s="226"/>
+      <c r="D49" s="226"/>
+      <c r="E49" s="226"/>
+      <c r="F49" s="226"/>
+      <c r="G49" s="226"/>
+      <c r="H49" s="234"/>
+      <c r="I49" s="235"/>
+      <c r="J49" s="235"/>
+      <c r="K49" s="235"/>
+      <c r="L49" s="235"/>
+      <c r="M49" s="236"/>
+      <c r="N49" s="227"/>
+      <c r="O49" s="228"/>
+      <c r="P49" s="229"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="210"/>
-      <c r="S49" s="210"/>
+      <c r="R49" s="230"/>
+      <c r="S49" s="230"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="203"/>
-      <c r="D50" s="203"/>
-      <c r="E50" s="203"/>
-      <c r="F50" s="203"/>
-      <c r="G50" s="203"/>
-      <c r="H50" s="204"/>
-      <c r="I50" s="205"/>
-      <c r="J50" s="205"/>
-      <c r="K50" s="205"/>
-      <c r="L50" s="205"/>
-      <c r="M50" s="206"/>
-      <c r="N50" s="207"/>
-      <c r="O50" s="208"/>
-      <c r="P50" s="209"/>
+      <c r="C50" s="226"/>
+      <c r="D50" s="226"/>
+      <c r="E50" s="226"/>
+      <c r="F50" s="226"/>
+      <c r="G50" s="226"/>
+      <c r="H50" s="234"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="236"/>
+      <c r="N50" s="227"/>
+      <c r="O50" s="228"/>
+      <c r="P50" s="229"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="210"/>
-      <c r="S50" s="210"/>
+      <c r="R50" s="230"/>
+      <c r="S50" s="230"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="203"/>
-      <c r="D51" s="203"/>
-      <c r="E51" s="203"/>
-      <c r="F51" s="203"/>
-      <c r="G51" s="203"/>
-      <c r="H51" s="204"/>
-      <c r="I51" s="205"/>
-      <c r="J51" s="205"/>
-      <c r="K51" s="205"/>
-      <c r="L51" s="205"/>
-      <c r="M51" s="206"/>
-      <c r="N51" s="207"/>
-      <c r="O51" s="208"/>
-      <c r="P51" s="209"/>
+      <c r="C51" s="226"/>
+      <c r="D51" s="226"/>
+      <c r="E51" s="226"/>
+      <c r="F51" s="226"/>
+      <c r="G51" s="226"/>
+      <c r="H51" s="234"/>
+      <c r="I51" s="235"/>
+      <c r="J51" s="235"/>
+      <c r="K51" s="235"/>
+      <c r="L51" s="235"/>
+      <c r="M51" s="236"/>
+      <c r="N51" s="227"/>
+      <c r="O51" s="228"/>
+      <c r="P51" s="229"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="210"/>
-      <c r="S51" s="210"/>
+      <c r="R51" s="230"/>
+      <c r="S51" s="230"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="203"/>
-      <c r="D52" s="203"/>
-      <c r="E52" s="203"/>
-      <c r="F52" s="203"/>
-      <c r="G52" s="203"/>
-      <c r="H52" s="204"/>
-      <c r="I52" s="205"/>
-      <c r="J52" s="205"/>
-      <c r="K52" s="205"/>
-      <c r="L52" s="205"/>
-      <c r="M52" s="206"/>
-      <c r="N52" s="207"/>
-      <c r="O52" s="208"/>
-      <c r="P52" s="209"/>
+      <c r="C52" s="226"/>
+      <c r="D52" s="226"/>
+      <c r="E52" s="226"/>
+      <c r="F52" s="226"/>
+      <c r="G52" s="226"/>
+      <c r="H52" s="234"/>
+      <c r="I52" s="235"/>
+      <c r="J52" s="235"/>
+      <c r="K52" s="235"/>
+      <c r="L52" s="235"/>
+      <c r="M52" s="236"/>
+      <c r="N52" s="227"/>
+      <c r="O52" s="228"/>
+      <c r="P52" s="229"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="210"/>
-      <c r="S52" s="210"/>
+      <c r="R52" s="230"/>
+      <c r="S52" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -12910,194 +13125,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF9DA33-68CC-4411-A4B9-D21FFCCD1191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D351F8-CB54-4746-9B54-EA68144AC375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="780" windowWidth="11415" windowHeight="8955" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="114">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -588,16 +588,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>「未入力」と表示される</t>
-    <rPh sb="1" eb="4">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>期限、メモが未入力の場合のタスク一覧表示</t>
     <rPh sb="0" eb="2">
       <t>キゲン</t>
@@ -694,6 +684,69 @@
     <t>〇</t>
     <phoneticPr fontId="7"/>
   </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>ログアウト状態でのページ表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-list.jsp</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>期限は「未入力」と表示され、メモは元のメモが表示される</t>
+    <rPh sb="0" eb="2">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
 </sst>
 </file>
 
@@ -702,7 +755,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -817,6 +870,14 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1678,14 +1739,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2277,6 +2339,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2389,7 +2456,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="ハイパーリンク" xfId="5" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{6F8E72F5-98DE-405A-B9D4-A66D21EFE385}"/>
     <cellStyle name="標準 2 2" xfId="1" xr:uid="{79379184-E0E4-48AE-9057-633A6B8D7415}"/>
@@ -4291,7 +4359,7 @@
       <c r="B12" s="86"/>
       <c r="C12" s="87"/>
       <c r="D12" s="105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" s="86"/>
       <c r="F12" s="86"/>
@@ -10010,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="T16" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U16" s="48"/>
       <c r="V16" s="48"/>
@@ -10058,7 +10126,7 @@
         <v>27</v>
       </c>
       <c r="T17" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U17" s="48"/>
       <c r="V17" s="48"/>
@@ -10106,7 +10174,7 @@
         <v>27</v>
       </c>
       <c r="T18" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
@@ -10147,9 +10215,15 @@
       </c>
       <c r="P19" s="184"/>
       <c r="Q19" s="185"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="47"/>
+      <c r="R19" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S19" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T19" s="47" t="s">
+        <v>107</v>
+      </c>
       <c r="U19" s="48"/>
       <c r="V19" s="48"/>
       <c r="W19" s="48"/>
@@ -10171,7 +10245,7 @@
       </c>
       <c r="F20" s="185"/>
       <c r="G20" s="194" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H20" s="184"/>
       <c r="I20" s="185"/>
@@ -10185,13 +10259,19 @@
       <c r="M20" s="184"/>
       <c r="N20" s="185"/>
       <c r="O20" s="195" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="P20" s="184"/>
       <c r="Q20" s="185"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46"/>
-      <c r="T20" s="47"/>
+      <c r="R20" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S20" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T20" s="47" t="s">
+        <v>107</v>
+      </c>
       <c r="U20" s="48"/>
       <c r="V20" s="48"/>
       <c r="W20" s="48"/>
@@ -10213,7 +10293,7 @@
       </c>
       <c r="F21" s="185"/>
       <c r="G21" s="194" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H21" s="184"/>
       <c r="I21" s="185"/>
@@ -10227,7 +10307,7 @@
       <c r="M21" s="184"/>
       <c r="N21" s="185"/>
       <c r="O21" s="195" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P21" s="184"/>
       <c r="Q21" s="185"/>
@@ -10238,7 +10318,7 @@
         <v>27</v>
       </c>
       <c r="T21" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U21" s="48"/>
       <c r="V21" s="48"/>
@@ -10248,26 +10328,46 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A22" s="192"/>
+      <c r="A22" s="192">
+        <v>7</v>
+      </c>
       <c r="B22" s="185"/>
-      <c r="C22" s="193"/>
+      <c r="C22" s="193" t="s">
+        <v>59</v>
+      </c>
       <c r="D22" s="185"/>
-      <c r="E22" s="193"/>
+      <c r="E22" s="193" t="s">
+        <v>108</v>
+      </c>
       <c r="F22" s="185"/>
-      <c r="G22" s="194"/>
+      <c r="G22" s="194" t="s">
+        <v>109</v>
+      </c>
       <c r="H22" s="184"/>
       <c r="I22" s="185"/>
-      <c r="J22" s="194"/>
+      <c r="J22" s="194" t="s">
+        <v>110</v>
+      </c>
       <c r="K22" s="185"/>
-      <c r="L22" s="195"/>
-      <c r="M22" s="184"/>
-      <c r="N22" s="185"/>
-      <c r="O22" s="195"/>
-      <c r="P22" s="184"/>
-      <c r="Q22" s="185"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="47"/>
+      <c r="L22" s="197" t="s">
+        <v>111</v>
+      </c>
+      <c r="M22" s="198"/>
+      <c r="N22" s="198"/>
+      <c r="O22" s="199" t="s">
+        <v>112</v>
+      </c>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="68"/>
+      <c r="R22" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S22" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T22" s="47" t="s">
+        <v>107</v>
+      </c>
       <c r="U22" s="48"/>
       <c r="V22" s="48"/>
       <c r="W22" s="48"/>
@@ -10500,23 +10600,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="200"/>
-      <c r="B31" s="199"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="199"/>
-      <c r="E31" s="201"/>
-      <c r="F31" s="199"/>
-      <c r="G31" s="202"/>
-      <c r="H31" s="198"/>
-      <c r="I31" s="199"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="199"/>
-      <c r="L31" s="197"/>
-      <c r="M31" s="198"/>
-      <c r="N31" s="199"/>
-      <c r="O31" s="197"/>
-      <c r="P31" s="198"/>
-      <c r="Q31" s="199"/>
+      <c r="A31" s="203"/>
+      <c r="B31" s="202"/>
+      <c r="C31" s="204"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="205"/>
+      <c r="H31" s="201"/>
+      <c r="I31" s="202"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="202"/>
+      <c r="L31" s="200"/>
+      <c r="M31" s="201"/>
+      <c r="N31" s="202"/>
+      <c r="O31" s="200"/>
+      <c r="P31" s="201"/>
+      <c r="Q31" s="202"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11652,6 +11752,9 @@
     <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
+  <hyperlinks>
+    <hyperlink ref="L22" r:id="rId1" xr:uid="{70F16E29-4C19-40D6-A6FE-AC67A8668308}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -11672,72 +11775,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="212" t="s">
+      <c r="A1" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="213" t="s">
+      <c r="B1" s="215"/>
+      <c r="C1" s="216" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="214"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="216" t="s">
+      <c r="D1" s="217"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="219" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="218"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="221"/>
       <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="216" t="s">
+      <c r="O1" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="218"/>
+      <c r="P1" s="221"/>
       <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="216" t="s">
+      <c r="R1" s="219" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="218"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="212"/>
-      <c r="B2" s="212"/>
-      <c r="C2" s="213" t="s">
+      <c r="A2" s="215"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="216" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="216" t="s">
+      <c r="D2" s="217"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="219" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="217"/>
-      <c r="I2" s="217"/>
-      <c r="J2" s="217"/>
-      <c r="K2" s="217"/>
-      <c r="L2" s="217"/>
-      <c r="M2" s="218"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="220"/>
+      <c r="J2" s="220"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="221"/>
       <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="219">
+      <c r="O2" s="222">
         <v>45818</v>
       </c>
-      <c r="P2" s="220"/>
+      <c r="P2" s="223"/>
       <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="221" t="s">
+      <c r="R2" s="224" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="222"/>
+      <c r="S2" s="225"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11767,1053 +11870,1053 @@
       <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="203" t="s">
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="204"/>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
-      <c r="M4" s="205"/>
-      <c r="N4" s="203" t="s">
+      <c r="I4" s="207"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="206" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="204"/>
-      <c r="P4" s="205"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="208"/>
       <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="203" t="s">
+      <c r="R4" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="205"/>
+      <c r="S4" s="208"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59">
         <v>1</v>
       </c>
       <c r="B5" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="206" t="s">
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="206"/>
-      <c r="E5" s="206"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="206"/>
-      <c r="H5" s="206" t="s">
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
+      <c r="M5" s="209"/>
+      <c r="N5" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="206"/>
-      <c r="J5" s="206"/>
-      <c r="K5" s="206"/>
-      <c r="L5" s="206"/>
-      <c r="M5" s="206"/>
-      <c r="N5" s="207" t="s">
-        <v>107</v>
-      </c>
-      <c r="O5" s="208"/>
-      <c r="P5" s="209"/>
+      <c r="O5" s="211"/>
+      <c r="P5" s="212"/>
       <c r="Q5" s="64">
         <v>45818</v>
       </c>
-      <c r="R5" s="210"/>
-      <c r="S5" s="211"/>
+      <c r="R5" s="213"/>
+      <c r="S5" s="214"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="228"/>
-      <c r="O6" s="229"/>
-      <c r="P6" s="230"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="231"/>
+      <c r="O6" s="232"/>
+      <c r="P6" s="233"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="227"/>
-      <c r="S6" s="227"/>
+      <c r="R6" s="230"/>
+      <c r="S6" s="230"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="223"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="224"/>
-      <c r="O7" s="225"/>
-      <c r="P7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="227"/>
+      <c r="O7" s="228"/>
+      <c r="P7" s="229"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="227"/>
-      <c r="S7" s="227"/>
+      <c r="R7" s="230"/>
+      <c r="S7" s="230"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="223"/>
-      <c r="H8" s="223"/>
-      <c r="I8" s="223"/>
-      <c r="J8" s="223"/>
-      <c r="K8" s="223"/>
-      <c r="L8" s="223"/>
-      <c r="M8" s="223"/>
-      <c r="N8" s="224"/>
-      <c r="O8" s="225"/>
-      <c r="P8" s="226"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
+      <c r="G8" s="226"/>
+      <c r="H8" s="226"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="226"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="227"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="229"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="227"/>
-      <c r="S8" s="227"/>
+      <c r="R8" s="230"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="223"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="223"/>
-      <c r="K9" s="223"/>
-      <c r="L9" s="223"/>
-      <c r="M9" s="223"/>
-      <c r="N9" s="224"/>
-      <c r="O9" s="225"/>
-      <c r="P9" s="226"/>
+      <c r="C9" s="226"/>
+      <c r="D9" s="226"/>
+      <c r="E9" s="226"/>
+      <c r="F9" s="226"/>
+      <c r="G9" s="226"/>
+      <c r="H9" s="226"/>
+      <c r="I9" s="226"/>
+      <c r="J9" s="226"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="227"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="229"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="227"/>
-      <c r="S9" s="227"/>
+      <c r="R9" s="230"/>
+      <c r="S9" s="230"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="231"/>
-      <c r="I10" s="232"/>
-      <c r="J10" s="232"/>
-      <c r="K10" s="232"/>
-      <c r="L10" s="232"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="224"/>
-      <c r="O10" s="225"/>
-      <c r="P10" s="226"/>
+      <c r="C10" s="226"/>
+      <c r="D10" s="226"/>
+      <c r="E10" s="226"/>
+      <c r="F10" s="226"/>
+      <c r="G10" s="226"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="227"/>
+      <c r="O10" s="228"/>
+      <c r="P10" s="229"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="227"/>
-      <c r="S10" s="227"/>
+      <c r="R10" s="230"/>
+      <c r="S10" s="230"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="223"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="223"/>
-      <c r="F11" s="223"/>
-      <c r="G11" s="223"/>
-      <c r="H11" s="231"/>
-      <c r="I11" s="232"/>
-      <c r="J11" s="232"/>
-      <c r="K11" s="232"/>
-      <c r="L11" s="232"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="224"/>
-      <c r="O11" s="225"/>
-      <c r="P11" s="226"/>
+      <c r="C11" s="226"/>
+      <c r="D11" s="226"/>
+      <c r="E11" s="226"/>
+      <c r="F11" s="226"/>
+      <c r="G11" s="226"/>
+      <c r="H11" s="234"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235"/>
+      <c r="L11" s="235"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="227"/>
+      <c r="O11" s="228"/>
+      <c r="P11" s="229"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="227"/>
-      <c r="S11" s="227"/>
+      <c r="R11" s="230"/>
+      <c r="S11" s="230"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="223"/>
-      <c r="D12" s="223"/>
-      <c r="E12" s="223"/>
-      <c r="F12" s="223"/>
-      <c r="G12" s="223"/>
-      <c r="H12" s="231"/>
-      <c r="I12" s="232"/>
-      <c r="J12" s="232"/>
-      <c r="K12" s="232"/>
-      <c r="L12" s="232"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="224"/>
-      <c r="O12" s="225"/>
-      <c r="P12" s="226"/>
+      <c r="C12" s="226"/>
+      <c r="D12" s="226"/>
+      <c r="E12" s="226"/>
+      <c r="F12" s="226"/>
+      <c r="G12" s="226"/>
+      <c r="H12" s="234"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="235"/>
+      <c r="L12" s="235"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="228"/>
+      <c r="P12" s="229"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="227"/>
-      <c r="S12" s="227"/>
+      <c r="R12" s="230"/>
+      <c r="S12" s="230"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="223"/>
-      <c r="D13" s="223"/>
-      <c r="E13" s="223"/>
-      <c r="F13" s="223"/>
-      <c r="G13" s="223"/>
-      <c r="H13" s="231"/>
-      <c r="I13" s="232"/>
-      <c r="J13" s="232"/>
-      <c r="K13" s="232"/>
-      <c r="L13" s="232"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="224"/>
-      <c r="O13" s="225"/>
-      <c r="P13" s="226"/>
+      <c r="C13" s="226"/>
+      <c r="D13" s="226"/>
+      <c r="E13" s="226"/>
+      <c r="F13" s="226"/>
+      <c r="G13" s="226"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="235"/>
+      <c r="L13" s="235"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="227"/>
+      <c r="O13" s="228"/>
+      <c r="P13" s="229"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="227"/>
-      <c r="S13" s="227"/>
+      <c r="R13" s="230"/>
+      <c r="S13" s="230"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="223"/>
-      <c r="G14" s="223"/>
-      <c r="H14" s="231"/>
-      <c r="I14" s="232"/>
-      <c r="J14" s="232"/>
-      <c r="K14" s="232"/>
-      <c r="L14" s="232"/>
-      <c r="M14" s="233"/>
-      <c r="N14" s="224"/>
-      <c r="O14" s="225"/>
-      <c r="P14" s="226"/>
+      <c r="C14" s="226"/>
+      <c r="D14" s="226"/>
+      <c r="E14" s="226"/>
+      <c r="F14" s="226"/>
+      <c r="G14" s="226"/>
+      <c r="H14" s="234"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235"/>
+      <c r="L14" s="235"/>
+      <c r="M14" s="236"/>
+      <c r="N14" s="227"/>
+      <c r="O14" s="228"/>
+      <c r="P14" s="229"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="227"/>
-      <c r="S14" s="227"/>
+      <c r="R14" s="230"/>
+      <c r="S14" s="230"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="223"/>
-      <c r="D15" s="223"/>
-      <c r="E15" s="223"/>
-      <c r="F15" s="223"/>
-      <c r="G15" s="223"/>
-      <c r="H15" s="231"/>
-      <c r="I15" s="232"/>
-      <c r="J15" s="232"/>
-      <c r="K15" s="232"/>
-      <c r="L15" s="232"/>
-      <c r="M15" s="233"/>
-      <c r="N15" s="224"/>
-      <c r="O15" s="225"/>
-      <c r="P15" s="226"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="226"/>
+      <c r="E15" s="226"/>
+      <c r="F15" s="226"/>
+      <c r="G15" s="226"/>
+      <c r="H15" s="234"/>
+      <c r="I15" s="235"/>
+      <c r="J15" s="235"/>
+      <c r="K15" s="235"/>
+      <c r="L15" s="235"/>
+      <c r="M15" s="236"/>
+      <c r="N15" s="227"/>
+      <c r="O15" s="228"/>
+      <c r="P15" s="229"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="227"/>
-      <c r="S15" s="227"/>
+      <c r="R15" s="230"/>
+      <c r="S15" s="230"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="223"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="231"/>
-      <c r="I16" s="232"/>
-      <c r="J16" s="232"/>
-      <c r="K16" s="232"/>
-      <c r="L16" s="232"/>
-      <c r="M16" s="233"/>
-      <c r="N16" s="224"/>
-      <c r="O16" s="225"/>
-      <c r="P16" s="226"/>
+      <c r="C16" s="226"/>
+      <c r="D16" s="226"/>
+      <c r="E16" s="226"/>
+      <c r="F16" s="226"/>
+      <c r="G16" s="226"/>
+      <c r="H16" s="234"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235"/>
+      <c r="L16" s="235"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="227"/>
+      <c r="O16" s="228"/>
+      <c r="P16" s="229"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="227"/>
-      <c r="S16" s="227"/>
+      <c r="R16" s="230"/>
+      <c r="S16" s="230"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="223"/>
-      <c r="D17" s="223"/>
-      <c r="E17" s="223"/>
-      <c r="F17" s="223"/>
-      <c r="G17" s="223"/>
-      <c r="H17" s="231"/>
-      <c r="I17" s="232"/>
-      <c r="J17" s="232"/>
-      <c r="K17" s="232"/>
-      <c r="L17" s="232"/>
-      <c r="M17" s="233"/>
-      <c r="N17" s="224"/>
-      <c r="O17" s="225"/>
-      <c r="P17" s="226"/>
+      <c r="C17" s="226"/>
+      <c r="D17" s="226"/>
+      <c r="E17" s="226"/>
+      <c r="F17" s="226"/>
+      <c r="G17" s="226"/>
+      <c r="H17" s="234"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="235"/>
+      <c r="L17" s="235"/>
+      <c r="M17" s="236"/>
+      <c r="N17" s="227"/>
+      <c r="O17" s="228"/>
+      <c r="P17" s="229"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="227"/>
-      <c r="S17" s="227"/>
+      <c r="R17" s="230"/>
+      <c r="S17" s="230"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="223"/>
-      <c r="E18" s="223"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="231"/>
-      <c r="I18" s="232"/>
-      <c r="J18" s="232"/>
-      <c r="K18" s="232"/>
-      <c r="L18" s="232"/>
-      <c r="M18" s="233"/>
-      <c r="N18" s="224"/>
-      <c r="O18" s="225"/>
-      <c r="P18" s="226"/>
+      <c r="C18" s="226"/>
+      <c r="D18" s="226"/>
+      <c r="E18" s="226"/>
+      <c r="F18" s="226"/>
+      <c r="G18" s="226"/>
+      <c r="H18" s="234"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
+      <c r="M18" s="236"/>
+      <c r="N18" s="227"/>
+      <c r="O18" s="228"/>
+      <c r="P18" s="229"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="227"/>
-      <c r="S18" s="227"/>
+      <c r="R18" s="230"/>
+      <c r="S18" s="230"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="223"/>
-      <c r="D19" s="223"/>
-      <c r="E19" s="223"/>
-      <c r="F19" s="223"/>
-      <c r="G19" s="223"/>
-      <c r="H19" s="231"/>
-      <c r="I19" s="232"/>
-      <c r="J19" s="232"/>
-      <c r="K19" s="232"/>
-      <c r="L19" s="232"/>
-      <c r="M19" s="233"/>
-      <c r="N19" s="224"/>
-      <c r="O19" s="225"/>
-      <c r="P19" s="226"/>
+      <c r="C19" s="226"/>
+      <c r="D19" s="226"/>
+      <c r="E19" s="226"/>
+      <c r="F19" s="226"/>
+      <c r="G19" s="226"/>
+      <c r="H19" s="234"/>
+      <c r="I19" s="235"/>
+      <c r="J19" s="235"/>
+      <c r="K19" s="235"/>
+      <c r="L19" s="235"/>
+      <c r="M19" s="236"/>
+      <c r="N19" s="227"/>
+      <c r="O19" s="228"/>
+      <c r="P19" s="229"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="227"/>
-      <c r="S19" s="227"/>
+      <c r="R19" s="230"/>
+      <c r="S19" s="230"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="223"/>
-      <c r="D20" s="223"/>
-      <c r="E20" s="223"/>
-      <c r="F20" s="223"/>
-      <c r="G20" s="223"/>
-      <c r="H20" s="231"/>
-      <c r="I20" s="232"/>
-      <c r="J20" s="232"/>
-      <c r="K20" s="232"/>
-      <c r="L20" s="232"/>
-      <c r="M20" s="233"/>
-      <c r="N20" s="224"/>
-      <c r="O20" s="225"/>
-      <c r="P20" s="226"/>
+      <c r="C20" s="226"/>
+      <c r="D20" s="226"/>
+      <c r="E20" s="226"/>
+      <c r="F20" s="226"/>
+      <c r="G20" s="226"/>
+      <c r="H20" s="234"/>
+      <c r="I20" s="235"/>
+      <c r="J20" s="235"/>
+      <c r="K20" s="235"/>
+      <c r="L20" s="235"/>
+      <c r="M20" s="236"/>
+      <c r="N20" s="227"/>
+      <c r="O20" s="228"/>
+      <c r="P20" s="229"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="227"/>
-      <c r="S20" s="227"/>
+      <c r="R20" s="230"/>
+      <c r="S20" s="230"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="223"/>
-      <c r="D21" s="223"/>
-      <c r="E21" s="223"/>
-      <c r="F21" s="223"/>
-      <c r="G21" s="223"/>
-      <c r="H21" s="231"/>
-      <c r="I21" s="232"/>
-      <c r="J21" s="232"/>
-      <c r="K21" s="232"/>
-      <c r="L21" s="232"/>
-      <c r="M21" s="233"/>
-      <c r="N21" s="224"/>
-      <c r="O21" s="225"/>
-      <c r="P21" s="226"/>
+      <c r="C21" s="226"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="226"/>
+      <c r="F21" s="226"/>
+      <c r="G21" s="226"/>
+      <c r="H21" s="234"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
+      <c r="M21" s="236"/>
+      <c r="N21" s="227"/>
+      <c r="O21" s="228"/>
+      <c r="P21" s="229"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="227"/>
-      <c r="S21" s="227"/>
+      <c r="R21" s="230"/>
+      <c r="S21" s="230"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="223"/>
-      <c r="D22" s="223"/>
-      <c r="E22" s="223"/>
-      <c r="F22" s="223"/>
-      <c r="G22" s="223"/>
-      <c r="H22" s="231"/>
-      <c r="I22" s="232"/>
-      <c r="J22" s="232"/>
-      <c r="K22" s="232"/>
-      <c r="L22" s="232"/>
-      <c r="M22" s="233"/>
-      <c r="N22" s="224"/>
-      <c r="O22" s="225"/>
-      <c r="P22" s="226"/>
+      <c r="C22" s="226"/>
+      <c r="D22" s="226"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="226"/>
+      <c r="G22" s="226"/>
+      <c r="H22" s="234"/>
+      <c r="I22" s="235"/>
+      <c r="J22" s="235"/>
+      <c r="K22" s="235"/>
+      <c r="L22" s="235"/>
+      <c r="M22" s="236"/>
+      <c r="N22" s="227"/>
+      <c r="O22" s="228"/>
+      <c r="P22" s="229"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="227"/>
-      <c r="S22" s="227"/>
+      <c r="R22" s="230"/>
+      <c r="S22" s="230"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="223"/>
-      <c r="D23" s="223"/>
-      <c r="E23" s="223"/>
-      <c r="F23" s="223"/>
-      <c r="G23" s="223"/>
-      <c r="H23" s="231"/>
-      <c r="I23" s="232"/>
-      <c r="J23" s="232"/>
-      <c r="K23" s="232"/>
-      <c r="L23" s="232"/>
-      <c r="M23" s="233"/>
-      <c r="N23" s="224"/>
-      <c r="O23" s="225"/>
-      <c r="P23" s="226"/>
+      <c r="C23" s="226"/>
+      <c r="D23" s="226"/>
+      <c r="E23" s="226"/>
+      <c r="F23" s="226"/>
+      <c r="G23" s="226"/>
+      <c r="H23" s="234"/>
+      <c r="I23" s="235"/>
+      <c r="J23" s="235"/>
+      <c r="K23" s="235"/>
+      <c r="L23" s="235"/>
+      <c r="M23" s="236"/>
+      <c r="N23" s="227"/>
+      <c r="O23" s="228"/>
+      <c r="P23" s="229"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="227"/>
-      <c r="S23" s="227"/>
+      <c r="R23" s="230"/>
+      <c r="S23" s="230"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="223"/>
-      <c r="D24" s="223"/>
-      <c r="E24" s="223"/>
-      <c r="F24" s="223"/>
-      <c r="G24" s="223"/>
-      <c r="H24" s="231"/>
-      <c r="I24" s="232"/>
-      <c r="J24" s="232"/>
-      <c r="K24" s="232"/>
-      <c r="L24" s="232"/>
-      <c r="M24" s="233"/>
-      <c r="N24" s="224"/>
-      <c r="O24" s="225"/>
-      <c r="P24" s="226"/>
+      <c r="C24" s="226"/>
+      <c r="D24" s="226"/>
+      <c r="E24" s="226"/>
+      <c r="F24" s="226"/>
+      <c r="G24" s="226"/>
+      <c r="H24" s="234"/>
+      <c r="I24" s="235"/>
+      <c r="J24" s="235"/>
+      <c r="K24" s="235"/>
+      <c r="L24" s="235"/>
+      <c r="M24" s="236"/>
+      <c r="N24" s="227"/>
+      <c r="O24" s="228"/>
+      <c r="P24" s="229"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="227"/>
-      <c r="S24" s="227"/>
+      <c r="R24" s="230"/>
+      <c r="S24" s="230"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="223"/>
-      <c r="D25" s="223"/>
-      <c r="E25" s="223"/>
-      <c r="F25" s="223"/>
-      <c r="G25" s="223"/>
-      <c r="H25" s="231"/>
-      <c r="I25" s="232"/>
-      <c r="J25" s="232"/>
-      <c r="K25" s="232"/>
-      <c r="L25" s="232"/>
-      <c r="M25" s="233"/>
-      <c r="N25" s="224"/>
-      <c r="O25" s="225"/>
-      <c r="P25" s="226"/>
+      <c r="C25" s="226"/>
+      <c r="D25" s="226"/>
+      <c r="E25" s="226"/>
+      <c r="F25" s="226"/>
+      <c r="G25" s="226"/>
+      <c r="H25" s="234"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
+      <c r="M25" s="236"/>
+      <c r="N25" s="227"/>
+      <c r="O25" s="228"/>
+      <c r="P25" s="229"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="227"/>
-      <c r="S25" s="227"/>
+      <c r="R25" s="230"/>
+      <c r="S25" s="230"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="223"/>
-      <c r="D26" s="223"/>
-      <c r="E26" s="223"/>
-      <c r="F26" s="223"/>
-      <c r="G26" s="223"/>
-      <c r="H26" s="231"/>
-      <c r="I26" s="232"/>
-      <c r="J26" s="232"/>
-      <c r="K26" s="232"/>
-      <c r="L26" s="232"/>
-      <c r="M26" s="233"/>
-      <c r="N26" s="224"/>
-      <c r="O26" s="225"/>
-      <c r="P26" s="226"/>
+      <c r="C26" s="226"/>
+      <c r="D26" s="226"/>
+      <c r="E26" s="226"/>
+      <c r="F26" s="226"/>
+      <c r="G26" s="226"/>
+      <c r="H26" s="234"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
+      <c r="M26" s="236"/>
+      <c r="N26" s="227"/>
+      <c r="O26" s="228"/>
+      <c r="P26" s="229"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="227"/>
-      <c r="S26" s="227"/>
+      <c r="R26" s="230"/>
+      <c r="S26" s="230"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="223"/>
-      <c r="D27" s="223"/>
-      <c r="E27" s="223"/>
-      <c r="F27" s="223"/>
-      <c r="G27" s="223"/>
-      <c r="H27" s="231"/>
-      <c r="I27" s="232"/>
-      <c r="J27" s="232"/>
-      <c r="K27" s="232"/>
-      <c r="L27" s="232"/>
-      <c r="M27" s="233"/>
-      <c r="N27" s="224"/>
-      <c r="O27" s="225"/>
-      <c r="P27" s="226"/>
+      <c r="C27" s="226"/>
+      <c r="D27" s="226"/>
+      <c r="E27" s="226"/>
+      <c r="F27" s="226"/>
+      <c r="G27" s="226"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="235"/>
+      <c r="J27" s="235"/>
+      <c r="K27" s="235"/>
+      <c r="L27" s="235"/>
+      <c r="M27" s="236"/>
+      <c r="N27" s="227"/>
+      <c r="O27" s="228"/>
+      <c r="P27" s="229"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="227"/>
-      <c r="S27" s="227"/>
+      <c r="R27" s="230"/>
+      <c r="S27" s="230"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="223"/>
-      <c r="D28" s="223"/>
-      <c r="E28" s="223"/>
-      <c r="F28" s="223"/>
-      <c r="G28" s="223"/>
-      <c r="H28" s="231"/>
-      <c r="I28" s="232"/>
-      <c r="J28" s="232"/>
-      <c r="K28" s="232"/>
-      <c r="L28" s="232"/>
-      <c r="M28" s="233"/>
-      <c r="N28" s="224"/>
-      <c r="O28" s="225"/>
-      <c r="P28" s="226"/>
+      <c r="C28" s="226"/>
+      <c r="D28" s="226"/>
+      <c r="E28" s="226"/>
+      <c r="F28" s="226"/>
+      <c r="G28" s="226"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="235"/>
+      <c r="J28" s="235"/>
+      <c r="K28" s="235"/>
+      <c r="L28" s="235"/>
+      <c r="M28" s="236"/>
+      <c r="N28" s="227"/>
+      <c r="O28" s="228"/>
+      <c r="P28" s="229"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="227"/>
-      <c r="S28" s="227"/>
+      <c r="R28" s="230"/>
+      <c r="S28" s="230"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="223"/>
-      <c r="D29" s="223"/>
-      <c r="E29" s="223"/>
-      <c r="F29" s="223"/>
-      <c r="G29" s="223"/>
-      <c r="H29" s="231"/>
-      <c r="I29" s="232"/>
-      <c r="J29" s="232"/>
-      <c r="K29" s="232"/>
-      <c r="L29" s="232"/>
-      <c r="M29" s="233"/>
-      <c r="N29" s="224"/>
-      <c r="O29" s="225"/>
-      <c r="P29" s="226"/>
+      <c r="C29" s="226"/>
+      <c r="D29" s="226"/>
+      <c r="E29" s="226"/>
+      <c r="F29" s="226"/>
+      <c r="G29" s="226"/>
+      <c r="H29" s="234"/>
+      <c r="I29" s="235"/>
+      <c r="J29" s="235"/>
+      <c r="K29" s="235"/>
+      <c r="L29" s="235"/>
+      <c r="M29" s="236"/>
+      <c r="N29" s="227"/>
+      <c r="O29" s="228"/>
+      <c r="P29" s="229"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="227"/>
-      <c r="S29" s="227"/>
+      <c r="R29" s="230"/>
+      <c r="S29" s="230"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="223"/>
-      <c r="D30" s="223"/>
-      <c r="E30" s="223"/>
-      <c r="F30" s="223"/>
-      <c r="G30" s="223"/>
-      <c r="H30" s="231"/>
-      <c r="I30" s="232"/>
-      <c r="J30" s="232"/>
-      <c r="K30" s="232"/>
-      <c r="L30" s="232"/>
-      <c r="M30" s="233"/>
-      <c r="N30" s="224"/>
-      <c r="O30" s="225"/>
-      <c r="P30" s="226"/>
+      <c r="C30" s="226"/>
+      <c r="D30" s="226"/>
+      <c r="E30" s="226"/>
+      <c r="F30" s="226"/>
+      <c r="G30" s="226"/>
+      <c r="H30" s="234"/>
+      <c r="I30" s="235"/>
+      <c r="J30" s="235"/>
+      <c r="K30" s="235"/>
+      <c r="L30" s="235"/>
+      <c r="M30" s="236"/>
+      <c r="N30" s="227"/>
+      <c r="O30" s="228"/>
+      <c r="P30" s="229"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="227"/>
-      <c r="S30" s="227"/>
+      <c r="R30" s="230"/>
+      <c r="S30" s="230"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="223"/>
-      <c r="D31" s="223"/>
-      <c r="E31" s="223"/>
-      <c r="F31" s="223"/>
-      <c r="G31" s="223"/>
-      <c r="H31" s="231"/>
-      <c r="I31" s="232"/>
-      <c r="J31" s="232"/>
-      <c r="K31" s="232"/>
-      <c r="L31" s="232"/>
-      <c r="M31" s="233"/>
-      <c r="N31" s="224"/>
-      <c r="O31" s="225"/>
-      <c r="P31" s="226"/>
+      <c r="C31" s="226"/>
+      <c r="D31" s="226"/>
+      <c r="E31" s="226"/>
+      <c r="F31" s="226"/>
+      <c r="G31" s="226"/>
+      <c r="H31" s="234"/>
+      <c r="I31" s="235"/>
+      <c r="J31" s="235"/>
+      <c r="K31" s="235"/>
+      <c r="L31" s="235"/>
+      <c r="M31" s="236"/>
+      <c r="N31" s="227"/>
+      <c r="O31" s="228"/>
+      <c r="P31" s="229"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="227"/>
-      <c r="S31" s="227"/>
+      <c r="R31" s="230"/>
+      <c r="S31" s="230"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="223"/>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="223"/>
-      <c r="G32" s="223"/>
-      <c r="H32" s="231"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="232"/>
-      <c r="K32" s="232"/>
-      <c r="L32" s="232"/>
-      <c r="M32" s="233"/>
-      <c r="N32" s="224"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="226"/>
+      <c r="C32" s="226"/>
+      <c r="D32" s="226"/>
+      <c r="E32" s="226"/>
+      <c r="F32" s="226"/>
+      <c r="G32" s="226"/>
+      <c r="H32" s="234"/>
+      <c r="I32" s="235"/>
+      <c r="J32" s="235"/>
+      <c r="K32" s="235"/>
+      <c r="L32" s="235"/>
+      <c r="M32" s="236"/>
+      <c r="N32" s="227"/>
+      <c r="O32" s="228"/>
+      <c r="P32" s="229"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="227"/>
-      <c r="S32" s="227"/>
+      <c r="R32" s="230"/>
+      <c r="S32" s="230"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="223"/>
-      <c r="F33" s="223"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="231"/>
-      <c r="I33" s="232"/>
-      <c r="J33" s="232"/>
-      <c r="K33" s="232"/>
-      <c r="L33" s="232"/>
-      <c r="M33" s="233"/>
-      <c r="N33" s="224"/>
-      <c r="O33" s="225"/>
-      <c r="P33" s="226"/>
+      <c r="C33" s="226"/>
+      <c r="D33" s="226"/>
+      <c r="E33" s="226"/>
+      <c r="F33" s="226"/>
+      <c r="G33" s="226"/>
+      <c r="H33" s="234"/>
+      <c r="I33" s="235"/>
+      <c r="J33" s="235"/>
+      <c r="K33" s="235"/>
+      <c r="L33" s="235"/>
+      <c r="M33" s="236"/>
+      <c r="N33" s="227"/>
+      <c r="O33" s="228"/>
+      <c r="P33" s="229"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="227"/>
-      <c r="S33" s="227"/>
+      <c r="R33" s="230"/>
+      <c r="S33" s="230"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="223"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="223"/>
-      <c r="F34" s="223"/>
-      <c r="G34" s="223"/>
-      <c r="H34" s="231"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="232"/>
-      <c r="M34" s="233"/>
-      <c r="N34" s="224"/>
-      <c r="O34" s="225"/>
-      <c r="P34" s="226"/>
+      <c r="C34" s="226"/>
+      <c r="D34" s="226"/>
+      <c r="E34" s="226"/>
+      <c r="F34" s="226"/>
+      <c r="G34" s="226"/>
+      <c r="H34" s="234"/>
+      <c r="I34" s="235"/>
+      <c r="J34" s="235"/>
+      <c r="K34" s="235"/>
+      <c r="L34" s="235"/>
+      <c r="M34" s="236"/>
+      <c r="N34" s="227"/>
+      <c r="O34" s="228"/>
+      <c r="P34" s="229"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="227"/>
-      <c r="S34" s="227"/>
+      <c r="R34" s="230"/>
+      <c r="S34" s="230"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="223"/>
-      <c r="E35" s="223"/>
-      <c r="F35" s="223"/>
-      <c r="G35" s="223"/>
-      <c r="H35" s="231"/>
-      <c r="I35" s="232"/>
-      <c r="J35" s="232"/>
-      <c r="K35" s="232"/>
-      <c r="L35" s="232"/>
-      <c r="M35" s="233"/>
-      <c r="N35" s="224"/>
-      <c r="O35" s="225"/>
-      <c r="P35" s="226"/>
+      <c r="C35" s="226"/>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="226"/>
+      <c r="G35" s="226"/>
+      <c r="H35" s="234"/>
+      <c r="I35" s="235"/>
+      <c r="J35" s="235"/>
+      <c r="K35" s="235"/>
+      <c r="L35" s="235"/>
+      <c r="M35" s="236"/>
+      <c r="N35" s="227"/>
+      <c r="O35" s="228"/>
+      <c r="P35" s="229"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="227"/>
-      <c r="S35" s="227"/>
+      <c r="R35" s="230"/>
+      <c r="S35" s="230"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="231"/>
-      <c r="I36" s="232"/>
-      <c r="J36" s="232"/>
-      <c r="K36" s="232"/>
-      <c r="L36" s="232"/>
-      <c r="M36" s="233"/>
-      <c r="N36" s="224"/>
-      <c r="O36" s="225"/>
-      <c r="P36" s="226"/>
+      <c r="C36" s="226"/>
+      <c r="D36" s="226"/>
+      <c r="E36" s="226"/>
+      <c r="F36" s="226"/>
+      <c r="G36" s="226"/>
+      <c r="H36" s="234"/>
+      <c r="I36" s="235"/>
+      <c r="J36" s="235"/>
+      <c r="K36" s="235"/>
+      <c r="L36" s="235"/>
+      <c r="M36" s="236"/>
+      <c r="N36" s="227"/>
+      <c r="O36" s="228"/>
+      <c r="P36" s="229"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="227"/>
-      <c r="S36" s="227"/>
+      <c r="R36" s="230"/>
+      <c r="S36" s="230"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="223"/>
-      <c r="D37" s="223"/>
-      <c r="E37" s="223"/>
-      <c r="F37" s="223"/>
-      <c r="G37" s="223"/>
-      <c r="H37" s="231"/>
-      <c r="I37" s="232"/>
-      <c r="J37" s="232"/>
-      <c r="K37" s="232"/>
-      <c r="L37" s="232"/>
-      <c r="M37" s="233"/>
-      <c r="N37" s="224"/>
-      <c r="O37" s="225"/>
-      <c r="P37" s="226"/>
+      <c r="C37" s="226"/>
+      <c r="D37" s="226"/>
+      <c r="E37" s="226"/>
+      <c r="F37" s="226"/>
+      <c r="G37" s="226"/>
+      <c r="H37" s="234"/>
+      <c r="I37" s="235"/>
+      <c r="J37" s="235"/>
+      <c r="K37" s="235"/>
+      <c r="L37" s="235"/>
+      <c r="M37" s="236"/>
+      <c r="N37" s="227"/>
+      <c r="O37" s="228"/>
+      <c r="P37" s="229"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="227"/>
-      <c r="S37" s="227"/>
+      <c r="R37" s="230"/>
+      <c r="S37" s="230"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="223"/>
-      <c r="D38" s="223"/>
-      <c r="E38" s="223"/>
-      <c r="F38" s="223"/>
-      <c r="G38" s="223"/>
-      <c r="H38" s="231"/>
-      <c r="I38" s="232"/>
-      <c r="J38" s="232"/>
-      <c r="K38" s="232"/>
-      <c r="L38" s="232"/>
-      <c r="M38" s="233"/>
-      <c r="N38" s="224"/>
-      <c r="O38" s="225"/>
-      <c r="P38" s="226"/>
+      <c r="C38" s="226"/>
+      <c r="D38" s="226"/>
+      <c r="E38" s="226"/>
+      <c r="F38" s="226"/>
+      <c r="G38" s="226"/>
+      <c r="H38" s="234"/>
+      <c r="I38" s="235"/>
+      <c r="J38" s="235"/>
+      <c r="K38" s="235"/>
+      <c r="L38" s="235"/>
+      <c r="M38" s="236"/>
+      <c r="N38" s="227"/>
+      <c r="O38" s="228"/>
+      <c r="P38" s="229"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="227"/>
-      <c r="S38" s="227"/>
+      <c r="R38" s="230"/>
+      <c r="S38" s="230"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="223"/>
-      <c r="D39" s="223"/>
-      <c r="E39" s="223"/>
-      <c r="F39" s="223"/>
-      <c r="G39" s="223"/>
-      <c r="H39" s="231"/>
-      <c r="I39" s="232"/>
-      <c r="J39" s="232"/>
-      <c r="K39" s="232"/>
-      <c r="L39" s="232"/>
-      <c r="M39" s="233"/>
-      <c r="N39" s="224"/>
-      <c r="O39" s="225"/>
-      <c r="P39" s="226"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="226"/>
+      <c r="E39" s="226"/>
+      <c r="F39" s="226"/>
+      <c r="G39" s="226"/>
+      <c r="H39" s="234"/>
+      <c r="I39" s="235"/>
+      <c r="J39" s="235"/>
+      <c r="K39" s="235"/>
+      <c r="L39" s="235"/>
+      <c r="M39" s="236"/>
+      <c r="N39" s="227"/>
+      <c r="O39" s="228"/>
+      <c r="P39" s="229"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="227"/>
-      <c r="S39" s="227"/>
+      <c r="R39" s="230"/>
+      <c r="S39" s="230"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="223"/>
-      <c r="D40" s="223"/>
-      <c r="E40" s="223"/>
-      <c r="F40" s="223"/>
-      <c r="G40" s="223"/>
-      <c r="H40" s="231"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="233"/>
-      <c r="N40" s="224"/>
-      <c r="O40" s="225"/>
-      <c r="P40" s="226"/>
+      <c r="C40" s="226"/>
+      <c r="D40" s="226"/>
+      <c r="E40" s="226"/>
+      <c r="F40" s="226"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="235"/>
+      <c r="J40" s="235"/>
+      <c r="K40" s="235"/>
+      <c r="L40" s="235"/>
+      <c r="M40" s="236"/>
+      <c r="N40" s="227"/>
+      <c r="O40" s="228"/>
+      <c r="P40" s="229"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="227"/>
-      <c r="S40" s="227"/>
+      <c r="R40" s="230"/>
+      <c r="S40" s="230"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="223"/>
-      <c r="D41" s="223"/>
-      <c r="E41" s="223"/>
-      <c r="F41" s="223"/>
-      <c r="G41" s="223"/>
-      <c r="H41" s="231"/>
-      <c r="I41" s="232"/>
-      <c r="J41" s="232"/>
-      <c r="K41" s="232"/>
-      <c r="L41" s="232"/>
-      <c r="M41" s="233"/>
-      <c r="N41" s="224"/>
-      <c r="O41" s="225"/>
-      <c r="P41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="226"/>
+      <c r="E41" s="226"/>
+      <c r="F41" s="226"/>
+      <c r="G41" s="226"/>
+      <c r="H41" s="234"/>
+      <c r="I41" s="235"/>
+      <c r="J41" s="235"/>
+      <c r="K41" s="235"/>
+      <c r="L41" s="235"/>
+      <c r="M41" s="236"/>
+      <c r="N41" s="227"/>
+      <c r="O41" s="228"/>
+      <c r="P41" s="229"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="227"/>
-      <c r="S41" s="227"/>
+      <c r="R41" s="230"/>
+      <c r="S41" s="230"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="223"/>
-      <c r="D42" s="223"/>
-      <c r="E42" s="223"/>
-      <c r="F42" s="223"/>
-      <c r="G42" s="223"/>
-      <c r="H42" s="231"/>
-      <c r="I42" s="232"/>
-      <c r="J42" s="232"/>
-      <c r="K42" s="232"/>
-      <c r="L42" s="232"/>
-      <c r="M42" s="233"/>
-      <c r="N42" s="224"/>
-      <c r="O42" s="225"/>
-      <c r="P42" s="226"/>
+      <c r="C42" s="226"/>
+      <c r="D42" s="226"/>
+      <c r="E42" s="226"/>
+      <c r="F42" s="226"/>
+      <c r="G42" s="226"/>
+      <c r="H42" s="234"/>
+      <c r="I42" s="235"/>
+      <c r="J42" s="235"/>
+      <c r="K42" s="235"/>
+      <c r="L42" s="235"/>
+      <c r="M42" s="236"/>
+      <c r="N42" s="227"/>
+      <c r="O42" s="228"/>
+      <c r="P42" s="229"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="227"/>
-      <c r="S42" s="227"/>
+      <c r="R42" s="230"/>
+      <c r="S42" s="230"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="223"/>
-      <c r="D43" s="223"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="231"/>
-      <c r="I43" s="232"/>
-      <c r="J43" s="232"/>
-      <c r="K43" s="232"/>
-      <c r="L43" s="232"/>
-      <c r="M43" s="233"/>
-      <c r="N43" s="224"/>
-      <c r="O43" s="225"/>
-      <c r="P43" s="226"/>
+      <c r="C43" s="226"/>
+      <c r="D43" s="226"/>
+      <c r="E43" s="226"/>
+      <c r="F43" s="226"/>
+      <c r="G43" s="226"/>
+      <c r="H43" s="234"/>
+      <c r="I43" s="235"/>
+      <c r="J43" s="235"/>
+      <c r="K43" s="235"/>
+      <c r="L43" s="235"/>
+      <c r="M43" s="236"/>
+      <c r="N43" s="227"/>
+      <c r="O43" s="228"/>
+      <c r="P43" s="229"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="227"/>
-      <c r="S43" s="227"/>
+      <c r="R43" s="230"/>
+      <c r="S43" s="230"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="223"/>
-      <c r="D44" s="223"/>
-      <c r="E44" s="223"/>
-      <c r="F44" s="223"/>
-      <c r="G44" s="223"/>
-      <c r="H44" s="231"/>
-      <c r="I44" s="232"/>
-      <c r="J44" s="232"/>
-      <c r="K44" s="232"/>
-      <c r="L44" s="232"/>
-      <c r="M44" s="233"/>
-      <c r="N44" s="224"/>
-      <c r="O44" s="225"/>
-      <c r="P44" s="226"/>
+      <c r="C44" s="226"/>
+      <c r="D44" s="226"/>
+      <c r="E44" s="226"/>
+      <c r="F44" s="226"/>
+      <c r="G44" s="226"/>
+      <c r="H44" s="234"/>
+      <c r="I44" s="235"/>
+      <c r="J44" s="235"/>
+      <c r="K44" s="235"/>
+      <c r="L44" s="235"/>
+      <c r="M44" s="236"/>
+      <c r="N44" s="227"/>
+      <c r="O44" s="228"/>
+      <c r="P44" s="229"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="227"/>
-      <c r="S44" s="227"/>
+      <c r="R44" s="230"/>
+      <c r="S44" s="230"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="223"/>
-      <c r="D45" s="223"/>
-      <c r="E45" s="223"/>
-      <c r="F45" s="223"/>
-      <c r="G45" s="223"/>
-      <c r="H45" s="231"/>
-      <c r="I45" s="232"/>
-      <c r="J45" s="232"/>
-      <c r="K45" s="232"/>
-      <c r="L45" s="232"/>
-      <c r="M45" s="233"/>
-      <c r="N45" s="224"/>
-      <c r="O45" s="225"/>
-      <c r="P45" s="226"/>
+      <c r="C45" s="226"/>
+      <c r="D45" s="226"/>
+      <c r="E45" s="226"/>
+      <c r="F45" s="226"/>
+      <c r="G45" s="226"/>
+      <c r="H45" s="234"/>
+      <c r="I45" s="235"/>
+      <c r="J45" s="235"/>
+      <c r="K45" s="235"/>
+      <c r="L45" s="235"/>
+      <c r="M45" s="236"/>
+      <c r="N45" s="227"/>
+      <c r="O45" s="228"/>
+      <c r="P45" s="229"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="227"/>
-      <c r="S45" s="227"/>
+      <c r="R45" s="230"/>
+      <c r="S45" s="230"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="223"/>
-      <c r="D46" s="223"/>
-      <c r="E46" s="223"/>
-      <c r="F46" s="223"/>
-      <c r="G46" s="223"/>
-      <c r="H46" s="231"/>
-      <c r="I46" s="232"/>
-      <c r="J46" s="232"/>
-      <c r="K46" s="232"/>
-      <c r="L46" s="232"/>
-      <c r="M46" s="233"/>
-      <c r="N46" s="224"/>
-      <c r="O46" s="225"/>
-      <c r="P46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="226"/>
+      <c r="H46" s="234"/>
+      <c r="I46" s="235"/>
+      <c r="J46" s="235"/>
+      <c r="K46" s="235"/>
+      <c r="L46" s="235"/>
+      <c r="M46" s="236"/>
+      <c r="N46" s="227"/>
+      <c r="O46" s="228"/>
+      <c r="P46" s="229"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="227"/>
-      <c r="S46" s="227"/>
+      <c r="R46" s="230"/>
+      <c r="S46" s="230"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="223"/>
-      <c r="D47" s="223"/>
-      <c r="E47" s="223"/>
-      <c r="F47" s="223"/>
-      <c r="G47" s="223"/>
-      <c r="H47" s="231"/>
-      <c r="I47" s="232"/>
-      <c r="J47" s="232"/>
-      <c r="K47" s="232"/>
-      <c r="L47" s="232"/>
-      <c r="M47" s="233"/>
-      <c r="N47" s="224"/>
-      <c r="O47" s="225"/>
-      <c r="P47" s="226"/>
+      <c r="C47" s="226"/>
+      <c r="D47" s="226"/>
+      <c r="E47" s="226"/>
+      <c r="F47" s="226"/>
+      <c r="G47" s="226"/>
+      <c r="H47" s="234"/>
+      <c r="I47" s="235"/>
+      <c r="J47" s="235"/>
+      <c r="K47" s="235"/>
+      <c r="L47" s="235"/>
+      <c r="M47" s="236"/>
+      <c r="N47" s="227"/>
+      <c r="O47" s="228"/>
+      <c r="P47" s="229"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="227"/>
-      <c r="S47" s="227"/>
+      <c r="R47" s="230"/>
+      <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="223"/>
-      <c r="D48" s="223"/>
-      <c r="E48" s="223"/>
-      <c r="F48" s="223"/>
-      <c r="G48" s="223"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="232"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="232"/>
-      <c r="L48" s="232"/>
-      <c r="M48" s="233"/>
-      <c r="N48" s="224"/>
-      <c r="O48" s="225"/>
-      <c r="P48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="234"/>
+      <c r="I48" s="235"/>
+      <c r="J48" s="235"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="236"/>
+      <c r="N48" s="227"/>
+      <c r="O48" s="228"/>
+      <c r="P48" s="229"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="227"/>
-      <c r="S48" s="227"/>
+      <c r="R48" s="230"/>
+      <c r="S48" s="230"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="223"/>
-      <c r="D49" s="223"/>
-      <c r="E49" s="223"/>
-      <c r="F49" s="223"/>
-      <c r="G49" s="223"/>
-      <c r="H49" s="231"/>
-      <c r="I49" s="232"/>
-      <c r="J49" s="232"/>
-      <c r="K49" s="232"/>
-      <c r="L49" s="232"/>
-      <c r="M49" s="233"/>
-      <c r="N49" s="224"/>
-      <c r="O49" s="225"/>
-      <c r="P49" s="226"/>
+      <c r="C49" s="226"/>
+      <c r="D49" s="226"/>
+      <c r="E49" s="226"/>
+      <c r="F49" s="226"/>
+      <c r="G49" s="226"/>
+      <c r="H49" s="234"/>
+      <c r="I49" s="235"/>
+      <c r="J49" s="235"/>
+      <c r="K49" s="235"/>
+      <c r="L49" s="235"/>
+      <c r="M49" s="236"/>
+      <c r="N49" s="227"/>
+      <c r="O49" s="228"/>
+      <c r="P49" s="229"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="227"/>
-      <c r="S49" s="227"/>
+      <c r="R49" s="230"/>
+      <c r="S49" s="230"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="223"/>
-      <c r="D50" s="223"/>
-      <c r="E50" s="223"/>
-      <c r="F50" s="223"/>
-      <c r="G50" s="223"/>
-      <c r="H50" s="231"/>
-      <c r="I50" s="232"/>
-      <c r="J50" s="232"/>
-      <c r="K50" s="232"/>
-      <c r="L50" s="232"/>
-      <c r="M50" s="233"/>
-      <c r="N50" s="224"/>
-      <c r="O50" s="225"/>
-      <c r="P50" s="226"/>
+      <c r="C50" s="226"/>
+      <c r="D50" s="226"/>
+      <c r="E50" s="226"/>
+      <c r="F50" s="226"/>
+      <c r="G50" s="226"/>
+      <c r="H50" s="234"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="236"/>
+      <c r="N50" s="227"/>
+      <c r="O50" s="228"/>
+      <c r="P50" s="229"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="227"/>
-      <c r="S50" s="227"/>
+      <c r="R50" s="230"/>
+      <c r="S50" s="230"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="223"/>
-      <c r="D51" s="223"/>
-      <c r="E51" s="223"/>
-      <c r="F51" s="223"/>
-      <c r="G51" s="223"/>
-      <c r="H51" s="231"/>
-      <c r="I51" s="232"/>
-      <c r="J51" s="232"/>
-      <c r="K51" s="232"/>
-      <c r="L51" s="232"/>
-      <c r="M51" s="233"/>
-      <c r="N51" s="224"/>
-      <c r="O51" s="225"/>
-      <c r="P51" s="226"/>
+      <c r="C51" s="226"/>
+      <c r="D51" s="226"/>
+      <c r="E51" s="226"/>
+      <c r="F51" s="226"/>
+      <c r="G51" s="226"/>
+      <c r="H51" s="234"/>
+      <c r="I51" s="235"/>
+      <c r="J51" s="235"/>
+      <c r="K51" s="235"/>
+      <c r="L51" s="235"/>
+      <c r="M51" s="236"/>
+      <c r="N51" s="227"/>
+      <c r="O51" s="228"/>
+      <c r="P51" s="229"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="227"/>
-      <c r="S51" s="227"/>
+      <c r="R51" s="230"/>
+      <c r="S51" s="230"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="223"/>
-      <c r="D52" s="223"/>
-      <c r="E52" s="223"/>
-      <c r="F52" s="223"/>
-      <c r="G52" s="223"/>
-      <c r="H52" s="231"/>
-      <c r="I52" s="232"/>
-      <c r="J52" s="232"/>
-      <c r="K52" s="232"/>
-      <c r="L52" s="232"/>
-      <c r="M52" s="233"/>
-      <c r="N52" s="224"/>
-      <c r="O52" s="225"/>
-      <c r="P52" s="226"/>
+      <c r="C52" s="226"/>
+      <c r="D52" s="226"/>
+      <c r="E52" s="226"/>
+      <c r="F52" s="226"/>
+      <c r="G52" s="226"/>
+      <c r="H52" s="234"/>
+      <c r="I52" s="235"/>
+      <c r="J52" s="235"/>
+      <c r="K52" s="235"/>
+      <c r="L52" s="235"/>
+      <c r="M52" s="236"/>
+      <c r="N52" s="227"/>
+      <c r="O52" s="228"/>
+      <c r="P52" s="229"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="227"/>
-      <c r="S52" s="227"/>
+      <c r="R52" s="230"/>
+      <c r="S52" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="205">

--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D351F8-CB54-4746-9B54-EA68144AC375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6B46A5-136B-458D-AF10-ECF8C53E89DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,15 @@
     <sheet name="詳細クラス図" sheetId="7" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="8" r:id="rId6"/>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="9" r:id="rId7"/>
+    <sheet name="エビデンス" sheetId="10" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <definedNames>
+    <definedName name="あ">#REF!</definedName>
+    <definedName name="ああ">#REF!</definedName>
     <definedName name="範囲１" localSheetId="6">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
@@ -30,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="124">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -99,14 +106,14 @@
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>56期</t>
     <rPh sb="2" eb="3">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>山本岬樹</t>
@@ -116,11 +123,11 @@
     <rPh sb="2" eb="4">
       <t>ミサキキ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>画面名称</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -130,7 +137,7 @@
     <rPh sb="0" eb="2">
       <t>ヤマガタ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ユースケース名</t>
@@ -143,7 +150,7 @@
   </si>
   <si>
     <t>ユーザー</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>事前条件</t>
@@ -242,33 +249,33 @@
     <rPh sb="4" eb="6">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>submit</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>メニューへ戻る</t>
     <rPh sb="5" eb="6">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>menu.jsp</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>POST</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧</t>
     <rPh sb="3" eb="5">
       <t>イチラン</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧が表示される</t>
@@ -278,7 +285,7 @@
     <rPh sb="6" eb="8">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログインが完了しており、データベースと接続できている</t>
@@ -288,7 +295,7 @@
     <rPh sb="19" eb="21">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>①データベースの接続に失敗した場合"データベースに接続できませんでした"と表示される。
@@ -320,7 +327,7 @@
     <rPh sb="74" eb="76">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>1
@@ -344,14 +351,14 @@
     <rPh sb="90" eb="92">
       <t>ショウサイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧画面</t>
     <rPh sb="3" eb="5">
       <t>イチラン</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>JUnitテスト仕様書兼報告書</t>
@@ -364,14 +371,14 @@
     <rPh sb="12" eb="15">
       <t>ホウコクショ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>作成者</t>
@@ -381,25 +388,25 @@
     <rPh sb="0" eb="3">
       <t>カイシャメイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>コンサイズ</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>サブシステム名</t>
     <rPh sb="6" eb="7">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>作成日</t>
     <rPh sb="0" eb="3">
       <t>サクセイビ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>実施者</t>
@@ -409,29 +416,29 @@
     <rPh sb="2" eb="3">
       <t>シャ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>No</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>分類</t>
     <rPh sb="0" eb="2">
       <t>ブンルイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>テストクラス</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>検証するメソッド</t>
     <rPh sb="0" eb="2">
       <t>ケンショウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>期待する結果</t>
@@ -441,14 +448,14 @@
     <rPh sb="4" eb="6">
       <t>ケッカ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>実施日</t>
     <rPh sb="0" eb="3">
       <t>ジッシビ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>備考・特記事項</t>
@@ -461,7 +468,7 @@
     <rPh sb="5" eb="7">
       <t>ジコウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>メニュー画面からタスク一覧表示へページ遷移</t>
@@ -477,7 +484,7 @@
     <rPh sb="19" eb="21">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧表示ボタンを押下する</t>
@@ -487,7 +494,7 @@
     <rPh sb="11" eb="13">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧表示画面が表示される</t>
@@ -500,7 +507,7 @@
     <rPh sb="10" eb="12">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログイン状態かつデータベースに接続されていること</t>
@@ -510,7 +517,7 @@
     <rPh sb="15" eb="17">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>データベースに接続されていないときのタスク一覧表示ボタンの押下</t>
@@ -523,7 +530,7 @@
     <rPh sb="29" eb="31">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>エラー画面へ遷移する
@@ -531,19 +538,19 @@
     <rPh sb="25" eb="27">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">正常系
 </t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスクは現在ありませんというメッセージが表示される</t>
     <rPh sb="20" eb="22">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>登録されているタスクがない場合のタスク一覧表示</t>
@@ -556,7 +563,7 @@
     <rPh sb="19" eb="23">
       <t>イチランヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>データベースに接続されているときのタスク一覧表示ボタンの押下</t>
@@ -572,7 +579,7 @@
     <rPh sb="28" eb="30">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>登録されているタスク一覧が表示される</t>
@@ -585,7 +592,7 @@
     <rPh sb="13" eb="15">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>期限、メモが未入力の場合のタスク一覧表示</t>
@@ -604,7 +611,7 @@
     <rPh sb="18" eb="20">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスクID、タスク名、カテゴリID、ユーザーID、ステータスコード、登録日時、更新日時の表示</t>
@@ -620,7 +627,7 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>必ず登録した内容が表示される</t>
@@ -636,7 +643,7 @@
     <rPh sb="9" eb="11">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>1タスク詳細画面に遷移する。
@@ -653,22 +660,22 @@
     <rPh sb="23" eb="24">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>正常系</t>
     <rPh sb="0" eb="3">
       <t>セイジョウケイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>TaskDAOTest</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>select()</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>返ってくる値がNullではない。</t>
@@ -678,15 +685,15 @@
     <rPh sb="5" eb="6">
       <t>アタイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>異常系</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログアウト状態でのページ表示</t>
@@ -696,18 +703,18 @@
     <rPh sb="12" eb="14">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログアウト状態であること</t>
     <rPh sb="5" eb="7">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>http://localhost:8080/taskUN/task-list.jsp</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
@@ -726,7 +733,7 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>期限は「未入力」と表示され、メモは元のメモが表示される</t>
@@ -745,7 +752,74 @@
     <rPh sb="22" eb="24">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>テストエビデンス</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>グループ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>承認印</t>
+    <rPh sb="0" eb="3">
+      <t>ショウニンイン</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>機能名称</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>タスク一覧表示</t>
+    <rPh sb="3" eb="7">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -755,11 +829,19 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -879,6 +961,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -900,7 +996,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="71">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -1738,20 +1834,350 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="268">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="16" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1760,645 +2186,459 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="15" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="10" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2410,57 +2650,127 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="1" fillId="0" borderId="71" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="ハイパーリンク" xfId="5" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{6F8E72F5-98DE-405A-B9D4-A66D21EFE385}"/>
     <cellStyle name="標準 2 2" xfId="1" xr:uid="{79379184-E0E4-48AE-9057-633A6B8D7415}"/>
+    <cellStyle name="標準 3" xfId="6" xr:uid="{A8C89FDD-A49A-45D7-BA64-F3E587223BD4}"/>
     <cellStyle name="標準_生産計画ED書" xfId="3" xr:uid="{7EBA00B9-77D1-4E43-9CBA-6456FE0380AD}"/>
     <cellStyle name="標準_東京理科大DBレイアウト" xfId="4" xr:uid="{4DC3AB47-9300-45FE-A4F0-1EE38BCFF06E}"/>
   </cellStyles>
@@ -2797,6 +3107,60 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ユースケース記述"/>
+      <sheetName val="画面設計書"/>
+      <sheetName val="画面遷移図"/>
+      <sheetName val="テスト仕様書兼結果報告書"/>
+      <sheetName val="エビデンス"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ユースケース記述"/>
+      <sheetName val="画面設計書"/>
+      <sheetName val="画面遷移図"/>
+      <sheetName val="詳細クラス図"/>
+      <sheetName val="テスト仕様書兼結果報告書"/>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="カバレッジレポート"/>
+      <sheetName val="エビデンス"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4155,7 +4519,7 @@
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="G15:H15"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -4173,19 +4537,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="97"/>
+      <c r="F1" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="82"/>
+      <c r="G1" s="97"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4197,190 +4561,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="100" t="s">
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="101"/>
-      <c r="F2" s="100" t="s">
+      <c r="E2" s="111"/>
+      <c r="F2" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="104">
+      <c r="G2" s="111"/>
+      <c r="H2" s="114">
         <v>45805</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="77"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="93"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="96"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="83" t="s">
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="84"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="99"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="89"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="89"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="88" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="89"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="87" customHeight="1">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="87"/>
-      <c r="D9" s="105" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="89"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="112"/>
-      <c r="B10" s="114" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="89"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="113"/>
-      <c r="B11" s="114" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="105" t="s">
+      <c r="C11" s="76"/>
+      <c r="D11" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="89"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="78"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="105" t="s">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="89"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="107"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="110"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5371,6 +5735,18 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5386,20 +5762,8 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -6820,7 +7184,7 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -6909,23 +7273,23 @@
       <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="140"/>
+      <c r="B5" s="137"/>
       <c r="C5" s="131"/>
-      <c r="D5" s="145" t="s">
+      <c r="D5" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="146"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="144" t="s">
+      <c r="A6" s="141" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="67"/>
@@ -6936,19 +7300,19 @@
       <c r="G6" s="67"/>
       <c r="H6" s="67"/>
       <c r="I6" s="67"/>
-      <c r="J6" s="137"/>
+      <c r="J6" s="145"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="147"/>
-      <c r="B7" s="148"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="148"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="149"/>
+      <c r="A7" s="146"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="148"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="125"/>
@@ -6960,7 +7324,7 @@
       <c r="G8" s="70"/>
       <c r="H8" s="70"/>
       <c r="I8" s="70"/>
-      <c r="J8" s="150"/>
+      <c r="J8" s="149"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="125"/>
@@ -6972,7 +7336,7 @@
       <c r="G9" s="70"/>
       <c r="H9" s="70"/>
       <c r="I9" s="70"/>
-      <c r="J9" s="150"/>
+      <c r="J9" s="149"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="125"/>
@@ -6984,7 +7348,7 @@
       <c r="G10" s="70"/>
       <c r="H10" s="70"/>
       <c r="I10" s="70"/>
-      <c r="J10" s="150"/>
+      <c r="J10" s="149"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="125"/>
@@ -6996,7 +7360,7 @@
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
-      <c r="J11" s="150"/>
+      <c r="J11" s="149"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="125"/>
@@ -7008,7 +7372,7 @@
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
       <c r="I12" s="70"/>
-      <c r="J12" s="150"/>
+      <c r="J12" s="149"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="125"/>
@@ -7020,10 +7384,10 @@
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
       <c r="I13" s="70"/>
-      <c r="J13" s="150"/>
+      <c r="J13" s="149"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="144" t="s">
+      <c r="A14" s="141" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="67"/>
@@ -7034,15 +7398,15 @@
       <c r="G14" s="67"/>
       <c r="H14" s="67"/>
       <c r="I14" s="67"/>
-      <c r="J14" s="137"/>
+      <c r="J14" s="145"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="144" t="s">
+      <c r="A15" s="141" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="67"/>
       <c r="C15" s="68"/>
-      <c r="D15" s="136" t="s">
+      <c r="D15" s="150" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="67"/>
@@ -7057,7 +7421,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="144" t="s">
+      <c r="A16" s="141" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="67"/>
@@ -7078,10 +7442,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="67"/>
-      <c r="J16" s="137"/>
+      <c r="J16" s="145"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="138">
+      <c r="A17" s="142">
         <v>1</v>
       </c>
       <c r="B17" s="67"/>
@@ -7096,80 +7460,80 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="136"/>
+      <c r="H17" s="150"/>
       <c r="I17" s="67"/>
-      <c r="J17" s="137"/>
+      <c r="J17" s="145"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="138"/>
+      <c r="A18" s="142"/>
       <c r="B18" s="67"/>
       <c r="C18" s="68"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="136"/>
+      <c r="H18" s="150"/>
       <c r="I18" s="67"/>
-      <c r="J18" s="137"/>
+      <c r="J18" s="145"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="138"/>
+      <c r="A19" s="142"/>
       <c r="B19" s="67"/>
       <c r="C19" s="68"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="136"/>
+      <c r="H19" s="150"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="137"/>
+      <c r="J19" s="145"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="138"/>
+      <c r="A20" s="142"/>
       <c r="B20" s="67"/>
       <c r="C20" s="68"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="136"/>
+      <c r="H20" s="150"/>
       <c r="I20" s="67"/>
-      <c r="J20" s="137"/>
+      <c r="J20" s="145"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="138"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="67"/>
       <c r="C21" s="68"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="136"/>
+      <c r="H21" s="150"/>
       <c r="I21" s="67"/>
-      <c r="J21" s="137"/>
+      <c r="J21" s="145"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="138"/>
+      <c r="A22" s="142"/>
       <c r="B22" s="67"/>
       <c r="C22" s="68"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="136"/>
+      <c r="H22" s="150"/>
       <c r="I22" s="67"/>
-      <c r="J22" s="137"/>
+      <c r="J22" s="145"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="143"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="152"/>
-      <c r="I23" s="142"/>
+      <c r="I23" s="139"/>
       <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8151,11 +8515,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8172,18 +8541,13 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -9597,7 +9961,7 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -9616,7 +9980,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="203" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="161"/>
@@ -9627,14 +9991,14 @@
       <c r="G1" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
       <c r="J1" s="170"/>
       <c r="K1" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
       <c r="N1" s="170"/>
       <c r="O1" s="169" t="s">
         <v>7</v>
@@ -9647,7 +10011,7 @@
       <c r="S1" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="182"/>
+      <c r="T1" s="200"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="163"/>
@@ -9659,16 +10023,16 @@
       <c r="G2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
       <c r="J2" s="172"/>
       <c r="K2" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="189"/>
-      <c r="M2" s="189"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
       <c r="N2" s="172"/>
-      <c r="O2" s="190">
+      <c r="O2" s="205">
         <v>45817</v>
       </c>
       <c r="P2" s="172"/>
@@ -9677,7 +10041,7 @@
       </c>
       <c r="R2" s="172"/>
       <c r="S2" s="171"/>
-      <c r="T2" s="176"/>
+      <c r="T2" s="194"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="163"/>
@@ -9699,7 +10063,7 @@
       <c r="Q3" s="173"/>
       <c r="R3" s="165"/>
       <c r="S3" s="173"/>
-      <c r="T3" s="177"/>
+      <c r="T3" s="195"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="166"/>
@@ -9721,85 +10085,85 @@
       <c r="Q4" s="174"/>
       <c r="R4" s="168"/>
       <c r="S4" s="174"/>
-      <c r="T4" s="178"/>
+      <c r="T4" s="196"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="179" t="s">
+      <c r="A5" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
       <c r="F5" s="170"/>
-      <c r="G5" s="181" t="s">
+      <c r="G5" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="180"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="180"/>
-      <c r="T5" s="182"/>
+      <c r="H5" s="198"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="198"/>
+      <c r="K5" s="198"/>
+      <c r="L5" s="198"/>
+      <c r="M5" s="198"/>
+      <c r="N5" s="198"/>
+      <c r="O5" s="198"/>
+      <c r="P5" s="198"/>
+      <c r="Q5" s="198"/>
+      <c r="R5" s="198"/>
+      <c r="S5" s="198"/>
+      <c r="T5" s="200"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="183" t="s">
+      <c r="A6" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="186" t="s">
+      <c r="B6" s="183"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="184"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
-      <c r="K6" s="184"/>
-      <c r="L6" s="184"/>
-      <c r="M6" s="184"/>
-      <c r="N6" s="184"/>
-      <c r="O6" s="184"/>
-      <c r="P6" s="184"/>
-      <c r="Q6" s="184"/>
-      <c r="R6" s="184"/>
-      <c r="S6" s="184"/>
-      <c r="T6" s="187"/>
+      <c r="H6" s="183"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="183"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="183"/>
+      <c r="Q6" s="183"/>
+      <c r="R6" s="183"/>
+      <c r="S6" s="183"/>
+      <c r="T6" s="202"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="183" t="s">
+      <c r="A7" s="192" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="184"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="184"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="186" t="s">
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="201" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="184"/>
-      <c r="I7" s="184"/>
-      <c r="J7" s="184"/>
-      <c r="K7" s="184"/>
-      <c r="L7" s="184"/>
-      <c r="M7" s="184"/>
-      <c r="N7" s="184"/>
-      <c r="O7" s="184"/>
-      <c r="P7" s="184"/>
-      <c r="Q7" s="184"/>
-      <c r="R7" s="184"/>
-      <c r="S7" s="184"/>
-      <c r="T7" s="187"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="183"/>
+      <c r="M7" s="183"/>
+      <c r="N7" s="183"/>
+      <c r="O7" s="183"/>
+      <c r="P7" s="183"/>
+      <c r="Q7" s="183"/>
+      <c r="R7" s="183"/>
+      <c r="S7" s="183"/>
+      <c r="T7" s="202"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9998,37 +10362,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="183" t="s">
+      <c r="A15" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="185"/>
-      <c r="C15" s="196" t="s">
+      <c r="B15" s="184"/>
+      <c r="C15" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="185"/>
+      <c r="D15" s="184"/>
       <c r="E15" s="191" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="185"/>
+      <c r="F15" s="184"/>
       <c r="G15" s="191" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="184"/>
-      <c r="I15" s="185"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="184"/>
       <c r="J15" s="191" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="185"/>
+      <c r="K15" s="184"/>
       <c r="L15" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="184"/>
-      <c r="N15" s="185"/>
+      <c r="M15" s="183"/>
+      <c r="N15" s="184"/>
       <c r="O15" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="184"/>
-      <c r="Q15" s="185"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="184"/>
       <c r="R15" s="44" t="s">
         <v>56</v>
       </c>
@@ -10040,37 +10404,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="192">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="193" t="s">
+      <c r="B16" s="184"/>
+      <c r="C16" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="185"/>
-      <c r="E16" s="193" t="s">
+      <c r="D16" s="184"/>
+      <c r="E16" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="185"/>
-      <c r="G16" s="194" t="s">
+      <c r="F16" s="184"/>
+      <c r="G16" s="187" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="184"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="194" t="s">
+      <c r="H16" s="183"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="185"/>
-      <c r="L16" s="195" t="s">
+      <c r="K16" s="184"/>
+      <c r="L16" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="184"/>
-      <c r="N16" s="185"/>
-      <c r="O16" s="195" t="s">
+      <c r="M16" s="183"/>
+      <c r="N16" s="184"/>
+      <c r="O16" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="184"/>
-      <c r="Q16" s="185"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="184"/>
       <c r="R16" s="65">
         <v>45825</v>
       </c>
@@ -10088,37 +10452,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="192">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="185"/>
-      <c r="C17" s="193" t="s">
+      <c r="B17" s="184"/>
+      <c r="C17" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="185"/>
-      <c r="E17" s="193" t="s">
+      <c r="D17" s="184"/>
+      <c r="E17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="185"/>
-      <c r="G17" s="194" t="s">
+      <c r="F17" s="184"/>
+      <c r="G17" s="187" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="184"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="194" t="s">
+      <c r="H17" s="183"/>
+      <c r="I17" s="184"/>
+      <c r="J17" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="185"/>
-      <c r="L17" s="195" t="s">
+      <c r="K17" s="184"/>
+      <c r="L17" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M17" s="184"/>
-      <c r="N17" s="185"/>
-      <c r="O17" s="195" t="s">
+      <c r="M17" s="183"/>
+      <c r="N17" s="184"/>
+      <c r="O17" s="182" t="s">
         <v>98</v>
       </c>
-      <c r="P17" s="184"/>
-      <c r="Q17" s="185"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="184"/>
       <c r="R17" s="65">
         <v>45825</v>
       </c>
@@ -10136,37 +10500,37 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="192">
+      <c r="A18" s="185">
         <v>3</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="193" t="s">
+      <c r="B18" s="184"/>
+      <c r="C18" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="185"/>
-      <c r="E18" s="193" t="s">
+      <c r="D18" s="184"/>
+      <c r="E18" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="185"/>
-      <c r="G18" s="194" t="s">
+      <c r="F18" s="184"/>
+      <c r="G18" s="187" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="184"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="194" t="s">
+      <c r="H18" s="183"/>
+      <c r="I18" s="184"/>
+      <c r="J18" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="185"/>
-      <c r="L18" s="195" t="s">
+      <c r="K18" s="184"/>
+      <c r="L18" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M18" s="184"/>
-      <c r="N18" s="185"/>
-      <c r="O18" s="195" t="s">
+      <c r="M18" s="183"/>
+      <c r="N18" s="184"/>
+      <c r="O18" s="182" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="184"/>
-      <c r="Q18" s="185"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="184"/>
       <c r="R18" s="65">
         <v>45825</v>
       </c>
@@ -10184,37 +10548,37 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A19" s="192">
+      <c r="A19" s="185">
         <v>4</v>
       </c>
-      <c r="B19" s="185"/>
-      <c r="C19" s="193" t="s">
+      <c r="B19" s="184"/>
+      <c r="C19" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="185"/>
-      <c r="E19" s="193" t="s">
+      <c r="D19" s="184"/>
+      <c r="E19" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="185"/>
-      <c r="G19" s="194" t="s">
+      <c r="F19" s="184"/>
+      <c r="G19" s="187" t="s">
         <v>96</v>
       </c>
-      <c r="H19" s="184"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="194" t="s">
+      <c r="H19" s="183"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="185"/>
-      <c r="L19" s="195" t="s">
+      <c r="K19" s="184"/>
+      <c r="L19" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M19" s="184"/>
-      <c r="N19" s="185"/>
-      <c r="O19" s="195" t="s">
+      <c r="M19" s="183"/>
+      <c r="N19" s="184"/>
+      <c r="O19" s="182" t="s">
         <v>95</v>
       </c>
-      <c r="P19" s="184"/>
-      <c r="Q19" s="185"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="184"/>
       <c r="R19" s="65">
         <v>45825</v>
       </c>
@@ -10232,37 +10596,37 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A20" s="192">
+      <c r="A20" s="185">
         <v>5</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="193" t="s">
+      <c r="B20" s="184"/>
+      <c r="C20" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="185"/>
-      <c r="E20" s="193" t="s">
+      <c r="D20" s="184"/>
+      <c r="E20" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="185"/>
-      <c r="G20" s="194" t="s">
+      <c r="F20" s="184"/>
+      <c r="G20" s="187" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="184"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="194" t="s">
+      <c r="H20" s="183"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="185"/>
-      <c r="L20" s="195" t="s">
+      <c r="K20" s="184"/>
+      <c r="L20" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M20" s="184"/>
-      <c r="N20" s="185"/>
-      <c r="O20" s="195" t="s">
+      <c r="M20" s="183"/>
+      <c r="N20" s="184"/>
+      <c r="O20" s="182" t="s">
         <v>113</v>
       </c>
-      <c r="P20" s="184"/>
-      <c r="Q20" s="185"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="184"/>
       <c r="R20" s="65">
         <v>45825</v>
       </c>
@@ -10280,37 +10644,37 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A21" s="192">
+      <c r="A21" s="185">
         <v>6</v>
       </c>
-      <c r="B21" s="185"/>
-      <c r="C21" s="193" t="s">
+      <c r="B21" s="184"/>
+      <c r="C21" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="185"/>
-      <c r="E21" s="193" t="s">
+      <c r="D21" s="184"/>
+      <c r="E21" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="185"/>
-      <c r="G21" s="194" t="s">
+      <c r="F21" s="184"/>
+      <c r="G21" s="187" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="184"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="194" t="s">
+      <c r="H21" s="183"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K21" s="185"/>
-      <c r="L21" s="195" t="s">
+      <c r="K21" s="184"/>
+      <c r="L21" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M21" s="184"/>
-      <c r="N21" s="185"/>
-      <c r="O21" s="195" t="s">
+      <c r="M21" s="183"/>
+      <c r="N21" s="184"/>
+      <c r="O21" s="182" t="s">
         <v>101</v>
       </c>
-      <c r="P21" s="184"/>
-      <c r="Q21" s="185"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="184"/>
       <c r="R21" s="65">
         <v>45825</v>
       </c>
@@ -10328,33 +10692,33 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A22" s="192">
+      <c r="A22" s="185">
         <v>7</v>
       </c>
-      <c r="B22" s="185"/>
-      <c r="C22" s="193" t="s">
+      <c r="B22" s="184"/>
+      <c r="C22" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="185"/>
-      <c r="E22" s="193" t="s">
+      <c r="D22" s="184"/>
+      <c r="E22" s="186" t="s">
         <v>108</v>
       </c>
-      <c r="F22" s="185"/>
-      <c r="G22" s="194" t="s">
+      <c r="F22" s="184"/>
+      <c r="G22" s="187" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="184"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="194" t="s">
+      <c r="H22" s="183"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="187" t="s">
         <v>110</v>
       </c>
-      <c r="K22" s="185"/>
-      <c r="L22" s="197" t="s">
+      <c r="K22" s="184"/>
+      <c r="L22" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="M22" s="198"/>
-      <c r="N22" s="198"/>
-      <c r="O22" s="199" t="s">
+      <c r="M22" s="189"/>
+      <c r="N22" s="189"/>
+      <c r="O22" s="190" t="s">
         <v>112</v>
       </c>
       <c r="P22" s="67"/>
@@ -10376,23 +10740,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="192"/>
-      <c r="B23" s="185"/>
-      <c r="C23" s="193"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="193"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="194"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="194"/>
-      <c r="K23" s="185"/>
-      <c r="L23" s="195"/>
-      <c r="M23" s="184"/>
-      <c r="N23" s="185"/>
-      <c r="O23" s="195"/>
-      <c r="P23" s="184"/>
-      <c r="Q23" s="185"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="184"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="187"/>
+      <c r="H23" s="183"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="187"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="183"/>
+      <c r="N23" s="184"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="184"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -10404,23 +10768,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="192"/>
-      <c r="B24" s="185"/>
-      <c r="C24" s="193"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="193"/>
-      <c r="F24" s="185"/>
-      <c r="G24" s="194"/>
-      <c r="H24" s="184"/>
-      <c r="I24" s="185"/>
-      <c r="J24" s="194"/>
-      <c r="K24" s="185"/>
-      <c r="L24" s="195"/>
-      <c r="M24" s="184"/>
-      <c r="N24" s="185"/>
-      <c r="O24" s="195"/>
-      <c r="P24" s="184"/>
-      <c r="Q24" s="185"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="184"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="187"/>
+      <c r="H24" s="183"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="187"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="183"/>
+      <c r="N24" s="184"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="184"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -10432,23 +10796,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="192"/>
-      <c r="B25" s="185"/>
-      <c r="C25" s="193"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="193"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="194"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="194"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="195"/>
-      <c r="M25" s="184"/>
-      <c r="N25" s="185"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="184"/>
-      <c r="Q25" s="185"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="184"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="184"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="187"/>
+      <c r="H25" s="183"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="187"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="183"/>
+      <c r="N25" s="184"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="184"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -10460,23 +10824,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="192"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="193"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="193"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="194"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="194"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="195"/>
-      <c r="M26" s="184"/>
-      <c r="N26" s="185"/>
-      <c r="O26" s="195"/>
-      <c r="P26" s="184"/>
-      <c r="Q26" s="185"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="184"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="184"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="187"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="183"/>
+      <c r="N26" s="184"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="184"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -10488,23 +10852,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="192"/>
-      <c r="B27" s="185"/>
-      <c r="C27" s="193"/>
-      <c r="D27" s="185"/>
-      <c r="E27" s="193"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="194"/>
-      <c r="H27" s="184"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="194"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="195"/>
-      <c r="M27" s="184"/>
-      <c r="N27" s="185"/>
-      <c r="O27" s="195"/>
-      <c r="P27" s="184"/>
-      <c r="Q27" s="185"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="184"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="187"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="184"/>
+      <c r="J27" s="187"/>
+      <c r="K27" s="184"/>
+      <c r="L27" s="182"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="184"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="184"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -10516,23 +10880,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="192"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="193"/>
-      <c r="D28" s="185"/>
-      <c r="E28" s="193"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="194"/>
-      <c r="H28" s="184"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="194"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="195"/>
-      <c r="M28" s="184"/>
-      <c r="N28" s="185"/>
-      <c r="O28" s="195"/>
-      <c r="P28" s="184"/>
-      <c r="Q28" s="185"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="184"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="184"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="187"/>
+      <c r="H28" s="183"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="187"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="183"/>
+      <c r="N28" s="184"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="184"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -10544,23 +10908,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="192"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="193"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="193"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="184"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="194"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="195"/>
-      <c r="M29" s="184"/>
-      <c r="N29" s="185"/>
-      <c r="O29" s="195"/>
-      <c r="P29" s="184"/>
-      <c r="Q29" s="185"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="184"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="187"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="187"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="184"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -10572,23 +10936,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="192"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="193"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="193"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="194"/>
-      <c r="H30" s="184"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="194"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="195"/>
-      <c r="M30" s="184"/>
-      <c r="N30" s="185"/>
-      <c r="O30" s="195"/>
-      <c r="P30" s="184"/>
-      <c r="Q30" s="185"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="184"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="184"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="184"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="183"/>
+      <c r="I30" s="184"/>
+      <c r="J30" s="187"/>
+      <c r="K30" s="184"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="183"/>
+      <c r="N30" s="184"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="183"/>
+      <c r="Q30" s="184"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -10600,23 +10964,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="203"/>
-      <c r="B31" s="202"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="202"/>
-      <c r="G31" s="205"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="205"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="200"/>
-      <c r="M31" s="201"/>
-      <c r="N31" s="202"/>
-      <c r="O31" s="200"/>
-      <c r="P31" s="201"/>
-      <c r="Q31" s="202"/>
+      <c r="A31" s="179"/>
+      <c r="B31" s="178"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="178"/>
+      <c r="E31" s="180"/>
+      <c r="F31" s="178"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="176"/>
+      <c r="M31" s="177"/>
+      <c r="N31" s="178"/>
+      <c r="O31" s="176"/>
+      <c r="P31" s="177"/>
+      <c r="Q31" s="178"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11614,6 +11978,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -11635,123 +12114,8 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <hyperlinks>
     <hyperlink ref="L22" r:id="rId1" xr:uid="{70F16E29-4C19-40D6-A6FE-AC67A8668308}"/>
   </hyperlinks>
@@ -11775,72 +12139,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="226" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="216" t="s">
+      <c r="B1" s="226"/>
+      <c r="C1" s="227" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="219" t="s">
+      <c r="D1" s="228"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="221"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="232"/>
       <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="230" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="221"/>
+      <c r="P1" s="232"/>
       <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="219" t="s">
+      <c r="R1" s="230" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="221"/>
+      <c r="S1" s="232"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="215"/>
-      <c r="B2" s="215"/>
-      <c r="C2" s="216" t="s">
+      <c r="A2" s="226"/>
+      <c r="B2" s="226"/>
+      <c r="C2" s="227" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="217"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="219" t="s">
+      <c r="D2" s="228"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="230" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="220"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="220"/>
-      <c r="J2" s="220"/>
-      <c r="K2" s="220"/>
-      <c r="L2" s="220"/>
-      <c r="M2" s="221"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="M2" s="232"/>
       <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="222">
+      <c r="O2" s="233">
         <v>45818</v>
       </c>
-      <c r="P2" s="223"/>
+      <c r="P2" s="234"/>
       <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="224" t="s">
+      <c r="R2" s="235" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="225"/>
+      <c r="S2" s="236"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11870,33 +12234,33 @@
       <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="217" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="206" t="s">
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="219"/>
+      <c r="H4" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
-      <c r="M4" s="208"/>
-      <c r="N4" s="206" t="s">
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="217" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="207"/>
-      <c r="P4" s="208"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="219"/>
       <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="206" t="s">
+      <c r="R4" s="217" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="208"/>
+      <c r="S4" s="219"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59">
@@ -11905,1209 +12269,1021 @@
       <c r="B5" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="220" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209" t="s">
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="220" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="M5" s="209"/>
-      <c r="N5" s="210" t="s">
+      <c r="I5" s="220"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="M5" s="220"/>
+      <c r="N5" s="221" t="s">
         <v>106</v>
       </c>
-      <c r="O5" s="211"/>
-      <c r="P5" s="212"/>
+      <c r="O5" s="222"/>
+      <c r="P5" s="223"/>
       <c r="Q5" s="64">
         <v>45818</v>
       </c>
-      <c r="R5" s="213"/>
-      <c r="S5" s="214"/>
+      <c r="R5" s="224"/>
+      <c r="S5" s="225"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="226"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="226"/>
-      <c r="M6" s="226"/>
-      <c r="N6" s="231"/>
-      <c r="O6" s="232"/>
-      <c r="P6" s="233"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="206"/>
+      <c r="N6" s="214"/>
+      <c r="O6" s="215"/>
+      <c r="P6" s="216"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="230"/>
-      <c r="S6" s="230"/>
+      <c r="R6" s="213"/>
+      <c r="S6" s="213"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="227"/>
-      <c r="O7" s="228"/>
-      <c r="P7" s="229"/>
+      <c r="C7" s="206"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
+      <c r="J7" s="206"/>
+      <c r="K7" s="206"/>
+      <c r="L7" s="206"/>
+      <c r="M7" s="206"/>
+      <c r="N7" s="210"/>
+      <c r="O7" s="211"/>
+      <c r="P7" s="212"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="230"/>
-      <c r="S7" s="230"/>
+      <c r="R7" s="213"/>
+      <c r="S7" s="213"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="226"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226"/>
-      <c r="M8" s="226"/>
-      <c r="N8" s="227"/>
-      <c r="O8" s="228"/>
-      <c r="P8" s="229"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
+      <c r="J8" s="206"/>
+      <c r="K8" s="206"/>
+      <c r="L8" s="206"/>
+      <c r="M8" s="206"/>
+      <c r="N8" s="210"/>
+      <c r="O8" s="211"/>
+      <c r="P8" s="212"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="230"/>
-      <c r="S8" s="230"/>
+      <c r="R8" s="213"/>
+      <c r="S8" s="213"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="226"/>
-      <c r="D9" s="226"/>
-      <c r="E9" s="226"/>
-      <c r="F9" s="226"/>
-      <c r="G9" s="226"/>
-      <c r="H9" s="226"/>
-      <c r="I9" s="226"/>
-      <c r="J9" s="226"/>
-      <c r="K9" s="226"/>
-      <c r="L9" s="226"/>
-      <c r="M9" s="226"/>
-      <c r="N9" s="227"/>
-      <c r="O9" s="228"/>
-      <c r="P9" s="229"/>
+      <c r="C9" s="206"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
+      <c r="J9" s="206"/>
+      <c r="K9" s="206"/>
+      <c r="L9" s="206"/>
+      <c r="M9" s="206"/>
+      <c r="N9" s="210"/>
+      <c r="O9" s="211"/>
+      <c r="P9" s="212"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="230"/>
-      <c r="S9" s="230"/>
+      <c r="R9" s="213"/>
+      <c r="S9" s="213"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="226"/>
-      <c r="D10" s="226"/>
-      <c r="E10" s="226"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="226"/>
-      <c r="H10" s="234"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="227"/>
-      <c r="O10" s="228"/>
-      <c r="P10" s="229"/>
+      <c r="C10" s="206"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="208"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="208"/>
+      <c r="L10" s="208"/>
+      <c r="M10" s="209"/>
+      <c r="N10" s="210"/>
+      <c r="O10" s="211"/>
+      <c r="P10" s="212"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="230"/>
-      <c r="S10" s="230"/>
+      <c r="R10" s="213"/>
+      <c r="S10" s="213"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="226"/>
-      <c r="D11" s="226"/>
-      <c r="E11" s="226"/>
-      <c r="F11" s="226"/>
-      <c r="G11" s="226"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="235"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="227"/>
-      <c r="O11" s="228"/>
-      <c r="P11" s="229"/>
+      <c r="C11" s="206"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="208"/>
+      <c r="J11" s="208"/>
+      <c r="K11" s="208"/>
+      <c r="L11" s="208"/>
+      <c r="M11" s="209"/>
+      <c r="N11" s="210"/>
+      <c r="O11" s="211"/>
+      <c r="P11" s="212"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="230"/>
-      <c r="S11" s="230"/>
+      <c r="R11" s="213"/>
+      <c r="S11" s="213"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="226"/>
-      <c r="D12" s="226"/>
-      <c r="E12" s="226"/>
-      <c r="F12" s="226"/>
-      <c r="G12" s="226"/>
-      <c r="H12" s="234"/>
-      <c r="I12" s="235"/>
-      <c r="J12" s="235"/>
-      <c r="K12" s="235"/>
-      <c r="L12" s="235"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="227"/>
-      <c r="O12" s="228"/>
-      <c r="P12" s="229"/>
+      <c r="C12" s="206"/>
+      <c r="D12" s="206"/>
+      <c r="E12" s="206"/>
+      <c r="F12" s="206"/>
+      <c r="G12" s="206"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="208"/>
+      <c r="L12" s="208"/>
+      <c r="M12" s="209"/>
+      <c r="N12" s="210"/>
+      <c r="O12" s="211"/>
+      <c r="P12" s="212"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="230"/>
-      <c r="S12" s="230"/>
+      <c r="R12" s="213"/>
+      <c r="S12" s="213"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="226"/>
-      <c r="D13" s="226"/>
-      <c r="E13" s="226"/>
-      <c r="F13" s="226"/>
-      <c r="G13" s="226"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
-      <c r="M13" s="236"/>
-      <c r="N13" s="227"/>
-      <c r="O13" s="228"/>
-      <c r="P13" s="229"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
+      <c r="F13" s="206"/>
+      <c r="G13" s="206"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="208"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="208"/>
+      <c r="L13" s="208"/>
+      <c r="M13" s="209"/>
+      <c r="N13" s="210"/>
+      <c r="O13" s="211"/>
+      <c r="P13" s="212"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="230"/>
-      <c r="S13" s="230"/>
+      <c r="R13" s="213"/>
+      <c r="S13" s="213"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="226"/>
-      <c r="D14" s="226"/>
-      <c r="E14" s="226"/>
-      <c r="F14" s="226"/>
-      <c r="G14" s="226"/>
-      <c r="H14" s="234"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
-      <c r="L14" s="235"/>
-      <c r="M14" s="236"/>
-      <c r="N14" s="227"/>
-      <c r="O14" s="228"/>
-      <c r="P14" s="229"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
+      <c r="M14" s="209"/>
+      <c r="N14" s="210"/>
+      <c r="O14" s="211"/>
+      <c r="P14" s="212"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="230"/>
-      <c r="S14" s="230"/>
+      <c r="R14" s="213"/>
+      <c r="S14" s="213"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="226"/>
-      <c r="D15" s="226"/>
-      <c r="E15" s="226"/>
-      <c r="F15" s="226"/>
-      <c r="G15" s="226"/>
-      <c r="H15" s="234"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="235"/>
-      <c r="L15" s="235"/>
-      <c r="M15" s="236"/>
-      <c r="N15" s="227"/>
-      <c r="O15" s="228"/>
-      <c r="P15" s="229"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="207"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="208"/>
+      <c r="K15" s="208"/>
+      <c r="L15" s="208"/>
+      <c r="M15" s="209"/>
+      <c r="N15" s="210"/>
+      <c r="O15" s="211"/>
+      <c r="P15" s="212"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="230"/>
-      <c r="S15" s="230"/>
+      <c r="R15" s="213"/>
+      <c r="S15" s="213"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="226"/>
-      <c r="D16" s="226"/>
-      <c r="E16" s="226"/>
-      <c r="F16" s="226"/>
-      <c r="G16" s="226"/>
-      <c r="H16" s="234"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="235"/>
-      <c r="L16" s="235"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="227"/>
-      <c r="O16" s="228"/>
-      <c r="P16" s="229"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+      <c r="F16" s="206"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="208"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="210"/>
+      <c r="O16" s="211"/>
+      <c r="P16" s="212"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="230"/>
-      <c r="S16" s="230"/>
+      <c r="R16" s="213"/>
+      <c r="S16" s="213"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="226"/>
-      <c r="D17" s="226"/>
-      <c r="E17" s="226"/>
-      <c r="F17" s="226"/>
-      <c r="G17" s="226"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="235"/>
-      <c r="L17" s="235"/>
-      <c r="M17" s="236"/>
-      <c r="N17" s="227"/>
-      <c r="O17" s="228"/>
-      <c r="P17" s="229"/>
+      <c r="C17" s="206"/>
+      <c r="D17" s="206"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="206"/>
+      <c r="G17" s="206"/>
+      <c r="H17" s="207"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="208"/>
+      <c r="M17" s="209"/>
+      <c r="N17" s="210"/>
+      <c r="O17" s="211"/>
+      <c r="P17" s="212"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="230"/>
-      <c r="S17" s="230"/>
+      <c r="R17" s="213"/>
+      <c r="S17" s="213"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="226"/>
-      <c r="D18" s="226"/>
-      <c r="E18" s="226"/>
-      <c r="F18" s="226"/>
-      <c r="G18" s="226"/>
-      <c r="H18" s="234"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
-      <c r="M18" s="236"/>
-      <c r="N18" s="227"/>
-      <c r="O18" s="228"/>
-      <c r="P18" s="229"/>
+      <c r="C18" s="206"/>
+      <c r="D18" s="206"/>
+      <c r="E18" s="206"/>
+      <c r="F18" s="206"/>
+      <c r="G18" s="206"/>
+      <c r="H18" s="207"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="208"/>
+      <c r="L18" s="208"/>
+      <c r="M18" s="209"/>
+      <c r="N18" s="210"/>
+      <c r="O18" s="211"/>
+      <c r="P18" s="212"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="230"/>
-      <c r="S18" s="230"/>
+      <c r="R18" s="213"/>
+      <c r="S18" s="213"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="226"/>
-      <c r="D19" s="226"/>
-      <c r="E19" s="226"/>
-      <c r="F19" s="226"/>
-      <c r="G19" s="226"/>
-      <c r="H19" s="234"/>
-      <c r="I19" s="235"/>
-      <c r="J19" s="235"/>
-      <c r="K19" s="235"/>
-      <c r="L19" s="235"/>
-      <c r="M19" s="236"/>
-      <c r="N19" s="227"/>
-      <c r="O19" s="228"/>
-      <c r="P19" s="229"/>
+      <c r="C19" s="206"/>
+      <c r="D19" s="206"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="206"/>
+      <c r="G19" s="206"/>
+      <c r="H19" s="207"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="208"/>
+      <c r="L19" s="208"/>
+      <c r="M19" s="209"/>
+      <c r="N19" s="210"/>
+      <c r="O19" s="211"/>
+      <c r="P19" s="212"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="230"/>
-      <c r="S19" s="230"/>
+      <c r="R19" s="213"/>
+      <c r="S19" s="213"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="226"/>
-      <c r="D20" s="226"/>
-      <c r="E20" s="226"/>
-      <c r="F20" s="226"/>
-      <c r="G20" s="226"/>
-      <c r="H20" s="234"/>
-      <c r="I20" s="235"/>
-      <c r="J20" s="235"/>
-      <c r="K20" s="235"/>
-      <c r="L20" s="235"/>
-      <c r="M20" s="236"/>
-      <c r="N20" s="227"/>
-      <c r="O20" s="228"/>
-      <c r="P20" s="229"/>
+      <c r="C20" s="206"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="206"/>
+      <c r="F20" s="206"/>
+      <c r="G20" s="206"/>
+      <c r="H20" s="207"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
+      <c r="L20" s="208"/>
+      <c r="M20" s="209"/>
+      <c r="N20" s="210"/>
+      <c r="O20" s="211"/>
+      <c r="P20" s="212"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="230"/>
-      <c r="S20" s="230"/>
+      <c r="R20" s="213"/>
+      <c r="S20" s="213"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="226"/>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="234"/>
-      <c r="I21" s="235"/>
-      <c r="J21" s="235"/>
-      <c r="K21" s="235"/>
-      <c r="L21" s="235"/>
-      <c r="M21" s="236"/>
-      <c r="N21" s="227"/>
-      <c r="O21" s="228"/>
-      <c r="P21" s="229"/>
+      <c r="C21" s="206"/>
+      <c r="D21" s="206"/>
+      <c r="E21" s="206"/>
+      <c r="F21" s="206"/>
+      <c r="G21" s="206"/>
+      <c r="H21" s="207"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="208"/>
+      <c r="L21" s="208"/>
+      <c r="M21" s="209"/>
+      <c r="N21" s="210"/>
+      <c r="O21" s="211"/>
+      <c r="P21" s="212"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="230"/>
-      <c r="S21" s="230"/>
+      <c r="R21" s="213"/>
+      <c r="S21" s="213"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="226"/>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="234"/>
-      <c r="I22" s="235"/>
-      <c r="J22" s="235"/>
-      <c r="K22" s="235"/>
-      <c r="L22" s="235"/>
-      <c r="M22" s="236"/>
-      <c r="N22" s="227"/>
-      <c r="O22" s="228"/>
-      <c r="P22" s="229"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="207"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="208"/>
+      <c r="K22" s="208"/>
+      <c r="L22" s="208"/>
+      <c r="M22" s="209"/>
+      <c r="N22" s="210"/>
+      <c r="O22" s="211"/>
+      <c r="P22" s="212"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="230"/>
-      <c r="S22" s="230"/>
+      <c r="R22" s="213"/>
+      <c r="S22" s="213"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="226"/>
-      <c r="D23" s="226"/>
-      <c r="E23" s="226"/>
-      <c r="F23" s="226"/>
-      <c r="G23" s="226"/>
-      <c r="H23" s="234"/>
-      <c r="I23" s="235"/>
-      <c r="J23" s="235"/>
-      <c r="K23" s="235"/>
-      <c r="L23" s="235"/>
-      <c r="M23" s="236"/>
-      <c r="N23" s="227"/>
-      <c r="O23" s="228"/>
-      <c r="P23" s="229"/>
+      <c r="C23" s="206"/>
+      <c r="D23" s="206"/>
+      <c r="E23" s="206"/>
+      <c r="F23" s="206"/>
+      <c r="G23" s="206"/>
+      <c r="H23" s="207"/>
+      <c r="I23" s="208"/>
+      <c r="J23" s="208"/>
+      <c r="K23" s="208"/>
+      <c r="L23" s="208"/>
+      <c r="M23" s="209"/>
+      <c r="N23" s="210"/>
+      <c r="O23" s="211"/>
+      <c r="P23" s="212"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="230"/>
-      <c r="S23" s="230"/>
+      <c r="R23" s="213"/>
+      <c r="S23" s="213"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="226"/>
-      <c r="D24" s="226"/>
-      <c r="E24" s="226"/>
-      <c r="F24" s="226"/>
-      <c r="G24" s="226"/>
-      <c r="H24" s="234"/>
-      <c r="I24" s="235"/>
-      <c r="J24" s="235"/>
-      <c r="K24" s="235"/>
-      <c r="L24" s="235"/>
-      <c r="M24" s="236"/>
-      <c r="N24" s="227"/>
-      <c r="O24" s="228"/>
-      <c r="P24" s="229"/>
+      <c r="C24" s="206"/>
+      <c r="D24" s="206"/>
+      <c r="E24" s="206"/>
+      <c r="F24" s="206"/>
+      <c r="G24" s="206"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="208"/>
+      <c r="J24" s="208"/>
+      <c r="K24" s="208"/>
+      <c r="L24" s="208"/>
+      <c r="M24" s="209"/>
+      <c r="N24" s="210"/>
+      <c r="O24" s="211"/>
+      <c r="P24" s="212"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="230"/>
-      <c r="S24" s="230"/>
+      <c r="R24" s="213"/>
+      <c r="S24" s="213"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="226"/>
-      <c r="D25" s="226"/>
-      <c r="E25" s="226"/>
-      <c r="F25" s="226"/>
-      <c r="G25" s="226"/>
-      <c r="H25" s="234"/>
-      <c r="I25" s="235"/>
-      <c r="J25" s="235"/>
-      <c r="K25" s="235"/>
-      <c r="L25" s="235"/>
-      <c r="M25" s="236"/>
-      <c r="N25" s="227"/>
-      <c r="O25" s="228"/>
-      <c r="P25" s="229"/>
+      <c r="C25" s="206"/>
+      <c r="D25" s="206"/>
+      <c r="E25" s="206"/>
+      <c r="F25" s="206"/>
+      <c r="G25" s="206"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="208"/>
+      <c r="J25" s="208"/>
+      <c r="K25" s="208"/>
+      <c r="L25" s="208"/>
+      <c r="M25" s="209"/>
+      <c r="N25" s="210"/>
+      <c r="O25" s="211"/>
+      <c r="P25" s="212"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="230"/>
-      <c r="S25" s="230"/>
+      <c r="R25" s="213"/>
+      <c r="S25" s="213"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="226"/>
-      <c r="D26" s="226"/>
-      <c r="E26" s="226"/>
-      <c r="F26" s="226"/>
-      <c r="G26" s="226"/>
-      <c r="H26" s="234"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
-      <c r="M26" s="236"/>
-      <c r="N26" s="227"/>
-      <c r="O26" s="228"/>
-      <c r="P26" s="229"/>
+      <c r="C26" s="206"/>
+      <c r="D26" s="206"/>
+      <c r="E26" s="206"/>
+      <c r="F26" s="206"/>
+      <c r="G26" s="206"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
+      <c r="M26" s="209"/>
+      <c r="N26" s="210"/>
+      <c r="O26" s="211"/>
+      <c r="P26" s="212"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="230"/>
-      <c r="S26" s="230"/>
+      <c r="R26" s="213"/>
+      <c r="S26" s="213"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="226"/>
-      <c r="D27" s="226"/>
-      <c r="E27" s="226"/>
-      <c r="F27" s="226"/>
-      <c r="G27" s="226"/>
-      <c r="H27" s="234"/>
-      <c r="I27" s="235"/>
-      <c r="J27" s="235"/>
-      <c r="K27" s="235"/>
-      <c r="L27" s="235"/>
-      <c r="M27" s="236"/>
-      <c r="N27" s="227"/>
-      <c r="O27" s="228"/>
-      <c r="P27" s="229"/>
+      <c r="C27" s="206"/>
+      <c r="D27" s="206"/>
+      <c r="E27" s="206"/>
+      <c r="F27" s="206"/>
+      <c r="G27" s="206"/>
+      <c r="H27" s="207"/>
+      <c r="I27" s="208"/>
+      <c r="J27" s="208"/>
+      <c r="K27" s="208"/>
+      <c r="L27" s="208"/>
+      <c r="M27" s="209"/>
+      <c r="N27" s="210"/>
+      <c r="O27" s="211"/>
+      <c r="P27" s="212"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="230"/>
-      <c r="S27" s="230"/>
+      <c r="R27" s="213"/>
+      <c r="S27" s="213"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="234"/>
-      <c r="I28" s="235"/>
-      <c r="J28" s="235"/>
-      <c r="K28" s="235"/>
-      <c r="L28" s="235"/>
-      <c r="M28" s="236"/>
-      <c r="N28" s="227"/>
-      <c r="O28" s="228"/>
-      <c r="P28" s="229"/>
+      <c r="C28" s="206"/>
+      <c r="D28" s="206"/>
+      <c r="E28" s="206"/>
+      <c r="F28" s="206"/>
+      <c r="G28" s="206"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="208"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="208"/>
+      <c r="L28" s="208"/>
+      <c r="M28" s="209"/>
+      <c r="N28" s="210"/>
+      <c r="O28" s="211"/>
+      <c r="P28" s="212"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="230"/>
-      <c r="S28" s="230"/>
+      <c r="R28" s="213"/>
+      <c r="S28" s="213"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="226"/>
-      <c r="D29" s="226"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="226"/>
-      <c r="G29" s="226"/>
-      <c r="H29" s="234"/>
-      <c r="I29" s="235"/>
-      <c r="J29" s="235"/>
-      <c r="K29" s="235"/>
-      <c r="L29" s="235"/>
-      <c r="M29" s="236"/>
-      <c r="N29" s="227"/>
-      <c r="O29" s="228"/>
-      <c r="P29" s="229"/>
+      <c r="C29" s="206"/>
+      <c r="D29" s="206"/>
+      <c r="E29" s="206"/>
+      <c r="F29" s="206"/>
+      <c r="G29" s="206"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="208"/>
+      <c r="J29" s="208"/>
+      <c r="K29" s="208"/>
+      <c r="L29" s="208"/>
+      <c r="M29" s="209"/>
+      <c r="N29" s="210"/>
+      <c r="O29" s="211"/>
+      <c r="P29" s="212"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="230"/>
-      <c r="S29" s="230"/>
+      <c r="R29" s="213"/>
+      <c r="S29" s="213"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="226"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="226"/>
-      <c r="F30" s="226"/>
-      <c r="G30" s="226"/>
-      <c r="H30" s="234"/>
-      <c r="I30" s="235"/>
-      <c r="J30" s="235"/>
-      <c r="K30" s="235"/>
-      <c r="L30" s="235"/>
-      <c r="M30" s="236"/>
-      <c r="N30" s="227"/>
-      <c r="O30" s="228"/>
-      <c r="P30" s="229"/>
+      <c r="C30" s="206"/>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="206"/>
+      <c r="G30" s="206"/>
+      <c r="H30" s="207"/>
+      <c r="I30" s="208"/>
+      <c r="J30" s="208"/>
+      <c r="K30" s="208"/>
+      <c r="L30" s="208"/>
+      <c r="M30" s="209"/>
+      <c r="N30" s="210"/>
+      <c r="O30" s="211"/>
+      <c r="P30" s="212"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="230"/>
-      <c r="S30" s="230"/>
+      <c r="R30" s="213"/>
+      <c r="S30" s="213"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="226"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="234"/>
-      <c r="I31" s="235"/>
-      <c r="J31" s="235"/>
-      <c r="K31" s="235"/>
-      <c r="L31" s="235"/>
-      <c r="M31" s="236"/>
-      <c r="N31" s="227"/>
-      <c r="O31" s="228"/>
-      <c r="P31" s="229"/>
+      <c r="C31" s="206"/>
+      <c r="D31" s="206"/>
+      <c r="E31" s="206"/>
+      <c r="F31" s="206"/>
+      <c r="G31" s="206"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="208"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="209"/>
+      <c r="N31" s="210"/>
+      <c r="O31" s="211"/>
+      <c r="P31" s="212"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="230"/>
-      <c r="S31" s="230"/>
+      <c r="R31" s="213"/>
+      <c r="S31" s="213"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="226"/>
-      <c r="D32" s="226"/>
-      <c r="E32" s="226"/>
-      <c r="F32" s="226"/>
-      <c r="G32" s="226"/>
-      <c r="H32" s="234"/>
-      <c r="I32" s="235"/>
-      <c r="J32" s="235"/>
-      <c r="K32" s="235"/>
-      <c r="L32" s="235"/>
-      <c r="M32" s="236"/>
-      <c r="N32" s="227"/>
-      <c r="O32" s="228"/>
-      <c r="P32" s="229"/>
+      <c r="C32" s="206"/>
+      <c r="D32" s="206"/>
+      <c r="E32" s="206"/>
+      <c r="F32" s="206"/>
+      <c r="G32" s="206"/>
+      <c r="H32" s="207"/>
+      <c r="I32" s="208"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="208"/>
+      <c r="L32" s="208"/>
+      <c r="M32" s="209"/>
+      <c r="N32" s="210"/>
+      <c r="O32" s="211"/>
+      <c r="P32" s="212"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="230"/>
-      <c r="S32" s="230"/>
+      <c r="R32" s="213"/>
+      <c r="S32" s="213"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="226"/>
-      <c r="D33" s="226"/>
-      <c r="E33" s="226"/>
-      <c r="F33" s="226"/>
-      <c r="G33" s="226"/>
-      <c r="H33" s="234"/>
-      <c r="I33" s="235"/>
-      <c r="J33" s="235"/>
-      <c r="K33" s="235"/>
-      <c r="L33" s="235"/>
-      <c r="M33" s="236"/>
-      <c r="N33" s="227"/>
-      <c r="O33" s="228"/>
-      <c r="P33" s="229"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="206"/>
+      <c r="E33" s="206"/>
+      <c r="F33" s="206"/>
+      <c r="G33" s="206"/>
+      <c r="H33" s="207"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="209"/>
+      <c r="N33" s="210"/>
+      <c r="O33" s="211"/>
+      <c r="P33" s="212"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="230"/>
-      <c r="S33" s="230"/>
+      <c r="R33" s="213"/>
+      <c r="S33" s="213"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="226"/>
-      <c r="D34" s="226"/>
-      <c r="E34" s="226"/>
-      <c r="F34" s="226"/>
-      <c r="G34" s="226"/>
-      <c r="H34" s="234"/>
-      <c r="I34" s="235"/>
-      <c r="J34" s="235"/>
-      <c r="K34" s="235"/>
-      <c r="L34" s="235"/>
-      <c r="M34" s="236"/>
-      <c r="N34" s="227"/>
-      <c r="O34" s="228"/>
-      <c r="P34" s="229"/>
+      <c r="C34" s="206"/>
+      <c r="D34" s="206"/>
+      <c r="E34" s="206"/>
+      <c r="F34" s="206"/>
+      <c r="G34" s="206"/>
+      <c r="H34" s="207"/>
+      <c r="I34" s="208"/>
+      <c r="J34" s="208"/>
+      <c r="K34" s="208"/>
+      <c r="L34" s="208"/>
+      <c r="M34" s="209"/>
+      <c r="N34" s="210"/>
+      <c r="O34" s="211"/>
+      <c r="P34" s="212"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="230"/>
-      <c r="S34" s="230"/>
+      <c r="R34" s="213"/>
+      <c r="S34" s="213"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="226"/>
-      <c r="D35" s="226"/>
-      <c r="E35" s="226"/>
-      <c r="F35" s="226"/>
-      <c r="G35" s="226"/>
-      <c r="H35" s="234"/>
-      <c r="I35" s="235"/>
-      <c r="J35" s="235"/>
-      <c r="K35" s="235"/>
-      <c r="L35" s="235"/>
-      <c r="M35" s="236"/>
-      <c r="N35" s="227"/>
-      <c r="O35" s="228"/>
-      <c r="P35" s="229"/>
+      <c r="C35" s="206"/>
+      <c r="D35" s="206"/>
+      <c r="E35" s="206"/>
+      <c r="F35" s="206"/>
+      <c r="G35" s="206"/>
+      <c r="H35" s="207"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="208"/>
+      <c r="K35" s="208"/>
+      <c r="L35" s="208"/>
+      <c r="M35" s="209"/>
+      <c r="N35" s="210"/>
+      <c r="O35" s="211"/>
+      <c r="P35" s="212"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="230"/>
-      <c r="S35" s="230"/>
+      <c r="R35" s="213"/>
+      <c r="S35" s="213"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="226"/>
-      <c r="D36" s="226"/>
-      <c r="E36" s="226"/>
-      <c r="F36" s="226"/>
-      <c r="G36" s="226"/>
-      <c r="H36" s="234"/>
-      <c r="I36" s="235"/>
-      <c r="J36" s="235"/>
-      <c r="K36" s="235"/>
-      <c r="L36" s="235"/>
-      <c r="M36" s="236"/>
-      <c r="N36" s="227"/>
-      <c r="O36" s="228"/>
-      <c r="P36" s="229"/>
+      <c r="C36" s="206"/>
+      <c r="D36" s="206"/>
+      <c r="E36" s="206"/>
+      <c r="F36" s="206"/>
+      <c r="G36" s="206"/>
+      <c r="H36" s="207"/>
+      <c r="I36" s="208"/>
+      <c r="J36" s="208"/>
+      <c r="K36" s="208"/>
+      <c r="L36" s="208"/>
+      <c r="M36" s="209"/>
+      <c r="N36" s="210"/>
+      <c r="O36" s="211"/>
+      <c r="P36" s="212"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="230"/>
-      <c r="S36" s="230"/>
+      <c r="R36" s="213"/>
+      <c r="S36" s="213"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="226"/>
-      <c r="D37" s="226"/>
-      <c r="E37" s="226"/>
-      <c r="F37" s="226"/>
-      <c r="G37" s="226"/>
-      <c r="H37" s="234"/>
-      <c r="I37" s="235"/>
-      <c r="J37" s="235"/>
-      <c r="K37" s="235"/>
-      <c r="L37" s="235"/>
-      <c r="M37" s="236"/>
-      <c r="N37" s="227"/>
-      <c r="O37" s="228"/>
-      <c r="P37" s="229"/>
+      <c r="C37" s="206"/>
+      <c r="D37" s="206"/>
+      <c r="E37" s="206"/>
+      <c r="F37" s="206"/>
+      <c r="G37" s="206"/>
+      <c r="H37" s="207"/>
+      <c r="I37" s="208"/>
+      <c r="J37" s="208"/>
+      <c r="K37" s="208"/>
+      <c r="L37" s="208"/>
+      <c r="M37" s="209"/>
+      <c r="N37" s="210"/>
+      <c r="O37" s="211"/>
+      <c r="P37" s="212"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="230"/>
-      <c r="S37" s="230"/>
+      <c r="R37" s="213"/>
+      <c r="S37" s="213"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="226"/>
-      <c r="D38" s="226"/>
-      <c r="E38" s="226"/>
-      <c r="F38" s="226"/>
-      <c r="G38" s="226"/>
-      <c r="H38" s="234"/>
-      <c r="I38" s="235"/>
-      <c r="J38" s="235"/>
-      <c r="K38" s="235"/>
-      <c r="L38" s="235"/>
-      <c r="M38" s="236"/>
-      <c r="N38" s="227"/>
-      <c r="O38" s="228"/>
-      <c r="P38" s="229"/>
+      <c r="C38" s="206"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="206"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="207"/>
+      <c r="I38" s="208"/>
+      <c r="J38" s="208"/>
+      <c r="K38" s="208"/>
+      <c r="L38" s="208"/>
+      <c r="M38" s="209"/>
+      <c r="N38" s="210"/>
+      <c r="O38" s="211"/>
+      <c r="P38" s="212"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="230"/>
-      <c r="S38" s="230"/>
+      <c r="R38" s="213"/>
+      <c r="S38" s="213"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="226"/>
-      <c r="D39" s="226"/>
-      <c r="E39" s="226"/>
-      <c r="F39" s="226"/>
-      <c r="G39" s="226"/>
-      <c r="H39" s="234"/>
-      <c r="I39" s="235"/>
-      <c r="J39" s="235"/>
-      <c r="K39" s="235"/>
-      <c r="L39" s="235"/>
-      <c r="M39" s="236"/>
-      <c r="N39" s="227"/>
-      <c r="O39" s="228"/>
-      <c r="P39" s="229"/>
+      <c r="C39" s="206"/>
+      <c r="D39" s="206"/>
+      <c r="E39" s="206"/>
+      <c r="F39" s="206"/>
+      <c r="G39" s="206"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="209"/>
+      <c r="N39" s="210"/>
+      <c r="O39" s="211"/>
+      <c r="P39" s="212"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="230"/>
-      <c r="S39" s="230"/>
+      <c r="R39" s="213"/>
+      <c r="S39" s="213"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="226"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="235"/>
-      <c r="J40" s="235"/>
-      <c r="K40" s="235"/>
-      <c r="L40" s="235"/>
-      <c r="M40" s="236"/>
-      <c r="N40" s="227"/>
-      <c r="O40" s="228"/>
-      <c r="P40" s="229"/>
+      <c r="C40" s="206"/>
+      <c r="D40" s="206"/>
+      <c r="E40" s="206"/>
+      <c r="F40" s="206"/>
+      <c r="G40" s="206"/>
+      <c r="H40" s="207"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="209"/>
+      <c r="N40" s="210"/>
+      <c r="O40" s="211"/>
+      <c r="P40" s="212"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="230"/>
-      <c r="S40" s="230"/>
+      <c r="R40" s="213"/>
+      <c r="S40" s="213"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="226"/>
-      <c r="D41" s="226"/>
-      <c r="E41" s="226"/>
-      <c r="F41" s="226"/>
-      <c r="G41" s="226"/>
-      <c r="H41" s="234"/>
-      <c r="I41" s="235"/>
-      <c r="J41" s="235"/>
-      <c r="K41" s="235"/>
-      <c r="L41" s="235"/>
-      <c r="M41" s="236"/>
-      <c r="N41" s="227"/>
-      <c r="O41" s="228"/>
-      <c r="P41" s="229"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="206"/>
+      <c r="E41" s="206"/>
+      <c r="F41" s="206"/>
+      <c r="G41" s="206"/>
+      <c r="H41" s="207"/>
+      <c r="I41" s="208"/>
+      <c r="J41" s="208"/>
+      <c r="K41" s="208"/>
+      <c r="L41" s="208"/>
+      <c r="M41" s="209"/>
+      <c r="N41" s="210"/>
+      <c r="O41" s="211"/>
+      <c r="P41" s="212"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="230"/>
-      <c r="S41" s="230"/>
+      <c r="R41" s="213"/>
+      <c r="S41" s="213"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="226"/>
-      <c r="D42" s="226"/>
-      <c r="E42" s="226"/>
-      <c r="F42" s="226"/>
-      <c r="G42" s="226"/>
-      <c r="H42" s="234"/>
-      <c r="I42" s="235"/>
-      <c r="J42" s="235"/>
-      <c r="K42" s="235"/>
-      <c r="L42" s="235"/>
-      <c r="M42" s="236"/>
-      <c r="N42" s="227"/>
-      <c r="O42" s="228"/>
-      <c r="P42" s="229"/>
+      <c r="C42" s="206"/>
+      <c r="D42" s="206"/>
+      <c r="E42" s="206"/>
+      <c r="F42" s="206"/>
+      <c r="G42" s="206"/>
+      <c r="H42" s="207"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="208"/>
+      <c r="K42" s="208"/>
+      <c r="L42" s="208"/>
+      <c r="M42" s="209"/>
+      <c r="N42" s="210"/>
+      <c r="O42" s="211"/>
+      <c r="P42" s="212"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="230"/>
-      <c r="S42" s="230"/>
+      <c r="R42" s="213"/>
+      <c r="S42" s="213"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="226"/>
-      <c r="D43" s="226"/>
-      <c r="E43" s="226"/>
-      <c r="F43" s="226"/>
-      <c r="G43" s="226"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="235"/>
-      <c r="J43" s="235"/>
-      <c r="K43" s="235"/>
-      <c r="L43" s="235"/>
-      <c r="M43" s="236"/>
-      <c r="N43" s="227"/>
-      <c r="O43" s="228"/>
-      <c r="P43" s="229"/>
+      <c r="C43" s="206"/>
+      <c r="D43" s="206"/>
+      <c r="E43" s="206"/>
+      <c r="F43" s="206"/>
+      <c r="G43" s="206"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="208"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="209"/>
+      <c r="N43" s="210"/>
+      <c r="O43" s="211"/>
+      <c r="P43" s="212"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="230"/>
-      <c r="S43" s="230"/>
+      <c r="R43" s="213"/>
+      <c r="S43" s="213"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="226"/>
-      <c r="D44" s="226"/>
-      <c r="E44" s="226"/>
-      <c r="F44" s="226"/>
-      <c r="G44" s="226"/>
-      <c r="H44" s="234"/>
-      <c r="I44" s="235"/>
-      <c r="J44" s="235"/>
-      <c r="K44" s="235"/>
-      <c r="L44" s="235"/>
-      <c r="M44" s="236"/>
-      <c r="N44" s="227"/>
-      <c r="O44" s="228"/>
-      <c r="P44" s="229"/>
+      <c r="C44" s="206"/>
+      <c r="D44" s="206"/>
+      <c r="E44" s="206"/>
+      <c r="F44" s="206"/>
+      <c r="G44" s="206"/>
+      <c r="H44" s="207"/>
+      <c r="I44" s="208"/>
+      <c r="J44" s="208"/>
+      <c r="K44" s="208"/>
+      <c r="L44" s="208"/>
+      <c r="M44" s="209"/>
+      <c r="N44" s="210"/>
+      <c r="O44" s="211"/>
+      <c r="P44" s="212"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="230"/>
-      <c r="S44" s="230"/>
+      <c r="R44" s="213"/>
+      <c r="S44" s="213"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="226"/>
-      <c r="D45" s="226"/>
-      <c r="E45" s="226"/>
-      <c r="F45" s="226"/>
-      <c r="G45" s="226"/>
-      <c r="H45" s="234"/>
-      <c r="I45" s="235"/>
-      <c r="J45" s="235"/>
-      <c r="K45" s="235"/>
-      <c r="L45" s="235"/>
-      <c r="M45" s="236"/>
-      <c r="N45" s="227"/>
-      <c r="O45" s="228"/>
-      <c r="P45" s="229"/>
+      <c r="C45" s="206"/>
+      <c r="D45" s="206"/>
+      <c r="E45" s="206"/>
+      <c r="F45" s="206"/>
+      <c r="G45" s="206"/>
+      <c r="H45" s="207"/>
+      <c r="I45" s="208"/>
+      <c r="J45" s="208"/>
+      <c r="K45" s="208"/>
+      <c r="L45" s="208"/>
+      <c r="M45" s="209"/>
+      <c r="N45" s="210"/>
+      <c r="O45" s="211"/>
+      <c r="P45" s="212"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="230"/>
-      <c r="S45" s="230"/>
+      <c r="R45" s="213"/>
+      <c r="S45" s="213"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="226"/>
-      <c r="D46" s="226"/>
-      <c r="E46" s="226"/>
-      <c r="F46" s="226"/>
-      <c r="G46" s="226"/>
-      <c r="H46" s="234"/>
-      <c r="I46" s="235"/>
-      <c r="J46" s="235"/>
-      <c r="K46" s="235"/>
-      <c r="L46" s="235"/>
-      <c r="M46" s="236"/>
-      <c r="N46" s="227"/>
-      <c r="O46" s="228"/>
-      <c r="P46" s="229"/>
+      <c r="C46" s="206"/>
+      <c r="D46" s="206"/>
+      <c r="E46" s="206"/>
+      <c r="F46" s="206"/>
+      <c r="G46" s="206"/>
+      <c r="H46" s="207"/>
+      <c r="I46" s="208"/>
+      <c r="J46" s="208"/>
+      <c r="K46" s="208"/>
+      <c r="L46" s="208"/>
+      <c r="M46" s="209"/>
+      <c r="N46" s="210"/>
+      <c r="O46" s="211"/>
+      <c r="P46" s="212"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="230"/>
-      <c r="S46" s="230"/>
+      <c r="R46" s="213"/>
+      <c r="S46" s="213"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="226"/>
-      <c r="D47" s="226"/>
-      <c r="E47" s="226"/>
-      <c r="F47" s="226"/>
-      <c r="G47" s="226"/>
-      <c r="H47" s="234"/>
-      <c r="I47" s="235"/>
-      <c r="J47" s="235"/>
-      <c r="K47" s="235"/>
-      <c r="L47" s="235"/>
-      <c r="M47" s="236"/>
-      <c r="N47" s="227"/>
-      <c r="O47" s="228"/>
-      <c r="P47" s="229"/>
+      <c r="C47" s="206"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="206"/>
+      <c r="F47" s="206"/>
+      <c r="G47" s="206"/>
+      <c r="H47" s="207"/>
+      <c r="I47" s="208"/>
+      <c r="J47" s="208"/>
+      <c r="K47" s="208"/>
+      <c r="L47" s="208"/>
+      <c r="M47" s="209"/>
+      <c r="N47" s="210"/>
+      <c r="O47" s="211"/>
+      <c r="P47" s="212"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="230"/>
-      <c r="S47" s="230"/>
+      <c r="R47" s="213"/>
+      <c r="S47" s="213"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="226"/>
-      <c r="D48" s="226"/>
-      <c r="E48" s="226"/>
-      <c r="F48" s="226"/>
-      <c r="G48" s="226"/>
-      <c r="H48" s="234"/>
-      <c r="I48" s="235"/>
-      <c r="J48" s="235"/>
-      <c r="K48" s="235"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="236"/>
-      <c r="N48" s="227"/>
-      <c r="O48" s="228"/>
-      <c r="P48" s="229"/>
+      <c r="C48" s="206"/>
+      <c r="D48" s="206"/>
+      <c r="E48" s="206"/>
+      <c r="F48" s="206"/>
+      <c r="G48" s="206"/>
+      <c r="H48" s="207"/>
+      <c r="I48" s="208"/>
+      <c r="J48" s="208"/>
+      <c r="K48" s="208"/>
+      <c r="L48" s="208"/>
+      <c r="M48" s="209"/>
+      <c r="N48" s="210"/>
+      <c r="O48" s="211"/>
+      <c r="P48" s="212"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="230"/>
-      <c r="S48" s="230"/>
+      <c r="R48" s="213"/>
+      <c r="S48" s="213"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="226"/>
-      <c r="D49" s="226"/>
-      <c r="E49" s="226"/>
-      <c r="F49" s="226"/>
-      <c r="G49" s="226"/>
-      <c r="H49" s="234"/>
-      <c r="I49" s="235"/>
-      <c r="J49" s="235"/>
-      <c r="K49" s="235"/>
-      <c r="L49" s="235"/>
-      <c r="M49" s="236"/>
-      <c r="N49" s="227"/>
-      <c r="O49" s="228"/>
-      <c r="P49" s="229"/>
+      <c r="C49" s="206"/>
+      <c r="D49" s="206"/>
+      <c r="E49" s="206"/>
+      <c r="F49" s="206"/>
+      <c r="G49" s="206"/>
+      <c r="H49" s="207"/>
+      <c r="I49" s="208"/>
+      <c r="J49" s="208"/>
+      <c r="K49" s="208"/>
+      <c r="L49" s="208"/>
+      <c r="M49" s="209"/>
+      <c r="N49" s="210"/>
+      <c r="O49" s="211"/>
+      <c r="P49" s="212"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="230"/>
-      <c r="S49" s="230"/>
+      <c r="R49" s="213"/>
+      <c r="S49" s="213"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="226"/>
-      <c r="D50" s="226"/>
-      <c r="E50" s="226"/>
-      <c r="F50" s="226"/>
-      <c r="G50" s="226"/>
-      <c r="H50" s="234"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="236"/>
-      <c r="N50" s="227"/>
-      <c r="O50" s="228"/>
-      <c r="P50" s="229"/>
+      <c r="C50" s="206"/>
+      <c r="D50" s="206"/>
+      <c r="E50" s="206"/>
+      <c r="F50" s="206"/>
+      <c r="G50" s="206"/>
+      <c r="H50" s="207"/>
+      <c r="I50" s="208"/>
+      <c r="J50" s="208"/>
+      <c r="K50" s="208"/>
+      <c r="L50" s="208"/>
+      <c r="M50" s="209"/>
+      <c r="N50" s="210"/>
+      <c r="O50" s="211"/>
+      <c r="P50" s="212"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="230"/>
-      <c r="S50" s="230"/>
+      <c r="R50" s="213"/>
+      <c r="S50" s="213"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="226"/>
-      <c r="D51" s="226"/>
-      <c r="E51" s="226"/>
-      <c r="F51" s="226"/>
-      <c r="G51" s="226"/>
-      <c r="H51" s="234"/>
-      <c r="I51" s="235"/>
-      <c r="J51" s="235"/>
-      <c r="K51" s="235"/>
-      <c r="L51" s="235"/>
-      <c r="M51" s="236"/>
-      <c r="N51" s="227"/>
-      <c r="O51" s="228"/>
-      <c r="P51" s="229"/>
+      <c r="C51" s="206"/>
+      <c r="D51" s="206"/>
+      <c r="E51" s="206"/>
+      <c r="F51" s="206"/>
+      <c r="G51" s="206"/>
+      <c r="H51" s="207"/>
+      <c r="I51" s="208"/>
+      <c r="J51" s="208"/>
+      <c r="K51" s="208"/>
+      <c r="L51" s="208"/>
+      <c r="M51" s="209"/>
+      <c r="N51" s="210"/>
+      <c r="O51" s="211"/>
+      <c r="P51" s="212"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="230"/>
-      <c r="S51" s="230"/>
+      <c r="R51" s="213"/>
+      <c r="S51" s="213"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="226"/>
-      <c r="D52" s="226"/>
-      <c r="E52" s="226"/>
-      <c r="F52" s="226"/>
-      <c r="G52" s="226"/>
-      <c r="H52" s="234"/>
-      <c r="I52" s="235"/>
-      <c r="J52" s="235"/>
-      <c r="K52" s="235"/>
-      <c r="L52" s="235"/>
-      <c r="M52" s="236"/>
-      <c r="N52" s="227"/>
-      <c r="O52" s="228"/>
-      <c r="P52" s="229"/>
+      <c r="C52" s="206"/>
+      <c r="D52" s="206"/>
+      <c r="E52" s="206"/>
+      <c r="F52" s="206"/>
+      <c r="G52" s="206"/>
+      <c r="H52" s="207"/>
+      <c r="I52" s="208"/>
+      <c r="J52" s="208"/>
+      <c r="K52" s="208"/>
+      <c r="L52" s="208"/>
+      <c r="M52" s="209"/>
+      <c r="N52" s="210"/>
+      <c r="O52" s="211"/>
+      <c r="P52" s="212"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="230"/>
-      <c r="S52" s="230"/>
+      <c r="R52" s="213"/>
+      <c r="S52" s="213"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -13125,10 +13301,638 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6EFE86-1180-4D50-ACA3-098C2E0D25EC}">
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="247"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A1" s="237" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="238"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="240" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="241"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="242" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="241"/>
+      <c r="I1" s="243" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="244"/>
+      <c r="K1" s="243" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="244"/>
+      <c r="M1" s="243" t="s">
+        <v>119</v>
+      </c>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="248"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="237" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="250"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="237" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="250"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="265">
+        <v>45827</v>
+      </c>
+      <c r="J2" s="238"/>
+      <c r="K2" s="266" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="238"/>
+      <c r="M2" s="237"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="251"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A3" s="252"/>
+      <c r="B3" s="253"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="252"/>
+      <c r="N3" s="253"/>
+      <c r="O3" s="251"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="237" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="238"/>
+      <c r="C4" s="267" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="M4" s="255"/>
+      <c r="N4" s="256"/>
+      <c r="O4" s="251"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A5" s="252"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="M5" s="258"/>
+      <c r="N5" s="259"/>
+      <c r="O5" s="251"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A6" s="243" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="244"/>
+      <c r="C6" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="245"/>
+      <c r="E6" s="245"/>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
+      <c r="I6" s="245"/>
+      <c r="J6" s="245"/>
+      <c r="K6" s="245"/>
+      <c r="L6" s="245"/>
+      <c r="M6" s="245"/>
+      <c r="N6" s="244"/>
+      <c r="O6" s="251"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="237">
+        <v>1</v>
+      </c>
+      <c r="B7" s="238"/>
+      <c r="C7" s="260"/>
+      <c r="D7" s="260"/>
+      <c r="E7" s="260"/>
+      <c r="F7" s="260"/>
+      <c r="G7" s="260"/>
+      <c r="H7" s="260"/>
+      <c r="I7" s="260"/>
+      <c r="J7" s="260"/>
+      <c r="K7" s="260"/>
+      <c r="L7" s="260"/>
+      <c r="M7" s="260"/>
+      <c r="N7" s="260"/>
+      <c r="O7" s="251"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="248"/>
+      <c r="B8" s="249"/>
+      <c r="O8" s="251"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="248"/>
+      <c r="B9" s="249"/>
+      <c r="N9" s="261"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="248"/>
+      <c r="B10" s="249"/>
+      <c r="O10" s="251"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="248"/>
+      <c r="B11" s="249"/>
+      <c r="O11" s="251"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="248"/>
+      <c r="B12" s="249"/>
+      <c r="O12" s="251"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="248"/>
+      <c r="B13" s="249"/>
+      <c r="O13" s="251"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="248"/>
+      <c r="B14" s="249"/>
+      <c r="O14" s="251"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A15" s="252"/>
+      <c r="B15" s="253"/>
+      <c r="C15" s="262"/>
+      <c r="D15" s="262"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="262"/>
+      <c r="G15" s="262"/>
+      <c r="H15" s="262"/>
+      <c r="I15" s="262"/>
+      <c r="J15" s="262"/>
+      <c r="K15" s="262"/>
+      <c r="L15" s="262"/>
+      <c r="M15" s="262"/>
+      <c r="N15" s="263"/>
+      <c r="O15" s="251"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="237">
+        <v>2</v>
+      </c>
+      <c r="B16" s="238"/>
+      <c r="C16" s="260"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="260"/>
+      <c r="G16" s="260"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="260"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="260"/>
+      <c r="L16" s="260"/>
+      <c r="M16" s="260"/>
+      <c r="N16" s="261"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="248"/>
+      <c r="B17" s="249"/>
+      <c r="N17" s="261"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="248"/>
+      <c r="B18" s="249"/>
+      <c r="N18" s="261"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="248"/>
+      <c r="B19" s="249"/>
+      <c r="N19" s="261"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="248"/>
+      <c r="B20" s="249"/>
+      <c r="N20" s="261"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="248"/>
+      <c r="B21" s="249"/>
+      <c r="N21" s="261"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="248"/>
+      <c r="B22" s="249"/>
+      <c r="N22" s="261"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="248"/>
+      <c r="B23" s="249"/>
+      <c r="N23" s="261"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A24" s="252"/>
+      <c r="B24" s="253"/>
+      <c r="C24" s="262"/>
+      <c r="D24" s="262"/>
+      <c r="E24" s="262"/>
+      <c r="F24" s="262"/>
+      <c r="G24" s="262"/>
+      <c r="H24" s="262"/>
+      <c r="I24" s="262"/>
+      <c r="J24" s="262"/>
+      <c r="K24" s="262"/>
+      <c r="L24" s="262"/>
+      <c r="M24" s="262"/>
+      <c r="N24" s="263"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="237">
+        <v>3</v>
+      </c>
+      <c r="B25" s="238"/>
+      <c r="C25" s="260"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
+      <c r="M25" s="260"/>
+      <c r="N25" s="261"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="248"/>
+      <c r="B26" s="249"/>
+      <c r="N26" s="261"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="248"/>
+      <c r="B27" s="249"/>
+      <c r="N27" s="261"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="248"/>
+      <c r="B28" s="249"/>
+      <c r="N28" s="261"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="248"/>
+      <c r="B29" s="249"/>
+      <c r="N29" s="261"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="248"/>
+      <c r="B30" s="249"/>
+      <c r="N30" s="261"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="248"/>
+      <c r="B31" s="249"/>
+      <c r="N31" s="261"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="248"/>
+      <c r="B32" s="249"/>
+      <c r="N32" s="261"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A33" s="252"/>
+      <c r="B33" s="253"/>
+      <c r="C33" s="262"/>
+      <c r="D33" s="262"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="262"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="262"/>
+      <c r="J33" s="262"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="262"/>
+      <c r="N33" s="261"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="237">
+        <v>4</v>
+      </c>
+      <c r="B34" s="238"/>
+      <c r="C34" s="260"/>
+      <c r="D34" s="260"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="260"/>
+      <c r="G34" s="260"/>
+      <c r="H34" s="260"/>
+      <c r="I34" s="260"/>
+      <c r="J34" s="260"/>
+      <c r="K34" s="260"/>
+      <c r="L34" s="260"/>
+      <c r="M34" s="260"/>
+      <c r="N34" s="264"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="248"/>
+      <c r="B35" s="249"/>
+      <c r="N35" s="261"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="248"/>
+      <c r="B36" s="249"/>
+      <c r="N36" s="261"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="248"/>
+      <c r="B37" s="249"/>
+      <c r="N37" s="261"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="248"/>
+      <c r="B38" s="249"/>
+      <c r="N38" s="261"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="248"/>
+      <c r="B39" s="249"/>
+      <c r="N39" s="261"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="248"/>
+      <c r="B40" s="249"/>
+      <c r="N40" s="261"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="248"/>
+      <c r="B41" s="249"/>
+      <c r="N41" s="261"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A42" s="252"/>
+      <c r="B42" s="253"/>
+      <c r="C42" s="262"/>
+      <c r="D42" s="262"/>
+      <c r="E42" s="262"/>
+      <c r="F42" s="262"/>
+      <c r="G42" s="262"/>
+      <c r="H42" s="262"/>
+      <c r="I42" s="262"/>
+      <c r="J42" s="262"/>
+      <c r="K42" s="262"/>
+      <c r="L42" s="262"/>
+      <c r="M42" s="262"/>
+      <c r="N42" s="263"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C2:E3"/>
+    <mergeCell ref="F2:H3"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D351F8-CB54-4746-9B54-EA68144AC375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11D6C3C-C15C-4486-882A-85DD460B50A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="詳細クラス図" sheetId="7" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="8" r:id="rId6"/>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="9" r:id="rId7"/>
+    <sheet name="エビデンス" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="範囲１" localSheetId="6">#REF!</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="124">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -99,14 +100,14 @@
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>56期</t>
     <rPh sb="2" eb="3">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>山本岬樹</t>
@@ -116,11 +117,11 @@
     <rPh sb="2" eb="4">
       <t>ミサキキ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>画面名称</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -130,7 +131,7 @@
     <rPh sb="0" eb="2">
       <t>ヤマガタ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ユースケース名</t>
@@ -143,7 +144,7 @@
   </si>
   <si>
     <t>ユーザー</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>事前条件</t>
@@ -242,33 +243,33 @@
     <rPh sb="4" eb="6">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>submit</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>メニューへ戻る</t>
     <rPh sb="5" eb="6">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>menu.jsp</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>POST</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧</t>
     <rPh sb="3" eb="5">
       <t>イチラン</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧が表示される</t>
@@ -278,7 +279,7 @@
     <rPh sb="6" eb="8">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログインが完了しており、データベースと接続できている</t>
@@ -288,7 +289,7 @@
     <rPh sb="19" eb="21">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>①データベースの接続に失敗した場合"データベースに接続できませんでした"と表示される。
@@ -320,7 +321,7 @@
     <rPh sb="74" eb="76">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>1
@@ -344,14 +345,14 @@
     <rPh sb="90" eb="92">
       <t>ショウサイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧画面</t>
     <rPh sb="3" eb="5">
       <t>イチラン</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>JUnitテスト仕様書兼報告書</t>
@@ -364,14 +365,14 @@
     <rPh sb="12" eb="15">
       <t>ホウコクショ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>作成者</t>
@@ -381,25 +382,25 @@
     <rPh sb="0" eb="3">
       <t>カイシャメイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>コンサイズ</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>サブシステム名</t>
     <rPh sb="6" eb="7">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>作成日</t>
     <rPh sb="0" eb="3">
       <t>サクセイビ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>実施者</t>
@@ -409,29 +410,29 @@
     <rPh sb="2" eb="3">
       <t>シャ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>No</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>分類</t>
     <rPh sb="0" eb="2">
       <t>ブンルイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>テストクラス</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>検証するメソッド</t>
     <rPh sb="0" eb="2">
       <t>ケンショウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>期待する結果</t>
@@ -441,14 +442,14 @@
     <rPh sb="4" eb="6">
       <t>ケッカ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>実施日</t>
     <rPh sb="0" eb="3">
       <t>ジッシビ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>備考・特記事項</t>
@@ -461,7 +462,7 @@
     <rPh sb="5" eb="7">
       <t>ジコウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>メニュー画面からタスク一覧表示へページ遷移</t>
@@ -477,7 +478,7 @@
     <rPh sb="19" eb="21">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧表示ボタンを押下する</t>
@@ -487,7 +488,7 @@
     <rPh sb="11" eb="13">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク一覧表示画面が表示される</t>
@@ -500,7 +501,7 @@
     <rPh sb="10" eb="12">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログイン状態かつデータベースに接続されていること</t>
@@ -510,7 +511,7 @@
     <rPh sb="15" eb="17">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>データベースに接続されていないときのタスク一覧表示ボタンの押下</t>
@@ -523,7 +524,7 @@
     <rPh sb="29" eb="31">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>エラー画面へ遷移する
@@ -531,19 +532,19 @@
     <rPh sb="25" eb="27">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">正常系
 </t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスクは現在ありませんというメッセージが表示される</t>
     <rPh sb="20" eb="22">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>登録されているタスクがない場合のタスク一覧表示</t>
@@ -556,7 +557,7 @@
     <rPh sb="19" eb="23">
       <t>イチランヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>データベースに接続されているときのタスク一覧表示ボタンの押下</t>
@@ -572,7 +573,7 @@
     <rPh sb="28" eb="30">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>登録されているタスク一覧が表示される</t>
@@ -585,7 +586,7 @@
     <rPh sb="13" eb="15">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>期限、メモが未入力の場合のタスク一覧表示</t>
@@ -604,7 +605,7 @@
     <rPh sb="18" eb="20">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスクID、タスク名、カテゴリID、ユーザーID、ステータスコード、登録日時、更新日時の表示</t>
@@ -620,7 +621,7 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>必ず登録した内容が表示される</t>
@@ -636,7 +637,7 @@
     <rPh sb="9" eb="11">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>1タスク詳細画面に遷移する。
@@ -653,22 +654,22 @@
     <rPh sb="23" eb="24">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>正常系</t>
     <rPh sb="0" eb="3">
       <t>セイジョウケイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>TaskDAOTest</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>select()</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>返ってくる値がNullではない。</t>
@@ -678,15 +679,15 @@
     <rPh sb="5" eb="6">
       <t>アタイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>異常系</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログアウト状態でのページ表示</t>
@@ -696,18 +697,18 @@
     <rPh sb="12" eb="14">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログアウト状態であること</t>
     <rPh sb="5" eb="7">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>http://localhost:8080/taskUN/task-list.jsp</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
@@ -726,7 +727,7 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>期限は「未入力」と表示され、メモは元のメモが表示される</t>
@@ -745,7 +746,77 @@
     <rPh sb="22" eb="24">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>テストエビデンス</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>グループ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>承認印</t>
+    <rPh sb="0" eb="3">
+      <t>ショウニンイン</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>機能名称</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>タスク一覧表示</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -755,11 +826,19 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -879,6 +958,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -900,7 +993,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="71">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -1738,20 +1831,350 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="268">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="16" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1760,645 +2183,459 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="15" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="10" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2410,57 +2647,127 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="1" fillId="0" borderId="71" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="ハイパーリンク" xfId="5" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{6F8E72F5-98DE-405A-B9D4-A66D21EFE385}"/>
     <cellStyle name="標準 2 2" xfId="1" xr:uid="{79379184-E0E4-48AE-9057-633A6B8D7415}"/>
+    <cellStyle name="標準 3" xfId="6" xr:uid="{CEE6DF7F-CA9B-4CC0-BF7D-BFB06425A72A}"/>
     <cellStyle name="標準_生産計画ED書" xfId="3" xr:uid="{7EBA00B9-77D1-4E43-9CBA-6456FE0380AD}"/>
     <cellStyle name="標準_東京理科大DBレイアウト" xfId="4" xr:uid="{4DC3AB47-9300-45FE-A4F0-1EE38BCFF06E}"/>
   </cellStyles>
@@ -4155,7 +4462,7 @@
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="G15:H15"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -4173,19 +4480,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="97"/>
+      <c r="F1" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="82"/>
+      <c r="G1" s="97"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4197,190 +4504,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="100" t="s">
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="101"/>
-      <c r="F2" s="100" t="s">
+      <c r="E2" s="111"/>
+      <c r="F2" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="104">
+      <c r="G2" s="111"/>
+      <c r="H2" s="114">
         <v>45805</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="77"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="93"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="96"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="83" t="s">
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="84"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="99"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="89"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="89"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="88" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="89"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="87" customHeight="1">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="87"/>
-      <c r="D9" s="105" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="89"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="112"/>
-      <c r="B10" s="114" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="89"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="113"/>
-      <c r="B11" s="114" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="105" t="s">
+      <c r="C11" s="76"/>
+      <c r="D11" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="89"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="78"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="105" t="s">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="89"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="107"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="110"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5371,6 +5678,18 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5386,20 +5705,8 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -6820,7 +7127,7 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -6909,23 +7216,23 @@
       <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="140"/>
+      <c r="B5" s="137"/>
       <c r="C5" s="131"/>
-      <c r="D5" s="145" t="s">
+      <c r="D5" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="146"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="144" t="s">
+      <c r="A6" s="141" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="67"/>
@@ -6936,19 +7243,19 @@
       <c r="G6" s="67"/>
       <c r="H6" s="67"/>
       <c r="I6" s="67"/>
-      <c r="J6" s="137"/>
+      <c r="J6" s="145"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="147"/>
-      <c r="B7" s="148"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="148"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="149"/>
+      <c r="A7" s="146"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="148"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="125"/>
@@ -6960,7 +7267,7 @@
       <c r="G8" s="70"/>
       <c r="H8" s="70"/>
       <c r="I8" s="70"/>
-      <c r="J8" s="150"/>
+      <c r="J8" s="149"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="125"/>
@@ -6972,7 +7279,7 @@
       <c r="G9" s="70"/>
       <c r="H9" s="70"/>
       <c r="I9" s="70"/>
-      <c r="J9" s="150"/>
+      <c r="J9" s="149"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="125"/>
@@ -6984,7 +7291,7 @@
       <c r="G10" s="70"/>
       <c r="H10" s="70"/>
       <c r="I10" s="70"/>
-      <c r="J10" s="150"/>
+      <c r="J10" s="149"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="125"/>
@@ -6996,7 +7303,7 @@
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
-      <c r="J11" s="150"/>
+      <c r="J11" s="149"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="125"/>
@@ -7008,7 +7315,7 @@
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
       <c r="I12" s="70"/>
-      <c r="J12" s="150"/>
+      <c r="J12" s="149"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="125"/>
@@ -7020,10 +7327,10 @@
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
       <c r="I13" s="70"/>
-      <c r="J13" s="150"/>
+      <c r="J13" s="149"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="144" t="s">
+      <c r="A14" s="141" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="67"/>
@@ -7034,15 +7341,15 @@
       <c r="G14" s="67"/>
       <c r="H14" s="67"/>
       <c r="I14" s="67"/>
-      <c r="J14" s="137"/>
+      <c r="J14" s="145"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="144" t="s">
+      <c r="A15" s="141" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="67"/>
       <c r="C15" s="68"/>
-      <c r="D15" s="136" t="s">
+      <c r="D15" s="150" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="67"/>
@@ -7057,7 +7364,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="144" t="s">
+      <c r="A16" s="141" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="67"/>
@@ -7078,10 +7385,10 @@
         <v>10</v>
       </c>
       <c r="I16" s="67"/>
-      <c r="J16" s="137"/>
+      <c r="J16" s="145"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="138">
+      <c r="A17" s="142">
         <v>1</v>
       </c>
       <c r="B17" s="67"/>
@@ -7096,80 +7403,80 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="136"/>
+      <c r="H17" s="150"/>
       <c r="I17" s="67"/>
-      <c r="J17" s="137"/>
+      <c r="J17" s="145"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="138"/>
+      <c r="A18" s="142"/>
       <c r="B18" s="67"/>
       <c r="C18" s="68"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="136"/>
+      <c r="H18" s="150"/>
       <c r="I18" s="67"/>
-      <c r="J18" s="137"/>
+      <c r="J18" s="145"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="138"/>
+      <c r="A19" s="142"/>
       <c r="B19" s="67"/>
       <c r="C19" s="68"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="136"/>
+      <c r="H19" s="150"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="137"/>
+      <c r="J19" s="145"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="138"/>
+      <c r="A20" s="142"/>
       <c r="B20" s="67"/>
       <c r="C20" s="68"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="136"/>
+      <c r="H20" s="150"/>
       <c r="I20" s="67"/>
-      <c r="J20" s="137"/>
+      <c r="J20" s="145"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="138"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="67"/>
       <c r="C21" s="68"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="136"/>
+      <c r="H21" s="150"/>
       <c r="I21" s="67"/>
-      <c r="J21" s="137"/>
+      <c r="J21" s="145"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="138"/>
+      <c r="A22" s="142"/>
       <c r="B22" s="67"/>
       <c r="C22" s="68"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="136"/>
+      <c r="H22" s="150"/>
       <c r="I22" s="67"/>
-      <c r="J22" s="137"/>
+      <c r="J22" s="145"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="143"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="152"/>
-      <c r="I23" s="142"/>
+      <c r="I23" s="139"/>
       <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8151,11 +8458,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8172,18 +8484,13 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -9597,7 +9904,7 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -9616,7 +9923,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="203" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="161"/>
@@ -9627,14 +9934,14 @@
       <c r="G1" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
       <c r="J1" s="170"/>
       <c r="K1" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
       <c r="N1" s="170"/>
       <c r="O1" s="169" t="s">
         <v>7</v>
@@ -9647,7 +9954,7 @@
       <c r="S1" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="182"/>
+      <c r="T1" s="200"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="163"/>
@@ -9659,16 +9966,16 @@
       <c r="G2" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
       <c r="J2" s="172"/>
       <c r="K2" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="189"/>
-      <c r="M2" s="189"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
       <c r="N2" s="172"/>
-      <c r="O2" s="190">
+      <c r="O2" s="205">
         <v>45817</v>
       </c>
       <c r="P2" s="172"/>
@@ -9677,7 +9984,7 @@
       </c>
       <c r="R2" s="172"/>
       <c r="S2" s="171"/>
-      <c r="T2" s="176"/>
+      <c r="T2" s="194"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="163"/>
@@ -9699,7 +10006,7 @@
       <c r="Q3" s="173"/>
       <c r="R3" s="165"/>
       <c r="S3" s="173"/>
-      <c r="T3" s="177"/>
+      <c r="T3" s="195"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="166"/>
@@ -9721,85 +10028,85 @@
       <c r="Q4" s="174"/>
       <c r="R4" s="168"/>
       <c r="S4" s="174"/>
-      <c r="T4" s="178"/>
+      <c r="T4" s="196"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="179" t="s">
+      <c r="A5" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
       <c r="F5" s="170"/>
-      <c r="G5" s="181" t="s">
+      <c r="G5" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="180"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="180"/>
-      <c r="T5" s="182"/>
+      <c r="H5" s="198"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="198"/>
+      <c r="K5" s="198"/>
+      <c r="L5" s="198"/>
+      <c r="M5" s="198"/>
+      <c r="N5" s="198"/>
+      <c r="O5" s="198"/>
+      <c r="P5" s="198"/>
+      <c r="Q5" s="198"/>
+      <c r="R5" s="198"/>
+      <c r="S5" s="198"/>
+      <c r="T5" s="200"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="183" t="s">
+      <c r="A6" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="186" t="s">
+      <c r="B6" s="183"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="184"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
-      <c r="K6" s="184"/>
-      <c r="L6" s="184"/>
-      <c r="M6" s="184"/>
-      <c r="N6" s="184"/>
-      <c r="O6" s="184"/>
-      <c r="P6" s="184"/>
-      <c r="Q6" s="184"/>
-      <c r="R6" s="184"/>
-      <c r="S6" s="184"/>
-      <c r="T6" s="187"/>
+      <c r="H6" s="183"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="183"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="183"/>
+      <c r="Q6" s="183"/>
+      <c r="R6" s="183"/>
+      <c r="S6" s="183"/>
+      <c r="T6" s="202"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="183" t="s">
+      <c r="A7" s="192" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="184"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="184"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="186" t="s">
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="201" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="184"/>
-      <c r="I7" s="184"/>
-      <c r="J7" s="184"/>
-      <c r="K7" s="184"/>
-      <c r="L7" s="184"/>
-      <c r="M7" s="184"/>
-      <c r="N7" s="184"/>
-      <c r="O7" s="184"/>
-      <c r="P7" s="184"/>
-      <c r="Q7" s="184"/>
-      <c r="R7" s="184"/>
-      <c r="S7" s="184"/>
-      <c r="T7" s="187"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="183"/>
+      <c r="M7" s="183"/>
+      <c r="N7" s="183"/>
+      <c r="O7" s="183"/>
+      <c r="P7" s="183"/>
+      <c r="Q7" s="183"/>
+      <c r="R7" s="183"/>
+      <c r="S7" s="183"/>
+      <c r="T7" s="202"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -9998,37 +10305,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="183" t="s">
+      <c r="A15" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="185"/>
-      <c r="C15" s="196" t="s">
+      <c r="B15" s="184"/>
+      <c r="C15" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="185"/>
+      <c r="D15" s="184"/>
       <c r="E15" s="191" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="185"/>
+      <c r="F15" s="184"/>
       <c r="G15" s="191" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="184"/>
-      <c r="I15" s="185"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="184"/>
       <c r="J15" s="191" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="185"/>
+      <c r="K15" s="184"/>
       <c r="L15" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="184"/>
-      <c r="N15" s="185"/>
+      <c r="M15" s="183"/>
+      <c r="N15" s="184"/>
       <c r="O15" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="184"/>
-      <c r="Q15" s="185"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="184"/>
       <c r="R15" s="44" t="s">
         <v>56</v>
       </c>
@@ -10040,37 +10347,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="192">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="193" t="s">
+      <c r="B16" s="184"/>
+      <c r="C16" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="185"/>
-      <c r="E16" s="193" t="s">
+      <c r="D16" s="184"/>
+      <c r="E16" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="185"/>
-      <c r="G16" s="194" t="s">
+      <c r="F16" s="184"/>
+      <c r="G16" s="187" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="184"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="194" t="s">
+      <c r="H16" s="183"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="185"/>
-      <c r="L16" s="195" t="s">
+      <c r="K16" s="184"/>
+      <c r="L16" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="184"/>
-      <c r="N16" s="185"/>
-      <c r="O16" s="195" t="s">
+      <c r="M16" s="183"/>
+      <c r="N16" s="184"/>
+      <c r="O16" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="184"/>
-      <c r="Q16" s="185"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="184"/>
       <c r="R16" s="65">
         <v>45825</v>
       </c>
@@ -10088,37 +10395,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1">
-      <c r="A17" s="192">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="185"/>
-      <c r="C17" s="193" t="s">
+      <c r="B17" s="184"/>
+      <c r="C17" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="185"/>
-      <c r="E17" s="193" t="s">
+      <c r="D17" s="184"/>
+      <c r="E17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="185"/>
-      <c r="G17" s="194" t="s">
+      <c r="F17" s="184"/>
+      <c r="G17" s="187" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="184"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="194" t="s">
+      <c r="H17" s="183"/>
+      <c r="I17" s="184"/>
+      <c r="J17" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="185"/>
-      <c r="L17" s="195" t="s">
+      <c r="K17" s="184"/>
+      <c r="L17" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M17" s="184"/>
-      <c r="N17" s="185"/>
-      <c r="O17" s="195" t="s">
+      <c r="M17" s="183"/>
+      <c r="N17" s="184"/>
+      <c r="O17" s="182" t="s">
         <v>98</v>
       </c>
-      <c r="P17" s="184"/>
-      <c r="Q17" s="185"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="184"/>
       <c r="R17" s="65">
         <v>45825</v>
       </c>
@@ -10136,37 +10443,37 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="48" customHeight="1">
-      <c r="A18" s="192">
+      <c r="A18" s="185">
         <v>3</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="193" t="s">
+      <c r="B18" s="184"/>
+      <c r="C18" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="185"/>
-      <c r="E18" s="193" t="s">
+      <c r="D18" s="184"/>
+      <c r="E18" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="185"/>
-      <c r="G18" s="194" t="s">
+      <c r="F18" s="184"/>
+      <c r="G18" s="187" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="184"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="194" t="s">
+      <c r="H18" s="183"/>
+      <c r="I18" s="184"/>
+      <c r="J18" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="185"/>
-      <c r="L18" s="195" t="s">
+      <c r="K18" s="184"/>
+      <c r="L18" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M18" s="184"/>
-      <c r="N18" s="185"/>
-      <c r="O18" s="195" t="s">
+      <c r="M18" s="183"/>
+      <c r="N18" s="184"/>
+      <c r="O18" s="182" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="184"/>
-      <c r="Q18" s="185"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="184"/>
       <c r="R18" s="65">
         <v>45825</v>
       </c>
@@ -10184,37 +10491,37 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A19" s="192">
+      <c r="A19" s="185">
         <v>4</v>
       </c>
-      <c r="B19" s="185"/>
-      <c r="C19" s="193" t="s">
+      <c r="B19" s="184"/>
+      <c r="C19" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="185"/>
-      <c r="E19" s="193" t="s">
+      <c r="D19" s="184"/>
+      <c r="E19" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="185"/>
-      <c r="G19" s="194" t="s">
+      <c r="F19" s="184"/>
+      <c r="G19" s="187" t="s">
         <v>96</v>
       </c>
-      <c r="H19" s="184"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="194" t="s">
+      <c r="H19" s="183"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="185"/>
-      <c r="L19" s="195" t="s">
+      <c r="K19" s="184"/>
+      <c r="L19" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M19" s="184"/>
-      <c r="N19" s="185"/>
-      <c r="O19" s="195" t="s">
+      <c r="M19" s="183"/>
+      <c r="N19" s="184"/>
+      <c r="O19" s="182" t="s">
         <v>95</v>
       </c>
-      <c r="P19" s="184"/>
-      <c r="Q19" s="185"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="184"/>
       <c r="R19" s="65">
         <v>45825</v>
       </c>
@@ -10232,37 +10539,37 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A20" s="192">
+      <c r="A20" s="185">
         <v>5</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="193" t="s">
+      <c r="B20" s="184"/>
+      <c r="C20" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="185"/>
-      <c r="E20" s="193" t="s">
+      <c r="D20" s="184"/>
+      <c r="E20" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="185"/>
-      <c r="G20" s="194" t="s">
+      <c r="F20" s="184"/>
+      <c r="G20" s="187" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="184"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="194" t="s">
+      <c r="H20" s="183"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="185"/>
-      <c r="L20" s="195" t="s">
+      <c r="K20" s="184"/>
+      <c r="L20" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M20" s="184"/>
-      <c r="N20" s="185"/>
-      <c r="O20" s="195" t="s">
+      <c r="M20" s="183"/>
+      <c r="N20" s="184"/>
+      <c r="O20" s="182" t="s">
         <v>113</v>
       </c>
-      <c r="P20" s="184"/>
-      <c r="Q20" s="185"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="184"/>
       <c r="R20" s="65">
         <v>45825</v>
       </c>
@@ -10280,37 +10587,37 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A21" s="192">
+      <c r="A21" s="185">
         <v>6</v>
       </c>
-      <c r="B21" s="185"/>
-      <c r="C21" s="193" t="s">
+      <c r="B21" s="184"/>
+      <c r="C21" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="185"/>
-      <c r="E21" s="193" t="s">
+      <c r="D21" s="184"/>
+      <c r="E21" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="185"/>
-      <c r="G21" s="194" t="s">
+      <c r="F21" s="184"/>
+      <c r="G21" s="187" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="184"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="194" t="s">
+      <c r="H21" s="183"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="187" t="s">
         <v>91</v>
       </c>
-      <c r="K21" s="185"/>
-      <c r="L21" s="195" t="s">
+      <c r="K21" s="184"/>
+      <c r="L21" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="M21" s="184"/>
-      <c r="N21" s="185"/>
-      <c r="O21" s="195" t="s">
+      <c r="M21" s="183"/>
+      <c r="N21" s="184"/>
+      <c r="O21" s="182" t="s">
         <v>101</v>
       </c>
-      <c r="P21" s="184"/>
-      <c r="Q21" s="185"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="184"/>
       <c r="R21" s="65">
         <v>45825</v>
       </c>
@@ -10328,33 +10635,33 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="55.5" customHeight="1">
-      <c r="A22" s="192">
+      <c r="A22" s="185">
         <v>7</v>
       </c>
-      <c r="B22" s="185"/>
-      <c r="C22" s="193" t="s">
+      <c r="B22" s="184"/>
+      <c r="C22" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="185"/>
-      <c r="E22" s="193" t="s">
+      <c r="D22" s="184"/>
+      <c r="E22" s="186" t="s">
         <v>108</v>
       </c>
-      <c r="F22" s="185"/>
-      <c r="G22" s="194" t="s">
+      <c r="F22" s="184"/>
+      <c r="G22" s="187" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="184"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="194" t="s">
+      <c r="H22" s="183"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="187" t="s">
         <v>110</v>
       </c>
-      <c r="K22" s="185"/>
-      <c r="L22" s="197" t="s">
+      <c r="K22" s="184"/>
+      <c r="L22" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="M22" s="198"/>
-      <c r="N22" s="198"/>
-      <c r="O22" s="199" t="s">
+      <c r="M22" s="189"/>
+      <c r="N22" s="189"/>
+      <c r="O22" s="190" t="s">
         <v>112</v>
       </c>
       <c r="P22" s="67"/>
@@ -10376,23 +10683,23 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="192"/>
-      <c r="B23" s="185"/>
-      <c r="C23" s="193"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="193"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="194"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="194"/>
-      <c r="K23" s="185"/>
-      <c r="L23" s="195"/>
-      <c r="M23" s="184"/>
-      <c r="N23" s="185"/>
-      <c r="O23" s="195"/>
-      <c r="P23" s="184"/>
-      <c r="Q23" s="185"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="184"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="187"/>
+      <c r="H23" s="183"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="187"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="183"/>
+      <c r="N23" s="184"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="184"/>
       <c r="R23" s="46"/>
       <c r="S23" s="46"/>
       <c r="T23" s="47"/>
@@ -10404,23 +10711,23 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="192"/>
-      <c r="B24" s="185"/>
-      <c r="C24" s="193"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="193"/>
-      <c r="F24" s="185"/>
-      <c r="G24" s="194"/>
-      <c r="H24" s="184"/>
-      <c r="I24" s="185"/>
-      <c r="J24" s="194"/>
-      <c r="K24" s="185"/>
-      <c r="L24" s="195"/>
-      <c r="M24" s="184"/>
-      <c r="N24" s="185"/>
-      <c r="O24" s="195"/>
-      <c r="P24" s="184"/>
-      <c r="Q24" s="185"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="184"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="187"/>
+      <c r="H24" s="183"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="187"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="183"/>
+      <c r="N24" s="184"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="184"/>
       <c r="R24" s="46"/>
       <c r="S24" s="46"/>
       <c r="T24" s="47"/>
@@ -10432,23 +10739,23 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="192"/>
-      <c r="B25" s="185"/>
-      <c r="C25" s="193"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="193"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="194"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="194"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="195"/>
-      <c r="M25" s="184"/>
-      <c r="N25" s="185"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="184"/>
-      <c r="Q25" s="185"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="184"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="184"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="187"/>
+      <c r="H25" s="183"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="187"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="183"/>
+      <c r="N25" s="184"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="184"/>
       <c r="R25" s="46"/>
       <c r="S25" s="46"/>
       <c r="T25" s="47"/>
@@ -10460,23 +10767,23 @@
       <c r="Z25" s="48"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="192"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="193"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="193"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="194"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="194"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="195"/>
-      <c r="M26" s="184"/>
-      <c r="N26" s="185"/>
-      <c r="O26" s="195"/>
-      <c r="P26" s="184"/>
-      <c r="Q26" s="185"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="184"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="184"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="187"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="183"/>
+      <c r="N26" s="184"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="184"/>
       <c r="R26" s="46"/>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -10488,23 +10795,23 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="192"/>
-      <c r="B27" s="185"/>
-      <c r="C27" s="193"/>
-      <c r="D27" s="185"/>
-      <c r="E27" s="193"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="194"/>
-      <c r="H27" s="184"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="194"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="195"/>
-      <c r="M27" s="184"/>
-      <c r="N27" s="185"/>
-      <c r="O27" s="195"/>
-      <c r="P27" s="184"/>
-      <c r="Q27" s="185"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="184"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="187"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="184"/>
+      <c r="J27" s="187"/>
+      <c r="K27" s="184"/>
+      <c r="L27" s="182"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="184"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="184"/>
       <c r="R27" s="46"/>
       <c r="S27" s="46"/>
       <c r="T27" s="47"/>
@@ -10516,23 +10823,23 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="192"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="193"/>
-      <c r="D28" s="185"/>
-      <c r="E28" s="193"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="194"/>
-      <c r="H28" s="184"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="194"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="195"/>
-      <c r="M28" s="184"/>
-      <c r="N28" s="185"/>
-      <c r="O28" s="195"/>
-      <c r="P28" s="184"/>
-      <c r="Q28" s="185"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="184"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="184"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="187"/>
+      <c r="H28" s="183"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="187"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="183"/>
+      <c r="N28" s="184"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="184"/>
       <c r="R28" s="46"/>
       <c r="S28" s="46"/>
       <c r="T28" s="47"/>
@@ -10544,23 +10851,23 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="192"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="193"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="193"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="184"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="194"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="195"/>
-      <c r="M29" s="184"/>
-      <c r="N29" s="185"/>
-      <c r="O29" s="195"/>
-      <c r="P29" s="184"/>
-      <c r="Q29" s="185"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="184"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="187"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="187"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="184"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
       <c r="R29" s="46"/>
       <c r="S29" s="46"/>
       <c r="T29" s="47"/>
@@ -10572,23 +10879,23 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="192"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="193"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="193"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="194"/>
-      <c r="H30" s="184"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="194"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="195"/>
-      <c r="M30" s="184"/>
-      <c r="N30" s="185"/>
-      <c r="O30" s="195"/>
-      <c r="P30" s="184"/>
-      <c r="Q30" s="185"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="184"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="184"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="184"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="183"/>
+      <c r="I30" s="184"/>
+      <c r="J30" s="187"/>
+      <c r="K30" s="184"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="183"/>
+      <c r="N30" s="184"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="183"/>
+      <c r="Q30" s="184"/>
       <c r="R30" s="46"/>
       <c r="S30" s="46"/>
       <c r="T30" s="47"/>
@@ -10600,23 +10907,23 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="203"/>
-      <c r="B31" s="202"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="202"/>
-      <c r="G31" s="205"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="205"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="200"/>
-      <c r="M31" s="201"/>
-      <c r="N31" s="202"/>
-      <c r="O31" s="200"/>
-      <c r="P31" s="201"/>
-      <c r="Q31" s="202"/>
+      <c r="A31" s="179"/>
+      <c r="B31" s="178"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="178"/>
+      <c r="E31" s="180"/>
+      <c r="F31" s="178"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="176"/>
+      <c r="M31" s="177"/>
+      <c r="N31" s="178"/>
+      <c r="O31" s="176"/>
+      <c r="P31" s="177"/>
+      <c r="Q31" s="178"/>
       <c r="R31" s="49"/>
       <c r="S31" s="49"/>
       <c r="T31" s="50"/>
@@ -11614,6 +11921,121 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -11635,123 +12057,8 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <hyperlinks>
     <hyperlink ref="L22" r:id="rId1" xr:uid="{70F16E29-4C19-40D6-A6FE-AC67A8668308}"/>
   </hyperlinks>
@@ -11775,72 +12082,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="226" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="216" t="s">
+      <c r="B1" s="226"/>
+      <c r="C1" s="227" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="219" t="s">
+      <c r="D1" s="228"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="221"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="232"/>
       <c r="N1" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="230" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="221"/>
+      <c r="P1" s="232"/>
       <c r="Q1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="219" t="s">
+      <c r="R1" s="230" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="221"/>
+      <c r="S1" s="232"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="215"/>
-      <c r="B2" s="215"/>
-      <c r="C2" s="216" t="s">
+      <c r="A2" s="226"/>
+      <c r="B2" s="226"/>
+      <c r="C2" s="227" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="217"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="219" t="s">
+      <c r="D2" s="228"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="230" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="220"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="220"/>
-      <c r="J2" s="220"/>
-      <c r="K2" s="220"/>
-      <c r="L2" s="220"/>
-      <c r="M2" s="221"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="M2" s="232"/>
       <c r="N2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="222">
+      <c r="O2" s="233">
         <v>45818</v>
       </c>
-      <c r="P2" s="223"/>
+      <c r="P2" s="234"/>
       <c r="Q2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="224" t="s">
+      <c r="R2" s="235" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="225"/>
+      <c r="S2" s="236"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="55"/>
@@ -11870,33 +12177,33 @@
       <c r="B4" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="217" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="206" t="s">
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="219"/>
+      <c r="H4" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
-      <c r="M4" s="208"/>
-      <c r="N4" s="206" t="s">
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="217" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="207"/>
-      <c r="P4" s="208"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="219"/>
       <c r="Q4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="206" t="s">
+      <c r="R4" s="217" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="208"/>
+      <c r="S4" s="219"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="59">
@@ -11905,1209 +12212,1021 @@
       <c r="B5" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="220" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209" t="s">
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="220" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="M5" s="209"/>
-      <c r="N5" s="210" t="s">
+      <c r="I5" s="220"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="M5" s="220"/>
+      <c r="N5" s="221" t="s">
         <v>106</v>
       </c>
-      <c r="O5" s="211"/>
-      <c r="P5" s="212"/>
+      <c r="O5" s="222"/>
+      <c r="P5" s="223"/>
       <c r="Q5" s="64">
         <v>45818</v>
       </c>
-      <c r="R5" s="213"/>
-      <c r="S5" s="214"/>
+      <c r="R5" s="224"/>
+      <c r="S5" s="225"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="226"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="226"/>
-      <c r="M6" s="226"/>
-      <c r="N6" s="231"/>
-      <c r="O6" s="232"/>
-      <c r="P6" s="233"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="206"/>
+      <c r="N6" s="214"/>
+      <c r="O6" s="215"/>
+      <c r="P6" s="216"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="230"/>
-      <c r="S6" s="230"/>
+      <c r="R6" s="213"/>
+      <c r="S6" s="213"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="227"/>
-      <c r="O7" s="228"/>
-      <c r="P7" s="229"/>
+      <c r="C7" s="206"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
+      <c r="J7" s="206"/>
+      <c r="K7" s="206"/>
+      <c r="L7" s="206"/>
+      <c r="M7" s="206"/>
+      <c r="N7" s="210"/>
+      <c r="O7" s="211"/>
+      <c r="P7" s="212"/>
       <c r="Q7" s="62"/>
-      <c r="R7" s="230"/>
-      <c r="S7" s="230"/>
+      <c r="R7" s="213"/>
+      <c r="S7" s="213"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="226"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226"/>
-      <c r="M8" s="226"/>
-      <c r="N8" s="227"/>
-      <c r="O8" s="228"/>
-      <c r="P8" s="229"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
+      <c r="J8" s="206"/>
+      <c r="K8" s="206"/>
+      <c r="L8" s="206"/>
+      <c r="M8" s="206"/>
+      <c r="N8" s="210"/>
+      <c r="O8" s="211"/>
+      <c r="P8" s="212"/>
       <c r="Q8" s="62"/>
-      <c r="R8" s="230"/>
-      <c r="S8" s="230"/>
+      <c r="R8" s="213"/>
+      <c r="S8" s="213"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
-      <c r="C9" s="226"/>
-      <c r="D9" s="226"/>
-      <c r="E9" s="226"/>
-      <c r="F9" s="226"/>
-      <c r="G9" s="226"/>
-      <c r="H9" s="226"/>
-      <c r="I9" s="226"/>
-      <c r="J9" s="226"/>
-      <c r="K9" s="226"/>
-      <c r="L9" s="226"/>
-      <c r="M9" s="226"/>
-      <c r="N9" s="227"/>
-      <c r="O9" s="228"/>
-      <c r="P9" s="229"/>
+      <c r="C9" s="206"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
+      <c r="J9" s="206"/>
+      <c r="K9" s="206"/>
+      <c r="L9" s="206"/>
+      <c r="M9" s="206"/>
+      <c r="N9" s="210"/>
+      <c r="O9" s="211"/>
+      <c r="P9" s="212"/>
       <c r="Q9" s="61"/>
-      <c r="R9" s="230"/>
-      <c r="S9" s="230"/>
+      <c r="R9" s="213"/>
+      <c r="S9" s="213"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="61"/>
       <c r="B10" s="61"/>
-      <c r="C10" s="226"/>
-      <c r="D10" s="226"/>
-      <c r="E10" s="226"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="226"/>
-      <c r="H10" s="234"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="227"/>
-      <c r="O10" s="228"/>
-      <c r="P10" s="229"/>
+      <c r="C10" s="206"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="208"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="208"/>
+      <c r="L10" s="208"/>
+      <c r="M10" s="209"/>
+      <c r="N10" s="210"/>
+      <c r="O10" s="211"/>
+      <c r="P10" s="212"/>
       <c r="Q10" s="62"/>
-      <c r="R10" s="230"/>
-      <c r="S10" s="230"/>
+      <c r="R10" s="213"/>
+      <c r="S10" s="213"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="61"/>
       <c r="B11" s="61"/>
-      <c r="C11" s="226"/>
-      <c r="D11" s="226"/>
-      <c r="E11" s="226"/>
-      <c r="F11" s="226"/>
-      <c r="G11" s="226"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="235"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="227"/>
-      <c r="O11" s="228"/>
-      <c r="P11" s="229"/>
+      <c r="C11" s="206"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="208"/>
+      <c r="J11" s="208"/>
+      <c r="K11" s="208"/>
+      <c r="L11" s="208"/>
+      <c r="M11" s="209"/>
+      <c r="N11" s="210"/>
+      <c r="O11" s="211"/>
+      <c r="P11" s="212"/>
       <c r="Q11" s="61"/>
-      <c r="R11" s="230"/>
-      <c r="S11" s="230"/>
+      <c r="R11" s="213"/>
+      <c r="S11" s="213"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
-      <c r="C12" s="226"/>
-      <c r="D12" s="226"/>
-      <c r="E12" s="226"/>
-      <c r="F12" s="226"/>
-      <c r="G12" s="226"/>
-      <c r="H12" s="234"/>
-      <c r="I12" s="235"/>
-      <c r="J12" s="235"/>
-      <c r="K12" s="235"/>
-      <c r="L12" s="235"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="227"/>
-      <c r="O12" s="228"/>
-      <c r="P12" s="229"/>
+      <c r="C12" s="206"/>
+      <c r="D12" s="206"/>
+      <c r="E12" s="206"/>
+      <c r="F12" s="206"/>
+      <c r="G12" s="206"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="208"/>
+      <c r="L12" s="208"/>
+      <c r="M12" s="209"/>
+      <c r="N12" s="210"/>
+      <c r="O12" s="211"/>
+      <c r="P12" s="212"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="230"/>
-      <c r="S12" s="230"/>
+      <c r="R12" s="213"/>
+      <c r="S12" s="213"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
-      <c r="C13" s="226"/>
-      <c r="D13" s="226"/>
-      <c r="E13" s="226"/>
-      <c r="F13" s="226"/>
-      <c r="G13" s="226"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
-      <c r="M13" s="236"/>
-      <c r="N13" s="227"/>
-      <c r="O13" s="228"/>
-      <c r="P13" s="229"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
+      <c r="F13" s="206"/>
+      <c r="G13" s="206"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="208"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="208"/>
+      <c r="L13" s="208"/>
+      <c r="M13" s="209"/>
+      <c r="N13" s="210"/>
+      <c r="O13" s="211"/>
+      <c r="P13" s="212"/>
       <c r="Q13" s="61"/>
-      <c r="R13" s="230"/>
-      <c r="S13" s="230"/>
+      <c r="R13" s="213"/>
+      <c r="S13" s="213"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="61"/>
       <c r="B14" s="61"/>
-      <c r="C14" s="226"/>
-      <c r="D14" s="226"/>
-      <c r="E14" s="226"/>
-      <c r="F14" s="226"/>
-      <c r="G14" s="226"/>
-      <c r="H14" s="234"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
-      <c r="L14" s="235"/>
-      <c r="M14" s="236"/>
-      <c r="N14" s="227"/>
-      <c r="O14" s="228"/>
-      <c r="P14" s="229"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
+      <c r="M14" s="209"/>
+      <c r="N14" s="210"/>
+      <c r="O14" s="211"/>
+      <c r="P14" s="212"/>
       <c r="Q14" s="61"/>
-      <c r="R14" s="230"/>
-      <c r="S14" s="230"/>
+      <c r="R14" s="213"/>
+      <c r="S14" s="213"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
-      <c r="C15" s="226"/>
-      <c r="D15" s="226"/>
-      <c r="E15" s="226"/>
-      <c r="F15" s="226"/>
-      <c r="G15" s="226"/>
-      <c r="H15" s="234"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="235"/>
-      <c r="L15" s="235"/>
-      <c r="M15" s="236"/>
-      <c r="N15" s="227"/>
-      <c r="O15" s="228"/>
-      <c r="P15" s="229"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="207"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="208"/>
+      <c r="K15" s="208"/>
+      <c r="L15" s="208"/>
+      <c r="M15" s="209"/>
+      <c r="N15" s="210"/>
+      <c r="O15" s="211"/>
+      <c r="P15" s="212"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="230"/>
-      <c r="S15" s="230"/>
+      <c r="R15" s="213"/>
+      <c r="S15" s="213"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
-      <c r="C16" s="226"/>
-      <c r="D16" s="226"/>
-      <c r="E16" s="226"/>
-      <c r="F16" s="226"/>
-      <c r="G16" s="226"/>
-      <c r="H16" s="234"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="235"/>
-      <c r="L16" s="235"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="227"/>
-      <c r="O16" s="228"/>
-      <c r="P16" s="229"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+      <c r="F16" s="206"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="208"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="210"/>
+      <c r="O16" s="211"/>
+      <c r="P16" s="212"/>
       <c r="Q16" s="61"/>
-      <c r="R16" s="230"/>
-      <c r="S16" s="230"/>
+      <c r="R16" s="213"/>
+      <c r="S16" s="213"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="61"/>
       <c r="B17" s="61"/>
-      <c r="C17" s="226"/>
-      <c r="D17" s="226"/>
-      <c r="E17" s="226"/>
-      <c r="F17" s="226"/>
-      <c r="G17" s="226"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="235"/>
-      <c r="L17" s="235"/>
-      <c r="M17" s="236"/>
-      <c r="N17" s="227"/>
-      <c r="O17" s="228"/>
-      <c r="P17" s="229"/>
+      <c r="C17" s="206"/>
+      <c r="D17" s="206"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="206"/>
+      <c r="G17" s="206"/>
+      <c r="H17" s="207"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="208"/>
+      <c r="M17" s="209"/>
+      <c r="N17" s="210"/>
+      <c r="O17" s="211"/>
+      <c r="P17" s="212"/>
       <c r="Q17" s="61"/>
-      <c r="R17" s="230"/>
-      <c r="S17" s="230"/>
+      <c r="R17" s="213"/>
+      <c r="S17" s="213"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
-      <c r="C18" s="226"/>
-      <c r="D18" s="226"/>
-      <c r="E18" s="226"/>
-      <c r="F18" s="226"/>
-      <c r="G18" s="226"/>
-      <c r="H18" s="234"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
-      <c r="M18" s="236"/>
-      <c r="N18" s="227"/>
-      <c r="O18" s="228"/>
-      <c r="P18" s="229"/>
+      <c r="C18" s="206"/>
+      <c r="D18" s="206"/>
+      <c r="E18" s="206"/>
+      <c r="F18" s="206"/>
+      <c r="G18" s="206"/>
+      <c r="H18" s="207"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="208"/>
+      <c r="L18" s="208"/>
+      <c r="M18" s="209"/>
+      <c r="N18" s="210"/>
+      <c r="O18" s="211"/>
+      <c r="P18" s="212"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="230"/>
-      <c r="S18" s="230"/>
+      <c r="R18" s="213"/>
+      <c r="S18" s="213"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
-      <c r="C19" s="226"/>
-      <c r="D19" s="226"/>
-      <c r="E19" s="226"/>
-      <c r="F19" s="226"/>
-      <c r="G19" s="226"/>
-      <c r="H19" s="234"/>
-      <c r="I19" s="235"/>
-      <c r="J19" s="235"/>
-      <c r="K19" s="235"/>
-      <c r="L19" s="235"/>
-      <c r="M19" s="236"/>
-      <c r="N19" s="227"/>
-      <c r="O19" s="228"/>
-      <c r="P19" s="229"/>
+      <c r="C19" s="206"/>
+      <c r="D19" s="206"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="206"/>
+      <c r="G19" s="206"/>
+      <c r="H19" s="207"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="208"/>
+      <c r="L19" s="208"/>
+      <c r="M19" s="209"/>
+      <c r="N19" s="210"/>
+      <c r="O19" s="211"/>
+      <c r="P19" s="212"/>
       <c r="Q19" s="61"/>
-      <c r="R19" s="230"/>
-      <c r="S19" s="230"/>
+      <c r="R19" s="213"/>
+      <c r="S19" s="213"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
-      <c r="C20" s="226"/>
-      <c r="D20" s="226"/>
-      <c r="E20" s="226"/>
-      <c r="F20" s="226"/>
-      <c r="G20" s="226"/>
-      <c r="H20" s="234"/>
-      <c r="I20" s="235"/>
-      <c r="J20" s="235"/>
-      <c r="K20" s="235"/>
-      <c r="L20" s="235"/>
-      <c r="M20" s="236"/>
-      <c r="N20" s="227"/>
-      <c r="O20" s="228"/>
-      <c r="P20" s="229"/>
+      <c r="C20" s="206"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="206"/>
+      <c r="F20" s="206"/>
+      <c r="G20" s="206"/>
+      <c r="H20" s="207"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
+      <c r="L20" s="208"/>
+      <c r="M20" s="209"/>
+      <c r="N20" s="210"/>
+      <c r="O20" s="211"/>
+      <c r="P20" s="212"/>
       <c r="Q20" s="61"/>
-      <c r="R20" s="230"/>
-      <c r="S20" s="230"/>
+      <c r="R20" s="213"/>
+      <c r="S20" s="213"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
-      <c r="C21" s="226"/>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="234"/>
-      <c r="I21" s="235"/>
-      <c r="J21" s="235"/>
-      <c r="K21" s="235"/>
-      <c r="L21" s="235"/>
-      <c r="M21" s="236"/>
-      <c r="N21" s="227"/>
-      <c r="O21" s="228"/>
-      <c r="P21" s="229"/>
+      <c r="C21" s="206"/>
+      <c r="D21" s="206"/>
+      <c r="E21" s="206"/>
+      <c r="F21" s="206"/>
+      <c r="G21" s="206"/>
+      <c r="H21" s="207"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="208"/>
+      <c r="L21" s="208"/>
+      <c r="M21" s="209"/>
+      <c r="N21" s="210"/>
+      <c r="O21" s="211"/>
+      <c r="P21" s="212"/>
       <c r="Q21" s="61"/>
-      <c r="R21" s="230"/>
-      <c r="S21" s="230"/>
+      <c r="R21" s="213"/>
+      <c r="S21" s="213"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="226"/>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="234"/>
-      <c r="I22" s="235"/>
-      <c r="J22" s="235"/>
-      <c r="K22" s="235"/>
-      <c r="L22" s="235"/>
-      <c r="M22" s="236"/>
-      <c r="N22" s="227"/>
-      <c r="O22" s="228"/>
-      <c r="P22" s="229"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="207"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="208"/>
+      <c r="K22" s="208"/>
+      <c r="L22" s="208"/>
+      <c r="M22" s="209"/>
+      <c r="N22" s="210"/>
+      <c r="O22" s="211"/>
+      <c r="P22" s="212"/>
       <c r="Q22" s="61"/>
-      <c r="R22" s="230"/>
-      <c r="S22" s="230"/>
+      <c r="R22" s="213"/>
+      <c r="S22" s="213"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="61"/>
       <c r="B23" s="61"/>
-      <c r="C23" s="226"/>
-      <c r="D23" s="226"/>
-      <c r="E23" s="226"/>
-      <c r="F23" s="226"/>
-      <c r="G23" s="226"/>
-      <c r="H23" s="234"/>
-      <c r="I23" s="235"/>
-      <c r="J23" s="235"/>
-      <c r="K23" s="235"/>
-      <c r="L23" s="235"/>
-      <c r="M23" s="236"/>
-      <c r="N23" s="227"/>
-      <c r="O23" s="228"/>
-      <c r="P23" s="229"/>
+      <c r="C23" s="206"/>
+      <c r="D23" s="206"/>
+      <c r="E23" s="206"/>
+      <c r="F23" s="206"/>
+      <c r="G23" s="206"/>
+      <c r="H23" s="207"/>
+      <c r="I23" s="208"/>
+      <c r="J23" s="208"/>
+      <c r="K23" s="208"/>
+      <c r="L23" s="208"/>
+      <c r="M23" s="209"/>
+      <c r="N23" s="210"/>
+      <c r="O23" s="211"/>
+      <c r="P23" s="212"/>
       <c r="Q23" s="61"/>
-      <c r="R23" s="230"/>
-      <c r="S23" s="230"/>
+      <c r="R23" s="213"/>
+      <c r="S23" s="213"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="61"/>
-      <c r="C24" s="226"/>
-      <c r="D24" s="226"/>
-      <c r="E24" s="226"/>
-      <c r="F24" s="226"/>
-      <c r="G24" s="226"/>
-      <c r="H24" s="234"/>
-      <c r="I24" s="235"/>
-      <c r="J24" s="235"/>
-      <c r="K24" s="235"/>
-      <c r="L24" s="235"/>
-      <c r="M24" s="236"/>
-      <c r="N24" s="227"/>
-      <c r="O24" s="228"/>
-      <c r="P24" s="229"/>
+      <c r="C24" s="206"/>
+      <c r="D24" s="206"/>
+      <c r="E24" s="206"/>
+      <c r="F24" s="206"/>
+      <c r="G24" s="206"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="208"/>
+      <c r="J24" s="208"/>
+      <c r="K24" s="208"/>
+      <c r="L24" s="208"/>
+      <c r="M24" s="209"/>
+      <c r="N24" s="210"/>
+      <c r="O24" s="211"/>
+      <c r="P24" s="212"/>
       <c r="Q24" s="61"/>
-      <c r="R24" s="230"/>
-      <c r="S24" s="230"/>
+      <c r="R24" s="213"/>
+      <c r="S24" s="213"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
-      <c r="C25" s="226"/>
-      <c r="D25" s="226"/>
-      <c r="E25" s="226"/>
-      <c r="F25" s="226"/>
-      <c r="G25" s="226"/>
-      <c r="H25" s="234"/>
-      <c r="I25" s="235"/>
-      <c r="J25" s="235"/>
-      <c r="K25" s="235"/>
-      <c r="L25" s="235"/>
-      <c r="M25" s="236"/>
-      <c r="N25" s="227"/>
-      <c r="O25" s="228"/>
-      <c r="P25" s="229"/>
+      <c r="C25" s="206"/>
+      <c r="D25" s="206"/>
+      <c r="E25" s="206"/>
+      <c r="F25" s="206"/>
+      <c r="G25" s="206"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="208"/>
+      <c r="J25" s="208"/>
+      <c r="K25" s="208"/>
+      <c r="L25" s="208"/>
+      <c r="M25" s="209"/>
+      <c r="N25" s="210"/>
+      <c r="O25" s="211"/>
+      <c r="P25" s="212"/>
       <c r="Q25" s="61"/>
-      <c r="R25" s="230"/>
-      <c r="S25" s="230"/>
+      <c r="R25" s="213"/>
+      <c r="S25" s="213"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="61"/>
       <c r="B26" s="61"/>
-      <c r="C26" s="226"/>
-      <c r="D26" s="226"/>
-      <c r="E26" s="226"/>
-      <c r="F26" s="226"/>
-      <c r="G26" s="226"/>
-      <c r="H26" s="234"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
-      <c r="M26" s="236"/>
-      <c r="N26" s="227"/>
-      <c r="O26" s="228"/>
-      <c r="P26" s="229"/>
+      <c r="C26" s="206"/>
+      <c r="D26" s="206"/>
+      <c r="E26" s="206"/>
+      <c r="F26" s="206"/>
+      <c r="G26" s="206"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
+      <c r="M26" s="209"/>
+      <c r="N26" s="210"/>
+      <c r="O26" s="211"/>
+      <c r="P26" s="212"/>
       <c r="Q26" s="61"/>
-      <c r="R26" s="230"/>
-      <c r="S26" s="230"/>
+      <c r="R26" s="213"/>
+      <c r="S26" s="213"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="226"/>
-      <c r="D27" s="226"/>
-      <c r="E27" s="226"/>
-      <c r="F27" s="226"/>
-      <c r="G27" s="226"/>
-      <c r="H27" s="234"/>
-      <c r="I27" s="235"/>
-      <c r="J27" s="235"/>
-      <c r="K27" s="235"/>
-      <c r="L27" s="235"/>
-      <c r="M27" s="236"/>
-      <c r="N27" s="227"/>
-      <c r="O27" s="228"/>
-      <c r="P27" s="229"/>
+      <c r="C27" s="206"/>
+      <c r="D27" s="206"/>
+      <c r="E27" s="206"/>
+      <c r="F27" s="206"/>
+      <c r="G27" s="206"/>
+      <c r="H27" s="207"/>
+      <c r="I27" s="208"/>
+      <c r="J27" s="208"/>
+      <c r="K27" s="208"/>
+      <c r="L27" s="208"/>
+      <c r="M27" s="209"/>
+      <c r="N27" s="210"/>
+      <c r="O27" s="211"/>
+      <c r="P27" s="212"/>
       <c r="Q27" s="61"/>
-      <c r="R27" s="230"/>
-      <c r="S27" s="230"/>
+      <c r="R27" s="213"/>
+      <c r="S27" s="213"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="234"/>
-      <c r="I28" s="235"/>
-      <c r="J28" s="235"/>
-      <c r="K28" s="235"/>
-      <c r="L28" s="235"/>
-      <c r="M28" s="236"/>
-      <c r="N28" s="227"/>
-      <c r="O28" s="228"/>
-      <c r="P28" s="229"/>
+      <c r="C28" s="206"/>
+      <c r="D28" s="206"/>
+      <c r="E28" s="206"/>
+      <c r="F28" s="206"/>
+      <c r="G28" s="206"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="208"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="208"/>
+      <c r="L28" s="208"/>
+      <c r="M28" s="209"/>
+      <c r="N28" s="210"/>
+      <c r="O28" s="211"/>
+      <c r="P28" s="212"/>
       <c r="Q28" s="61"/>
-      <c r="R28" s="230"/>
-      <c r="S28" s="230"/>
+      <c r="R28" s="213"/>
+      <c r="S28" s="213"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
-      <c r="C29" s="226"/>
-      <c r="D29" s="226"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="226"/>
-      <c r="G29" s="226"/>
-      <c r="H29" s="234"/>
-      <c r="I29" s="235"/>
-      <c r="J29" s="235"/>
-      <c r="K29" s="235"/>
-      <c r="L29" s="235"/>
-      <c r="M29" s="236"/>
-      <c r="N29" s="227"/>
-      <c r="O29" s="228"/>
-      <c r="P29" s="229"/>
+      <c r="C29" s="206"/>
+      <c r="D29" s="206"/>
+      <c r="E29" s="206"/>
+      <c r="F29" s="206"/>
+      <c r="G29" s="206"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="208"/>
+      <c r="J29" s="208"/>
+      <c r="K29" s="208"/>
+      <c r="L29" s="208"/>
+      <c r="M29" s="209"/>
+      <c r="N29" s="210"/>
+      <c r="O29" s="211"/>
+      <c r="P29" s="212"/>
       <c r="Q29" s="61"/>
-      <c r="R29" s="230"/>
-      <c r="S29" s="230"/>
+      <c r="R29" s="213"/>
+      <c r="S29" s="213"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="61"/>
       <c r="B30" s="61"/>
-      <c r="C30" s="226"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="226"/>
-      <c r="F30" s="226"/>
-      <c r="G30" s="226"/>
-      <c r="H30" s="234"/>
-      <c r="I30" s="235"/>
-      <c r="J30" s="235"/>
-      <c r="K30" s="235"/>
-      <c r="L30" s="235"/>
-      <c r="M30" s="236"/>
-      <c r="N30" s="227"/>
-      <c r="O30" s="228"/>
-      <c r="P30" s="229"/>
+      <c r="C30" s="206"/>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="206"/>
+      <c r="G30" s="206"/>
+      <c r="H30" s="207"/>
+      <c r="I30" s="208"/>
+      <c r="J30" s="208"/>
+      <c r="K30" s="208"/>
+      <c r="L30" s="208"/>
+      <c r="M30" s="209"/>
+      <c r="N30" s="210"/>
+      <c r="O30" s="211"/>
+      <c r="P30" s="212"/>
       <c r="Q30" s="61"/>
-      <c r="R30" s="230"/>
-      <c r="S30" s="230"/>
+      <c r="R30" s="213"/>
+      <c r="S30" s="213"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="226"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="234"/>
-      <c r="I31" s="235"/>
-      <c r="J31" s="235"/>
-      <c r="K31" s="235"/>
-      <c r="L31" s="235"/>
-      <c r="M31" s="236"/>
-      <c r="N31" s="227"/>
-      <c r="O31" s="228"/>
-      <c r="P31" s="229"/>
+      <c r="C31" s="206"/>
+      <c r="D31" s="206"/>
+      <c r="E31" s="206"/>
+      <c r="F31" s="206"/>
+      <c r="G31" s="206"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="208"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="209"/>
+      <c r="N31" s="210"/>
+      <c r="O31" s="211"/>
+      <c r="P31" s="212"/>
       <c r="Q31" s="61"/>
-      <c r="R31" s="230"/>
-      <c r="S31" s="230"/>
+      <c r="R31" s="213"/>
+      <c r="S31" s="213"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="61"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="226"/>
-      <c r="D32" s="226"/>
-      <c r="E32" s="226"/>
-      <c r="F32" s="226"/>
-      <c r="G32" s="226"/>
-      <c r="H32" s="234"/>
-      <c r="I32" s="235"/>
-      <c r="J32" s="235"/>
-      <c r="K32" s="235"/>
-      <c r="L32" s="235"/>
-      <c r="M32" s="236"/>
-      <c r="N32" s="227"/>
-      <c r="O32" s="228"/>
-      <c r="P32" s="229"/>
+      <c r="C32" s="206"/>
+      <c r="D32" s="206"/>
+      <c r="E32" s="206"/>
+      <c r="F32" s="206"/>
+      <c r="G32" s="206"/>
+      <c r="H32" s="207"/>
+      <c r="I32" s="208"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="208"/>
+      <c r="L32" s="208"/>
+      <c r="M32" s="209"/>
+      <c r="N32" s="210"/>
+      <c r="O32" s="211"/>
+      <c r="P32" s="212"/>
       <c r="Q32" s="61"/>
-      <c r="R32" s="230"/>
-      <c r="S32" s="230"/>
+      <c r="R32" s="213"/>
+      <c r="S32" s="213"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
-      <c r="C33" s="226"/>
-      <c r="D33" s="226"/>
-      <c r="E33" s="226"/>
-      <c r="F33" s="226"/>
-      <c r="G33" s="226"/>
-      <c r="H33" s="234"/>
-      <c r="I33" s="235"/>
-      <c r="J33" s="235"/>
-      <c r="K33" s="235"/>
-      <c r="L33" s="235"/>
-      <c r="M33" s="236"/>
-      <c r="N33" s="227"/>
-      <c r="O33" s="228"/>
-      <c r="P33" s="229"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="206"/>
+      <c r="E33" s="206"/>
+      <c r="F33" s="206"/>
+      <c r="G33" s="206"/>
+      <c r="H33" s="207"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="209"/>
+      <c r="N33" s="210"/>
+      <c r="O33" s="211"/>
+      <c r="P33" s="212"/>
       <c r="Q33" s="61"/>
-      <c r="R33" s="230"/>
-      <c r="S33" s="230"/>
+      <c r="R33" s="213"/>
+      <c r="S33" s="213"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="226"/>
-      <c r="D34" s="226"/>
-      <c r="E34" s="226"/>
-      <c r="F34" s="226"/>
-      <c r="G34" s="226"/>
-      <c r="H34" s="234"/>
-      <c r="I34" s="235"/>
-      <c r="J34" s="235"/>
-      <c r="K34" s="235"/>
-      <c r="L34" s="235"/>
-      <c r="M34" s="236"/>
-      <c r="N34" s="227"/>
-      <c r="O34" s="228"/>
-      <c r="P34" s="229"/>
+      <c r="C34" s="206"/>
+      <c r="D34" s="206"/>
+      <c r="E34" s="206"/>
+      <c r="F34" s="206"/>
+      <c r="G34" s="206"/>
+      <c r="H34" s="207"/>
+      <c r="I34" s="208"/>
+      <c r="J34" s="208"/>
+      <c r="K34" s="208"/>
+      <c r="L34" s="208"/>
+      <c r="M34" s="209"/>
+      <c r="N34" s="210"/>
+      <c r="O34" s="211"/>
+      <c r="P34" s="212"/>
       <c r="Q34" s="61"/>
-      <c r="R34" s="230"/>
-      <c r="S34" s="230"/>
+      <c r="R34" s="213"/>
+      <c r="S34" s="213"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
-      <c r="C35" s="226"/>
-      <c r="D35" s="226"/>
-      <c r="E35" s="226"/>
-      <c r="F35" s="226"/>
-      <c r="G35" s="226"/>
-      <c r="H35" s="234"/>
-      <c r="I35" s="235"/>
-      <c r="J35" s="235"/>
-      <c r="K35" s="235"/>
-      <c r="L35" s="235"/>
-      <c r="M35" s="236"/>
-      <c r="N35" s="227"/>
-      <c r="O35" s="228"/>
-      <c r="P35" s="229"/>
+      <c r="C35" s="206"/>
+      <c r="D35" s="206"/>
+      <c r="E35" s="206"/>
+      <c r="F35" s="206"/>
+      <c r="G35" s="206"/>
+      <c r="H35" s="207"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="208"/>
+      <c r="K35" s="208"/>
+      <c r="L35" s="208"/>
+      <c r="M35" s="209"/>
+      <c r="N35" s="210"/>
+      <c r="O35" s="211"/>
+      <c r="P35" s="212"/>
       <c r="Q35" s="61"/>
-      <c r="R35" s="230"/>
-      <c r="S35" s="230"/>
+      <c r="R35" s="213"/>
+      <c r="S35" s="213"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="61"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="226"/>
-      <c r="D36" s="226"/>
-      <c r="E36" s="226"/>
-      <c r="F36" s="226"/>
-      <c r="G36" s="226"/>
-      <c r="H36" s="234"/>
-      <c r="I36" s="235"/>
-      <c r="J36" s="235"/>
-      <c r="K36" s="235"/>
-      <c r="L36" s="235"/>
-      <c r="M36" s="236"/>
-      <c r="N36" s="227"/>
-      <c r="O36" s="228"/>
-      <c r="P36" s="229"/>
+      <c r="C36" s="206"/>
+      <c r="D36" s="206"/>
+      <c r="E36" s="206"/>
+      <c r="F36" s="206"/>
+      <c r="G36" s="206"/>
+      <c r="H36" s="207"/>
+      <c r="I36" s="208"/>
+      <c r="J36" s="208"/>
+      <c r="K36" s="208"/>
+      <c r="L36" s="208"/>
+      <c r="M36" s="209"/>
+      <c r="N36" s="210"/>
+      <c r="O36" s="211"/>
+      <c r="P36" s="212"/>
       <c r="Q36" s="61"/>
-      <c r="R36" s="230"/>
-      <c r="S36" s="230"/>
+      <c r="R36" s="213"/>
+      <c r="S36" s="213"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
-      <c r="C37" s="226"/>
-      <c r="D37" s="226"/>
-      <c r="E37" s="226"/>
-      <c r="F37" s="226"/>
-      <c r="G37" s="226"/>
-      <c r="H37" s="234"/>
-      <c r="I37" s="235"/>
-      <c r="J37" s="235"/>
-      <c r="K37" s="235"/>
-      <c r="L37" s="235"/>
-      <c r="M37" s="236"/>
-      <c r="N37" s="227"/>
-      <c r="O37" s="228"/>
-      <c r="P37" s="229"/>
+      <c r="C37" s="206"/>
+      <c r="D37" s="206"/>
+      <c r="E37" s="206"/>
+      <c r="F37" s="206"/>
+      <c r="G37" s="206"/>
+      <c r="H37" s="207"/>
+      <c r="I37" s="208"/>
+      <c r="J37" s="208"/>
+      <c r="K37" s="208"/>
+      <c r="L37" s="208"/>
+      <c r="M37" s="209"/>
+      <c r="N37" s="210"/>
+      <c r="O37" s="211"/>
+      <c r="P37" s="212"/>
       <c r="Q37" s="61"/>
-      <c r="R37" s="230"/>
-      <c r="S37" s="230"/>
+      <c r="R37" s="213"/>
+      <c r="S37" s="213"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="61"/>
       <c r="B38" s="61"/>
-      <c r="C38" s="226"/>
-      <c r="D38" s="226"/>
-      <c r="E38" s="226"/>
-      <c r="F38" s="226"/>
-      <c r="G38" s="226"/>
-      <c r="H38" s="234"/>
-      <c r="I38" s="235"/>
-      <c r="J38" s="235"/>
-      <c r="K38" s="235"/>
-      <c r="L38" s="235"/>
-      <c r="M38" s="236"/>
-      <c r="N38" s="227"/>
-      <c r="O38" s="228"/>
-      <c r="P38" s="229"/>
+      <c r="C38" s="206"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="206"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="207"/>
+      <c r="I38" s="208"/>
+      <c r="J38" s="208"/>
+      <c r="K38" s="208"/>
+      <c r="L38" s="208"/>
+      <c r="M38" s="209"/>
+      <c r="N38" s="210"/>
+      <c r="O38" s="211"/>
+      <c r="P38" s="212"/>
       <c r="Q38" s="61"/>
-      <c r="R38" s="230"/>
-      <c r="S38" s="230"/>
+      <c r="R38" s="213"/>
+      <c r="S38" s="213"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="226"/>
-      <c r="D39" s="226"/>
-      <c r="E39" s="226"/>
-      <c r="F39" s="226"/>
-      <c r="G39" s="226"/>
-      <c r="H39" s="234"/>
-      <c r="I39" s="235"/>
-      <c r="J39" s="235"/>
-      <c r="K39" s="235"/>
-      <c r="L39" s="235"/>
-      <c r="M39" s="236"/>
-      <c r="N39" s="227"/>
-      <c r="O39" s="228"/>
-      <c r="P39" s="229"/>
+      <c r="C39" s="206"/>
+      <c r="D39" s="206"/>
+      <c r="E39" s="206"/>
+      <c r="F39" s="206"/>
+      <c r="G39" s="206"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="209"/>
+      <c r="N39" s="210"/>
+      <c r="O39" s="211"/>
+      <c r="P39" s="212"/>
       <c r="Q39" s="61"/>
-      <c r="R39" s="230"/>
-      <c r="S39" s="230"/>
+      <c r="R39" s="213"/>
+      <c r="S39" s="213"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="61"/>
       <c r="B40" s="61"/>
-      <c r="C40" s="226"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="235"/>
-      <c r="J40" s="235"/>
-      <c r="K40" s="235"/>
-      <c r="L40" s="235"/>
-      <c r="M40" s="236"/>
-      <c r="N40" s="227"/>
-      <c r="O40" s="228"/>
-      <c r="P40" s="229"/>
+      <c r="C40" s="206"/>
+      <c r="D40" s="206"/>
+      <c r="E40" s="206"/>
+      <c r="F40" s="206"/>
+      <c r="G40" s="206"/>
+      <c r="H40" s="207"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="209"/>
+      <c r="N40" s="210"/>
+      <c r="O40" s="211"/>
+      <c r="P40" s="212"/>
       <c r="Q40" s="61"/>
-      <c r="R40" s="230"/>
-      <c r="S40" s="230"/>
+      <c r="R40" s="213"/>
+      <c r="S40" s="213"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
-      <c r="C41" s="226"/>
-      <c r="D41" s="226"/>
-      <c r="E41" s="226"/>
-      <c r="F41" s="226"/>
-      <c r="G41" s="226"/>
-      <c r="H41" s="234"/>
-      <c r="I41" s="235"/>
-      <c r="J41" s="235"/>
-      <c r="K41" s="235"/>
-      <c r="L41" s="235"/>
-      <c r="M41" s="236"/>
-      <c r="N41" s="227"/>
-      <c r="O41" s="228"/>
-      <c r="P41" s="229"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="206"/>
+      <c r="E41" s="206"/>
+      <c r="F41" s="206"/>
+      <c r="G41" s="206"/>
+      <c r="H41" s="207"/>
+      <c r="I41" s="208"/>
+      <c r="J41" s="208"/>
+      <c r="K41" s="208"/>
+      <c r="L41" s="208"/>
+      <c r="M41" s="209"/>
+      <c r="N41" s="210"/>
+      <c r="O41" s="211"/>
+      <c r="P41" s="212"/>
       <c r="Q41" s="61"/>
-      <c r="R41" s="230"/>
-      <c r="S41" s="230"/>
+      <c r="R41" s="213"/>
+      <c r="S41" s="213"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="61"/>
       <c r="B42" s="61"/>
-      <c r="C42" s="226"/>
-      <c r="D42" s="226"/>
-      <c r="E42" s="226"/>
-      <c r="F42" s="226"/>
-      <c r="G42" s="226"/>
-      <c r="H42" s="234"/>
-      <c r="I42" s="235"/>
-      <c r="J42" s="235"/>
-      <c r="K42" s="235"/>
-      <c r="L42" s="235"/>
-      <c r="M42" s="236"/>
-      <c r="N42" s="227"/>
-      <c r="O42" s="228"/>
-      <c r="P42" s="229"/>
+      <c r="C42" s="206"/>
+      <c r="D42" s="206"/>
+      <c r="E42" s="206"/>
+      <c r="F42" s="206"/>
+      <c r="G42" s="206"/>
+      <c r="H42" s="207"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="208"/>
+      <c r="K42" s="208"/>
+      <c r="L42" s="208"/>
+      <c r="M42" s="209"/>
+      <c r="N42" s="210"/>
+      <c r="O42" s="211"/>
+      <c r="P42" s="212"/>
       <c r="Q42" s="61"/>
-      <c r="R42" s="230"/>
-      <c r="S42" s="230"/>
+      <c r="R42" s="213"/>
+      <c r="S42" s="213"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
-      <c r="C43" s="226"/>
-      <c r="D43" s="226"/>
-      <c r="E43" s="226"/>
-      <c r="F43" s="226"/>
-      <c r="G43" s="226"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="235"/>
-      <c r="J43" s="235"/>
-      <c r="K43" s="235"/>
-      <c r="L43" s="235"/>
-      <c r="M43" s="236"/>
-      <c r="N43" s="227"/>
-      <c r="O43" s="228"/>
-      <c r="P43" s="229"/>
+      <c r="C43" s="206"/>
+      <c r="D43" s="206"/>
+      <c r="E43" s="206"/>
+      <c r="F43" s="206"/>
+      <c r="G43" s="206"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="208"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="209"/>
+      <c r="N43" s="210"/>
+      <c r="O43" s="211"/>
+      <c r="P43" s="212"/>
       <c r="Q43" s="61"/>
-      <c r="R43" s="230"/>
-      <c r="S43" s="230"/>
+      <c r="R43" s="213"/>
+      <c r="S43" s="213"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="61"/>
       <c r="B44" s="61"/>
-      <c r="C44" s="226"/>
-      <c r="D44" s="226"/>
-      <c r="E44" s="226"/>
-      <c r="F44" s="226"/>
-      <c r="G44" s="226"/>
-      <c r="H44" s="234"/>
-      <c r="I44" s="235"/>
-      <c r="J44" s="235"/>
-      <c r="K44" s="235"/>
-      <c r="L44" s="235"/>
-      <c r="M44" s="236"/>
-      <c r="N44" s="227"/>
-      <c r="O44" s="228"/>
-      <c r="P44" s="229"/>
+      <c r="C44" s="206"/>
+      <c r="D44" s="206"/>
+      <c r="E44" s="206"/>
+      <c r="F44" s="206"/>
+      <c r="G44" s="206"/>
+      <c r="H44" s="207"/>
+      <c r="I44" s="208"/>
+      <c r="J44" s="208"/>
+      <c r="K44" s="208"/>
+      <c r="L44" s="208"/>
+      <c r="M44" s="209"/>
+      <c r="N44" s="210"/>
+      <c r="O44" s="211"/>
+      <c r="P44" s="212"/>
       <c r="Q44" s="61"/>
-      <c r="R44" s="230"/>
-      <c r="S44" s="230"/>
+      <c r="R44" s="213"/>
+      <c r="S44" s="213"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
-      <c r="C45" s="226"/>
-      <c r="D45" s="226"/>
-      <c r="E45" s="226"/>
-      <c r="F45" s="226"/>
-      <c r="G45" s="226"/>
-      <c r="H45" s="234"/>
-      <c r="I45" s="235"/>
-      <c r="J45" s="235"/>
-      <c r="K45" s="235"/>
-      <c r="L45" s="235"/>
-      <c r="M45" s="236"/>
-      <c r="N45" s="227"/>
-      <c r="O45" s="228"/>
-      <c r="P45" s="229"/>
+      <c r="C45" s="206"/>
+      <c r="D45" s="206"/>
+      <c r="E45" s="206"/>
+      <c r="F45" s="206"/>
+      <c r="G45" s="206"/>
+      <c r="H45" s="207"/>
+      <c r="I45" s="208"/>
+      <c r="J45" s="208"/>
+      <c r="K45" s="208"/>
+      <c r="L45" s="208"/>
+      <c r="M45" s="209"/>
+      <c r="N45" s="210"/>
+      <c r="O45" s="211"/>
+      <c r="P45" s="212"/>
       <c r="Q45" s="61"/>
-      <c r="R45" s="230"/>
-      <c r="S45" s="230"/>
+      <c r="R45" s="213"/>
+      <c r="S45" s="213"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="61"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="226"/>
-      <c r="D46" s="226"/>
-      <c r="E46" s="226"/>
-      <c r="F46" s="226"/>
-      <c r="G46" s="226"/>
-      <c r="H46" s="234"/>
-      <c r="I46" s="235"/>
-      <c r="J46" s="235"/>
-      <c r="K46" s="235"/>
-      <c r="L46" s="235"/>
-      <c r="M46" s="236"/>
-      <c r="N46" s="227"/>
-      <c r="O46" s="228"/>
-      <c r="P46" s="229"/>
+      <c r="C46" s="206"/>
+      <c r="D46" s="206"/>
+      <c r="E46" s="206"/>
+      <c r="F46" s="206"/>
+      <c r="G46" s="206"/>
+      <c r="H46" s="207"/>
+      <c r="I46" s="208"/>
+      <c r="J46" s="208"/>
+      <c r="K46" s="208"/>
+      <c r="L46" s="208"/>
+      <c r="M46" s="209"/>
+      <c r="N46" s="210"/>
+      <c r="O46" s="211"/>
+      <c r="P46" s="212"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="230"/>
-      <c r="S46" s="230"/>
+      <c r="R46" s="213"/>
+      <c r="S46" s="213"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
-      <c r="C47" s="226"/>
-      <c r="D47" s="226"/>
-      <c r="E47" s="226"/>
-      <c r="F47" s="226"/>
-      <c r="G47" s="226"/>
-      <c r="H47" s="234"/>
-      <c r="I47" s="235"/>
-      <c r="J47" s="235"/>
-      <c r="K47" s="235"/>
-      <c r="L47" s="235"/>
-      <c r="M47" s="236"/>
-      <c r="N47" s="227"/>
-      <c r="O47" s="228"/>
-      <c r="P47" s="229"/>
+      <c r="C47" s="206"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="206"/>
+      <c r="F47" s="206"/>
+      <c r="G47" s="206"/>
+      <c r="H47" s="207"/>
+      <c r="I47" s="208"/>
+      <c r="J47" s="208"/>
+      <c r="K47" s="208"/>
+      <c r="L47" s="208"/>
+      <c r="M47" s="209"/>
+      <c r="N47" s="210"/>
+      <c r="O47" s="211"/>
+      <c r="P47" s="212"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="230"/>
-      <c r="S47" s="230"/>
+      <c r="R47" s="213"/>
+      <c r="S47" s="213"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="61"/>
       <c r="B48" s="61"/>
-      <c r="C48" s="226"/>
-      <c r="D48" s="226"/>
-      <c r="E48" s="226"/>
-      <c r="F48" s="226"/>
-      <c r="G48" s="226"/>
-      <c r="H48" s="234"/>
-      <c r="I48" s="235"/>
-      <c r="J48" s="235"/>
-      <c r="K48" s="235"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="236"/>
-      <c r="N48" s="227"/>
-      <c r="O48" s="228"/>
-      <c r="P48" s="229"/>
+      <c r="C48" s="206"/>
+      <c r="D48" s="206"/>
+      <c r="E48" s="206"/>
+      <c r="F48" s="206"/>
+      <c r="G48" s="206"/>
+      <c r="H48" s="207"/>
+      <c r="I48" s="208"/>
+      <c r="J48" s="208"/>
+      <c r="K48" s="208"/>
+      <c r="L48" s="208"/>
+      <c r="M48" s="209"/>
+      <c r="N48" s="210"/>
+      <c r="O48" s="211"/>
+      <c r="P48" s="212"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="230"/>
-      <c r="S48" s="230"/>
+      <c r="R48" s="213"/>
+      <c r="S48" s="213"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
-      <c r="C49" s="226"/>
-      <c r="D49" s="226"/>
-      <c r="E49" s="226"/>
-      <c r="F49" s="226"/>
-      <c r="G49" s="226"/>
-      <c r="H49" s="234"/>
-      <c r="I49" s="235"/>
-      <c r="J49" s="235"/>
-      <c r="K49" s="235"/>
-      <c r="L49" s="235"/>
-      <c r="M49" s="236"/>
-      <c r="N49" s="227"/>
-      <c r="O49" s="228"/>
-      <c r="P49" s="229"/>
+      <c r="C49" s="206"/>
+      <c r="D49" s="206"/>
+      <c r="E49" s="206"/>
+      <c r="F49" s="206"/>
+      <c r="G49" s="206"/>
+      <c r="H49" s="207"/>
+      <c r="I49" s="208"/>
+      <c r="J49" s="208"/>
+      <c r="K49" s="208"/>
+      <c r="L49" s="208"/>
+      <c r="M49" s="209"/>
+      <c r="N49" s="210"/>
+      <c r="O49" s="211"/>
+      <c r="P49" s="212"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="230"/>
-      <c r="S49" s="230"/>
+      <c r="R49" s="213"/>
+      <c r="S49" s="213"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="61"/>
       <c r="B50" s="61"/>
-      <c r="C50" s="226"/>
-      <c r="D50" s="226"/>
-      <c r="E50" s="226"/>
-      <c r="F50" s="226"/>
-      <c r="G50" s="226"/>
-      <c r="H50" s="234"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="236"/>
-      <c r="N50" s="227"/>
-      <c r="O50" s="228"/>
-      <c r="P50" s="229"/>
+      <c r="C50" s="206"/>
+      <c r="D50" s="206"/>
+      <c r="E50" s="206"/>
+      <c r="F50" s="206"/>
+      <c r="G50" s="206"/>
+      <c r="H50" s="207"/>
+      <c r="I50" s="208"/>
+      <c r="J50" s="208"/>
+      <c r="K50" s="208"/>
+      <c r="L50" s="208"/>
+      <c r="M50" s="209"/>
+      <c r="N50" s="210"/>
+      <c r="O50" s="211"/>
+      <c r="P50" s="212"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="230"/>
-      <c r="S50" s="230"/>
+      <c r="R50" s="213"/>
+      <c r="S50" s="213"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
-      <c r="C51" s="226"/>
-      <c r="D51" s="226"/>
-      <c r="E51" s="226"/>
-      <c r="F51" s="226"/>
-      <c r="G51" s="226"/>
-      <c r="H51" s="234"/>
-      <c r="I51" s="235"/>
-      <c r="J51" s="235"/>
-      <c r="K51" s="235"/>
-      <c r="L51" s="235"/>
-      <c r="M51" s="236"/>
-      <c r="N51" s="227"/>
-      <c r="O51" s="228"/>
-      <c r="P51" s="229"/>
+      <c r="C51" s="206"/>
+      <c r="D51" s="206"/>
+      <c r="E51" s="206"/>
+      <c r="F51" s="206"/>
+      <c r="G51" s="206"/>
+      <c r="H51" s="207"/>
+      <c r="I51" s="208"/>
+      <c r="J51" s="208"/>
+      <c r="K51" s="208"/>
+      <c r="L51" s="208"/>
+      <c r="M51" s="209"/>
+      <c r="N51" s="210"/>
+      <c r="O51" s="211"/>
+      <c r="P51" s="212"/>
       <c r="Q51" s="61"/>
-      <c r="R51" s="230"/>
-      <c r="S51" s="230"/>
+      <c r="R51" s="213"/>
+      <c r="S51" s="213"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="61"/>
       <c r="B52" s="61"/>
-      <c r="C52" s="226"/>
-      <c r="D52" s="226"/>
-      <c r="E52" s="226"/>
-      <c r="F52" s="226"/>
-      <c r="G52" s="226"/>
-      <c r="H52" s="234"/>
-      <c r="I52" s="235"/>
-      <c r="J52" s="235"/>
-      <c r="K52" s="235"/>
-      <c r="L52" s="235"/>
-      <c r="M52" s="236"/>
-      <c r="N52" s="227"/>
-      <c r="O52" s="228"/>
-      <c r="P52" s="229"/>
+      <c r="C52" s="206"/>
+      <c r="D52" s="206"/>
+      <c r="E52" s="206"/>
+      <c r="F52" s="206"/>
+      <c r="G52" s="206"/>
+      <c r="H52" s="207"/>
+      <c r="I52" s="208"/>
+      <c r="J52" s="208"/>
+      <c r="K52" s="208"/>
+      <c r="L52" s="208"/>
+      <c r="M52" s="209"/>
+      <c r="N52" s="210"/>
+      <c r="O52" s="211"/>
+      <c r="P52" s="212"/>
       <c r="Q52" s="61"/>
-      <c r="R52" s="230"/>
-      <c r="S52" s="230"/>
+      <c r="R52" s="213"/>
+      <c r="S52" s="213"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -13125,10 +13244,848 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210DC9A3-1AF4-4E08-9335-F510FB3A9446}">
+  <dimension ref="A1:O69"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="247"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A1" s="237" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="238"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="240" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="241"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="242" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="241"/>
+      <c r="I1" s="243" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="244"/>
+      <c r="K1" s="243" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="244"/>
+      <c r="M1" s="243" t="s">
+        <v>119</v>
+      </c>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="248"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="237" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="250"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="237" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="250"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="265">
+        <v>45827</v>
+      </c>
+      <c r="J2" s="238"/>
+      <c r="K2" s="266" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="238"/>
+      <c r="M2" s="237"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="251"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A3" s="252"/>
+      <c r="B3" s="253"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="252"/>
+      <c r="N3" s="253"/>
+      <c r="O3" s="251"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="237" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="238"/>
+      <c r="C4" s="267" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="M4" s="255"/>
+      <c r="N4" s="256"/>
+      <c r="O4" s="251"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A5" s="252"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="M5" s="258"/>
+      <c r="N5" s="259"/>
+      <c r="O5" s="251"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A6" s="243" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="244"/>
+      <c r="C6" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="245"/>
+      <c r="E6" s="245"/>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
+      <c r="I6" s="245"/>
+      <c r="J6" s="245"/>
+      <c r="K6" s="245"/>
+      <c r="L6" s="245"/>
+      <c r="M6" s="245"/>
+      <c r="N6" s="244"/>
+      <c r="O6" s="251"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="237">
+        <v>1</v>
+      </c>
+      <c r="B7" s="238"/>
+      <c r="C7" s="260"/>
+      <c r="D7" s="260"/>
+      <c r="E7" s="260"/>
+      <c r="F7" s="260"/>
+      <c r="G7" s="260"/>
+      <c r="H7" s="260"/>
+      <c r="I7" s="260"/>
+      <c r="J7" s="260"/>
+      <c r="K7" s="260"/>
+      <c r="L7" s="260"/>
+      <c r="M7" s="260"/>
+      <c r="N7" s="260"/>
+      <c r="O7" s="251"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="248"/>
+      <c r="B8" s="249"/>
+      <c r="O8" s="251"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="248"/>
+      <c r="B9" s="249"/>
+      <c r="N9" s="261"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="248"/>
+      <c r="B10" s="249"/>
+      <c r="O10" s="251"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="248"/>
+      <c r="B11" s="249"/>
+      <c r="O11" s="251"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="248"/>
+      <c r="B12" s="249"/>
+      <c r="O12" s="251"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="248"/>
+      <c r="B13" s="249"/>
+      <c r="O13" s="251"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="248"/>
+      <c r="B14" s="249"/>
+      <c r="O14" s="251"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A15" s="252"/>
+      <c r="B15" s="253"/>
+      <c r="C15" s="262"/>
+      <c r="D15" s="262"/>
+      <c r="E15" s="262"/>
+      <c r="F15" s="262"/>
+      <c r="G15" s="262"/>
+      <c r="H15" s="262"/>
+      <c r="I15" s="262"/>
+      <c r="J15" s="262"/>
+      <c r="K15" s="262"/>
+      <c r="L15" s="262"/>
+      <c r="M15" s="262"/>
+      <c r="N15" s="263"/>
+      <c r="O15" s="251"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="237">
+        <v>2</v>
+      </c>
+      <c r="B16" s="238"/>
+      <c r="C16" s="260"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="260"/>
+      <c r="G16" s="260"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="260"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="260"/>
+      <c r="L16" s="260"/>
+      <c r="M16" s="260"/>
+      <c r="N16" s="261"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="248"/>
+      <c r="B17" s="249"/>
+      <c r="N17" s="261"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="248"/>
+      <c r="B18" s="249"/>
+      <c r="N18" s="261"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="248"/>
+      <c r="B19" s="249"/>
+      <c r="N19" s="261"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="248"/>
+      <c r="B20" s="249"/>
+      <c r="N20" s="261"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="248"/>
+      <c r="B21" s="249"/>
+      <c r="N21" s="261"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="248"/>
+      <c r="B22" s="249"/>
+      <c r="N22" s="261"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="248"/>
+      <c r="B23" s="249"/>
+      <c r="N23" s="261"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A24" s="252"/>
+      <c r="B24" s="253"/>
+      <c r="C24" s="262"/>
+      <c r="D24" s="262"/>
+      <c r="E24" s="262"/>
+      <c r="F24" s="262"/>
+      <c r="G24" s="262"/>
+      <c r="H24" s="262"/>
+      <c r="I24" s="262"/>
+      <c r="J24" s="262"/>
+      <c r="K24" s="262"/>
+      <c r="L24" s="262"/>
+      <c r="M24" s="262"/>
+      <c r="N24" s="263"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="237">
+        <v>3</v>
+      </c>
+      <c r="B25" s="238"/>
+      <c r="C25" s="260"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
+      <c r="M25" s="260"/>
+      <c r="N25" s="261"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="248"/>
+      <c r="B26" s="249"/>
+      <c r="N26" s="261"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="248"/>
+      <c r="B27" s="249"/>
+      <c r="N27" s="261"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="248"/>
+      <c r="B28" s="249"/>
+      <c r="N28" s="261"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="248"/>
+      <c r="B29" s="249"/>
+      <c r="N29" s="261"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="248"/>
+      <c r="B30" s="249"/>
+      <c r="N30" s="261"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="248"/>
+      <c r="B31" s="249"/>
+      <c r="N31" s="261"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="248"/>
+      <c r="B32" s="249"/>
+      <c r="N32" s="261"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A33" s="252"/>
+      <c r="B33" s="253"/>
+      <c r="C33" s="262"/>
+      <c r="D33" s="262"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="262"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="262"/>
+      <c r="J33" s="262"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="262"/>
+      <c r="N33" s="261"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="237">
+        <v>4</v>
+      </c>
+      <c r="B34" s="238"/>
+      <c r="C34" s="260"/>
+      <c r="D34" s="260"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="260"/>
+      <c r="G34" s="260"/>
+      <c r="H34" s="260"/>
+      <c r="I34" s="260"/>
+      <c r="J34" s="260"/>
+      <c r="K34" s="260"/>
+      <c r="L34" s="260"/>
+      <c r="M34" s="260"/>
+      <c r="N34" s="264"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="248"/>
+      <c r="B35" s="249"/>
+      <c r="N35" s="261"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="248"/>
+      <c r="B36" s="249"/>
+      <c r="N36" s="261"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="248"/>
+      <c r="B37" s="249"/>
+      <c r="N37" s="261"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="248"/>
+      <c r="B38" s="249"/>
+      <c r="N38" s="261"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="248"/>
+      <c r="B39" s="249"/>
+      <c r="N39" s="261"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="248"/>
+      <c r="B40" s="249"/>
+      <c r="N40" s="261"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="248"/>
+      <c r="B41" s="249"/>
+      <c r="N41" s="261"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A42" s="252"/>
+      <c r="B42" s="253"/>
+      <c r="C42" s="262"/>
+      <c r="D42" s="262"/>
+      <c r="E42" s="262"/>
+      <c r="F42" s="262"/>
+      <c r="G42" s="262"/>
+      <c r="H42" s="262"/>
+      <c r="I42" s="262"/>
+      <c r="J42" s="262"/>
+      <c r="K42" s="262"/>
+      <c r="L42" s="262"/>
+      <c r="M42" s="262"/>
+      <c r="N42" s="263"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="237">
+        <v>5</v>
+      </c>
+      <c r="B43" s="238"/>
+      <c r="C43" s="260"/>
+      <c r="D43" s="260"/>
+      <c r="E43" s="260"/>
+      <c r="F43" s="260"/>
+      <c r="G43" s="260"/>
+      <c r="H43" s="260"/>
+      <c r="I43" s="260"/>
+      <c r="J43" s="260"/>
+      <c r="K43" s="260"/>
+      <c r="L43" s="260"/>
+      <c r="M43" s="260"/>
+      <c r="N43" s="264"/>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="248"/>
+      <c r="B44" s="249"/>
+      <c r="N44" s="261"/>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="248"/>
+      <c r="B45" s="249"/>
+      <c r="N45" s="261"/>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="248"/>
+      <c r="B46" s="249"/>
+      <c r="N46" s="261"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="248"/>
+      <c r="B47" s="249"/>
+      <c r="N47" s="261"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="248"/>
+      <c r="B48" s="249"/>
+      <c r="N48" s="261"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="248"/>
+      <c r="B49" s="249"/>
+      <c r="N49" s="261"/>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="248"/>
+      <c r="B50" s="249"/>
+      <c r="N50" s="261"/>
+    </row>
+    <row r="51" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A51" s="252"/>
+      <c r="B51" s="253"/>
+      <c r="C51" s="262"/>
+      <c r="D51" s="262"/>
+      <c r="E51" s="262"/>
+      <c r="F51" s="262"/>
+      <c r="G51" s="262"/>
+      <c r="H51" s="262"/>
+      <c r="I51" s="262"/>
+      <c r="J51" s="262"/>
+      <c r="K51" s="262"/>
+      <c r="L51" s="262"/>
+      <c r="M51" s="262"/>
+      <c r="N51" s="263"/>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="237">
+        <v>6</v>
+      </c>
+      <c r="B52" s="238"/>
+      <c r="C52" s="260"/>
+      <c r="D52" s="260"/>
+      <c r="E52" s="260"/>
+      <c r="F52" s="260"/>
+      <c r="G52" s="260"/>
+      <c r="H52" s="260"/>
+      <c r="I52" s="260"/>
+      <c r="J52" s="260"/>
+      <c r="K52" s="260"/>
+      <c r="L52" s="260"/>
+      <c r="M52" s="260"/>
+      <c r="N52" s="264"/>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="248"/>
+      <c r="B53" s="249"/>
+      <c r="N53" s="261"/>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="248"/>
+      <c r="B54" s="249"/>
+      <c r="N54" s="261"/>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="248"/>
+      <c r="B55" s="249"/>
+      <c r="N55" s="261"/>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="248"/>
+      <c r="B56" s="249"/>
+      <c r="N56" s="261"/>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="248"/>
+      <c r="B57" s="249"/>
+      <c r="N57" s="261"/>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="248"/>
+      <c r="B58" s="249"/>
+      <c r="N58" s="261"/>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="248"/>
+      <c r="B59" s="249"/>
+      <c r="N59" s="261"/>
+    </row>
+    <row r="60" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A60" s="252"/>
+      <c r="B60" s="253"/>
+      <c r="C60" s="262"/>
+      <c r="D60" s="262"/>
+      <c r="E60" s="262"/>
+      <c r="F60" s="262"/>
+      <c r="G60" s="262"/>
+      <c r="H60" s="262"/>
+      <c r="I60" s="262"/>
+      <c r="J60" s="262"/>
+      <c r="K60" s="262"/>
+      <c r="L60" s="262"/>
+      <c r="M60" s="262"/>
+      <c r="N60" s="263"/>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="237">
+        <v>7</v>
+      </c>
+      <c r="B61" s="238"/>
+      <c r="C61" s="260"/>
+      <c r="D61" s="260"/>
+      <c r="E61" s="260"/>
+      <c r="F61" s="260"/>
+      <c r="G61" s="260"/>
+      <c r="H61" s="260"/>
+      <c r="I61" s="260"/>
+      <c r="J61" s="260"/>
+      <c r="K61" s="260"/>
+      <c r="L61" s="260"/>
+      <c r="M61" s="260"/>
+      <c r="N61" s="264"/>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="248"/>
+      <c r="B62" s="249"/>
+      <c r="N62" s="261"/>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="248"/>
+      <c r="B63" s="249"/>
+      <c r="N63" s="261"/>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="248"/>
+      <c r="B64" s="249"/>
+      <c r="N64" s="261"/>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="248"/>
+      <c r="B65" s="249"/>
+      <c r="N65" s="261"/>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="248"/>
+      <c r="B66" s="249"/>
+      <c r="N66" s="261"/>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" s="248"/>
+      <c r="B67" s="249"/>
+      <c r="N67" s="261"/>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="248"/>
+      <c r="B68" s="249"/>
+      <c r="N68" s="261"/>
+    </row>
+    <row r="69" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A69" s="252"/>
+      <c r="B69" s="253"/>
+      <c r="C69" s="262"/>
+      <c r="D69" s="262"/>
+      <c r="E69" s="262"/>
+      <c r="F69" s="262"/>
+      <c r="G69" s="262"/>
+      <c r="H69" s="262"/>
+      <c r="I69" s="262"/>
+      <c r="J69" s="262"/>
+      <c r="K69" s="262"/>
+      <c r="L69" s="262"/>
+      <c r="M69" s="262"/>
+      <c r="N69" s="263"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A43:B51"/>
+    <mergeCell ref="A52:B60"/>
+    <mergeCell ref="A61:B69"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C2:E3"/>
+    <mergeCell ref="F2:H3"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/タスク一覧設計書.xlsx
+++ b/Documents/タスク一覧設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11D6C3C-C15C-4486-882A-85DD460B50A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8183D1-77C5-4E9F-B1EE-00E896722D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2159,6 +2159,42 @@
     <xf numFmtId="56" fontId="11" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2183,6 +2219,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2193,11 +2262,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2213,9 +2330,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2228,84 +2342,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2369,6 +2405,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2387,18 +2432,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2411,9 +2450,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2489,96 +2525,177 @@
     <xf numFmtId="56" fontId="6" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2587,179 +2704,62 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="1" fillId="0" borderId="71" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -3313,85 +3313,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3411,46 +3411,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="73" t="s">
+      <c r="E8" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="70"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="82"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="66" t="s">
+      <c r="G13" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="68"/>
-      <c r="I13" s="66" t="s">
+      <c r="H13" s="80"/>
+      <c r="I13" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="67"/>
-      <c r="K13" s="68"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="80"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="66"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="68"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="80"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="66"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="80"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3459,13 +3459,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4480,19 +4480,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="109" t="s">
+      <c r="B1" s="103"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="97"/>
-      <c r="F1" s="109" t="s">
+      <c r="E1" s="94"/>
+      <c r="F1" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="97"/>
+      <c r="G1" s="94"/>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
@@ -4504,190 +4504,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="103"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="110" t="s">
+      <c r="A2" s="105"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="111"/>
-      <c r="F2" s="110" t="s">
+      <c r="E2" s="113"/>
+      <c r="F2" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="114">
+      <c r="G2" s="113"/>
+      <c r="H2" s="116">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="92"/>
+      <c r="J2" s="89"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="103"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="93"/>
+      <c r="A3" s="105"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="90"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="91"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="95" t="s">
+      <c r="A5" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98" t="s">
+      <c r="B5" s="93"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="99"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="96"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="84" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="78"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="101"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="84" t="s">
+      <c r="B7" s="98"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="78"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="84" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="78"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="101"/>
     </row>
     <row r="9" spans="1:10" ht="87" customHeight="1">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="88" t="s">
+      <c r="B9" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="77" t="s">
+      <c r="C9" s="99"/>
+      <c r="D9" s="117" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="78"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="101"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="88" t="s">
+      <c r="A10" s="124"/>
+      <c r="B10" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="78"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="101"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88" t="s">
+      <c r="A11" s="125"/>
+      <c r="B11" s="126" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77" t="s">
+      <c r="C11" s="99"/>
+      <c r="D11" s="117" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="78"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="101"/>
     </row>
     <row r="12" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="77" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="78"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="83"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="119"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5678,18 +5678,6 @@
     <row r="1000" s="21" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5705,6 +5693,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5723,19 +5723,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="131"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="143"/>
+      <c r="F1" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="131"/>
+      <c r="G1" s="143"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5747,48 +5747,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="125"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="132" t="s">
+      <c r="A2" s="137"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="133"/>
-      <c r="F2" s="132" t="s">
+      <c r="E2" s="145"/>
+      <c r="F2" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="133"/>
-      <c r="H2" s="115">
+      <c r="G2" s="145"/>
+      <c r="H2" s="127">
         <v>45807</v>
       </c>
-      <c r="I2" s="118" t="s">
+      <c r="I2" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="119"/>
+      <c r="J2" s="131"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="125"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="120"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="132"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="127"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="121"/>
+      <c r="A4" s="139"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="133"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -7148,19 +7148,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="131"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="143"/>
+      <c r="F1" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="131"/>
+      <c r="G1" s="143"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7172,190 +7172,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="125"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="132" t="s">
+      <c r="A2" s="137"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="133"/>
-      <c r="F2" s="132" t="s">
+      <c r="E2" s="145"/>
+      <c r="F2" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="133"/>
-      <c r="H2" s="115">
+      <c r="G2" s="145"/>
+      <c r="H2" s="127">
         <v>45810</v>
       </c>
-      <c r="I2" s="118" t="s">
+      <c r="I2" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="119"/>
+      <c r="J2" s="131"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="125"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="120"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="132"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="120"/>
+      <c r="A4" s="137"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="132"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="137"/>
-      <c r="C5" s="131"/>
-      <c r="D5" s="143" t="s">
+      <c r="B5" s="152"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="157" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
-      <c r="J5" s="144"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="158"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="141" t="s">
+      <c r="A6" s="156" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="145"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="149"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="146"/>
-      <c r="B7" s="147"/>
-      <c r="C7" s="147"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="148"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="161"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="125"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="149"/>
+      <c r="A8" s="137"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="162"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="125"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="149"/>
+      <c r="A9" s="137"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="162"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="125"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="149"/>
+      <c r="A10" s="137"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="162"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="125"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="149"/>
+      <c r="A11" s="137"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="162"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="125"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="149"/>
+      <c r="A12" s="137"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="162"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="125"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="149"/>
+      <c r="A13" s="137"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="162"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="141" t="s">
+      <c r="A14" s="156" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="145"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="149"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="141" t="s">
+      <c r="A15" s="156" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="150" t="s">
+      <c r="B15" s="79"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="68"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="13" t="s">
         <v>16</v>
       </c>
@@ -7364,11 +7364,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="68"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="13" t="s">
         <v>18</v>
       </c>
@@ -7381,18 +7381,18 @@
       <c r="G16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="151" t="s">
+      <c r="H16" s="163" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="67"/>
-      <c r="J16" s="145"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="149"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="150">
         <v>1</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="68"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="80"/>
       <c r="D17" s="15" t="s">
         <v>62</v>
       </c>
@@ -7403,81 +7403,81 @@
       <c r="G17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="150"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="145"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="149"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="68"/>
+      <c r="A18" s="150"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="80"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="145"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="149"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="68"/>
+      <c r="A19" s="150"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="150"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="145"/>
+      <c r="H19" s="148"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="149"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="68"/>
+      <c r="A20" s="150"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="150"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="145"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="149"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="68"/>
+      <c r="A21" s="150"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="150"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="145"/>
+      <c r="H21" s="148"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="149"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="68"/>
+      <c r="A22" s="150"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="150"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="145"/>
+      <c r="H22" s="148"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="149"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="138"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
+      <c r="A23" s="153"/>
+      <c r="B23" s="154"/>
+      <c r="C23" s="155"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="152"/>
-      <c r="I23" s="139"/>
-      <c r="J23" s="153"/>
+      <c r="H23" s="164"/>
+      <c r="I23" s="154"/>
+      <c r="J23" s="165"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8458,16 +8458,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8484,11 +8479,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8509,19 +8509,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="172" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="169" t="s">
+      <c r="B1" s="173"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="181" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="169" t="s">
+      <c r="E1" s="182"/>
+      <c r="F1" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="182"/>
       <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
@@ -8533,48 +8533,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="171" t="s">
+      <c r="A2" s="175"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="177"/>
+      <c r="D2" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="172"/>
-      <c r="F2" s="171" t="s">
+      <c r="E2" s="184"/>
+      <c r="F2" s="183" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="172"/>
-      <c r="H2" s="175">
+      <c r="G2" s="184"/>
+      <c r="H2" s="187">
         <v>45810</v>
       </c>
-      <c r="I2" s="154" t="s">
+      <c r="I2" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="157"/>
+      <c r="J2" s="169"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="163"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="165